--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Lommen</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -801,42 +801,166 @@
           <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
-      <c r="O2" s="11" t="inlineStr"/>
-      <c r="P2" s="11" t="inlineStr"/>
-      <c r="Q2" s="11" t="inlineStr"/>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr"/>
-      <c r="T2" s="11" t="inlineStr"/>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr"/>
-      <c r="W2" s="11" t="inlineStr"/>
-      <c r="X2" s="12" t="inlineStr"/>
-      <c r="Y2" s="12" t="inlineStr"/>
-      <c r="Z2" s="12" t="inlineStr"/>
-      <c r="AA2" s="12" t="inlineStr"/>
-      <c r="AB2" s="12" t="inlineStr"/>
-      <c r="AC2" s="12" t="inlineStr"/>
-      <c r="AD2" s="12" t="inlineStr"/>
-      <c r="AE2" s="12" t="inlineStr"/>
-      <c r="AF2" s="13" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>未报告(7级量表)</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P2" s="11" t="inlineStr">
+        <is>
+          <t>2-back; numerical updating; alpha-span</t>
+        </is>
+      </c>
+      <c r="Q2" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R2" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S2" s="11" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="T2" s="11" t="inlineStr">
+        <is>
+          <t>≤30天</t>
+        </is>
+      </c>
+      <c r="U2" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W2" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
+        <is>
+          <t>Backward Digit Span</t>
+        </is>
+      </c>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>Faces &amp; Names; Shopping List</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE2" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF2" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG2" s="13" t="inlineStr"/>
       <c r="AH2" s="13" t="inlineStr"/>
-      <c r="AI2" s="14" t="inlineStr"/>
-      <c r="AJ2" s="14" t="inlineStr"/>
-      <c r="AK2" s="14" t="inlineStr"/>
-      <c r="AL2" s="14" t="inlineStr"/>
-      <c r="AM2" s="14" t="inlineStr"/>
-      <c r="AN2" s="14" t="inlineStr"/>
-      <c r="AO2" s="15" t="inlineStr"/>
+      <c r="AI2" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ2" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK2" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL2" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM2" s="14" t="inlineStr">
+        <is>
+          <t>教育(7级量表)</t>
+        </is>
+      </c>
+      <c r="AN2" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO2" s="15" t="inlineStr">
+        <is>
+          <t>按基线EF高/低分组分析调节效应</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="8" t="n">
@@ -844,7 +968,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -860,42 +984,160 @@
           <t>Psychological research</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr"/>
-      <c r="G3" s="10" t="inlineStr"/>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
-      <c r="O3" s="11" t="inlineStr"/>
-      <c r="P3" s="11" t="inlineStr"/>
-      <c r="Q3" s="11" t="inlineStr"/>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr"/>
-      <c r="T3" s="11" t="inlineStr"/>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr"/>
-      <c r="W3" s="11" t="inlineStr"/>
-      <c r="X3" s="12" t="inlineStr"/>
-      <c r="Y3" s="12" t="inlineStr"/>
-      <c r="Z3" s="12" t="inlineStr"/>
-      <c r="AA3" s="12" t="inlineStr"/>
-      <c r="AB3" s="12" t="inlineStr"/>
-      <c r="AC3" s="12" t="inlineStr"/>
-      <c r="AD3" s="12" t="inlineStr"/>
-      <c r="AE3" s="12" t="inlineStr"/>
-      <c r="AF3" s="13" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal)</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
+        <is>
+          <t>Backward Corsi blocks</t>
+        </is>
+      </c>
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>Verbal fluency; Raven matrices; Culture Fair</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE3" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF3" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG3" s="13" t="inlineStr"/>
       <c r="AH3" s="13" t="inlineStr"/>
-      <c r="AI3" s="14" t="inlineStr"/>
-      <c r="AJ3" s="14" t="inlineStr"/>
-      <c r="AK3" s="14" t="inlineStr"/>
-      <c r="AL3" s="14" t="inlineStr"/>
-      <c r="AM3" s="14" t="inlineStr"/>
-      <c r="AN3" s="14" t="inlineStr"/>
-      <c r="AO3" s="15" t="inlineStr"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ3" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK3" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL3" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM3" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN3" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO3" s="15" t="inlineStr">
+        <is>
+          <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="8" t="n">
@@ -903,7 +1145,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Salminen</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
@@ -919,42 +1161,166 @@
           <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="11" t="inlineStr"/>
-      <c r="Q4" s="11" t="inlineStr"/>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr"/>
-      <c r="T4" s="11" t="inlineStr"/>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr"/>
-      <c r="W4" s="11" t="inlineStr"/>
-      <c r="X4" s="12" t="inlineStr"/>
-      <c r="Y4" s="12" t="inlineStr"/>
-      <c r="Z4" s="12" t="inlineStr"/>
-      <c r="AA4" s="12" t="inlineStr"/>
-      <c r="AB4" s="12" t="inlineStr"/>
-      <c r="AC4" s="12" t="inlineStr"/>
-      <c r="AD4" s="12" t="inlineStr"/>
-      <c r="AE4" s="12" t="inlineStr"/>
-      <c r="AF4" s="13" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>社区/大学</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>≥28</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (auditory-visual)</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S4" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>3-6</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
+        <is>
+          <t>AV n-back (untrained stimuli)</t>
+        </is>
+      </c>
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>Task switching; Attentional blink (T2)</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF4" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG4" s="13" t="inlineStr"/>
       <c r="AH4" s="13" t="inlineStr"/>
-      <c r="AI4" s="14" t="inlineStr"/>
-      <c r="AJ4" s="14" t="inlineStr"/>
-      <c r="AK4" s="14" t="inlineStr"/>
-      <c r="AL4" s="14" t="inlineStr"/>
-      <c r="AM4" s="14" t="inlineStr"/>
-      <c r="AN4" s="14" t="inlineStr"/>
-      <c r="AO4" s="15" t="inlineStr"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK4" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+        </is>
+      </c>
+      <c r="AL4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM4" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN4" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO4" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="8" t="n">
@@ -962,7 +1328,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>Tays</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -978,42 +1344,158 @@
           <t>PloS one</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="11" t="inlineStr"/>
-      <c r="Q5" s="11" t="inlineStr"/>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr"/>
-      <c r="T5" s="11" t="inlineStr"/>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr"/>
-      <c r="W5" s="11" t="inlineStr"/>
-      <c r="X5" s="12" t="inlineStr"/>
-      <c r="Y5" s="12" t="inlineStr"/>
-      <c r="Z5" s="12" t="inlineStr"/>
-      <c r="AA5" s="12" t="inlineStr"/>
-      <c r="AB5" s="12" t="inlineStr"/>
-      <c r="AC5" s="12" t="inlineStr"/>
-      <c r="AD5" s="12" t="inlineStr"/>
-      <c r="AE5" s="12" t="inlineStr"/>
-      <c r="AF5" s="13" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>64.38</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>Verbal WM; Visuospatial WM; OSpan</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
+        <is>
+          <t>Spatial 2-back</t>
+        </is>
+      </c>
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>Digit span; Stroop</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE5" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF5" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG5" s="13" t="inlineStr"/>
       <c r="AH5" s="13" t="inlineStr"/>
-      <c r="AI5" s="14" t="inlineStr"/>
-      <c r="AJ5" s="14" t="inlineStr"/>
-      <c r="AK5" s="14" t="inlineStr"/>
-      <c r="AL5" s="14" t="inlineStr"/>
-      <c r="AM5" s="14" t="inlineStr"/>
-      <c r="AN5" s="14" t="inlineStr"/>
-      <c r="AO5" s="15" t="inlineStr"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ5" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK5" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL5" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM5" s="14" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="AN5" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO5" s="15" t="inlineStr">
+        <is>
+          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="8" t="n">
@@ -1021,7 +1503,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Vesterinen</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1037,42 +1519,170 @@
           <t>Brain and behavior</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="11" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
-      <c r="Q6" s="11" t="inlineStr"/>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="11" t="inlineStr"/>
-      <c r="X6" s="12" t="inlineStr"/>
-      <c r="Y6" s="12" t="inlineStr"/>
-      <c r="Z6" s="12" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q6" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
+        <is>
+          <t>N-back (untrained level)</t>
+        </is>
+      </c>
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA6" s="12" t="inlineStr"/>
-      <c r="AB6" s="12" t="inlineStr"/>
-      <c r="AC6" s="12" t="inlineStr"/>
-      <c r="AD6" s="12" t="inlineStr"/>
-      <c r="AE6" s="12" t="inlineStr"/>
-      <c r="AF6" s="13" t="inlineStr"/>
-      <c r="AG6" s="13" t="inlineStr"/>
-      <c r="AH6" s="13" t="inlineStr"/>
-      <c r="AI6" s="14" t="inlineStr"/>
-      <c r="AJ6" s="14" t="inlineStr"/>
-      <c r="AK6" s="14" t="inlineStr"/>
-      <c r="AL6" s="14" t="inlineStr"/>
-      <c r="AM6" s="14" t="inlineStr"/>
-      <c r="AN6" s="14" t="inlineStr"/>
-      <c r="AO6" s="15" t="inlineStr"/>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD6" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF6" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG6" s="13" t="inlineStr">
+        <is>
+          <t>EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AH6" s="13" t="inlineStr">
+        <is>
+          <t>训练后P300振幅变化与任务难度相关</t>
+        </is>
+      </c>
+      <c r="AI6" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ6" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK6" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL6" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM6" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN6" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO6" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1080,7 +1690,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>Brum</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1096,42 +1706,162 @@
           <t>Aging &amp; mental health</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="10" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr"/>
-      <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
-      <c r="Q7" s="11" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="11" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="11" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="11" t="inlineStr"/>
-      <c r="X7" s="12" t="inlineStr"/>
-      <c r="Y7" s="12" t="inlineStr"/>
-      <c r="Z7" s="12" t="inlineStr"/>
-      <c r="AA7" s="12" t="inlineStr"/>
-      <c r="AB7" s="12" t="inlineStr"/>
-      <c r="AC7" s="12" t="inlineStr"/>
-      <c r="AD7" s="12" t="inlineStr"/>
-      <c r="AE7" s="12" t="inlineStr"/>
-      <c r="AF7" s="13" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>67.17</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>CERAD+CDT</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal, Borella protocol)</t>
+        </is>
+      </c>
+      <c r="Q7" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X7" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" s="12" t="inlineStr">
+        <is>
+          <t>Letter-Number Sequencing; Visuospatial WM</t>
+        </is>
+      </c>
+      <c r="Z7" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA7" s="12" t="inlineStr">
+        <is>
+          <t>Stroop; Processing speed; Fluid intelligence</t>
+        </is>
+      </c>
+      <c r="AB7" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF7" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG7" s="13" t="inlineStr"/>
       <c r="AH7" s="13" t="inlineStr"/>
-      <c r="AI7" s="14" t="inlineStr"/>
-      <c r="AJ7" s="14" t="inlineStr"/>
-      <c r="AK7" s="14" t="inlineStr"/>
-      <c r="AL7" s="14" t="inlineStr"/>
-      <c r="AM7" s="14" t="inlineStr"/>
-      <c r="AN7" s="14" t="inlineStr"/>
-      <c r="AO7" s="15" t="inlineStr"/>
+      <c r="AI7" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ7" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK7" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL7" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM7" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN7" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO7" s="15" t="inlineStr">
+        <is>
+          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="n">
@@ -1139,7 +1869,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -1155,42 +1885,176 @@
           <t>Psychology and aging</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
-      <c r="O8" s="11" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
-      <c r="Q8" s="11" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr"/>
-      <c r="S8" s="11" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="11" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
-      <c r="W8" s="11" t="inlineStr"/>
-      <c r="X8" s="12" t="inlineStr"/>
-      <c r="Y8" s="12" t="inlineStr"/>
-      <c r="Z8" s="12" t="inlineStr"/>
-      <c r="AA8" s="12" t="inlineStr"/>
-      <c r="AB8" s="12" t="inlineStr"/>
-      <c r="AC8" s="12" t="inlineStr"/>
-      <c r="AD8" s="12" t="inlineStr"/>
-      <c r="AE8" s="12" t="inlineStr"/>
-      <c r="AF8" s="13" t="inlineStr"/>
-      <c r="AG8" s="13" t="inlineStr"/>
-      <c r="AH8" s="13" t="inlineStr"/>
-      <c r="AI8" s="14" t="inlineStr"/>
-      <c r="AJ8" s="14" t="inlineStr"/>
-      <c r="AK8" s="14" t="inlineStr"/>
-      <c r="AL8" s="14" t="inlineStr"/>
-      <c r="AM8" s="14" t="inlineStr"/>
-      <c r="AN8" s="14" t="inlineStr"/>
-      <c r="AO8" s="15" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>≥6年</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>Gamified N-back (fruit-cutting game)</t>
+        </is>
+      </c>
+      <c r="Q8" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R8" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S8" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>自制(JavaScript游戏)</t>
+        </is>
+      </c>
+      <c r="X8" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (untrained)</t>
+        </is>
+      </c>
+      <c r="Z8" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA8" s="12" t="inlineStr">
+        <is>
+          <t>Inhibitory control; Visuospatial; Episodic memory</t>
+        </is>
+      </c>
+      <c r="AB8" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF8" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG8" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI+rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH8" s="13" t="inlineStr">
+        <is>
+          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
+        </is>
+      </c>
+      <c r="AI8" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ8" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK8" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL8" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM8" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN8" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO8" s="15" t="inlineStr">
+        <is>
+          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1198,7 +2062,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Guye</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1214,42 +2078,166 @@
           <t>Psychology and aging</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="10" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
-      <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
-      <c r="Q9" s="11" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
-      <c r="S9" s="11" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="11" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="11" t="inlineStr"/>
-      <c r="X9" s="12" t="inlineStr"/>
-      <c r="Y9" s="12" t="inlineStr"/>
-      <c r="Z9" s="12" t="inlineStr"/>
-      <c r="AA9" s="12" t="inlineStr"/>
-      <c r="AB9" s="12" t="inlineStr"/>
-      <c r="AC9" s="12" t="inlineStr"/>
-      <c r="AD9" s="12" t="inlineStr"/>
-      <c r="AE9" s="12" t="inlineStr"/>
-      <c r="AF9" s="13" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>未报告(0-7量表)</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>MMSE+GDS</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>≥26(MMSE)</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
+        </is>
+      </c>
+      <c r="Q9" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>自制(von Bastian protocol)</t>
+        </is>
+      </c>
+      <c r="X9" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" s="12" t="inlineStr">
+        <is>
+          <t>Visuospatial WM (3 tasks)</t>
+        </is>
+      </c>
+      <c r="Z9" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA9" s="12" t="inlineStr">
+        <is>
+          <t>Fluid intelligence; Inhibition; Shifting</t>
+        </is>
+      </c>
+      <c r="AB9" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD9" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE9" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF9" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG9" s="13" t="inlineStr"/>
       <c r="AH9" s="13" t="inlineStr"/>
-      <c r="AI9" s="14" t="inlineStr"/>
-      <c r="AJ9" s="14" t="inlineStr"/>
-      <c r="AK9" s="14" t="inlineStr"/>
-      <c r="AL9" s="14" t="inlineStr"/>
-      <c r="AM9" s="14" t="inlineStr"/>
-      <c r="AN9" s="14" t="inlineStr"/>
-      <c r="AO9" s="15" t="inlineStr"/>
+      <c r="AI9" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ9" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK9" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL9" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM9" s="14" t="inlineStr">
+        <is>
+          <t>教育(0-7量表)</t>
+        </is>
+      </c>
+      <c r="AN9" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO9" s="15" t="inlineStr">
+        <is>
+          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="n">
@@ -1257,7 +2245,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
@@ -1273,42 +2261,166 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr"/>
-      <c r="L10" s="10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr"/>
-      <c r="O10" s="11" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
-      <c r="Q10" s="11" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr"/>
-      <c r="S10" s="11" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="11" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="11" t="inlineStr"/>
-      <c r="X10" s="12" t="inlineStr"/>
-      <c r="Y10" s="12" t="inlineStr"/>
-      <c r="Z10" s="12" t="inlineStr"/>
-      <c r="AA10" s="12" t="inlineStr"/>
-      <c r="AB10" s="12" t="inlineStr"/>
-      <c r="AC10" s="12" t="inlineStr"/>
-      <c r="AD10" s="12" t="inlineStr"/>
-      <c r="AE10" s="12" t="inlineStr"/>
-      <c r="AF10" s="13" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Spain/Portugal</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>≥26</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q10" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>20+20</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X10" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span</t>
+        </is>
+      </c>
+      <c r="Z10" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA10" s="12" t="inlineStr">
+        <is>
+          <t>Raven APM (RAPM)</t>
+        </is>
+      </c>
+      <c r="AB10" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD10" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE10" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF10" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG10" s="13" t="inlineStr"/>
       <c r="AH10" s="13" t="inlineStr"/>
-      <c r="AI10" s="14" t="inlineStr"/>
-      <c r="AJ10" s="14" t="inlineStr"/>
-      <c r="AK10" s="14" t="inlineStr"/>
-      <c r="AL10" s="14" t="inlineStr"/>
-      <c r="AM10" s="14" t="inlineStr"/>
-      <c r="AN10" s="14" t="inlineStr"/>
-      <c r="AO10" s="15" t="inlineStr"/>
+      <c r="AI10" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="AJ10" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK10" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL10" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM10" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN10" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO10" s="15" t="inlineStr">
+        <is>
+          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="n">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -1219,10 +1219,8 @@
       <c r="S4" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>3-6</t>
-        </is>
+      <c r="T4" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="U4" s="11" t="inlineStr">
         <is>
@@ -1318,7 +1316,7 @@
       </c>
       <c r="AO4" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
+          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组；训练周数原文报告3-6周，取均值约4周</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1481,7 @@
       </c>
       <c r="AM5" s="14" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN5" s="14" t="inlineStr">
@@ -2428,7 +2426,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>Rudner</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -2444,42 +2442,166 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="10" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
-      <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
-      <c r="S11" s="11" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="11" t="inlineStr"/>
-      <c r="X11" s="12" t="inlineStr"/>
-      <c r="Y11" s="12" t="inlineStr"/>
-      <c r="Z11" s="12" t="inlineStr"/>
-      <c r="AA11" s="12" t="inlineStr"/>
-      <c r="AB11" s="12" t="inlineStr"/>
-      <c r="AC11" s="12" t="inlineStr"/>
-      <c r="AD11" s="12" t="inlineStr"/>
-      <c r="AE11" s="12" t="inlineStr"/>
-      <c r="AF11" s="13" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>≥23</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>Reading Span (Cogmed)</t>
+        </is>
+      </c>
+      <c r="Q11" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>Cogmed</t>
+        </is>
+      </c>
+      <c r="X11" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" s="12" t="inlineStr">
+        <is>
+          <t>Reading Span (untrained version)</t>
+        </is>
+      </c>
+      <c r="Z11" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>Speech-in-noise comprehension</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE11" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF11" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG11" s="13" t="inlineStr"/>
       <c r="AH11" s="13" t="inlineStr"/>
-      <c r="AI11" s="14" t="inlineStr"/>
-      <c r="AJ11" s="14" t="inlineStr"/>
-      <c r="AK11" s="14" t="inlineStr"/>
-      <c r="AL11" s="14" t="inlineStr"/>
-      <c r="AM11" s="14" t="inlineStr"/>
-      <c r="AN11" s="14" t="inlineStr"/>
-      <c r="AO11" s="15" t="inlineStr"/>
+      <c r="AI11" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ11" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK11" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL11" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM11" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN11" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO11" s="15" t="inlineStr">
+        <is>
+          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -2487,7 +2609,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>Berryhill</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -2503,42 +2625,170 @@
           <t>Brain stimulation</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr"/>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
-      <c r="Q12" s="11" t="inlineStr"/>
-      <c r="R12" s="11" t="inlineStr"/>
-      <c r="S12" s="11" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="11" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="11" t="inlineStr"/>
-      <c r="X12" s="12" t="inlineStr"/>
-      <c r="Y12" s="12" t="inlineStr"/>
-      <c r="Z12" s="12" t="inlineStr"/>
-      <c r="AA12" s="12" t="inlineStr"/>
-      <c r="AB12" s="12" t="inlineStr"/>
-      <c r="AC12" s="12" t="inlineStr"/>
-      <c r="AD12" s="12" t="inlineStr"/>
-      <c r="AE12" s="12" t="inlineStr"/>
-      <c r="AF12" s="13" t="inlineStr"/>
-      <c r="AG12" s="13" t="inlineStr"/>
-      <c r="AH12" s="13" t="inlineStr"/>
-      <c r="AI12" s="14" t="inlineStr"/>
-      <c r="AJ12" s="14" t="inlineStr"/>
-      <c r="AK12" s="14" t="inlineStr"/>
-      <c r="AL12" s="14" t="inlineStr"/>
-      <c r="AM12" s="14" t="inlineStr"/>
-      <c r="AN12" s="14" t="inlineStr"/>
-      <c r="AO12" s="15" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
+        </is>
+      </c>
+      <c r="Q12" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y12" s="12" t="inlineStr">
+        <is>
+          <t>Letter-Number Sequencing; 2-back</t>
+        </is>
+      </c>
+      <c r="Z12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>WCPA (everyday scheduling); Road Craft Test</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="12" t="inlineStr">
+        <is>
+          <t>η²=0.073(far transfer)</t>
+        </is>
+      </c>
+      <c r="AE12" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF12" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
+        </is>
+      </c>
+      <c r="AI12" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ12" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK12" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL12" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM12" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN12" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO12" s="15" t="inlineStr">
+        <is>
+          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -2546,7 +2796,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -2562,42 +2812,166 @@
           <t>Neural plasticity</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="10" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
-      <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
-      <c r="S13" s="11" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="11" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="11" t="inlineStr"/>
-      <c r="X13" s="12" t="inlineStr"/>
-      <c r="Y13" s="12" t="inlineStr"/>
-      <c r="Z13" s="12" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Visual Object Memory Task (VOMT)</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X13" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y13" s="12" t="inlineStr">
+        <is>
+          <t>VOMT (untrained stimuli)</t>
+        </is>
+      </c>
+      <c r="Z13" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA13" s="12" t="inlineStr"/>
-      <c r="AB13" s="12" t="inlineStr"/>
-      <c r="AC13" s="12" t="inlineStr"/>
-      <c r="AD13" s="12" t="inlineStr"/>
-      <c r="AE13" s="12" t="inlineStr"/>
-      <c r="AF13" s="13" t="inlineStr"/>
-      <c r="AG13" s="13" t="inlineStr"/>
-      <c r="AH13" s="13" t="inlineStr"/>
-      <c r="AI13" s="14" t="inlineStr"/>
-      <c r="AJ13" s="14" t="inlineStr"/>
-      <c r="AK13" s="14" t="inlineStr"/>
-      <c r="AL13" s="14" t="inlineStr"/>
-      <c r="AM13" s="14" t="inlineStr"/>
-      <c r="AN13" s="14" t="inlineStr"/>
-      <c r="AO13" s="15" t="inlineStr"/>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD13" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF13" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH13" s="13" t="inlineStr">
+        <is>
+          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+        </is>
+      </c>
+      <c r="AI13" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ13" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK13" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL13" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM13" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN13" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO13" s="15" t="inlineStr">
+        <is>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="n">
@@ -2605,7 +2979,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -2621,42 +2995,166 @@
           <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
-      <c r="O14" s="11" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
-      <c r="Q14" s="11" t="inlineStr"/>
-      <c r="R14" s="11" t="inlineStr"/>
-      <c r="S14" s="11" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="11" t="inlineStr"/>
-      <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="11" t="inlineStr"/>
-      <c r="X14" s="12" t="inlineStr"/>
-      <c r="Y14" s="12" t="inlineStr"/>
-      <c r="Z14" s="12" t="inlineStr"/>
-      <c r="AA14" s="12" t="inlineStr"/>
-      <c r="AB14" s="12" t="inlineStr"/>
-      <c r="AC14" s="12" t="inlineStr"/>
-      <c r="AD14" s="12" t="inlineStr"/>
-      <c r="AE14" s="12" t="inlineStr"/>
-      <c r="AF14" s="13" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>SVAMA</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal, modified)</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="T14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X14" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y14" s="12" t="inlineStr">
+        <is>
+          <t>Dot Matrix (visuospatial WM)</t>
+        </is>
+      </c>
+      <c r="Z14" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>TIADL (everyday functioning); EPT</t>
+        </is>
+      </c>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE14" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF14" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG14" s="13" t="inlineStr"/>
       <c r="AH14" s="13" t="inlineStr"/>
-      <c r="AI14" s="14" t="inlineStr"/>
-      <c r="AJ14" s="14" t="inlineStr"/>
-      <c r="AK14" s="14" t="inlineStr"/>
-      <c r="AL14" s="14" t="inlineStr"/>
-      <c r="AM14" s="14" t="inlineStr"/>
-      <c r="AN14" s="14" t="inlineStr"/>
-      <c r="AO14" s="15" t="inlineStr"/>
+      <c r="AI14" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ14" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK14" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL14" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM14" s="14" t="inlineStr">
+        <is>
+          <t>词汇测试</t>
+        </is>
+      </c>
+      <c r="AN14" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO14" s="15" t="inlineStr">
+        <is>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -2664,7 +3162,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -2680,42 +3178,168 @@
           <t>Journal of visualized experiments : JoVE</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
-      <c r="Q15" s="11" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="11" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="11" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="11" t="inlineStr"/>
-      <c r="X15" s="12" t="inlineStr"/>
-      <c r="Y15" s="12" t="inlineStr"/>
-      <c r="Z15" s="12" t="inlineStr"/>
-      <c r="AA15" s="12" t="inlineStr"/>
-      <c r="AB15" s="12" t="inlineStr"/>
-      <c r="AC15" s="12" t="inlineStr"/>
-      <c r="AD15" s="12" t="inlineStr"/>
-      <c r="AE15" s="12" t="inlineStr"/>
-      <c r="AF15" s="13" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S15" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V15" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X15" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y15" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (untrained)</t>
+        </is>
+      </c>
+      <c r="Z15" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Executive function</t>
+        </is>
+      </c>
+      <c r="AB15" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD15" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF15" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG15" s="13" t="inlineStr"/>
       <c r="AH15" s="13" t="inlineStr"/>
-      <c r="AI15" s="14" t="inlineStr"/>
-      <c r="AJ15" s="14" t="inlineStr"/>
-      <c r="AK15" s="14" t="inlineStr"/>
-      <c r="AL15" s="14" t="inlineStr"/>
-      <c r="AM15" s="14" t="inlineStr"/>
-      <c r="AN15" s="14" t="inlineStr"/>
-      <c r="AO15" s="15" t="inlineStr"/>
+      <c r="AI15" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ15" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK15" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL15" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM15" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN15" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO15" s="15" t="inlineStr">
+        <is>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n">
@@ -2723,7 +3347,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -2739,42 +3363,162 @@
           <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr"/>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
-      <c r="Q16" s="11" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr"/>
-      <c r="S16" s="11" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="11" t="inlineStr"/>
-      <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="11" t="inlineStr"/>
-      <c r="X16" s="12" t="inlineStr"/>
-      <c r="Y16" s="12" t="inlineStr"/>
-      <c r="Z16" s="12" t="inlineStr"/>
-      <c r="AA16" s="12" t="inlineStr"/>
-      <c r="AB16" s="12" t="inlineStr"/>
-      <c r="AC16" s="12" t="inlineStr"/>
-      <c r="AD16" s="12" t="inlineStr"/>
-      <c r="AE16" s="12" t="inlineStr"/>
-      <c r="AF16" s="13" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>29.66</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Adaptive n-back (0-5 back)</t>
+        </is>
+      </c>
+      <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S16" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X16" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y16" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span (backward)</t>
+        </is>
+      </c>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>CERAD episodic memory; Processing speed (LPS)</t>
+        </is>
+      </c>
+      <c r="AB16" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD16" s="12" t="inlineStr">
+        <is>
+          <t>d=0.78(教育组间)</t>
+        </is>
+      </c>
+      <c r="AE16" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF16" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG16" s="13" t="inlineStr"/>
       <c r="AH16" s="13" t="inlineStr"/>
-      <c r="AI16" s="14" t="inlineStr"/>
-      <c r="AJ16" s="14" t="inlineStr"/>
-      <c r="AK16" s="14" t="inlineStr"/>
-      <c r="AL16" s="14" t="inlineStr"/>
-      <c r="AM16" s="14" t="inlineStr"/>
-      <c r="AN16" s="14" t="inlineStr"/>
-      <c r="AO16" s="15" t="inlineStr"/>
+      <c r="AI16" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ16" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK16" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+        </is>
+      </c>
+      <c r="AL16" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM16" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN16" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO16" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -2782,7 +3526,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -2798,42 +3542,168 @@
           <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
-      <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="11" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="11" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="11" t="inlineStr"/>
-      <c r="X17" s="12" t="inlineStr"/>
-      <c r="Y17" s="12" t="inlineStr"/>
-      <c r="Z17" s="12" t="inlineStr"/>
-      <c r="AA17" s="12" t="inlineStr"/>
-      <c r="AB17" s="12" t="inlineStr"/>
-      <c r="AC17" s="12" t="inlineStr"/>
-      <c r="AD17" s="12" t="inlineStr"/>
-      <c r="AE17" s="12" t="inlineStr"/>
-      <c r="AF17" s="13" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>SVAMA</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal)</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X17" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y17" s="12" t="inlineStr">
+        <is>
+          <t>Dot Matrix (visuospatial WM)</t>
+        </is>
+      </c>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA17" s="12" t="inlineStr">
+        <is>
+          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE17" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF17" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG17" s="13" t="inlineStr"/>
       <c r="AH17" s="13" t="inlineStr"/>
-      <c r="AI17" s="14" t="inlineStr"/>
-      <c r="AJ17" s="14" t="inlineStr"/>
-      <c r="AK17" s="14" t="inlineStr"/>
-      <c r="AL17" s="14" t="inlineStr"/>
-      <c r="AM17" s="14" t="inlineStr"/>
-      <c r="AN17" s="14" t="inlineStr"/>
-      <c r="AO17" s="15" t="inlineStr"/>
+      <c r="AI17" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ17" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK17" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL17" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM17" s="14" t="inlineStr">
+        <is>
+          <t>词汇测试</t>
+        </is>
+      </c>
+      <c r="AN17" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO17" s="15" t="inlineStr">
+        <is>
+          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -2841,7 +3711,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Olivetti</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -2857,42 +3727,160 @@
           <t>Cognitive processing</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
-      <c r="Q18" s="11" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="11" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="11" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="11" t="inlineStr"/>
-      <c r="X18" s="12" t="inlineStr"/>
-      <c r="Y18" s="12" t="inlineStr"/>
-      <c r="Z18" s="12" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>医院/社区</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>MMSE+CDT</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>≥26(MMSE)</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>N-back (0-2 back, adaptive)</t>
+        </is>
+      </c>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X18" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y18" s="12" t="inlineStr">
+        <is>
+          <t>Corsi Block; Digit Span</t>
+        </is>
+      </c>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA18" s="12" t="inlineStr"/>
-      <c r="AB18" s="12" t="inlineStr"/>
-      <c r="AC18" s="12" t="inlineStr"/>
-      <c r="AD18" s="12" t="inlineStr"/>
-      <c r="AE18" s="12" t="inlineStr"/>
-      <c r="AF18" s="13" t="inlineStr"/>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD18" s="12" t="inlineStr">
+        <is>
+          <t>d=2.21(近迁移)</t>
+        </is>
+      </c>
+      <c r="AE18" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF18" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG18" s="13" t="inlineStr"/>
       <c r="AH18" s="13" t="inlineStr"/>
-      <c r="AI18" s="14" t="inlineStr"/>
-      <c r="AJ18" s="14" t="inlineStr"/>
-      <c r="AK18" s="14" t="inlineStr"/>
-      <c r="AL18" s="14" t="inlineStr"/>
-      <c r="AM18" s="14" t="inlineStr"/>
-      <c r="AN18" s="14" t="inlineStr"/>
-      <c r="AO18" s="15" t="inlineStr"/>
+      <c r="AI18" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ18" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK18" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL18" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM18" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN18" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO18" s="15" t="inlineStr">
+        <is>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2900,7 +3888,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -2916,42 +3904,164 @@
           <t>International journal of aging &amp; human development</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
-      <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
-      <c r="S19" s="11" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="11" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="11" t="inlineStr"/>
-      <c r="X19" s="12" t="inlineStr"/>
-      <c r="Y19" s="12" t="inlineStr"/>
-      <c r="Z19" s="12" t="inlineStr"/>
-      <c r="AA19" s="12" t="inlineStr"/>
-      <c r="AB19" s="12" t="inlineStr"/>
-      <c r="AC19" s="12" t="inlineStr"/>
-      <c r="AD19" s="12" t="inlineStr"/>
-      <c r="AE19" s="12" t="inlineStr"/>
-      <c r="AF19" s="13" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X19" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y19" s="12" t="inlineStr">
+        <is>
+          <t>Spatial WM (untrained)</t>
+        </is>
+      </c>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr">
+        <is>
+          <t>Reasoning; IADL (everyday function)</t>
+        </is>
+      </c>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD19" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE19" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF19" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG19" s="13" t="inlineStr"/>
       <c r="AH19" s="13" t="inlineStr"/>
-      <c r="AI19" s="14" t="inlineStr"/>
-      <c r="AJ19" s="14" t="inlineStr"/>
-      <c r="AK19" s="14" t="inlineStr"/>
-      <c r="AL19" s="14" t="inlineStr"/>
-      <c r="AM19" s="14" t="inlineStr"/>
-      <c r="AN19" s="14" t="inlineStr"/>
-      <c r="AO19" s="15" t="inlineStr"/>
+      <c r="AI19" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ19" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK19" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL19" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM19" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN19" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO19" s="15" t="inlineStr">
+        <is>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n">
@@ -2959,7 +4069,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
@@ -2975,42 +4085,166 @@
           <t>GeroScience</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
-      <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
-      <c r="Q20" s="11" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr"/>
-      <c r="S20" s="11" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="11" t="inlineStr"/>
-      <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="11" t="inlineStr"/>
-      <c r="X20" s="12" t="inlineStr"/>
-      <c r="Y20" s="12" t="inlineStr"/>
-      <c r="Z20" s="12" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>Multidomain cognitive training (WM+processing speed)</t>
+        </is>
+      </c>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U20" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>自制(tablet-based)</t>
+        </is>
+      </c>
+      <c r="X20" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y20" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (proximal)</t>
+        </is>
+      </c>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA20" s="12" t="inlineStr"/>
-      <c r="AB20" s="12" t="inlineStr"/>
-      <c r="AC20" s="12" t="inlineStr"/>
-      <c r="AD20" s="12" t="inlineStr"/>
-      <c r="AE20" s="12" t="inlineStr"/>
-      <c r="AF20" s="13" t="inlineStr"/>
-      <c r="AG20" s="13" t="inlineStr"/>
-      <c r="AH20" s="13" t="inlineStr"/>
-      <c r="AI20" s="14" t="inlineStr"/>
-      <c r="AJ20" s="14" t="inlineStr"/>
-      <c r="AK20" s="14" t="inlineStr"/>
-      <c r="AL20" s="14" t="inlineStr"/>
-      <c r="AM20" s="14" t="inlineStr"/>
-      <c r="AN20" s="14" t="inlineStr"/>
-      <c r="AO20" s="15" t="inlineStr"/>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD20" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE20" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF20" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG20" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI)</t>
+        </is>
+      </c>
+      <c r="AH20" s="13" t="inlineStr">
+        <is>
+          <t>白质高信号负荷高者训练获益更少</t>
+        </is>
+      </c>
+      <c r="AI20" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ20" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK20" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低WMH获益更多)</t>
+        </is>
+      </c>
+      <c r="AL20" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM20" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN20" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO20" s="15" t="inlineStr">
+        <is>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -3018,7 +4252,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -3034,42 +4268,174 @@
           <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr"/>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="11" t="inlineStr"/>
-      <c r="X21" s="12" t="inlineStr"/>
-      <c r="Y21" s="12" t="inlineStr"/>
-      <c r="Z21" s="12" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, 1-3 back)</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X21" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y21" s="12" t="inlineStr">
+        <is>
+          <t>Listening Span</t>
+        </is>
+      </c>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA21" s="12" t="inlineStr"/>
-      <c r="AB21" s="12" t="inlineStr"/>
-      <c r="AC21" s="12" t="inlineStr"/>
-      <c r="AD21" s="12" t="inlineStr"/>
-      <c r="AE21" s="12" t="inlineStr"/>
-      <c r="AF21" s="13" t="inlineStr"/>
-      <c r="AG21" s="13" t="inlineStr"/>
-      <c r="AH21" s="13" t="inlineStr"/>
-      <c r="AI21" s="14" t="inlineStr"/>
-      <c r="AJ21" s="14" t="inlineStr"/>
-      <c r="AK21" s="14" t="inlineStr"/>
-      <c r="AL21" s="14" t="inlineStr"/>
-      <c r="AM21" s="14" t="inlineStr"/>
-      <c r="AN21" s="14" t="inlineStr"/>
-      <c r="AO21" s="15" t="inlineStr"/>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC21" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD21" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE21" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF21" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG21" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH21" s="13" t="inlineStr">
+        <is>
+          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+        </is>
+      </c>
+      <c r="AI21" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ21" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK21" s="14" t="inlineStr">
+        <is>
+          <t>高&gt;低(类年轻激活者获益更多)</t>
+        </is>
+      </c>
+      <c r="AL21" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM21" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN21" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO21" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n">
@@ -3077,7 +4443,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>Tagliabue</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
@@ -3093,42 +4459,158 @@
           <t>Attention, perception &amp; psychophysics</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="11" t="inlineStr"/>
-      <c r="V22" s="11" t="inlineStr"/>
-      <c r="W22" s="11" t="inlineStr"/>
-      <c r="X22" s="12" t="inlineStr"/>
-      <c r="Y22" s="12" t="inlineStr"/>
-      <c r="Z22" s="12" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>社区(在线)</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>DMTS (delayed match-to-sample); Enumeration</t>
+        </is>
+      </c>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>自制(在线)</t>
+        </is>
+      </c>
+      <c r="X22" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y22" s="12" t="inlineStr">
+        <is>
+          <t>DMTS (visuospatial WM, k值)</t>
+        </is>
+      </c>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA22" s="12" t="inlineStr"/>
-      <c r="AB22" s="12" t="inlineStr"/>
-      <c r="AC22" s="12" t="inlineStr"/>
-      <c r="AD22" s="12" t="inlineStr"/>
-      <c r="AE22" s="12" t="inlineStr"/>
-      <c r="AF22" s="13" t="inlineStr"/>
+      <c r="AB22" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE22" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF22" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG22" s="13" t="inlineStr"/>
       <c r="AH22" s="13" t="inlineStr"/>
-      <c r="AI22" s="14" t="inlineStr"/>
-      <c r="AJ22" s="14" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
-      <c r="AL22" s="14" t="inlineStr"/>
-      <c r="AM22" s="14" t="inlineStr"/>
-      <c r="AN22" s="14" t="inlineStr"/>
-      <c r="AO22" s="15" t="inlineStr"/>
+      <c r="AI22" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ22" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK22" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低WM基线者获益更多)</t>
+        </is>
+      </c>
+      <c r="AL22" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM22" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN22" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO22" s="15" t="inlineStr">
+        <is>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -3136,7 +4618,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Zinke</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -3152,42 +4634,162 @@
           <t>Developmental psychology</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr"/>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="11" t="inlineStr"/>
-      <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="11" t="inlineStr"/>
-      <c r="X23" s="12" t="inlineStr"/>
-      <c r="Y23" s="12" t="inlineStr"/>
-      <c r="Z23" s="12" t="inlineStr"/>
-      <c r="AA23" s="12" t="inlineStr"/>
-      <c r="AB23" s="12" t="inlineStr"/>
-      <c r="AC23" s="12" t="inlineStr"/>
-      <c r="AD23" s="12" t="inlineStr"/>
-      <c r="AE23" s="12" t="inlineStr"/>
-      <c r="AF23" s="13" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>MMST</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S23" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y23" s="12" t="inlineStr">
+        <is>
+          <t>Verbal WM (untrained)</t>
+        </is>
+      </c>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA23" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Reasoning</t>
+        </is>
+      </c>
+      <c r="AB23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE23" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF23" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG23" s="13" t="inlineStr"/>
       <c r="AH23" s="13" t="inlineStr"/>
-      <c r="AI23" s="14" t="inlineStr"/>
-      <c r="AJ23" s="14" t="inlineStr"/>
-      <c r="AK23" s="14" t="inlineStr"/>
-      <c r="AL23" s="14" t="inlineStr"/>
-      <c r="AM23" s="14" t="inlineStr"/>
-      <c r="AN23" s="14" t="inlineStr"/>
-      <c r="AO23" s="15" t="inlineStr"/>
+      <c r="AI23" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ23" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK23" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低基线者近迁移更大)</t>
+        </is>
+      </c>
+      <c r="AL23" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM23" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN23" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO23" s="15" t="inlineStr">
+        <is>
+          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n">
@@ -3195,7 +4797,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Schmicker</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -3211,42 +4813,162 @@
           <t>Current aging science</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
-      <c r="Q24" s="11" t="inlineStr"/>
-      <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr"/>
-      <c r="T24" s="11" t="inlineStr"/>
-      <c r="U24" s="11" t="inlineStr"/>
-      <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="11" t="inlineStr"/>
-      <c r="X24" s="12" t="inlineStr"/>
-      <c r="Y24" s="12" t="inlineStr"/>
-      <c r="Z24" s="12" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y24" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span</t>
+        </is>
+      </c>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA24" s="12" t="inlineStr"/>
-      <c r="AB24" s="12" t="inlineStr"/>
-      <c r="AC24" s="12" t="inlineStr"/>
-      <c r="AD24" s="12" t="inlineStr"/>
-      <c r="AE24" s="12" t="inlineStr"/>
-      <c r="AF24" s="13" t="inlineStr"/>
+      <c r="AB24" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD24" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE24" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF24" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG24" s="13" t="inlineStr"/>
       <c r="AH24" s="13" t="inlineStr"/>
-      <c r="AI24" s="14" t="inlineStr"/>
-      <c r="AJ24" s="14" t="inlineStr"/>
-      <c r="AK24" s="14" t="inlineStr"/>
-      <c r="AL24" s="14" t="inlineStr"/>
-      <c r="AM24" s="14" t="inlineStr"/>
-      <c r="AN24" s="14" t="inlineStr"/>
-      <c r="AO24" s="15" t="inlineStr"/>
+      <c r="AI24" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ24" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK24" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL24" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM24" s="14" t="inlineStr">
+        <is>
+          <t>CRI(认知储备指数)</t>
+        </is>
+      </c>
+      <c r="AN24" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO24" s="15" t="inlineStr">
+        <is>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -3254,7 +4976,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -3270,42 +4992,164 @@
           <t>BMC research notes</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr"/>
-      <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-      <c r="U25" s="11" t="inlineStr"/>
-      <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="11" t="inlineStr"/>
-      <c r="X25" s="12" t="inlineStr"/>
-      <c r="Y25" s="12" t="inlineStr"/>
-      <c r="Z25" s="12" t="inlineStr"/>
-      <c r="AA25" s="12" t="inlineStr"/>
-      <c r="AB25" s="12" t="inlineStr"/>
-      <c r="AC25" s="12" t="inlineStr"/>
-      <c r="AD25" s="12" t="inlineStr"/>
-      <c r="AE25" s="12" t="inlineStr"/>
-      <c r="AF25" s="13" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, 1-3 back)</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T25" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>PsychoPy自制</t>
+        </is>
+      </c>
+      <c r="X25" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y25" s="12" t="inlineStr">
+        <is>
+          <t>N-back (untrained level)</t>
+        </is>
+      </c>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span; Corsi; Stroop</t>
+        </is>
+      </c>
+      <c r="AB25" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD25" s="12" t="inlineStr">
+        <is>
+          <t>η²p=0.05(训练×年龄交互)</t>
+        </is>
+      </c>
+      <c r="AE25" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF25" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG25" s="13" t="inlineStr"/>
       <c r="AH25" s="13" t="inlineStr"/>
-      <c r="AI25" s="14" t="inlineStr"/>
-      <c r="AJ25" s="14" t="inlineStr"/>
-      <c r="AK25" s="14" t="inlineStr"/>
-      <c r="AL25" s="14" t="inlineStr"/>
-      <c r="AM25" s="14" t="inlineStr"/>
-      <c r="AN25" s="14" t="inlineStr"/>
-      <c r="AO25" s="15" t="inlineStr"/>
+      <c r="AI25" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ25" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK25" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+        </is>
+      </c>
+      <c r="AL25" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM25" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN25" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO25" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n">
@@ -3313,7 +5157,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Jaeggi</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
@@ -3329,42 +5173,172 @@
           <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr"/>
-      <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr"/>
-      <c r="T26" s="11" t="inlineStr"/>
-      <c r="U26" s="11" t="inlineStr"/>
-      <c r="V26" s="11" t="inlineStr"/>
-      <c r="W26" s="11" t="inlineStr"/>
-      <c r="X26" s="12" t="inlineStr"/>
-      <c r="Y26" s="12" t="inlineStr"/>
-      <c r="Z26" s="12" t="inlineStr"/>
-      <c r="AA26" s="12" t="inlineStr"/>
-      <c r="AB26" s="12" t="inlineStr"/>
-      <c r="AC26" s="12" t="inlineStr"/>
-      <c r="AD26" s="12" t="inlineStr"/>
-      <c r="AE26" s="12" t="inlineStr"/>
-      <c r="AF26" s="13" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>GDS+GAD</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+        </is>
+      </c>
+      <c r="Q26" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T26" s="11" t="inlineStr">
+        <is>
+          <t>2-10</t>
+        </is>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V26" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>自制(tablet)</t>
+        </is>
+      </c>
+      <c r="X26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y26" s="12" t="inlineStr">
+        <is>
+          <t>Reading Span; Symmetry Span</t>
+        </is>
+      </c>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>Letter Sets; Visual LTM</t>
+        </is>
+      </c>
+      <c r="AB26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE26" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF26" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG26" s="13" t="inlineStr"/>
       <c r="AH26" s="13" t="inlineStr"/>
-      <c r="AI26" s="14" t="inlineStr"/>
-      <c r="AJ26" s="14" t="inlineStr"/>
-      <c r="AK26" s="14" t="inlineStr"/>
-      <c r="AL26" s="14" t="inlineStr"/>
-      <c r="AM26" s="14" t="inlineStr"/>
-      <c r="AN26" s="14" t="inlineStr"/>
-      <c r="AO26" s="15" t="inlineStr"/>
+      <c r="AI26" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ26" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK26" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL26" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM26" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN26" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO26" s="15" t="inlineStr">
+        <is>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2792,29 +2792,29 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
+          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Neural plasticity</t>
+          <t>Frontiers in Aging Neuroscience</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -2823,62 +2823,72 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>≥27</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="I13" s="10" t="n">
-        <v>68.84</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>Visual Object Memory Task (VOMT)</t>
-        </is>
-      </c>
-      <c r="Q13" s="11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S13" s="11" t="n">
-        <v>60</v>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T13" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U13" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
@@ -2893,15 +2903,19 @@
       </c>
       <c r="Y13" s="12" t="inlineStr">
         <is>
-          <t>VOMT (untrained stimuli)</t>
+          <t>OSPAN; WM tasks</t>
         </is>
       </c>
       <c r="Z13" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA13" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB13" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -2924,27 +2938,19 @@
       </c>
       <c r="AF13" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG13" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(rs-fMRI)</t>
-        </is>
-      </c>
-      <c r="AH13" s="13" t="inlineStr">
-        <is>
-          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr"/>
+      <c r="AH13" s="13" t="inlineStr"/>
       <c r="AI13" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ13" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK13" s="14" t="inlineStr">
@@ -2969,35 +2975,35 @@
       </c>
       <c r="AO13" s="15" t="inlineStr">
         <is>
-          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
+          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
+          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
+          <t>Neural plasticity</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -3006,29 +3012,23 @@
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4.65</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>14.48</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
@@ -3038,41 +3038,41 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, modified)</t>
+          <t>Visual Object Memory Task (VOMT)</t>
         </is>
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R14" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" s="11" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="T14" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X14" s="12" t="inlineStr">
@@ -3082,26 +3082,24 @@
       </c>
       <c r="Y14" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>VOMT (untrained stimuli)</t>
         </is>
       </c>
       <c r="Z14" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA14" s="12" t="inlineStr">
-        <is>
-          <t>TIADL (everyday functioning); EPT</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr"/>
       <c r="AB14" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC14" s="12" t="n">
-        <v>9</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD14" s="12" t="inlineStr">
         <is>
@@ -3115,11 +3113,19 @@
       </c>
       <c r="AF14" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG14" s="13" t="inlineStr"/>
-      <c r="AH14" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+        </is>
+      </c>
       <c r="AI14" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -3142,7 +3148,7 @@
       </c>
       <c r="AM14" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN14" s="14" t="inlineStr">
@@ -3152,35 +3158,35 @@
       </c>
       <c r="AO14" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
+          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
+          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -3189,20 +3195,20 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>66.7</v>
+        <v>32</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="K15" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
@@ -3211,22 +3217,22 @@
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Categorization WM Span (verbal, modified)</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
@@ -3235,13 +3241,13 @@
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U15" s="11" t="inlineStr">
         <is>
@@ -3255,7 +3261,7 @@
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X15" s="12" t="inlineStr">
@@ -3265,7 +3271,7 @@
       </c>
       <c r="Y15" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z15" s="12" t="inlineStr">
@@ -3275,18 +3281,16 @@
       </c>
       <c r="AA15" s="12" t="inlineStr">
         <is>
-          <t>Processing speed; Executive function</t>
+          <t>TIADL (everyday functioning); EPT</t>
         </is>
       </c>
       <c r="AB15" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC15" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AD15" s="12" t="inlineStr">
         <is>
@@ -3327,7 +3331,7 @@
       </c>
       <c r="AM15" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN15" s="14" t="inlineStr">
@@ -3337,13 +3341,13 @@
       </c>
       <c r="AO15" s="15" t="inlineStr">
         <is>
-          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -3351,16 +3355,16 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
+          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>Journal of visualized experiments : JoVE</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -3374,19 +3378,25 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>16.14</v>
+        <v>66.7</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -3395,7 +3405,7 @@
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
@@ -3405,7 +3415,7 @@
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>Adaptive n-back (0-5 back)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q16" s="11" t="inlineStr">
@@ -3414,13 +3424,13 @@
         </is>
       </c>
       <c r="R16" s="11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S16" s="11" t="n">
         <v>45</v>
       </c>
       <c r="T16" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U16" s="11" t="inlineStr">
         <is>
@@ -3444,7 +3454,7 @@
       </c>
       <c r="Y16" s="12" t="inlineStr">
         <is>
-          <t>Digit Span (backward)</t>
+          <t>WM tasks (untrained)</t>
         </is>
       </c>
       <c r="Z16" s="12" t="inlineStr">
@@ -3454,7 +3464,7 @@
       </c>
       <c r="AA16" s="12" t="inlineStr">
         <is>
-          <t>CERAD episodic memory; Processing speed (LPS)</t>
+          <t>Processing speed; Executive function</t>
         </is>
       </c>
       <c r="AB16" s="12" t="inlineStr">
@@ -3469,7 +3479,7 @@
       </c>
       <c r="AD16" s="12" t="inlineStr">
         <is>
-          <t>d=0.78(教育组间)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE16" s="12" t="inlineStr">
@@ -3491,22 +3501,22 @@
       </c>
       <c r="AJ16" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK16" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL16" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM16" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN16" s="14" t="inlineStr">
@@ -3516,35 +3526,35 @@
       </c>
       <c r="AO16" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
+          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -3553,46 +3563,38 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>16.14</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>Adaptive n-back (0-5 back)</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -3601,13 +3603,13 @@
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U17" s="11" t="inlineStr">
         <is>
@@ -3621,7 +3623,7 @@
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X17" s="12" t="inlineStr">
@@ -3631,7 +3633,7 @@
       </c>
       <c r="Y17" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>Digit Span (backward)</t>
         </is>
       </c>
       <c r="Z17" s="12" t="inlineStr">
@@ -3641,25 +3643,27 @@
       </c>
       <c r="AA17" s="12" t="inlineStr">
         <is>
-          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+          <t>CERAD episodic memory; Processing speed (LPS)</t>
         </is>
       </c>
       <c r="AB17" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC17" s="12" t="n">
-        <v>8</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD17" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.78(教育组间)</t>
         </is>
       </c>
       <c r="AE17" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF17" s="13" t="inlineStr">
@@ -3676,22 +3680,22 @@
       </c>
       <c r="AJ17" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK17" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL17" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM17" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN17" s="14" t="inlineStr">
@@ -3701,75 +3705,83 @@
       </c>
       <c r="AO17" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Olivetti</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
+          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Cognitive processing</t>
+          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>医院/社区</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>11.9</v>
+        <v>36</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>MMSE+CDT</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>≥26(MMSE)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>N-back (0-2 back, adaptive)</t>
+          <t>Categorization WM Span (verbal)</t>
         </is>
       </c>
       <c r="Q18" s="11" t="inlineStr">
@@ -3778,15 +3790,13 @@
         </is>
       </c>
       <c r="R18" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="T18" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U18" s="11" t="inlineStr">
         <is>
@@ -3800,7 +3810,7 @@
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X18" s="12" t="inlineStr">
@@ -3810,28 +3820,30 @@
       </c>
       <c r="Y18" s="12" t="inlineStr">
         <is>
-          <t>Corsi Block; Digit Span</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z18" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA18" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+        </is>
+      </c>
       <c r="AB18" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC18" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>8</v>
       </c>
       <c r="AD18" s="12" t="inlineStr">
         <is>
-          <t>d=2.21(近迁移)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE18" s="12" t="inlineStr">
@@ -3868,7 +3880,7 @@
       </c>
       <c r="AM18" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN18" s="14" t="inlineStr">
@@ -3878,92 +3890,92 @@
       </c>
       <c r="AO18" s="15" t="inlineStr">
         <is>
-          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
+          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Olivetti</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
+          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>International journal of aging &amp; human development</t>
+          <t>Cognitive processing</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院/社区</t>
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>68.55</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>5.74</v>
+        <v>5.89</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>11.9</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE+CDT</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥26(MMSE)</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+          <t>N-back (0-2 back, adaptive)</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R19" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>60</v>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T19" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U19" s="11" t="inlineStr">
         <is>
@@ -3987,19 +3999,15 @@
       </c>
       <c r="Y19" s="12" t="inlineStr">
         <is>
-          <t>Spatial WM (untrained)</t>
+          <t>Corsi Block; Digit Span</t>
         </is>
       </c>
       <c r="Z19" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA19" s="12" t="inlineStr">
-        <is>
-          <t>Reasoning; IADL (everyday function)</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr"/>
       <c r="AB19" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4012,7 +4020,7 @@
       </c>
       <c r="AD19" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=2.21(近迁移)</t>
         </is>
       </c>
       <c r="AE19" s="12" t="inlineStr">
@@ -4049,7 +4057,7 @@
       </c>
       <c r="AM19" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN19" s="14" t="inlineStr">
@@ -4059,30 +4067,30 @@
       </c>
       <c r="AO19" s="15" t="inlineStr">
         <is>
-          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
+          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>GeroScience</t>
+          <t>International journal of aging &amp; human development</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -4096,19 +4104,21 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>71</v>
+        <v>68.55</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>4.6</v>
+        <v>5.74</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>16.3</v>
+        <v>58</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -4127,22 +4137,22 @@
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>Multidomain cognitive training (WM+processing speed)</t>
+          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
         </is>
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R20" s="11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S20" s="11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="T20" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U20" s="11" t="inlineStr">
         <is>
@@ -4156,7 +4166,7 @@
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet-based)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X20" s="12" t="inlineStr">
@@ -4166,15 +4176,19 @@
       </c>
       <c r="Y20" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (proximal)</t>
+          <t>Spatial WM (untrained)</t>
         </is>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA20" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>Reasoning; IADL (everyday function)</t>
+        </is>
+      </c>
       <c r="AB20" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4192,37 +4206,29 @@
       </c>
       <c r="AE20" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF20" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG20" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(sMRI)</t>
-        </is>
-      </c>
-      <c r="AH20" s="13" t="inlineStr">
-        <is>
-          <t>白质高信号负荷高者训练获益更少</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG20" s="13" t="inlineStr"/>
+      <c r="AH20" s="13" t="inlineStr"/>
       <c r="AI20" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ20" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK20" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WMH获益更多)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL20" s="14" t="inlineStr">
@@ -4232,7 +4238,7 @@
       </c>
       <c r="AM20" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN20" s="14" t="inlineStr">
@@ -4242,35 +4248,35 @@
       </c>
       <c r="AO20" s="15" t="inlineStr">
         <is>
-          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
+          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
+          <t>GeroScience</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -4279,27 +4285,19 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -4313,12 +4311,12 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>Multidomain cognitive training (WM+processing speed)</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr">
@@ -4327,17 +4325,17 @@
         </is>
       </c>
       <c r="R21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T21" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="S21" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T21" s="11" t="n">
-        <v>6</v>
-      </c>
       <c r="U21" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V21" s="11" t="inlineStr">
@@ -4347,7 +4345,7 @@
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(tablet-based)</t>
         </is>
       </c>
       <c r="X21" s="12" t="inlineStr">
@@ -4357,7 +4355,7 @@
       </c>
       <c r="Y21" s="12" t="inlineStr">
         <is>
-          <t>Listening Span</t>
+          <t>WM tasks (proximal)</t>
         </is>
       </c>
       <c r="Z21" s="12" t="inlineStr">
@@ -4393,12 +4391,12 @@
       </c>
       <c r="AG21" s="13" t="inlineStr">
         <is>
-          <t>fMRI</t>
+          <t>fMRI(sMRI)</t>
         </is>
       </c>
       <c r="AH21" s="13" t="inlineStr">
         <is>
-          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+          <t>白质高信号负荷高者训练获益更少</t>
         </is>
       </c>
       <c r="AI21" s="14" t="inlineStr">
@@ -4413,7 +4411,7 @@
       </c>
       <c r="AK21" s="14" t="inlineStr">
         <is>
-          <t>高&gt;低(类年轻激活者获益更多)</t>
+          <t>低&gt;高(低WMH获益更多)</t>
         </is>
       </c>
       <c r="AL21" s="14" t="inlineStr">
@@ -4423,7 +4421,7 @@
       </c>
       <c r="AM21" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN21" s="14" t="inlineStr">
@@ -4433,53 +4431,59 @@
       </c>
       <c r="AO21" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Tagliabue</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
+          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Attention, perception &amp; psychophysics</t>
+          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>社区(在线)</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>48</v>
+        <v>30</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
@@ -4498,12 +4502,12 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>DMTS (delayed match-to-sample); Enumeration</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q22" s="11" t="inlineStr">
@@ -4512,17 +4516,17 @@
         </is>
       </c>
       <c r="R22" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="T22" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -4532,7 +4536,7 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>自制(在线)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X22" s="12" t="inlineStr">
@@ -4542,7 +4546,7 @@
       </c>
       <c r="Y22" s="12" t="inlineStr">
         <is>
-          <t>DMTS (visuospatial WM, k值)</t>
+          <t>Listening Span</t>
         </is>
       </c>
       <c r="Z22" s="12" t="inlineStr">
@@ -4553,11 +4557,13 @@
       <c r="AA22" s="12" t="inlineStr"/>
       <c r="AB22" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC22" s="12" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC22" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD22" s="12" t="inlineStr">
         <is>
@@ -4571,11 +4577,19 @@
       </c>
       <c r="AF22" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG22" s="13" t="inlineStr"/>
-      <c r="AH22" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG22" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH22" s="13" t="inlineStr">
+        <is>
+          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+        </is>
+      </c>
       <c r="AI22" s="14" t="inlineStr">
         <is>
           <t>高/低</t>
@@ -4588,7 +4602,7 @@
       </c>
       <c r="AK22" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WM基线者获益更多)</t>
+          <t>高&gt;低(类年轻激活者获益更多)</t>
         </is>
       </c>
       <c r="AL22" s="14" t="inlineStr">
@@ -4598,7 +4612,7 @@
       </c>
       <c r="AM22" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN22" s="14" t="inlineStr">
@@ -4608,53 +4622,53 @@
       </c>
       <c r="AO22" s="15" t="inlineStr">
         <is>
-          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Zinke</t>
+          <t>Tagliabue</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
+          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Developmental psychology</t>
+          <t>Attention, perception &amp; psychophysics</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>社区(在线)</t>
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>77.2</v>
+        <v>68.2</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>8.1</v>
+        <v>3</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -4663,7 +4677,7 @@
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>MMST</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -4673,12 +4687,12 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+          <t>DMTS (delayed match-to-sample); Enumeration</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr">
@@ -4687,56 +4701,52 @@
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="T23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>自制(在线)</t>
+        </is>
+      </c>
+      <c r="X23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y23" s="12" t="inlineStr">
+        <is>
+          <t>DMTS (visuospatial WM, k值)</t>
+        </is>
+      </c>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="12" t="inlineStr"/>
+      <c r="AB23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="X23" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y23" s="12" t="inlineStr">
-        <is>
-          <t>Verbal WM (untrained)</t>
-        </is>
-      </c>
-      <c r="Z23" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA23" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; Reasoning</t>
-        </is>
-      </c>
-      <c r="AB23" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC23" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="AD23" s="12" t="inlineStr">
         <is>
@@ -4767,17 +4777,17 @@
       </c>
       <c r="AK23" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低基线者近迁移更大)</t>
+          <t>低&gt;高(低WM基线者获益更多)</t>
         </is>
       </c>
       <c r="AL23" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM23" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN23" s="14" t="inlineStr">
@@ -4787,30 +4797,30 @@
       </c>
       <c r="AO23" s="15" t="inlineStr">
         <is>
-          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Schmicker</t>
+          <t>Zinke</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
+          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Current aging science</t>
+          <t>Developmental psychology</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -4824,18 +4834,16 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>80.5</v>
+        <v>77.2</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>8.1</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
@@ -4844,7 +4852,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMST</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -4854,12 +4862,12 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
         </is>
       </c>
       <c r="Q24" s="11" t="inlineStr">
@@ -4868,13 +4876,13 @@
         </is>
       </c>
       <c r="R24" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T24" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U24" s="11" t="inlineStr">
         <is>
@@ -4898,24 +4906,26 @@
       </c>
       <c r="Y24" s="12" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>Verbal WM (untrained)</t>
         </is>
       </c>
       <c r="Z24" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA24" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Reasoning</t>
+        </is>
+      </c>
       <c r="AB24" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC24" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AD24" s="12" t="inlineStr">
         <is>
@@ -4936,7 +4946,7 @@
       <c r="AH24" s="13" t="inlineStr"/>
       <c r="AI24" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ24" s="14" t="inlineStr">
@@ -4946,17 +4956,17 @@
       </c>
       <c r="AK24" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(低基线者近迁移更大)</t>
         </is>
       </c>
       <c r="AL24" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM24" s="14" t="inlineStr">
         <is>
-          <t>CRI(认知储备指数)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN24" s="14" t="inlineStr">
@@ -4966,35 +4976,35 @@
       </c>
       <c r="AO24" s="15" t="inlineStr">
         <is>
-          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
+          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Matysiak</t>
+          <t>Schmicker</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
+          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>BMC research notes</t>
+          <t>Current aging science</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -5003,16 +5013,18 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>66.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>88</v>
+        <v>6.4</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -5021,12 +5033,12 @@
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
@@ -5036,7 +5048,7 @@
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>N-back (adaptive)</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
@@ -5045,13 +5057,13 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U25" s="11" t="inlineStr">
         <is>
@@ -5065,7 +5077,7 @@
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
-          <t>PsychoPy自制</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X25" s="12" t="inlineStr">
@@ -5075,19 +5087,15 @@
       </c>
       <c r="Y25" s="12" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>Digit Span</t>
         </is>
       </c>
       <c r="Z25" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA25" s="12" t="inlineStr">
-        <is>
-          <t>Digit Span; Corsi; Stroop</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr"/>
       <c r="AB25" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -5100,7 +5108,7 @@
       </c>
       <c r="AD25" s="12" t="inlineStr">
         <is>
-          <t>η²p=0.05(训练×年龄交互)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE25" s="12" t="inlineStr">
@@ -5127,17 +5135,17 @@
       </c>
       <c r="AK25" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL25" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM25" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>CRI(认知储备指数)</t>
         </is>
       </c>
       <c r="AN25" s="14" t="inlineStr">
@@ -5147,35 +5155,35 @@
       </c>
       <c r="AO25" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Jaeggi</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
+          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
+          <t>BMC research notes</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -5184,22 +5192,16 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>183</v>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>88</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
@@ -5208,12 +5210,12 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>GDS+GAD</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
@@ -5223,7 +5225,7 @@
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q26" s="11" t="inlineStr">
@@ -5232,17 +5234,13 @@
         </is>
       </c>
       <c r="R26" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr">
-        <is>
-          <t>2-10</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="U26" s="11" t="inlineStr">
         <is>
@@ -5256,7 +5254,7 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet)</t>
+          <t>PsychoPy自制</t>
         </is>
       </c>
       <c r="X26" s="12" t="inlineStr">
@@ -5266,7 +5264,7 @@
       </c>
       <c r="Y26" s="12" t="inlineStr">
         <is>
-          <t>Reading Span; Symmetry Span</t>
+          <t>N-back (untrained level)</t>
         </is>
       </c>
       <c r="Z26" s="12" t="inlineStr">
@@ -5276,20 +5274,22 @@
       </c>
       <c r="AA26" s="12" t="inlineStr">
         <is>
-          <t>Letter Sets; Visual LTM</t>
+          <t>Digit Span; Corsi; Stroop</t>
         </is>
       </c>
       <c r="AB26" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC26" s="12" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD26" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²p=0.05(训练×年龄交互)</t>
         </is>
       </c>
       <c r="AE26" s="12" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="AK26" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL26" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM26" s="14" t="inlineStr">
@@ -5336,89 +5336,219 @@
       </c>
       <c r="AO26" s="15" t="inlineStr">
         <is>
-          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Jaeggi</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
+          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" s="10" t="inlineStr"/>
-      <c r="O27" s="11" t="inlineStr"/>
-      <c r="P27" s="11" t="inlineStr"/>
-      <c r="Q27" s="11" t="inlineStr"/>
-      <c r="R27" s="11" t="inlineStr"/>
-      <c r="S27" s="11" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
-      <c r="U27" s="11" t="inlineStr"/>
-      <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="11" t="inlineStr"/>
-      <c r="X27" s="12" t="inlineStr"/>
-      <c r="Y27" s="12" t="inlineStr"/>
-      <c r="Z27" s="12" t="inlineStr"/>
-      <c r="AA27" s="12" t="inlineStr"/>
-      <c r="AB27" s="12" t="inlineStr"/>
-      <c r="AC27" s="12" t="inlineStr"/>
-      <c r="AD27" s="12" t="inlineStr"/>
-      <c r="AE27" s="12" t="inlineStr"/>
-      <c r="AF27" s="13" t="inlineStr"/>
+          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>GDS+GAD</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>2-10</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>自制(tablet)</t>
+        </is>
+      </c>
+      <c r="X27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y27" s="12" t="inlineStr">
+        <is>
+          <t>Reading Span; Symmetry Span</t>
+        </is>
+      </c>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="12" t="inlineStr">
+        <is>
+          <t>Letter Sets; Visual LTM</t>
+        </is>
+      </c>
+      <c r="AB27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE27" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF27" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG27" s="13" t="inlineStr"/>
       <c r="AH27" s="13" t="inlineStr"/>
-      <c r="AI27" s="14" t="inlineStr"/>
-      <c r="AJ27" s="14" t="inlineStr"/>
-      <c r="AK27" s="14" t="inlineStr"/>
-      <c r="AL27" s="14" t="inlineStr"/>
-      <c r="AM27" s="14" t="inlineStr"/>
-      <c r="AN27" s="14" t="inlineStr"/>
-      <c r="AO27" s="15" t="inlineStr"/>
+      <c r="AI27" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ27" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK27" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL27" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM27" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN27" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO27" s="15" t="inlineStr">
+        <is>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
+          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr"/>
@@ -5460,19 +5590,19 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
+          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -5519,24 +5649,24 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
+          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Neuroreport</t>
+          <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
@@ -5578,24 +5708,24 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
+          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Neuroreport</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
@@ -5637,24 +5767,24 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>VK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
+          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr"/>
@@ -5696,24 +5826,24 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VK</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Novel television-based cognitive training improves working memory and executive function.</t>
+          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
@@ -5755,24 +5885,24 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Impact of working memory training on memory performance in old-old adults.</t>
+          <t>Novel television-based cognitive training improves working memory and executive function.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
@@ -5814,24 +5944,24 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
+          <t>Impact of working memory training on memory performance in old-old adults.</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
@@ -5873,24 +6003,24 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
+          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
@@ -5932,11 +6062,11 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -5944,12 +6074,12 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
+          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
@@ -5991,24 +6121,24 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>JA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
+          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Scientific reports</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
@@ -6050,24 +6180,24 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
+          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
@@ -6109,19 +6239,19 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>An evaluation of a working memory training scheme in older adults.</t>
+          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -6168,19 +6298,19 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
+          <t>An evaluation of a working memory training scheme in older adults.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -6227,24 +6357,24 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
+          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>BMC geriatrics</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
@@ -6286,24 +6416,24 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
+          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>BMC geriatrics</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr"/>
@@ -6345,24 +6475,24 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
+          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Gerontology</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
@@ -6404,24 +6534,24 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
+          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Gerontology</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
@@ -6463,24 +6593,24 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
+          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Aging brain</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
@@ -6522,24 +6652,24 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
+          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Aging brain</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
@@ -6581,24 +6711,24 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
+          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in neurology</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
@@ -6640,24 +6770,24 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
+          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
+          <t>Frontiers in neurology</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
@@ -6699,24 +6829,24 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
+          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
@@ -6758,24 +6888,24 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
+          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr"/>
@@ -6817,24 +6947,24 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
+          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr"/>
@@ -6876,24 +7006,24 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Cantarella</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
+          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Psychologie Française</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
@@ -6935,24 +7065,24 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Cantarella</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Impact of strategy use during N-Back training in older adults</t>
+          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Journal of Cognitive Psychology</t>
+          <t>Psychologie Française</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
@@ -6994,24 +7124,24 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
+          <t>Impact of strategy use during N-Back training in older adults</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Applied Cognitive Psychology</t>
+          <t>Journal of Cognitive Psychology</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
@@ -7053,24 +7183,24 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Lange</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+          <t>Applied Cognitive Psychology</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
@@ -7110,6 +7240,65 @@
       <c r="AN56" s="14" t="inlineStr"/>
       <c r="AO56" s="15" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="10" t="inlineStr"/>
+      <c r="H57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr"/>
+      <c r="Q57" s="11" t="inlineStr"/>
+      <c r="R57" s="11" t="inlineStr"/>
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr"/>
+      <c r="V57" s="11" t="inlineStr"/>
+      <c r="W57" s="11" t="inlineStr"/>
+      <c r="X57" s="12" t="inlineStr"/>
+      <c r="Y57" s="12" t="inlineStr"/>
+      <c r="Z57" s="12" t="inlineStr"/>
+      <c r="AA57" s="12" t="inlineStr"/>
+      <c r="AB57" s="12" t="inlineStr"/>
+      <c r="AC57" s="12" t="inlineStr"/>
+      <c r="AD57" s="12" t="inlineStr"/>
+      <c r="AE57" s="12" t="inlineStr"/>
+      <c r="AF57" s="13" t="inlineStr"/>
+      <c r="AG57" s="13" t="inlineStr"/>
+      <c r="AH57" s="13" t="inlineStr"/>
+      <c r="AI57" s="14" t="inlineStr"/>
+      <c r="AJ57" s="14" t="inlineStr"/>
+      <c r="AK57" s="14" t="inlineStr"/>
+      <c r="AL57" s="14" t="inlineStr"/>
+      <c r="AM57" s="14" t="inlineStr"/>
+      <c r="AN57" s="14" t="inlineStr"/>
+      <c r="AO57" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -3388,42 +3388,162 @@
           <t>Psychological research</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>大学</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" s="10" t="inlineStr"/>
-      <c r="O27" s="11" t="inlineStr"/>
-      <c r="P27" s="11" t="inlineStr"/>
-      <c r="Q27" s="11" t="inlineStr"/>
-      <c r="R27" s="11" t="inlineStr"/>
-      <c r="S27" s="11" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
-      <c r="U27" s="11" t="inlineStr"/>
-      <c r="V27" s="11" t="inlineStr"/>
-      <c r="W27" s="11" t="inlineStr"/>
-      <c r="X27" s="12" t="inlineStr"/>
-      <c r="Y27" s="12" t="inlineStr"/>
-      <c r="Z27" s="12" t="inlineStr"/>
-      <c r="AA27" s="12" t="inlineStr"/>
-      <c r="AB27" s="12" t="inlineStr"/>
-      <c r="AC27" s="12" t="inlineStr"/>
-      <c r="AD27" s="12" t="inlineStr"/>
-      <c r="AE27" s="12" t="inlineStr"/>
-      <c r="AF27" s="13" t="inlineStr"/>
+      <c r="L27" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>verbal n-back</t>
+        </is>
+      </c>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>2-4周</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y27" s="12" t="inlineStr">
+        <is>
+          <t>spatial n-back</t>
+        </is>
+      </c>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="12" t="inlineStr">
+        <is>
+          <t>fluid intelligence (Raven)</t>
+        </is>
+      </c>
+      <c r="AB27" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD27" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE27" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF27" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG27" s="13" t="inlineStr"/>
       <c r="AH27" s="13" t="inlineStr"/>
-      <c r="AI27" s="14" t="inlineStr"/>
-      <c r="AJ27" s="14" t="inlineStr"/>
-      <c r="AK27" s="14" t="inlineStr"/>
-      <c r="AL27" s="14" t="inlineStr"/>
-      <c r="AM27" s="14" t="inlineStr"/>
-      <c r="AN27" s="14" t="inlineStr"/>
-      <c r="AO27" s="15" t="inlineStr"/>
+      <c r="AI27" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ27" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK27" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL27" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM27" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN27" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO27" s="15" t="inlineStr">
+        <is>
+          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n">
@@ -3447,42 +3567,160 @@
           <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr"/>
-      <c r="I28" s="10" t="inlineStr"/>
-      <c r="J28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" s="10" t="inlineStr"/>
-      <c r="O28" s="11" t="inlineStr"/>
-      <c r="P28" s="11" t="inlineStr"/>
-      <c r="Q28" s="11" t="inlineStr"/>
-      <c r="R28" s="11" t="inlineStr"/>
-      <c r="S28" s="11" t="inlineStr"/>
-      <c r="T28" s="11" t="inlineStr"/>
-      <c r="U28" s="11" t="inlineStr"/>
-      <c r="V28" s="11" t="inlineStr"/>
-      <c r="W28" s="11" t="inlineStr"/>
-      <c r="X28" s="12" t="inlineStr"/>
-      <c r="Y28" s="12" t="inlineStr"/>
-      <c r="Z28" s="12" t="inlineStr"/>
-      <c r="AA28" s="12" t="inlineStr"/>
-      <c r="AB28" s="12" t="inlineStr"/>
-      <c r="AC28" s="12" t="inlineStr"/>
-      <c r="AD28" s="12" t="inlineStr"/>
-      <c r="AE28" s="12" t="inlineStr"/>
-      <c r="AF28" s="13" t="inlineStr"/>
+      <c r="L28" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>verbal WM span (CWMS)</t>
+        </is>
+      </c>
+      <c r="Q28" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R28" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S28" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V28" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X28" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y28" s="12" t="inlineStr">
+        <is>
+          <t>WM criterion task (CWMS)</t>
+        </is>
+      </c>
+      <c r="Z28" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
+        </is>
+      </c>
+      <c r="AB28" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC28" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD28" s="12" t="inlineStr">
+        <is>
+          <t>d&gt;=0.8 (large effect)</t>
+        </is>
+      </c>
+      <c r="AE28" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF28" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG28" s="13" t="inlineStr"/>
       <c r="AH28" s="13" t="inlineStr"/>
-      <c r="AI28" s="14" t="inlineStr"/>
-      <c r="AJ28" s="14" t="inlineStr"/>
-      <c r="AK28" s="14" t="inlineStr"/>
-      <c r="AL28" s="14" t="inlineStr"/>
-      <c r="AM28" s="14" t="inlineStr"/>
-      <c r="AN28" s="14" t="inlineStr"/>
-      <c r="AO28" s="15" t="inlineStr"/>
+      <c r="AI28" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ28" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK28" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL28" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM28" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN28" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO28" s="15" t="inlineStr">
+        <is>
+          <t>评估日常生活能力迁移效应</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -3506,42 +3744,162 @@
           <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr"/>
-      <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="10" t="inlineStr"/>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="11" t="inlineStr"/>
-      <c r="P29" s="11" t="inlineStr"/>
-      <c r="Q29" s="11" t="inlineStr"/>
-      <c r="R29" s="11" t="inlineStr"/>
-      <c r="S29" s="11" t="inlineStr"/>
-      <c r="T29" s="11" t="inlineStr"/>
-      <c r="U29" s="11" t="inlineStr"/>
-      <c r="V29" s="11" t="inlineStr"/>
-      <c r="W29" s="11" t="inlineStr"/>
-      <c r="X29" s="12" t="inlineStr"/>
-      <c r="Y29" s="12" t="inlineStr"/>
-      <c r="Z29" s="12" t="inlineStr"/>
-      <c r="AA29" s="12" t="inlineStr"/>
-      <c r="AB29" s="12" t="inlineStr"/>
-      <c r="AC29" s="12" t="inlineStr"/>
-      <c r="AD29" s="12" t="inlineStr"/>
-      <c r="AE29" s="12" t="inlineStr"/>
-      <c r="AF29" s="13" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>verbal WM span (CWMS)</t>
+        </is>
+      </c>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X29" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y29" s="12" t="inlineStr">
+        <is>
+          <t>WM updating task</t>
+        </is>
+      </c>
+      <c r="Z29" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA29" s="12" t="inlineStr">
+        <is>
+          <t>Language comprehension; Cattell fluid intelligence</t>
+        </is>
+      </c>
+      <c r="AB29" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC29" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD29" s="12" t="inlineStr">
+        <is>
+          <t>η²=0.15-0.26 (transfer)</t>
+        </is>
+      </c>
+      <c r="AE29" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF29" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG29" s="13" t="inlineStr"/>
       <c r="AH29" s="13" t="inlineStr"/>
-      <c r="AI29" s="14" t="inlineStr"/>
-      <c r="AJ29" s="14" t="inlineStr"/>
-      <c r="AK29" s="14" t="inlineStr"/>
-      <c r="AL29" s="14" t="inlineStr"/>
-      <c r="AM29" s="14" t="inlineStr"/>
-      <c r="AN29" s="14" t="inlineStr"/>
-      <c r="AO29" s="15" t="inlineStr"/>
+      <c r="AI29" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ29" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK29" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL29" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM29" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN29" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO29" s="15" t="inlineStr">
+        <is>
+          <t>6个月随访；语言理解力迁移</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n">
@@ -3565,42 +3923,154 @@
           <t>Neuroreport</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="10" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr"/>
-      <c r="I30" s="10" t="inlineStr"/>
-      <c r="J30" s="10" t="inlineStr"/>
-      <c r="K30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>医院</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>68</v>
+      </c>
       <c r="L30" s="10" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" s="10" t="inlineStr"/>
-      <c r="O30" s="11" t="inlineStr"/>
-      <c r="P30" s="11" t="inlineStr"/>
-      <c r="Q30" s="11" t="inlineStr"/>
-      <c r="R30" s="11" t="inlineStr"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>CACT (computer-assisted cognitive training)</t>
+        </is>
+      </c>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S30" s="11" t="inlineStr"/>
-      <c r="T30" s="11" t="inlineStr"/>
-      <c r="U30" s="11" t="inlineStr"/>
-      <c r="V30" s="11" t="inlineStr"/>
-      <c r="W30" s="11" t="inlineStr"/>
-      <c r="X30" s="12" t="inlineStr"/>
-      <c r="Y30" s="12" t="inlineStr"/>
-      <c r="Z30" s="12" t="inlineStr"/>
+      <c r="T30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>Maxmedica CACT</t>
+        </is>
+      </c>
+      <c r="X30" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y30" s="12" t="inlineStr">
+        <is>
+          <t>Verbal WM task; Digit span forward</t>
+        </is>
+      </c>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA30" s="12" t="inlineStr"/>
-      <c r="AB30" s="12" t="inlineStr"/>
-      <c r="AC30" s="12" t="inlineStr"/>
-      <c r="AD30" s="12" t="inlineStr"/>
-      <c r="AE30" s="12" t="inlineStr"/>
-      <c r="AF30" s="13" t="inlineStr"/>
+      <c r="AB30" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC30" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD30" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE30" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF30" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG30" s="13" t="inlineStr"/>
       <c r="AH30" s="13" t="inlineStr"/>
-      <c r="AI30" s="14" t="inlineStr"/>
-      <c r="AJ30" s="14" t="inlineStr"/>
-      <c r="AK30" s="14" t="inlineStr"/>
-      <c r="AL30" s="14" t="inlineStr"/>
-      <c r="AM30" s="14" t="inlineStr"/>
-      <c r="AN30" s="14" t="inlineStr"/>
-      <c r="AO30" s="15" t="inlineStr"/>
+      <c r="AI30" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ30" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK30" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL30" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM30" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN30" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO30" s="15" t="inlineStr">
+        <is>
+          <t>tDCS联合CACT；anodal vs sham tDCS</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -3624,42 +4094,154 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="K31" s="10" t="inlineStr"/>
       <c r="L31" s="10" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="11" t="inlineStr"/>
-      <c r="P31" s="11" t="inlineStr"/>
-      <c r="Q31" s="11" t="inlineStr"/>
-      <c r="R31" s="11" t="inlineStr"/>
-      <c r="S31" s="11" t="inlineStr"/>
-      <c r="T31" s="11" t="inlineStr"/>
-      <c r="U31" s="11" t="inlineStr"/>
-      <c r="V31" s="11" t="inlineStr"/>
-      <c r="W31" s="11" t="inlineStr"/>
-      <c r="X31" s="12" t="inlineStr"/>
-      <c r="Y31" s="12" t="inlineStr"/>
-      <c r="Z31" s="12" t="inlineStr"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P31" s="11" t="inlineStr">
+        <is>
+          <t>adaptive spatial n-back</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S31" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X31" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y31" s="12" t="inlineStr">
+        <is>
+          <t>WM composite score (5 tasks)</t>
+        </is>
+      </c>
+      <c r="Z31" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA31" s="12" t="inlineStr"/>
-      <c r="AB31" s="12" t="inlineStr"/>
-      <c r="AC31" s="12" t="inlineStr"/>
-      <c r="AD31" s="12" t="inlineStr"/>
-      <c r="AE31" s="12" t="inlineStr"/>
-      <c r="AF31" s="13" t="inlineStr"/>
+      <c r="AB31" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC31" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD31" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE31" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF31" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG31" s="13" t="inlineStr"/>
       <c r="AH31" s="13" t="inlineStr"/>
-      <c r="AI31" s="14" t="inlineStr"/>
-      <c r="AJ31" s="14" t="inlineStr"/>
-      <c r="AK31" s="14" t="inlineStr"/>
-      <c r="AL31" s="14" t="inlineStr"/>
-      <c r="AM31" s="14" t="inlineStr"/>
-      <c r="AN31" s="14" t="inlineStr"/>
-      <c r="AO31" s="15" t="inlineStr"/>
+      <c r="AI31" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ31" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK31" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL31" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM31" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN31" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO31" s="15" t="inlineStr">
+        <is>
+          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n">
@@ -3683,42 +4265,156 @@
           <t>Aging &amp; mental health</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-      <c r="K32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>医院</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>79</v>
+      </c>
       <c r="L32" s="10" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
-      <c r="O32" s="11" t="inlineStr"/>
-      <c r="P32" s="11" t="inlineStr"/>
-      <c r="Q32" s="11" t="inlineStr"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>computer-assisted cognitive training (multi-domain)</t>
+        </is>
+      </c>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="R32" s="11" t="inlineStr"/>
       <c r="S32" s="11" t="inlineStr"/>
-      <c r="T32" s="11" t="inlineStr"/>
-      <c r="U32" s="11" t="inlineStr"/>
-      <c r="V32" s="11" t="inlineStr"/>
-      <c r="W32" s="11" t="inlineStr"/>
-      <c r="X32" s="12" t="inlineStr"/>
-      <c r="Y32" s="12" t="inlineStr"/>
-      <c r="Z32" s="12" t="inlineStr"/>
-      <c r="AA32" s="12" t="inlineStr"/>
-      <c r="AB32" s="12" t="inlineStr"/>
-      <c r="AC32" s="12" t="inlineStr"/>
-      <c r="AD32" s="12" t="inlineStr"/>
-      <c r="AE32" s="12" t="inlineStr"/>
-      <c r="AF32" s="13" t="inlineStr"/>
+      <c r="T32" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X32" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y32" s="12" t="inlineStr">
+        <is>
+          <t>Primary WM; secondary WM (verbal/visual)</t>
+        </is>
+      </c>
+      <c r="Z32" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA32" s="12" t="inlineStr">
+        <is>
+          <t>Information processing speed; learning; interference tendency</t>
+        </is>
+      </c>
+      <c r="AB32" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC32" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD32" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE32" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF32" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG32" s="13" t="inlineStr"/>
       <c r="AH32" s="13" t="inlineStr"/>
-      <c r="AI32" s="14" t="inlineStr"/>
-      <c r="AJ32" s="14" t="inlineStr"/>
-      <c r="AK32" s="14" t="inlineStr"/>
-      <c r="AL32" s="14" t="inlineStr"/>
-      <c r="AM32" s="14" t="inlineStr"/>
-      <c r="AN32" s="14" t="inlineStr"/>
-      <c r="AO32" s="15" t="inlineStr"/>
+      <c r="AI32" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ32" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK32" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL32" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM32" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN32" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO32" s="15" t="inlineStr">
+        <is>
+          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -3742,42 +4438,154 @@
           <t>PloS one</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="I33" s="10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>7</v>
+      </c>
       <c r="K33" s="10" t="inlineStr"/>
       <c r="L33" s="10" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" s="10" t="inlineStr"/>
-      <c r="O33" s="11" t="inlineStr"/>
-      <c r="P33" s="11" t="inlineStr"/>
-      <c r="Q33" s="11" t="inlineStr"/>
-      <c r="R33" s="11" t="inlineStr"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
+        </is>
+      </c>
+      <c r="Q33" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>25</v>
+      </c>
       <c r="S33" s="11" t="inlineStr"/>
       <c r="T33" s="11" t="inlineStr"/>
-      <c r="U33" s="11" t="inlineStr"/>
-      <c r="V33" s="11" t="inlineStr"/>
-      <c r="W33" s="11" t="inlineStr"/>
-      <c r="X33" s="12" t="inlineStr"/>
-      <c r="Y33" s="12" t="inlineStr"/>
-      <c r="Z33" s="12" t="inlineStr"/>
-      <c r="AA33" s="12" t="inlineStr"/>
-      <c r="AB33" s="12" t="inlineStr"/>
-      <c r="AC33" s="12" t="inlineStr"/>
-      <c r="AD33" s="12" t="inlineStr"/>
-      <c r="AE33" s="12" t="inlineStr"/>
-      <c r="AF33" s="13" t="inlineStr"/>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>CogniFit</t>
+        </is>
+      </c>
+      <c r="X33" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y33" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (validated)</t>
+        </is>
+      </c>
+      <c r="Z33" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>Executive function tasks</t>
+        </is>
+      </c>
+      <c r="AB33" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC33" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD33" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE33" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF33" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG33" s="13" t="inlineStr"/>
       <c r="AH33" s="13" t="inlineStr"/>
-      <c r="AI33" s="14" t="inlineStr"/>
-      <c r="AJ33" s="14" t="inlineStr"/>
-      <c r="AK33" s="14" t="inlineStr"/>
-      <c r="AL33" s="14" t="inlineStr"/>
-      <c r="AM33" s="14" t="inlineStr"/>
-      <c r="AN33" s="14" t="inlineStr"/>
-      <c r="AO33" s="15" t="inlineStr"/>
+      <c r="AI33" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ33" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK33" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL33" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM33" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN33" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO33" s="15" t="inlineStr">
+        <is>
+          <t>互动电视（iTV）平台认知训练</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n">
@@ -3801,42 +4609,158 @@
           <t>Psychology and aging</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="10" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr"/>
-      <c r="I34" s="10" t="inlineStr"/>
-      <c r="J34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="10" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" s="10" t="inlineStr"/>
-      <c r="O34" s="11" t="inlineStr"/>
-      <c r="P34" s="11" t="inlineStr"/>
-      <c r="Q34" s="11" t="inlineStr"/>
-      <c r="R34" s="11" t="inlineStr"/>
-      <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
-      <c r="U34" s="11" t="inlineStr"/>
-      <c r="V34" s="11" t="inlineStr"/>
-      <c r="W34" s="11" t="inlineStr"/>
-      <c r="X34" s="12" t="inlineStr"/>
-      <c r="Y34" s="12" t="inlineStr"/>
-      <c r="Z34" s="12" t="inlineStr"/>
-      <c r="AA34" s="12" t="inlineStr"/>
-      <c r="AB34" s="12" t="inlineStr"/>
-      <c r="AC34" s="12" t="inlineStr"/>
-      <c r="AD34" s="12" t="inlineStr"/>
-      <c r="AE34" s="12" t="inlineStr"/>
-      <c r="AF34" s="13" t="inlineStr"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>WM process-based training (visual/spatial)</t>
+        </is>
+      </c>
+      <c r="Q34" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="S34" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T34" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X34" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y34" s="12" t="inlineStr">
+        <is>
+          <t>Visual WM (VLMT)</t>
+        </is>
+      </c>
+      <c r="Z34" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA34" s="12" t="inlineStr">
+        <is>
+          <t>Visual episodic memory</t>
+        </is>
+      </c>
+      <c r="AB34" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC34" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD34" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE34" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF34" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG34" s="13" t="inlineStr"/>
       <c r="AH34" s="13" t="inlineStr"/>
-      <c r="AI34" s="14" t="inlineStr"/>
-      <c r="AJ34" s="14" t="inlineStr"/>
-      <c r="AK34" s="14" t="inlineStr"/>
-      <c r="AL34" s="14" t="inlineStr"/>
-      <c r="AM34" s="14" t="inlineStr"/>
-      <c r="AN34" s="14" t="inlineStr"/>
-      <c r="AO34" s="15" t="inlineStr"/>
+      <c r="AI34" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ34" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK34" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL34" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM34" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN34" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO34" s="15" t="inlineStr">
+        <is>
+          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -3860,42 +4784,158 @@
           <t>Frontiers in psychology</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr"/>
-      <c r="I35" s="10" t="inlineStr"/>
-      <c r="J35" s="10" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" s="10" t="inlineStr"/>
-      <c r="O35" s="11" t="inlineStr"/>
-      <c r="P35" s="11" t="inlineStr"/>
-      <c r="Q35" s="11" t="inlineStr"/>
-      <c r="R35" s="11" t="inlineStr"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>adaptive verbal + spatial n-back</t>
+        </is>
+      </c>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>16</v>
+      </c>
       <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr"/>
-      <c r="U35" s="11" t="inlineStr"/>
-      <c r="V35" s="11" t="inlineStr"/>
-      <c r="W35" s="11" t="inlineStr"/>
-      <c r="X35" s="12" t="inlineStr"/>
-      <c r="Y35" s="12" t="inlineStr"/>
-      <c r="Z35" s="12" t="inlineStr"/>
-      <c r="AA35" s="12" t="inlineStr"/>
-      <c r="AB35" s="12" t="inlineStr"/>
-      <c r="AC35" s="12" t="inlineStr"/>
-      <c r="AD35" s="12" t="inlineStr"/>
-      <c r="AE35" s="12" t="inlineStr"/>
-      <c r="AF35" s="13" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr">
+        <is>
+          <t>4-8周</t>
+        </is>
+      </c>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>自制（居家在线）</t>
+        </is>
+      </c>
+      <c r="X35" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y35" s="12" t="inlineStr">
+        <is>
+          <t>Digit span</t>
+        </is>
+      </c>
+      <c r="Z35" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="12" t="inlineStr">
+        <is>
+          <t>Abstract relational reasoning</t>
+        </is>
+      </c>
+      <c r="AB35" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC35" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD35" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE35" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF35" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG35" s="13" t="inlineStr"/>
       <c r="AH35" s="13" t="inlineStr"/>
-      <c r="AI35" s="14" t="inlineStr"/>
-      <c r="AJ35" s="14" t="inlineStr"/>
-      <c r="AK35" s="14" t="inlineStr"/>
-      <c r="AL35" s="14" t="inlineStr"/>
-      <c r="AM35" s="14" t="inlineStr"/>
-      <c r="AN35" s="14" t="inlineStr"/>
-      <c r="AO35" s="15" t="inlineStr"/>
+      <c r="AI35" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ35" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK35" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL35" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM35" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN35" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO35" s="15" t="inlineStr">
+        <is>
+          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n">
@@ -3919,42 +4959,160 @@
           <t>Frontiers in human neuroscience</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr"/>
-      <c r="I36" s="10" t="inlineStr"/>
-      <c r="J36" s="10" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="10" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" s="10" t="inlineStr"/>
-      <c r="O36" s="11" t="inlineStr"/>
-      <c r="P36" s="11" t="inlineStr"/>
-      <c r="Q36" s="11" t="inlineStr"/>
-      <c r="R36" s="11" t="inlineStr"/>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
+        <is>
+          <t>adaptive n-back</t>
+        </is>
+      </c>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="inlineStr"/>
-      <c r="U36" s="11" t="inlineStr"/>
-      <c r="V36" s="11" t="inlineStr"/>
-      <c r="W36" s="11" t="inlineStr"/>
-      <c r="X36" s="12" t="inlineStr"/>
-      <c r="Y36" s="12" t="inlineStr"/>
-      <c r="Z36" s="12" t="inlineStr"/>
+      <c r="T36" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X36" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y36" s="12" t="inlineStr">
+        <is>
+          <t>multimodal dual-task (visual+auditory)</t>
+        </is>
+      </c>
+      <c r="Z36" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA36" s="12" t="inlineStr"/>
-      <c r="AB36" s="12" t="inlineStr"/>
-      <c r="AC36" s="12" t="inlineStr"/>
-      <c r="AD36" s="12" t="inlineStr"/>
-      <c r="AE36" s="12" t="inlineStr"/>
-      <c r="AF36" s="13" t="inlineStr"/>
-      <c r="AG36" s="13" t="inlineStr"/>
-      <c r="AH36" s="13" t="inlineStr"/>
-      <c r="AI36" s="14" t="inlineStr"/>
-      <c r="AJ36" s="14" t="inlineStr"/>
-      <c r="AK36" s="14" t="inlineStr"/>
-      <c r="AL36" s="14" t="inlineStr"/>
-      <c r="AM36" s="14" t="inlineStr"/>
-      <c r="AN36" s="14" t="inlineStr"/>
-      <c r="AO36" s="15" t="inlineStr"/>
+      <c r="AB36" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC36" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD36" s="12" t="inlineStr">
+        <is>
+          <t>p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="AE36" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF36" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG36" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH36" s="13" t="inlineStr">
+        <is>
+          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
+        </is>
+      </c>
+      <c r="AI36" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ36" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK36" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL36" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM36" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN36" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO36" s="15" t="inlineStr">
+        <is>
+          <t>双任务迁移；fMRI子研究；先导研究</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -3978,42 +5136,144 @@
           <t>Scientific reports</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="10" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>137</v>
+      </c>
       <c r="I37" s="10" t="inlineStr"/>
       <c r="J37" s="10" t="inlineStr"/>
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" s="10" t="inlineStr"/>
-      <c r="O37" s="11" t="inlineStr"/>
-      <c r="P37" s="11" t="inlineStr"/>
-      <c r="Q37" s="11" t="inlineStr"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P37" s="11" t="inlineStr">
+        <is>
+          <t>Visual and Spatial WM training</t>
+        </is>
+      </c>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R37" s="11" t="inlineStr"/>
       <c r="S37" s="11" t="inlineStr"/>
       <c r="T37" s="11" t="inlineStr"/>
-      <c r="U37" s="11" t="inlineStr"/>
-      <c r="V37" s="11" t="inlineStr"/>
-      <c r="W37" s="11" t="inlineStr"/>
-      <c r="X37" s="12" t="inlineStr"/>
-      <c r="Y37" s="12" t="inlineStr"/>
-      <c r="Z37" s="12" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X37" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y37" s="12" t="inlineStr">
+        <is>
+          <t>Visual WM; Spatial WM</t>
+        </is>
+      </c>
+      <c r="Z37" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA37" s="12" t="inlineStr"/>
-      <c r="AB37" s="12" t="inlineStr"/>
-      <c r="AC37" s="12" t="inlineStr"/>
-      <c r="AD37" s="12" t="inlineStr"/>
-      <c r="AE37" s="12" t="inlineStr"/>
-      <c r="AF37" s="13" t="inlineStr"/>
+      <c r="AB37" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC37" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD37" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE37" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF37" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG37" s="13" t="inlineStr"/>
       <c r="AH37" s="13" t="inlineStr"/>
-      <c r="AI37" s="14" t="inlineStr"/>
-      <c r="AJ37" s="14" t="inlineStr"/>
-      <c r="AK37" s="14" t="inlineStr"/>
-      <c r="AL37" s="14" t="inlineStr"/>
-      <c r="AM37" s="14" t="inlineStr"/>
-      <c r="AN37" s="14" t="inlineStr"/>
-      <c r="AO37" s="15" t="inlineStr"/>
+      <c r="AI37" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ37" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK37" s="14" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AL37" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM37" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN37" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO37" s="15" t="inlineStr">
+        <is>
+          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n">
@@ -4037,42 +5297,150 @@
           <t>Psychological research</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr"/>
-      <c r="H38" s="10" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>103</v>
+      </c>
       <c r="I38" s="10" t="inlineStr"/>
       <c r="J38" s="10" t="inlineStr"/>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="10" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr"/>
-      <c r="O38" s="11" t="inlineStr"/>
-      <c r="P38" s="11" t="inlineStr"/>
-      <c r="Q38" s="11" t="inlineStr"/>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O38" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P38" s="11" t="inlineStr">
+        <is>
+          <t>commercial brain training app (multi-domain)</t>
+        </is>
+      </c>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R38" s="11" t="inlineStr"/>
       <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
-      <c r="U38" s="11" t="inlineStr"/>
-      <c r="V38" s="11" t="inlineStr"/>
-      <c r="W38" s="11" t="inlineStr"/>
-      <c r="X38" s="12" t="inlineStr"/>
-      <c r="Y38" s="12" t="inlineStr"/>
-      <c r="Z38" s="12" t="inlineStr"/>
-      <c r="AA38" s="12" t="inlineStr"/>
-      <c r="AB38" s="12" t="inlineStr"/>
-      <c r="AC38" s="12" t="inlineStr"/>
-      <c r="AD38" s="12" t="inlineStr"/>
-      <c r="AE38" s="12" t="inlineStr"/>
-      <c r="AF38" s="13" t="inlineStr"/>
+      <c r="T38" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>商业脑训练app</t>
+        </is>
+      </c>
+      <c r="X38" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y38" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (trained domain)</t>
+        </is>
+      </c>
+      <c r="Z38" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; attention; language</t>
+        </is>
+      </c>
+      <c r="AB38" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC38" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD38" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE38" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF38" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG38" s="13" t="inlineStr"/>
       <c r="AH38" s="13" t="inlineStr"/>
-      <c r="AI38" s="14" t="inlineStr"/>
-      <c r="AJ38" s="14" t="inlineStr"/>
-      <c r="AK38" s="14" t="inlineStr"/>
-      <c r="AL38" s="14" t="inlineStr"/>
-      <c r="AM38" s="14" t="inlineStr"/>
-      <c r="AN38" s="14" t="inlineStr"/>
-      <c r="AO38" s="15" t="inlineStr"/>
+      <c r="AI38" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ38" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK38" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL38" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM38" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN38" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO38" s="15" t="inlineStr">
+        <is>
+          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -4096,42 +5464,158 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>35</v>
+      </c>
       <c r="I39" s="10" t="inlineStr"/>
       <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" s="10" t="inlineStr"/>
-      <c r="O39" s="11" t="inlineStr"/>
-      <c r="P39" s="11" t="inlineStr"/>
-      <c r="Q39" s="11" t="inlineStr"/>
-      <c r="R39" s="11" t="inlineStr"/>
-      <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="inlineStr"/>
-      <c r="U39" s="11" t="inlineStr"/>
-      <c r="V39" s="11" t="inlineStr"/>
-      <c r="W39" s="11" t="inlineStr"/>
-      <c r="X39" s="12" t="inlineStr"/>
-      <c r="Y39" s="12" t="inlineStr"/>
-      <c r="Z39" s="12" t="inlineStr"/>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P39" s="11" t="inlineStr">
+        <is>
+          <t>Cogmed (adaptive WM training)</t>
+        </is>
+      </c>
+      <c r="Q39" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S39" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="T39" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>Cogmed</t>
+        </is>
+      </c>
+      <c r="X39" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y39" s="12" t="inlineStr">
+        <is>
+          <t>n-back (0-back, 1-back, 2-back)</t>
+        </is>
+      </c>
+      <c r="Z39" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA39" s="12" t="inlineStr"/>
-      <c r="AB39" s="12" t="inlineStr"/>
-      <c r="AC39" s="12" t="inlineStr"/>
-      <c r="AD39" s="12" t="inlineStr"/>
-      <c r="AE39" s="12" t="inlineStr"/>
-      <c r="AF39" s="13" t="inlineStr"/>
-      <c r="AG39" s="13" t="inlineStr"/>
-      <c r="AH39" s="13" t="inlineStr"/>
-      <c r="AI39" s="14" t="inlineStr"/>
-      <c r="AJ39" s="14" t="inlineStr"/>
-      <c r="AK39" s="14" t="inlineStr"/>
-      <c r="AL39" s="14" t="inlineStr"/>
-      <c r="AM39" s="14" t="inlineStr"/>
-      <c r="AN39" s="14" t="inlineStr"/>
-      <c r="AO39" s="15" t="inlineStr"/>
+      <c r="AB39" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC39" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD39" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE39" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF39" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG39" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH39" s="13" t="inlineStr">
+        <is>
+          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
+        </is>
+      </c>
+      <c r="AI39" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ39" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK39" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL39" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM39" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN39" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO39" s="15" t="inlineStr">
+        <is>
+          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n">
@@ -4155,42 +5639,154 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr"/>
-      <c r="G40" s="10" t="inlineStr"/>
-      <c r="H40" s="10" t="inlineStr"/>
-      <c r="I40" s="10" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" s="10" t="inlineStr"/>
-      <c r="O40" s="11" t="inlineStr"/>
-      <c r="P40" s="11" t="inlineStr"/>
-      <c r="Q40" s="11" t="inlineStr"/>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P40" s="11" t="inlineStr">
+        <is>
+          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
+        </is>
+      </c>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R40" s="11" t="inlineStr"/>
       <c r="S40" s="11" t="inlineStr"/>
-      <c r="T40" s="11" t="inlineStr"/>
-      <c r="U40" s="11" t="inlineStr"/>
-      <c r="V40" s="11" t="inlineStr"/>
-      <c r="W40" s="11" t="inlineStr"/>
-      <c r="X40" s="12" t="inlineStr"/>
-      <c r="Y40" s="12" t="inlineStr"/>
-      <c r="Z40" s="12" t="inlineStr"/>
-      <c r="AA40" s="12" t="inlineStr"/>
-      <c r="AB40" s="12" t="inlineStr"/>
-      <c r="AC40" s="12" t="inlineStr"/>
-      <c r="AD40" s="12" t="inlineStr"/>
-      <c r="AE40" s="12" t="inlineStr"/>
-      <c r="AF40" s="13" t="inlineStr"/>
+      <c r="T40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>自制（在线）</t>
+        </is>
+      </c>
+      <c r="X40" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y40" s="12" t="inlineStr">
+        <is>
+          <t>Auditory STM span; visuospatial STM</t>
+        </is>
+      </c>
+      <c r="Z40" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr">
+        <is>
+          <t>Long-term episodic memory</t>
+        </is>
+      </c>
+      <c r="AB40" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC40" s="12" t="inlineStr">
+        <is>
+          <t>3;6</t>
+        </is>
+      </c>
+      <c r="AD40" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE40" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF40" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG40" s="13" t="inlineStr"/>
       <c r="AH40" s="13" t="inlineStr"/>
-      <c r="AI40" s="14" t="inlineStr"/>
-      <c r="AJ40" s="14" t="inlineStr"/>
-      <c r="AK40" s="14" t="inlineStr"/>
-      <c r="AL40" s="14" t="inlineStr"/>
-      <c r="AM40" s="14" t="inlineStr"/>
-      <c r="AN40" s="14" t="inlineStr"/>
-      <c r="AO40" s="15" t="inlineStr"/>
+      <c r="AI40" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ40" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK40" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL40" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM40" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN40" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO40" s="15" t="inlineStr">
+        <is>
+          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -4214,42 +5810,146 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>97</v>
+      </c>
       <c r="I41" s="10" t="inlineStr"/>
       <c r="J41" s="10" t="inlineStr"/>
       <c r="K41" s="10" t="inlineStr"/>
       <c r="L41" s="10" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" s="10" t="inlineStr"/>
-      <c r="O41" s="11" t="inlineStr"/>
-      <c r="P41" s="11" t="inlineStr"/>
-      <c r="Q41" s="11" t="inlineStr"/>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P41" s="11" t="inlineStr">
+        <is>
+          <t>computerized WM training (web-based)</t>
+        </is>
+      </c>
+      <c r="Q41" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R41" s="11" t="inlineStr"/>
       <c r="S41" s="11" t="inlineStr"/>
-      <c r="T41" s="11" t="inlineStr"/>
-      <c r="U41" s="11" t="inlineStr"/>
-      <c r="V41" s="11" t="inlineStr"/>
-      <c r="W41" s="11" t="inlineStr"/>
-      <c r="X41" s="12" t="inlineStr"/>
-      <c r="Y41" s="12" t="inlineStr"/>
-      <c r="Z41" s="12" t="inlineStr"/>
+      <c r="T41" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>商业软件</t>
+        </is>
+      </c>
+      <c r="X41" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y41" s="12" t="inlineStr">
+        <is>
+          <t>Self-perceived cognitive failures (CFQ)</t>
+        </is>
+      </c>
+      <c r="Z41" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA41" s="12" t="inlineStr"/>
-      <c r="AB41" s="12" t="inlineStr"/>
-      <c r="AC41" s="12" t="inlineStr"/>
-      <c r="AD41" s="12" t="inlineStr"/>
-      <c r="AE41" s="12" t="inlineStr"/>
-      <c r="AF41" s="13" t="inlineStr"/>
+      <c r="AB41" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC41" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD41" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE41" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF41" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG41" s="13" t="inlineStr"/>
       <c r="AH41" s="13" t="inlineStr"/>
-      <c r="AI41" s="14" t="inlineStr"/>
-      <c r="AJ41" s="14" t="inlineStr"/>
-      <c r="AK41" s="14" t="inlineStr"/>
-      <c r="AL41" s="14" t="inlineStr"/>
-      <c r="AM41" s="14" t="inlineStr"/>
-      <c r="AN41" s="14" t="inlineStr"/>
-      <c r="AO41" s="15" t="inlineStr"/>
+      <c r="AI41" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ41" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK41" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL41" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM41" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN41" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO41" s="15" t="inlineStr">
+        <is>
+          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n">
@@ -4273,42 +5973,162 @@
           <t>BMC geriatrics</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="10" t="inlineStr"/>
-      <c r="H42" s="10" t="inlineStr"/>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" s="10" t="inlineStr"/>
-      <c r="O42" s="11" t="inlineStr"/>
-      <c r="P42" s="11" t="inlineStr"/>
-      <c r="Q42" s="11" t="inlineStr"/>
-      <c r="R42" s="11" t="inlineStr"/>
-      <c r="S42" s="11" t="inlineStr"/>
-      <c r="T42" s="11" t="inlineStr"/>
-      <c r="U42" s="11" t="inlineStr"/>
-      <c r="V42" s="11" t="inlineStr"/>
-      <c r="W42" s="11" t="inlineStr"/>
-      <c r="X42" s="12" t="inlineStr"/>
-      <c r="Y42" s="12" t="inlineStr"/>
-      <c r="Z42" s="12" t="inlineStr"/>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O42" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>verbal WM span (CWMS)</t>
+        </is>
+      </c>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S42" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T42" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X42" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y42" s="12" t="inlineStr">
+        <is>
+          <t>n-back task</t>
+        </is>
+      </c>
+      <c r="Z42" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA42" s="12" t="inlineStr"/>
-      <c r="AB42" s="12" t="inlineStr"/>
-      <c r="AC42" s="12" t="inlineStr"/>
-      <c r="AD42" s="12" t="inlineStr"/>
-      <c r="AE42" s="12" t="inlineStr"/>
-      <c r="AF42" s="13" t="inlineStr"/>
-      <c r="AG42" s="13" t="inlineStr"/>
-      <c r="AH42" s="13" t="inlineStr"/>
-      <c r="AI42" s="14" t="inlineStr"/>
-      <c r="AJ42" s="14" t="inlineStr"/>
-      <c r="AK42" s="14" t="inlineStr"/>
-      <c r="AL42" s="14" t="inlineStr"/>
-      <c r="AM42" s="14" t="inlineStr"/>
-      <c r="AN42" s="14" t="inlineStr"/>
-      <c r="AO42" s="15" t="inlineStr"/>
+      <c r="AB42" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC42" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD42" s="12" t="inlineStr">
+        <is>
+          <t>Cohen's d medium-large</t>
+        </is>
+      </c>
+      <c r="AE42" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF42" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG42" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH42" s="13" t="inlineStr">
+        <is>
+          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
+        </is>
+      </c>
+      <c r="AI42" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ42" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK42" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL42" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM42" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN42" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO42" s="15" t="inlineStr">
+        <is>
+          <t>先导研究；ERP神经相关；6个月随访</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -4332,42 +6152,150 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr"/>
-      <c r="G43" s="10" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>97</v>
+      </c>
       <c r="I43" s="10" t="inlineStr"/>
       <c r="J43" s="10" t="inlineStr"/>
       <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" s="10" t="inlineStr"/>
-      <c r="O43" s="11" t="inlineStr"/>
-      <c r="P43" s="11" t="inlineStr"/>
-      <c r="Q43" s="11" t="inlineStr"/>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P43" s="11" t="inlineStr">
+        <is>
+          <t>web-based WM or logic &amp; planning training</t>
+        </is>
+      </c>
+      <c r="Q43" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R43" s="11" t="inlineStr"/>
       <c r="S43" s="11" t="inlineStr"/>
-      <c r="T43" s="11" t="inlineStr"/>
-      <c r="U43" s="11" t="inlineStr"/>
-      <c r="V43" s="11" t="inlineStr"/>
-      <c r="W43" s="11" t="inlineStr"/>
-      <c r="X43" s="12" t="inlineStr"/>
-      <c r="Y43" s="12" t="inlineStr"/>
-      <c r="Z43" s="12" t="inlineStr"/>
-      <c r="AA43" s="12" t="inlineStr"/>
-      <c r="AB43" s="12" t="inlineStr"/>
-      <c r="AC43" s="12" t="inlineStr"/>
-      <c r="AD43" s="12" t="inlineStr"/>
-      <c r="AE43" s="12" t="inlineStr"/>
-      <c r="AF43" s="13" t="inlineStr"/>
+      <c r="T43" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>商业软件</t>
+        </is>
+      </c>
+      <c r="X43" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y43" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (near transfer)</t>
+        </is>
+      </c>
+      <c r="Z43" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="12" t="inlineStr">
+        <is>
+          <t>Planning; reasoning; processing speed; verbal fluency</t>
+        </is>
+      </c>
+      <c r="AB43" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC43" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD43" s="12" t="inlineStr">
+        <is>
+          <t>未报告 (Bayesian)</t>
+        </is>
+      </c>
+      <c r="AE43" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF43" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG43" s="13" t="inlineStr"/>
       <c r="AH43" s="13" t="inlineStr"/>
-      <c r="AI43" s="14" t="inlineStr"/>
-      <c r="AJ43" s="14" t="inlineStr"/>
-      <c r="AK43" s="14" t="inlineStr"/>
-      <c r="AL43" s="14" t="inlineStr"/>
-      <c r="AM43" s="14" t="inlineStr"/>
-      <c r="AN43" s="14" t="inlineStr"/>
-      <c r="AO43" s="15" t="inlineStr"/>
+      <c r="AI43" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ43" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK43" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL43" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM43" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN43" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO43" s="15" t="inlineStr">
+        <is>
+          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n">
@@ -4391,42 +6319,154 @@
           <t>Gerontology</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr"/>
-      <c r="G44" s="10" t="inlineStr"/>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" s="10" t="inlineStr"/>
-      <c r="O44" s="11" t="inlineStr"/>
-      <c r="P44" s="11" t="inlineStr"/>
-      <c r="Q44" s="11" t="inlineStr"/>
-      <c r="R44" s="11" t="inlineStr"/>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
+          <t>WM span tasks (5 tasks)</t>
+        </is>
+      </c>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S44" s="11" t="inlineStr"/>
       <c r="T44" s="11" t="inlineStr"/>
-      <c r="U44" s="11" t="inlineStr"/>
-      <c r="V44" s="11" t="inlineStr"/>
-      <c r="W44" s="11" t="inlineStr"/>
-      <c r="X44" s="12" t="inlineStr"/>
-      <c r="Y44" s="12" t="inlineStr"/>
-      <c r="Z44" s="12" t="inlineStr"/>
-      <c r="AA44" s="12" t="inlineStr"/>
-      <c r="AB44" s="12" t="inlineStr"/>
-      <c r="AC44" s="12" t="inlineStr"/>
-      <c r="AD44" s="12" t="inlineStr"/>
-      <c r="AE44" s="12" t="inlineStr"/>
-      <c r="AF44" s="13" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X44" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y44" s="12" t="inlineStr">
+        <is>
+          <t>trained WM tasks</t>
+        </is>
+      </c>
+      <c r="Z44" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>Executive functions (2 tests)</t>
+        </is>
+      </c>
+      <c r="AB44" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC44" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD44" s="12" t="inlineStr">
+        <is>
+          <t>d=0.5-0.8 (trained tasks)</t>
+        </is>
+      </c>
+      <c r="AE44" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF44" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG44" s="13" t="inlineStr"/>
       <c r="AH44" s="13" t="inlineStr"/>
-      <c r="AI44" s="14" t="inlineStr"/>
-      <c r="AJ44" s="14" t="inlineStr"/>
-      <c r="AK44" s="14" t="inlineStr"/>
-      <c r="AL44" s="14" t="inlineStr"/>
-      <c r="AM44" s="14" t="inlineStr"/>
-      <c r="AN44" s="14" t="inlineStr"/>
-      <c r="AO44" s="15" t="inlineStr"/>
+      <c r="AI44" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ44" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK44" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL44" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM44" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN44" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO44" s="15" t="inlineStr">
+        <is>
+          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -4450,42 +6490,152 @@
           <t>Frontiers in psychology</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="10" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr"/>
-      <c r="I45" s="10" t="inlineStr"/>
-      <c r="J45" s="10" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I45" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" s="10" t="inlineStr"/>
-      <c r="O45" s="11" t="inlineStr"/>
-      <c r="P45" s="11" t="inlineStr"/>
-      <c r="Q45" s="11" t="inlineStr"/>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>memory updating task (predictable vs unpredictable)</t>
+        </is>
+      </c>
+      <c r="Q45" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R45" s="11" t="inlineStr"/>
       <c r="S45" s="11" t="inlineStr"/>
       <c r="T45" s="11" t="inlineStr"/>
-      <c r="U45" s="11" t="inlineStr"/>
-      <c r="V45" s="11" t="inlineStr"/>
-      <c r="W45" s="11" t="inlineStr"/>
-      <c r="X45" s="12" t="inlineStr"/>
-      <c r="Y45" s="12" t="inlineStr"/>
-      <c r="Z45" s="12" t="inlineStr"/>
-      <c r="AA45" s="12" t="inlineStr"/>
-      <c r="AB45" s="12" t="inlineStr"/>
-      <c r="AC45" s="12" t="inlineStr"/>
-      <c r="AD45" s="12" t="inlineStr"/>
-      <c r="AE45" s="12" t="inlineStr"/>
-      <c r="AF45" s="13" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X45" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y45" s="12" t="inlineStr">
+        <is>
+          <t>WM updating task (novel)</t>
+        </is>
+      </c>
+      <c r="Z45" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="12" t="inlineStr">
+        <is>
+          <t>Episodic memory</t>
+        </is>
+      </c>
+      <c r="AB45" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC45" s="12" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AD45" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE45" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF45" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG45" s="13" t="inlineStr"/>
       <c r="AH45" s="13" t="inlineStr"/>
-      <c r="AI45" s="14" t="inlineStr"/>
-      <c r="AJ45" s="14" t="inlineStr"/>
-      <c r="AK45" s="14" t="inlineStr"/>
-      <c r="AL45" s="14" t="inlineStr"/>
-      <c r="AM45" s="14" t="inlineStr"/>
-      <c r="AN45" s="14" t="inlineStr"/>
-      <c r="AO45" s="15" t="inlineStr"/>
+      <c r="AI45" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ45" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK45" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL45" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM45" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN45" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO45" s="15" t="inlineStr">
+        <is>
+          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n">
@@ -4509,42 +6659,150 @@
           <t>Aging brain</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr"/>
-      <c r="G46" s="10" t="inlineStr"/>
-      <c r="H46" s="10" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>119</v>
+      </c>
       <c r="I46" s="10" t="inlineStr"/>
       <c r="J46" s="10" t="inlineStr"/>
       <c r="K46" s="10" t="inlineStr"/>
       <c r="L46" s="10" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" s="10" t="inlineStr"/>
-      <c r="O46" s="11" t="inlineStr"/>
-      <c r="P46" s="11" t="inlineStr"/>
-      <c r="Q46" s="11" t="inlineStr"/>
-      <c r="R46" s="11" t="inlineStr"/>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P46" s="11" t="inlineStr">
+        <is>
+          <t>n-back + metacognitive program (EngAge)</t>
+        </is>
+      </c>
+      <c r="Q46" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="S46" s="11" t="inlineStr"/>
       <c r="T46" s="11" t="inlineStr"/>
-      <c r="U46" s="11" t="inlineStr"/>
-      <c r="V46" s="11" t="inlineStr"/>
-      <c r="W46" s="11" t="inlineStr"/>
-      <c r="X46" s="12" t="inlineStr"/>
-      <c r="Y46" s="12" t="inlineStr"/>
-      <c r="Z46" s="12" t="inlineStr"/>
-      <c r="AA46" s="12" t="inlineStr"/>
-      <c r="AB46" s="12" t="inlineStr"/>
-      <c r="AC46" s="12" t="inlineStr"/>
-      <c r="AD46" s="12" t="inlineStr"/>
-      <c r="AE46" s="12" t="inlineStr"/>
-      <c r="AF46" s="13" t="inlineStr"/>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>自制（居家）</t>
+        </is>
+      </c>
+      <c r="X46" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y46" s="12" t="inlineStr">
+        <is>
+          <t>non-trained WM measures</t>
+        </is>
+      </c>
+      <c r="Z46" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA46" s="12" t="inlineStr">
+        <is>
+          <t>Inhibitory control; episodic memory</t>
+        </is>
+      </c>
+      <c r="AB46" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC46" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD46" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE46" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF46" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG46" s="13" t="inlineStr"/>
       <c r="AH46" s="13" t="inlineStr"/>
-      <c r="AI46" s="14" t="inlineStr"/>
-      <c r="AJ46" s="14" t="inlineStr"/>
-      <c r="AK46" s="14" t="inlineStr"/>
-      <c r="AL46" s="14" t="inlineStr"/>
-      <c r="AM46" s="14" t="inlineStr"/>
-      <c r="AN46" s="14" t="inlineStr"/>
-      <c r="AO46" s="15" t="inlineStr"/>
+      <c r="AI46" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ46" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK46" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL46" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM46" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN46" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO46" s="15" t="inlineStr">
+        <is>
+          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -4568,42 +6826,160 @@
           <t>Frontiers in human neuroscience</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr"/>
-      <c r="G47" s="10" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr"/>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="11" t="inlineStr"/>
-      <c r="P47" s="11" t="inlineStr"/>
-      <c r="Q47" s="11" t="inlineStr"/>
-      <c r="R47" s="11" t="inlineStr"/>
-      <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
-      <c r="U47" s="11" t="inlineStr"/>
-      <c r="V47" s="11" t="inlineStr"/>
-      <c r="W47" s="11" t="inlineStr"/>
-      <c r="X47" s="12" t="inlineStr"/>
-      <c r="Y47" s="12" t="inlineStr"/>
-      <c r="Z47" s="12" t="inlineStr"/>
-      <c r="AA47" s="12" t="inlineStr"/>
-      <c r="AB47" s="12" t="inlineStr"/>
-      <c r="AC47" s="12" t="inlineStr"/>
-      <c r="AD47" s="12" t="inlineStr"/>
-      <c r="AE47" s="12" t="inlineStr"/>
-      <c r="AF47" s="13" t="inlineStr"/>
+      <c r="L47" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P47" s="11" t="inlineStr">
+        <is>
+          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
+        </is>
+      </c>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S47" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T47" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X47" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y47" s="12" t="inlineStr">
+        <is>
+          <t>visuospatial WM; STM tasks</t>
+        </is>
+      </c>
+      <c r="Z47" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="12" t="inlineStr">
+        <is>
+          <t>fluid intelligence; processing speed; inhibitory measures</t>
+        </is>
+      </c>
+      <c r="AB47" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC47" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD47" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE47" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF47" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG47" s="13" t="inlineStr"/>
       <c r="AH47" s="13" t="inlineStr"/>
-      <c r="AI47" s="14" t="inlineStr"/>
-      <c r="AJ47" s="14" t="inlineStr"/>
-      <c r="AK47" s="14" t="inlineStr"/>
-      <c r="AL47" s="14" t="inlineStr"/>
-      <c r="AM47" s="14" t="inlineStr"/>
-      <c r="AN47" s="14" t="inlineStr"/>
-      <c r="AO47" s="15" t="inlineStr"/>
+      <c r="AI47" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ47" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK47" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL47" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM47" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN47" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO47" s="15" t="inlineStr">
+        <is>
+          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n">
@@ -4627,42 +7003,158 @@
           <t>Frontiers in neurology</t>
         </is>
       </c>
-      <c r="F48" s="10" t="inlineStr"/>
-      <c r="G48" s="10" t="inlineStr"/>
-      <c r="H48" s="10" t="inlineStr"/>
-      <c r="I48" s="10" t="inlineStr"/>
-      <c r="J48" s="10" t="inlineStr"/>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>6.5</v>
+      </c>
       <c r="K48" s="10" t="inlineStr"/>
       <c r="L48" s="10" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr"/>
-      <c r="O48" s="11" t="inlineStr"/>
-      <c r="P48" s="11" t="inlineStr"/>
-      <c r="Q48" s="11" t="inlineStr"/>
-      <c r="R48" s="11" t="inlineStr"/>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr"/>
-      <c r="U48" s="11" t="inlineStr"/>
-      <c r="V48" s="11" t="inlineStr"/>
-      <c r="W48" s="11" t="inlineStr"/>
-      <c r="X48" s="12" t="inlineStr"/>
-      <c r="Y48" s="12" t="inlineStr"/>
-      <c r="Z48" s="12" t="inlineStr"/>
-      <c r="AA48" s="12" t="inlineStr"/>
-      <c r="AB48" s="12" t="inlineStr"/>
-      <c r="AC48" s="12" t="inlineStr"/>
-      <c r="AD48" s="12" t="inlineStr"/>
-      <c r="AE48" s="12" t="inlineStr"/>
-      <c r="AF48" s="13" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
+        </is>
+      </c>
+      <c r="Q48" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S48" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>TMS</t>
+        </is>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X48" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y48" s="12" t="inlineStr">
+        <is>
+          <t>non-verbal logical reasoning</t>
+        </is>
+      </c>
+      <c r="Z48" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA48" s="12" t="inlineStr">
+        <is>
+          <t>Attention; memory; executive functions</t>
+        </is>
+      </c>
+      <c r="AB48" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC48" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD48" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE48" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF48" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG48" s="13" t="inlineStr"/>
       <c r="AH48" s="13" t="inlineStr"/>
-      <c r="AI48" s="14" t="inlineStr"/>
-      <c r="AJ48" s="14" t="inlineStr"/>
-      <c r="AK48" s="14" t="inlineStr"/>
-      <c r="AL48" s="14" t="inlineStr"/>
-      <c r="AM48" s="14" t="inlineStr"/>
-      <c r="AN48" s="14" t="inlineStr"/>
-      <c r="AO48" s="15" t="inlineStr"/>
+      <c r="AI48" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ48" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK48" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL48" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM48" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN48" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO48" s="15" t="inlineStr">
+        <is>
+          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -4686,42 +7178,158 @@
           <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr"/>
-      <c r="G49" s="10" t="inlineStr"/>
-      <c r="H49" s="10" t="inlineStr"/>
-      <c r="I49" s="10" t="inlineStr"/>
-      <c r="J49" s="10" t="inlineStr"/>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="I49" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K49" s="10" t="inlineStr"/>
       <c r="L49" s="10" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" s="10" t="inlineStr"/>
-      <c r="O49" s="11" t="inlineStr"/>
-      <c r="P49" s="11" t="inlineStr"/>
-      <c r="Q49" s="11" t="inlineStr"/>
-      <c r="R49" s="11" t="inlineStr"/>
-      <c r="S49" s="11" t="inlineStr"/>
-      <c r="T49" s="11" t="inlineStr"/>
-      <c r="U49" s="11" t="inlineStr"/>
-      <c r="V49" s="11" t="inlineStr"/>
-      <c r="W49" s="11" t="inlineStr"/>
-      <c r="X49" s="12" t="inlineStr"/>
-      <c r="Y49" s="12" t="inlineStr"/>
-      <c r="Z49" s="12" t="inlineStr"/>
-      <c r="AA49" s="12" t="inlineStr"/>
-      <c r="AB49" s="12" t="inlineStr"/>
-      <c r="AC49" s="12" t="inlineStr"/>
-      <c r="AD49" s="12" t="inlineStr"/>
-      <c r="AE49" s="12" t="inlineStr"/>
-      <c r="AF49" s="13" t="inlineStr"/>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="P49" s="11" t="inlineStr">
+        <is>
+          <t>letter updating task</t>
+        </is>
+      </c>
+      <c r="Q49" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R49" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S49" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X49" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y49" s="12" t="inlineStr">
+        <is>
+          <t>n-back (near transfer)</t>
+        </is>
+      </c>
+      <c r="Z49" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="12" t="inlineStr">
+        <is>
+          <t>executive/memory tasks</t>
+        </is>
+      </c>
+      <c r="AB49" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC49" s="12" t="inlineStr">
+        <is>
+          <t>1;7</t>
+        </is>
+      </c>
+      <c r="AD49" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE49" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF49" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG49" s="13" t="inlineStr"/>
       <c r="AH49" s="13" t="inlineStr"/>
-      <c r="AI49" s="14" t="inlineStr"/>
-      <c r="AJ49" s="14" t="inlineStr"/>
-      <c r="AK49" s="14" t="inlineStr"/>
-      <c r="AL49" s="14" t="inlineStr"/>
-      <c r="AM49" s="14" t="inlineStr"/>
-      <c r="AN49" s="14" t="inlineStr"/>
-      <c r="AO49" s="15" t="inlineStr"/>
+      <c r="AI49" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ49" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK49" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL49" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM49" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN49" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO49" s="15" t="inlineStr">
+        <is>
+          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n">
@@ -4745,42 +7353,152 @@
           <t>Frontiers in human neuroscience</t>
         </is>
       </c>
-      <c r="F50" s="10" t="inlineStr"/>
-      <c r="G50" s="10" t="inlineStr"/>
-      <c r="H50" s="10" t="inlineStr"/>
-      <c r="I50" s="10" t="inlineStr"/>
-      <c r="J50" s="10" t="inlineStr"/>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>487</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="K50" s="10" t="inlineStr"/>
       <c r="L50" s="10" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" s="10" t="inlineStr"/>
-      <c r="O50" s="11" t="inlineStr"/>
-      <c r="P50" s="11" t="inlineStr"/>
-      <c r="Q50" s="11" t="inlineStr"/>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>syllable span + auditory discrimination (IMPACT program)</t>
+        </is>
+      </c>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R50" s="11" t="inlineStr"/>
       <c r="S50" s="11" t="inlineStr"/>
       <c r="T50" s="11" t="inlineStr"/>
-      <c r="U50" s="11" t="inlineStr"/>
-      <c r="V50" s="11" t="inlineStr"/>
-      <c r="W50" s="11" t="inlineStr"/>
-      <c r="X50" s="12" t="inlineStr"/>
-      <c r="Y50" s="12" t="inlineStr"/>
-      <c r="Z50" s="12" t="inlineStr"/>
-      <c r="AA50" s="12" t="inlineStr"/>
-      <c r="AB50" s="12" t="inlineStr"/>
-      <c r="AC50" s="12" t="inlineStr"/>
-      <c r="AD50" s="12" t="inlineStr"/>
-      <c r="AE50" s="12" t="inlineStr"/>
-      <c r="AF50" s="13" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>Posit Science (IMPACT)</t>
+        </is>
+      </c>
+      <c r="X50" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y50" s="12" t="inlineStr">
+        <is>
+          <t>WM factor score</t>
+        </is>
+      </c>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="12" t="inlineStr">
+        <is>
+          <t>List memory; text memory</t>
+        </is>
+      </c>
+      <c r="AB50" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC50" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD50" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE50" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF50" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG50" s="13" t="inlineStr"/>
       <c r="AH50" s="13" t="inlineStr"/>
-      <c r="AI50" s="14" t="inlineStr"/>
-      <c r="AJ50" s="14" t="inlineStr"/>
-      <c r="AK50" s="14" t="inlineStr"/>
-      <c r="AL50" s="14" t="inlineStr"/>
-      <c r="AM50" s="14" t="inlineStr"/>
-      <c r="AN50" s="14" t="inlineStr"/>
-      <c r="AO50" s="15" t="inlineStr"/>
+      <c r="AI50" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ50" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK50" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL50" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM50" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN50" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO50" s="15" t="inlineStr">
+        <is>
+          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -4804,42 +7522,162 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr"/>
-      <c r="G51" s="10" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr"/>
-      <c r="I51" s="10" t="inlineStr"/>
-      <c r="J51" s="10" t="inlineStr"/>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I51" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="11" t="inlineStr"/>
-      <c r="P51" s="11" t="inlineStr"/>
-      <c r="Q51" s="11" t="inlineStr"/>
-      <c r="R51" s="11" t="inlineStr"/>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
-      <c r="U51" s="11" t="inlineStr"/>
-      <c r="V51" s="11" t="inlineStr"/>
-      <c r="W51" s="11" t="inlineStr"/>
-      <c r="X51" s="12" t="inlineStr"/>
-      <c r="Y51" s="12" t="inlineStr"/>
-      <c r="Z51" s="12" t="inlineStr"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>verbal WM span (CWMS)</t>
+        </is>
+      </c>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S51" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T51" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X51" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y51" s="12" t="inlineStr">
+        <is>
+          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
+        </is>
+      </c>
+      <c r="Z51" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA51" s="12" t="inlineStr"/>
-      <c r="AB51" s="12" t="inlineStr"/>
-      <c r="AC51" s="12" t="inlineStr"/>
-      <c r="AD51" s="12" t="inlineStr"/>
-      <c r="AE51" s="12" t="inlineStr"/>
-      <c r="AF51" s="13" t="inlineStr"/>
-      <c r="AG51" s="13" t="inlineStr"/>
-      <c r="AH51" s="13" t="inlineStr"/>
-      <c r="AI51" s="14" t="inlineStr"/>
-      <c r="AJ51" s="14" t="inlineStr"/>
-      <c r="AK51" s="14" t="inlineStr"/>
-      <c r="AL51" s="14" t="inlineStr"/>
-      <c r="AM51" s="14" t="inlineStr"/>
-      <c r="AN51" s="14" t="inlineStr"/>
-      <c r="AO51" s="15" t="inlineStr"/>
+      <c r="AB51" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC51" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD51" s="12" t="inlineStr">
+        <is>
+          <t>d=0.5-0.9</t>
+        </is>
+      </c>
+      <c r="AE51" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF51" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG51" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH51" s="13" t="inlineStr">
+        <is>
+          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
+        </is>
+      </c>
+      <c r="AI51" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ51" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK51" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL51" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM51" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN51" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO51" s="15" t="inlineStr">
+        <is>
+          <t>静息态EEG；额叶振荡活动；先导研究</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n">
@@ -4863,42 +7701,154 @@
           <t>Psychological research</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr"/>
-      <c r="G52" s="10" t="inlineStr"/>
-      <c r="H52" s="10" t="inlineStr"/>
-      <c r="I52" s="10" t="inlineStr"/>
-      <c r="J52" s="10" t="inlineStr"/>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="I52" s="10" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>7.04</v>
+      </c>
       <c r="K52" s="10" t="inlineStr"/>
       <c r="L52" s="10" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" s="10" t="inlineStr"/>
-      <c r="O52" s="11" t="inlineStr"/>
-      <c r="P52" s="11" t="inlineStr"/>
-      <c r="Q52" s="11" t="inlineStr"/>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O52" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P52" s="11" t="inlineStr">
+        <is>
+          <t>single-domain WM (n-back) or multidomain EF training</t>
+        </is>
+      </c>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R52" s="11" t="inlineStr"/>
       <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
-      <c r="U52" s="11" t="inlineStr"/>
-      <c r="V52" s="11" t="inlineStr"/>
-      <c r="W52" s="11" t="inlineStr"/>
-      <c r="X52" s="12" t="inlineStr"/>
-      <c r="Y52" s="12" t="inlineStr"/>
-      <c r="Z52" s="12" t="inlineStr"/>
-      <c r="AA52" s="12" t="inlineStr"/>
-      <c r="AB52" s="12" t="inlineStr"/>
-      <c r="AC52" s="12" t="inlineStr"/>
-      <c r="AD52" s="12" t="inlineStr"/>
-      <c r="AE52" s="12" t="inlineStr"/>
-      <c r="AF52" s="13" t="inlineStr"/>
+      <c r="T52" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X52" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y52" s="12" t="inlineStr">
+        <is>
+          <t>n-back; global EF accuracy</t>
+        </is>
+      </c>
+      <c r="Z52" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr">
+        <is>
+          <t>Prospective memory (Virtual Week); fluid intelligence</t>
+        </is>
+      </c>
+      <c r="AB52" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC52" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD52" s="12" t="inlineStr">
+        <is>
+          <t>未报告 (Bayesian)</t>
+        </is>
+      </c>
+      <c r="AE52" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF52" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG52" s="13" t="inlineStr"/>
       <c r="AH52" s="13" t="inlineStr"/>
-      <c r="AI52" s="14" t="inlineStr"/>
-      <c r="AJ52" s="14" t="inlineStr"/>
-      <c r="AK52" s="14" t="inlineStr"/>
-      <c r="AL52" s="14" t="inlineStr"/>
-      <c r="AM52" s="14" t="inlineStr"/>
-      <c r="AN52" s="14" t="inlineStr"/>
-      <c r="AO52" s="15" t="inlineStr"/>
+      <c r="AI52" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ52" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK52" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL52" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM52" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN52" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO52" s="15" t="inlineStr">
+        <is>
+          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -4922,42 +7872,158 @@
           <t>Psychologie Française</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr"/>
-      <c r="G53" s="10" t="inlineStr"/>
-      <c r="H53" s="10" t="inlineStr"/>
-      <c r="I53" s="10" t="inlineStr"/>
-      <c r="J53" s="10" t="inlineStr"/>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I53" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" s="10" t="inlineStr"/>
-      <c r="O53" s="11" t="inlineStr"/>
-      <c r="P53" s="11" t="inlineStr"/>
-      <c r="Q53" s="11" t="inlineStr"/>
-      <c r="R53" s="11" t="inlineStr"/>
-      <c r="S53" s="11" t="inlineStr"/>
-      <c r="T53" s="11" t="inlineStr"/>
-      <c r="U53" s="11" t="inlineStr"/>
-      <c r="V53" s="11" t="inlineStr"/>
-      <c r="W53" s="11" t="inlineStr"/>
-      <c r="X53" s="12" t="inlineStr"/>
-      <c r="Y53" s="12" t="inlineStr"/>
-      <c r="Z53" s="12" t="inlineStr"/>
-      <c r="AA53" s="12" t="inlineStr"/>
-      <c r="AB53" s="12" t="inlineStr"/>
-      <c r="AC53" s="12" t="inlineStr"/>
-      <c r="AD53" s="12" t="inlineStr"/>
-      <c r="AE53" s="12" t="inlineStr"/>
-      <c r="AF53" s="13" t="inlineStr"/>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O53" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P53" s="11" t="inlineStr">
+        <is>
+          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
+        </is>
+      </c>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S53" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T53" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X53" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y53" s="12" t="inlineStr">
+        <is>
+          <t>visuospatial WM criterion task</t>
+        </is>
+      </c>
+      <c r="Z53" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>verbal WM; visuospatial STM; reasoning</t>
+        </is>
+      </c>
+      <c r="AB53" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD53" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE53" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF53" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG53" s="13" t="inlineStr"/>
       <c r="AH53" s="13" t="inlineStr"/>
-      <c r="AI53" s="14" t="inlineStr"/>
-      <c r="AJ53" s="14" t="inlineStr"/>
-      <c r="AK53" s="14" t="inlineStr"/>
-      <c r="AL53" s="14" t="inlineStr"/>
-      <c r="AM53" s="14" t="inlineStr"/>
-      <c r="AN53" s="14" t="inlineStr"/>
-      <c r="AO53" s="15" t="inlineStr"/>
+      <c r="AI53" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ53" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK53" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL53" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM53" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN53" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO53" s="15" t="inlineStr">
+        <is>
+          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n">
@@ -4981,42 +8047,156 @@
           <t>Journal of Cognitive Psychology</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="10" t="inlineStr"/>
-      <c r="H54" s="10" t="inlineStr"/>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>26</v>
+      </c>
       <c r="I54" s="10" t="inlineStr"/>
       <c r="J54" s="10" t="inlineStr"/>
       <c r="K54" s="10" t="inlineStr"/>
       <c r="L54" s="10" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" s="10" t="inlineStr"/>
-      <c r="O54" s="11" t="inlineStr"/>
-      <c r="P54" s="11" t="inlineStr"/>
-      <c r="Q54" s="11" t="inlineStr"/>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P54" s="11" t="inlineStr">
+        <is>
+          <t>n-back (strategy vs no strategy)</t>
+        </is>
+      </c>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R54" s="11" t="inlineStr"/>
       <c r="S54" s="11" t="inlineStr"/>
       <c r="T54" s="11" t="inlineStr"/>
-      <c r="U54" s="11" t="inlineStr"/>
-      <c r="V54" s="11" t="inlineStr"/>
-      <c r="W54" s="11" t="inlineStr"/>
-      <c r="X54" s="12" t="inlineStr"/>
-      <c r="Y54" s="12" t="inlineStr"/>
-      <c r="Z54" s="12" t="inlineStr"/>
-      <c r="AA54" s="12" t="inlineStr"/>
-      <c r="AB54" s="12" t="inlineStr"/>
-      <c r="AC54" s="12" t="inlineStr"/>
-      <c r="AD54" s="12" t="inlineStr"/>
-      <c r="AE54" s="12" t="inlineStr"/>
-      <c r="AF54" s="13" t="inlineStr"/>
-      <c r="AG54" s="13" t="inlineStr"/>
-      <c r="AH54" s="13" t="inlineStr"/>
-      <c r="AI54" s="14" t="inlineStr"/>
-      <c r="AJ54" s="14" t="inlineStr"/>
-      <c r="AK54" s="14" t="inlineStr"/>
-      <c r="AL54" s="14" t="inlineStr"/>
-      <c r="AM54" s="14" t="inlineStr"/>
-      <c r="AN54" s="14" t="inlineStr"/>
-      <c r="AO54" s="15" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X54" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y54" s="12" t="inlineStr">
+        <is>
+          <t>n-back variant</t>
+        </is>
+      </c>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="12" t="inlineStr">
+        <is>
+          <t>P300 transfer measures</t>
+        </is>
+      </c>
+      <c r="AB54" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC54" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD54" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE54" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF54" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG54" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH54" s="13" t="inlineStr">
+        <is>
+          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
+        </is>
+      </c>
+      <c r="AI54" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ54" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK54" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL54" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM54" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN54" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO54" s="15" t="inlineStr">
+        <is>
+          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -5040,42 +8220,148 @@
           <t>Applied Cognitive Psychology</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="inlineStr"/>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>91</v>
+      </c>
       <c r="I55" s="10" t="inlineStr"/>
       <c r="J55" s="10" t="inlineStr"/>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" s="10" t="inlineStr"/>
-      <c r="O55" s="11" t="inlineStr"/>
-      <c r="P55" s="11" t="inlineStr"/>
-      <c r="Q55" s="11" t="inlineStr"/>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
+        </is>
+      </c>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="R55" s="11" t="inlineStr"/>
       <c r="S55" s="11" t="inlineStr"/>
       <c r="T55" s="11" t="inlineStr"/>
-      <c r="U55" s="11" t="inlineStr"/>
-      <c r="V55" s="11" t="inlineStr"/>
-      <c r="W55" s="11" t="inlineStr"/>
-      <c r="X55" s="12" t="inlineStr"/>
-      <c r="Y55" s="12" t="inlineStr"/>
-      <c r="Z55" s="12" t="inlineStr"/>
-      <c r="AA55" s="12" t="inlineStr"/>
-      <c r="AB55" s="12" t="inlineStr"/>
-      <c r="AC55" s="12" t="inlineStr"/>
-      <c r="AD55" s="12" t="inlineStr"/>
-      <c r="AE55" s="12" t="inlineStr"/>
-      <c r="AF55" s="13" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X55" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y55" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (near transfer)</t>
+        </is>
+      </c>
+      <c r="Z55" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="12" t="inlineStr">
+        <is>
+          <t>Short-term memory; processing speed; reasoning</t>
+        </is>
+      </c>
+      <c r="AB55" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC55" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD55" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE55" s="12" t="inlineStr">
+        <is>
+          <t>无迁移</t>
+        </is>
+      </c>
+      <c r="AF55" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG55" s="13" t="inlineStr"/>
       <c r="AH55" s="13" t="inlineStr"/>
-      <c r="AI55" s="14" t="inlineStr"/>
-      <c r="AJ55" s="14" t="inlineStr"/>
-      <c r="AK55" s="14" t="inlineStr"/>
-      <c r="AL55" s="14" t="inlineStr"/>
-      <c r="AM55" s="14" t="inlineStr"/>
-      <c r="AN55" s="14" t="inlineStr"/>
-      <c r="AO55" s="15" t="inlineStr"/>
+      <c r="AI55" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ55" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK55" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL55" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM55" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN55" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO55" s="15" t="inlineStr">
+        <is>
+          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n">
@@ -5099,42 +8385,156 @@
           <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr"/>
-      <c r="G56" s="10" t="inlineStr"/>
-      <c r="H56" s="10" t="inlineStr"/>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr"/>
-      <c r="K56" s="10" t="inlineStr"/>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="I56" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="10" t="n">
+        <v>100</v>
+      </c>
       <c r="L56" s="10" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" s="10" t="inlineStr"/>
-      <c r="O56" s="11" t="inlineStr"/>
-      <c r="P56" s="11" t="inlineStr"/>
-      <c r="Q56" s="11" t="inlineStr"/>
-      <c r="R56" s="11" t="inlineStr"/>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P56" s="11" t="inlineStr">
+        <is>
+          <t>adaptive WM updating (numerical updating + 1-back)</t>
+        </is>
+      </c>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="S56" s="11" t="inlineStr"/>
       <c r="T56" s="11" t="inlineStr"/>
-      <c r="U56" s="11" t="inlineStr"/>
-      <c r="V56" s="11" t="inlineStr"/>
-      <c r="W56" s="11" t="inlineStr"/>
-      <c r="X56" s="12" t="inlineStr"/>
-      <c r="Y56" s="12" t="inlineStr"/>
-      <c r="Z56" s="12" t="inlineStr"/>
-      <c r="AA56" s="12" t="inlineStr"/>
-      <c r="AB56" s="12" t="inlineStr"/>
-      <c r="AC56" s="12" t="inlineStr"/>
-      <c r="AD56" s="12" t="inlineStr"/>
-      <c r="AE56" s="12" t="inlineStr"/>
-      <c r="AF56" s="13" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X56" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y56" s="12" t="inlineStr">
+        <is>
+          <t>WM updating task</t>
+        </is>
+      </c>
+      <c r="Z56" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="12" t="inlineStr">
+        <is>
+          <t>Cognitive reappraisal (emotion regulation task)</t>
+        </is>
+      </c>
+      <c r="AB56" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC56" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD56" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE56" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF56" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG56" s="13" t="inlineStr"/>
       <c r="AH56" s="13" t="inlineStr"/>
-      <c r="AI56" s="14" t="inlineStr"/>
-      <c r="AJ56" s="14" t="inlineStr"/>
-      <c r="AK56" s="14" t="inlineStr"/>
-      <c r="AL56" s="14" t="inlineStr"/>
-      <c r="AM56" s="14" t="inlineStr"/>
-      <c r="AN56" s="14" t="inlineStr"/>
-      <c r="AO56" s="15" t="inlineStr"/>
+      <c r="AI56" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ56" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK56" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL56" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM56" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN56" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO56" s="15" t="inlineStr">
+        <is>
+          <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>RV</t>
+          <t>Rudner</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -2444,42 +2444,166 @@
           <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="10" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
-      <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
-      <c r="S11" s="11" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="11" t="inlineStr"/>
-      <c r="X11" s="12" t="inlineStr"/>
-      <c r="Y11" s="12" t="inlineStr"/>
-      <c r="Z11" s="12" t="inlineStr"/>
-      <c r="AA11" s="12" t="inlineStr"/>
-      <c r="AB11" s="12" t="inlineStr"/>
-      <c r="AC11" s="12" t="inlineStr"/>
-      <c r="AD11" s="12" t="inlineStr"/>
-      <c r="AE11" s="12" t="inlineStr"/>
-      <c r="AF11" s="13" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>64.95999999999999</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>MoCA</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>≥23</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>Reading Span (Cogmed)</t>
+        </is>
+      </c>
+      <c r="Q11" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>Cogmed</t>
+        </is>
+      </c>
+      <c r="X11" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" s="12" t="inlineStr">
+        <is>
+          <t>Reading Span (untrained version)</t>
+        </is>
+      </c>
+      <c r="Z11" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>Speech-in-noise comprehension</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE11" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF11" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG11" s="13" t="inlineStr"/>
       <c r="AH11" s="13" t="inlineStr"/>
-      <c r="AI11" s="14" t="inlineStr"/>
-      <c r="AJ11" s="14" t="inlineStr"/>
-      <c r="AK11" s="14" t="inlineStr"/>
-      <c r="AL11" s="14" t="inlineStr"/>
-      <c r="AM11" s="14" t="inlineStr"/>
-      <c r="AN11" s="14" t="inlineStr"/>
-      <c r="AO11" s="15" t="inlineStr"/>
+      <c r="AI11" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ11" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK11" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL11" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM11" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN11" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO11" s="15" t="inlineStr">
+        <is>
+          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -2487,7 +2611,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>Berryhill</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -2503,917 +2627,2777 @@
           <t>Brain stimulation</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
-      <c r="G12" s="10" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr"/>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr"/>
-      <c r="L12" s="10" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
-      <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
-      <c r="Q12" s="11" t="inlineStr"/>
-      <c r="R12" s="11" t="inlineStr"/>
-      <c r="S12" s="11" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="11" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="11" t="inlineStr"/>
-      <c r="X12" s="12" t="inlineStr"/>
-      <c r="Y12" s="12" t="inlineStr"/>
-      <c r="Z12" s="12" t="inlineStr"/>
-      <c r="AA12" s="12" t="inlineStr"/>
-      <c r="AB12" s="12" t="inlineStr"/>
-      <c r="AC12" s="12" t="inlineStr"/>
-      <c r="AD12" s="12" t="inlineStr"/>
-      <c r="AE12" s="12" t="inlineStr"/>
-      <c r="AF12" s="13" t="inlineStr"/>
-      <c r="AG12" s="13" t="inlineStr"/>
-      <c r="AH12" s="13" t="inlineStr"/>
-      <c r="AI12" s="14" t="inlineStr"/>
-      <c r="AJ12" s="14" t="inlineStr"/>
-      <c r="AK12" s="14" t="inlineStr"/>
-      <c r="AL12" s="14" t="inlineStr"/>
-      <c r="AM12" s="14" t="inlineStr"/>
-      <c r="AN12" s="14" t="inlineStr"/>
-      <c r="AO12" s="15" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
+        </is>
+      </c>
+      <c r="Q12" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R12" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y12" s="12" t="inlineStr">
+        <is>
+          <t>Letter-Number Sequencing; 2-back</t>
+        </is>
+      </c>
+      <c r="Z12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>WCPA (everyday scheduling); Road Craft Test</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="12" t="inlineStr">
+        <is>
+          <t>η²=0.073(far transfer)</t>
+        </is>
+      </c>
+      <c r="AE12" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF12" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
+        </is>
+      </c>
+      <c r="AI12" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ12" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK12" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL12" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM12" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN12" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO12" s="15" t="inlineStr">
+        <is>
+          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>14</v>
+      <c r="A13" s="9" t="n">
+        <v>13</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>2021</v>
+          <t>Matysiak</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2019</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
+          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Neural plasticity</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="10" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
-      <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
-      <c r="S13" s="11" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="11" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="11" t="inlineStr"/>
-      <c r="X13" s="12" t="inlineStr"/>
-      <c r="Y13" s="12" t="inlineStr"/>
-      <c r="Z13" s="12" t="inlineStr"/>
-      <c r="AA13" s="12" t="inlineStr"/>
-      <c r="AB13" s="12" t="inlineStr"/>
-      <c r="AC13" s="12" t="inlineStr"/>
-      <c r="AD13" s="12" t="inlineStr"/>
-      <c r="AE13" s="12" t="inlineStr"/>
-      <c r="AF13" s="13" t="inlineStr"/>
+          <t>Frontiers in Aging Neuroscience</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>≥27</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q13" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X13" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y13" s="12" t="inlineStr">
+        <is>
+          <t>OSPAN; WM tasks</t>
+        </is>
+      </c>
+      <c r="Z13" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Fluid intelligence</t>
+        </is>
+      </c>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD13" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF13" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG13" s="13" t="inlineStr"/>
       <c r="AH13" s="13" t="inlineStr"/>
-      <c r="AI13" s="14" t="inlineStr"/>
-      <c r="AJ13" s="14" t="inlineStr"/>
-      <c r="AK13" s="14" t="inlineStr"/>
-      <c r="AL13" s="14" t="inlineStr"/>
-      <c r="AM13" s="14" t="inlineStr"/>
-      <c r="AN13" s="14" t="inlineStr"/>
-      <c r="AO13" s="15" t="inlineStr"/>
+      <c r="AI13" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ13" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK13" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL13" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM13" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN13" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO13" s="15" t="inlineStr">
+        <is>
+          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
+          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
-      <c r="O14" s="11" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
-      <c r="Q14" s="11" t="inlineStr"/>
-      <c r="R14" s="11" t="inlineStr"/>
-      <c r="S14" s="11" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="11" t="inlineStr"/>
-      <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="11" t="inlineStr"/>
-      <c r="X14" s="12" t="inlineStr"/>
-      <c r="Y14" s="12" t="inlineStr"/>
-      <c r="Z14" s="12" t="inlineStr"/>
+          <t>Neural plasticity</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Visual Object Memory Task (VOMT)</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>tDCS</t>
+        </is>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X14" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y14" s="12" t="inlineStr">
+        <is>
+          <t>VOMT (untrained stimuli)</t>
+        </is>
+      </c>
+      <c r="Z14" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA14" s="12" t="inlineStr"/>
-      <c r="AB14" s="12" t="inlineStr"/>
-      <c r="AC14" s="12" t="inlineStr"/>
-      <c r="AD14" s="12" t="inlineStr"/>
-      <c r="AE14" s="12" t="inlineStr"/>
-      <c r="AF14" s="13" t="inlineStr"/>
-      <c r="AG14" s="13" t="inlineStr"/>
-      <c r="AH14" s="13" t="inlineStr"/>
-      <c r="AI14" s="14" t="inlineStr"/>
-      <c r="AJ14" s="14" t="inlineStr"/>
-      <c r="AK14" s="14" t="inlineStr"/>
-      <c r="AL14" s="14" t="inlineStr"/>
-      <c r="AM14" s="14" t="inlineStr"/>
-      <c r="AN14" s="14" t="inlineStr"/>
-      <c r="AO14" s="15" t="inlineStr"/>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD14" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE14" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF14" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+        </is>
+      </c>
+      <c r="AI14" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ14" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK14" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL14" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM14" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN14" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO14" s="15" t="inlineStr">
+        <is>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
+          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="11" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
-      <c r="Q15" s="11" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="11" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="11" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="11" t="inlineStr"/>
-      <c r="X15" s="12" t="inlineStr"/>
-      <c r="Y15" s="12" t="inlineStr"/>
-      <c r="Z15" s="12" t="inlineStr"/>
-      <c r="AA15" s="12" t="inlineStr"/>
-      <c r="AB15" s="12" t="inlineStr"/>
-      <c r="AC15" s="12" t="inlineStr"/>
-      <c r="AD15" s="12" t="inlineStr"/>
-      <c r="AE15" s="12" t="inlineStr"/>
-      <c r="AF15" s="13" t="inlineStr"/>
+          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>SVAMA</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal, modified)</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V15" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X15" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y15" s="12" t="inlineStr">
+        <is>
+          <t>Dot Matrix (visuospatial WM)</t>
+        </is>
+      </c>
+      <c r="Z15" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>TIADL (everyday functioning); EPT</t>
+        </is>
+      </c>
+      <c r="AB15" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF15" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG15" s="13" t="inlineStr"/>
       <c r="AH15" s="13" t="inlineStr"/>
-      <c r="AI15" s="14" t="inlineStr"/>
-      <c r="AJ15" s="14" t="inlineStr"/>
-      <c r="AK15" s="14" t="inlineStr"/>
-      <c r="AL15" s="14" t="inlineStr"/>
-      <c r="AM15" s="14" t="inlineStr"/>
-      <c r="AN15" s="14" t="inlineStr"/>
-      <c r="AO15" s="15" t="inlineStr"/>
+      <c r="AI15" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ15" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK15" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL15" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM15" s="14" t="inlineStr">
+        <is>
+          <t>词汇测试</t>
+        </is>
+      </c>
+      <c r="AN15" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO15" s="15" t="inlineStr">
+        <is>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
+          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="10" t="inlineStr"/>
-      <c r="L16" s="10" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr"/>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
-      <c r="Q16" s="11" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr"/>
-      <c r="S16" s="11" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="11" t="inlineStr"/>
-      <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="11" t="inlineStr"/>
-      <c r="X16" s="12" t="inlineStr"/>
-      <c r="Y16" s="12" t="inlineStr"/>
-      <c r="Z16" s="12" t="inlineStr"/>
-      <c r="AA16" s="12" t="inlineStr"/>
-      <c r="AB16" s="12" t="inlineStr"/>
-      <c r="AC16" s="12" t="inlineStr"/>
-      <c r="AD16" s="12" t="inlineStr"/>
-      <c r="AE16" s="12" t="inlineStr"/>
-      <c r="AF16" s="13" t="inlineStr"/>
+          <t>Journal of visualized experiments : JoVE</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q16" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R16" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S16" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X16" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y16" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (untrained)</t>
+        </is>
+      </c>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Executive function</t>
+        </is>
+      </c>
+      <c r="AB16" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD16" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE16" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF16" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG16" s="13" t="inlineStr"/>
       <c r="AH16" s="13" t="inlineStr"/>
-      <c r="AI16" s="14" t="inlineStr"/>
-      <c r="AJ16" s="14" t="inlineStr"/>
-      <c r="AK16" s="14" t="inlineStr"/>
-      <c r="AL16" s="14" t="inlineStr"/>
-      <c r="AM16" s="14" t="inlineStr"/>
-      <c r="AN16" s="14" t="inlineStr"/>
-      <c r="AO16" s="15" t="inlineStr"/>
+      <c r="AI16" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ16" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK16" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL16" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM16" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN16" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO16" s="15" t="inlineStr">
+        <is>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
+          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-      <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="10" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
-      <c r="Q17" s="11" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
-      <c r="S17" s="11" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="11" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="11" t="inlineStr"/>
-      <c r="X17" s="12" t="inlineStr"/>
-      <c r="Y17" s="12" t="inlineStr"/>
-      <c r="Z17" s="12" t="inlineStr"/>
-      <c r="AA17" s="12" t="inlineStr"/>
-      <c r="AB17" s="12" t="inlineStr"/>
-      <c r="AC17" s="12" t="inlineStr"/>
-      <c r="AD17" s="12" t="inlineStr"/>
-      <c r="AE17" s="12" t="inlineStr"/>
-      <c r="AF17" s="13" t="inlineStr"/>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>29.66</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Adaptive n-back (0-5 back)</t>
+        </is>
+      </c>
+      <c r="Q17" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S17" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X17" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y17" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span (backward)</t>
+        </is>
+      </c>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA17" s="12" t="inlineStr">
+        <is>
+          <t>CERAD episodic memory; Processing speed (LPS)</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD17" s="12" t="inlineStr">
+        <is>
+          <t>d=0.78(教育组间)</t>
+        </is>
+      </c>
+      <c r="AE17" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF17" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG17" s="13" t="inlineStr"/>
       <c r="AH17" s="13" t="inlineStr"/>
-      <c r="AI17" s="14" t="inlineStr"/>
-      <c r="AJ17" s="14" t="inlineStr"/>
-      <c r="AK17" s="14" t="inlineStr"/>
-      <c r="AL17" s="14" t="inlineStr"/>
-      <c r="AM17" s="14" t="inlineStr"/>
-      <c r="AN17" s="14" t="inlineStr"/>
-      <c r="AO17" s="15" t="inlineStr"/>
+      <c r="AI17" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ17" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK17" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+        </is>
+      </c>
+      <c r="AL17" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM17" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN17" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO17" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
+          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Cognitive processing</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr"/>
-      <c r="L18" s="10" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
-      <c r="Q18" s="11" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="11" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="11" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="11" t="inlineStr"/>
-      <c r="X18" s="12" t="inlineStr"/>
-      <c r="Y18" s="12" t="inlineStr"/>
-      <c r="Z18" s="12" t="inlineStr"/>
-      <c r="AA18" s="12" t="inlineStr"/>
-      <c r="AB18" s="12" t="inlineStr"/>
-      <c r="AC18" s="12" t="inlineStr"/>
-      <c r="AD18" s="12" t="inlineStr"/>
-      <c r="AE18" s="12" t="inlineStr"/>
-      <c r="AF18" s="13" t="inlineStr"/>
+          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>SVAMA</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal)</t>
+        </is>
+      </c>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X18" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y18" s="12" t="inlineStr">
+        <is>
+          <t>Dot Matrix (visuospatial WM)</t>
+        </is>
+      </c>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+        </is>
+      </c>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE18" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF18" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG18" s="13" t="inlineStr"/>
       <c r="AH18" s="13" t="inlineStr"/>
-      <c r="AI18" s="14" t="inlineStr"/>
-      <c r="AJ18" s="14" t="inlineStr"/>
-      <c r="AK18" s="14" t="inlineStr"/>
-      <c r="AL18" s="14" t="inlineStr"/>
-      <c r="AM18" s="14" t="inlineStr"/>
-      <c r="AN18" s="14" t="inlineStr"/>
-      <c r="AO18" s="15" t="inlineStr"/>
+      <c r="AI18" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ18" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK18" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL18" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM18" s="14" t="inlineStr">
+        <is>
+          <t>词汇测试</t>
+        </is>
+      </c>
+      <c r="AN18" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO18" s="15" t="inlineStr">
+        <is>
+          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Olivetti</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
+          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>International journal of aging &amp; human development</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="10" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
-      <c r="Q19" s="11" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
-      <c r="S19" s="11" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="11" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="11" t="inlineStr"/>
-      <c r="X19" s="12" t="inlineStr"/>
-      <c r="Y19" s="12" t="inlineStr"/>
-      <c r="Z19" s="12" t="inlineStr"/>
+          <t>Cognitive processing</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>医院/社区</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>MMSE+CDT</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>≥26(MMSE)</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>N-back (0-2 back, adaptive)</t>
+        </is>
+      </c>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X19" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y19" s="12" t="inlineStr">
+        <is>
+          <t>Corsi Block; Digit Span</t>
+        </is>
+      </c>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA19" s="12" t="inlineStr"/>
-      <c r="AB19" s="12" t="inlineStr"/>
-      <c r="AC19" s="12" t="inlineStr"/>
-      <c r="AD19" s="12" t="inlineStr"/>
-      <c r="AE19" s="12" t="inlineStr"/>
-      <c r="AF19" s="13" t="inlineStr"/>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD19" s="12" t="inlineStr">
+        <is>
+          <t>d=2.21(近迁移)</t>
+        </is>
+      </c>
+      <c r="AE19" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF19" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG19" s="13" t="inlineStr"/>
       <c r="AH19" s="13" t="inlineStr"/>
-      <c r="AI19" s="14" t="inlineStr"/>
-      <c r="AJ19" s="14" t="inlineStr"/>
-      <c r="AK19" s="14" t="inlineStr"/>
-      <c r="AL19" s="14" t="inlineStr"/>
-      <c r="AM19" s="14" t="inlineStr"/>
-      <c r="AN19" s="14" t="inlineStr"/>
-      <c r="AO19" s="15" t="inlineStr"/>
+      <c r="AI19" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ19" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK19" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL19" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM19" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN19" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO19" s="15" t="inlineStr">
+        <is>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
+          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>GeroScience</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
-      <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
-      <c r="Q20" s="11" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr"/>
-      <c r="S20" s="11" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="11" t="inlineStr"/>
-      <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="11" t="inlineStr"/>
-      <c r="X20" s="12" t="inlineStr"/>
-      <c r="Y20" s="12" t="inlineStr"/>
-      <c r="Z20" s="12" t="inlineStr"/>
-      <c r="AA20" s="12" t="inlineStr"/>
-      <c r="AB20" s="12" t="inlineStr"/>
-      <c r="AC20" s="12" t="inlineStr"/>
-      <c r="AD20" s="12" t="inlineStr"/>
-      <c r="AE20" s="12" t="inlineStr"/>
-      <c r="AF20" s="13" t="inlineStr"/>
+          <t>International journal of aging &amp; human development</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+        </is>
+      </c>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X20" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y20" s="12" t="inlineStr">
+        <is>
+          <t>Spatial WM (untrained)</t>
+        </is>
+      </c>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>Reasoning; IADL (everyday function)</t>
+        </is>
+      </c>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD20" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE20" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF20" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG20" s="13" t="inlineStr"/>
       <c r="AH20" s="13" t="inlineStr"/>
-      <c r="AI20" s="14" t="inlineStr"/>
-      <c r="AJ20" s="14" t="inlineStr"/>
-      <c r="AK20" s="14" t="inlineStr"/>
-      <c r="AL20" s="14" t="inlineStr"/>
-      <c r="AM20" s="14" t="inlineStr"/>
-      <c r="AN20" s="14" t="inlineStr"/>
-      <c r="AO20" s="15" t="inlineStr"/>
+      <c r="AI20" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ20" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK20" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL20" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM20" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN20" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO20" s="15" t="inlineStr">
+        <is>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
+          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr"/>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="11" t="inlineStr"/>
-      <c r="X21" s="12" t="inlineStr"/>
-      <c r="Y21" s="12" t="inlineStr"/>
-      <c r="Z21" s="12" t="inlineStr"/>
+          <t>GeroScience</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>Multidomain cognitive training (WM+processing speed)</t>
+        </is>
+      </c>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>自制(tablet-based)</t>
+        </is>
+      </c>
+      <c r="X21" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y21" s="12" t="inlineStr">
+        <is>
+          <t>WM tasks (proximal)</t>
+        </is>
+      </c>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA21" s="12" t="inlineStr"/>
-      <c r="AB21" s="12" t="inlineStr"/>
-      <c r="AC21" s="12" t="inlineStr"/>
-      <c r="AD21" s="12" t="inlineStr"/>
-      <c r="AE21" s="12" t="inlineStr"/>
-      <c r="AF21" s="13" t="inlineStr"/>
-      <c r="AG21" s="13" t="inlineStr"/>
-      <c r="AH21" s="13" t="inlineStr"/>
-      <c r="AI21" s="14" t="inlineStr"/>
-      <c r="AJ21" s="14" t="inlineStr"/>
-      <c r="AK21" s="14" t="inlineStr"/>
-      <c r="AL21" s="14" t="inlineStr"/>
-      <c r="AM21" s="14" t="inlineStr"/>
-      <c r="AN21" s="14" t="inlineStr"/>
-      <c r="AO21" s="15" t="inlineStr"/>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC21" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD21" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE21" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF21" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG21" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI)</t>
+        </is>
+      </c>
+      <c r="AH21" s="13" t="inlineStr">
+        <is>
+          <t>白质高信号负荷高者训练获益更少</t>
+        </is>
+      </c>
+      <c r="AI21" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ21" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK21" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低WMH获益更多)</t>
+        </is>
+      </c>
+      <c r="AL21" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM21" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN21" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO21" s="15" t="inlineStr">
+        <is>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
+          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Attention, perception &amp; psychophysics</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="11" t="inlineStr"/>
-      <c r="V22" s="11" t="inlineStr"/>
-      <c r="W22" s="11" t="inlineStr"/>
-      <c r="X22" s="12" t="inlineStr"/>
-      <c r="Y22" s="12" t="inlineStr"/>
-      <c r="Z22" s="12" t="inlineStr"/>
+          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, 1-3 back)</t>
+        </is>
+      </c>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X22" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y22" s="12" t="inlineStr">
+        <is>
+          <t>Listening Span</t>
+        </is>
+      </c>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA22" s="12" t="inlineStr"/>
-      <c r="AB22" s="12" t="inlineStr"/>
-      <c r="AC22" s="12" t="inlineStr"/>
-      <c r="AD22" s="12" t="inlineStr"/>
-      <c r="AE22" s="12" t="inlineStr"/>
-      <c r="AF22" s="13" t="inlineStr"/>
-      <c r="AG22" s="13" t="inlineStr"/>
-      <c r="AH22" s="13" t="inlineStr"/>
-      <c r="AI22" s="14" t="inlineStr"/>
-      <c r="AJ22" s="14" t="inlineStr"/>
-      <c r="AK22" s="14" t="inlineStr"/>
-      <c r="AL22" s="14" t="inlineStr"/>
-      <c r="AM22" s="14" t="inlineStr"/>
-      <c r="AN22" s="14" t="inlineStr"/>
-      <c r="AO22" s="15" t="inlineStr"/>
+      <c r="AB22" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC22" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE22" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF22" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG22" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH22" s="13" t="inlineStr">
+        <is>
+          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+        </is>
+      </c>
+      <c r="AI22" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ22" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK22" s="14" t="inlineStr">
+        <is>
+          <t>高&gt;低(类年轻激活者获益更多)</t>
+        </is>
+      </c>
+      <c r="AL22" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM22" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN22" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO22" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Tagliabue</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
+          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Developmental psychology</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr"/>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="11" t="inlineStr"/>
-      <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="11" t="inlineStr"/>
-      <c r="X23" s="12" t="inlineStr"/>
-      <c r="Y23" s="12" t="inlineStr"/>
-      <c r="Z23" s="12" t="inlineStr"/>
+          <t>Attention, perception &amp; psychophysics</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>社区(在线)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>DMTS (delayed match-to-sample); Enumeration</t>
+        </is>
+      </c>
+      <c r="Q23" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R23" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>自制(在线)</t>
+        </is>
+      </c>
+      <c r="X23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y23" s="12" t="inlineStr">
+        <is>
+          <t>DMTS (visuospatial WM, k值)</t>
+        </is>
+      </c>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA23" s="12" t="inlineStr"/>
-      <c r="AB23" s="12" t="inlineStr"/>
-      <c r="AC23" s="12" t="inlineStr"/>
-      <c r="AD23" s="12" t="inlineStr"/>
-      <c r="AE23" s="12" t="inlineStr"/>
-      <c r="AF23" s="13" t="inlineStr"/>
+      <c r="AB23" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE23" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF23" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG23" s="13" t="inlineStr"/>
       <c r="AH23" s="13" t="inlineStr"/>
-      <c r="AI23" s="14" t="inlineStr"/>
-      <c r="AJ23" s="14" t="inlineStr"/>
-      <c r="AK23" s="14" t="inlineStr"/>
-      <c r="AL23" s="14" t="inlineStr"/>
-      <c r="AM23" s="14" t="inlineStr"/>
-      <c r="AN23" s="14" t="inlineStr"/>
-      <c r="AO23" s="15" t="inlineStr"/>
+      <c r="AI23" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ23" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK23" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低WM基线者获益更多)</t>
+        </is>
+      </c>
+      <c r="AL23" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM23" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN23" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO23" s="15" t="inlineStr">
+        <is>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Zinke</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
+          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Current aging science</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
-      <c r="Q24" s="11" t="inlineStr"/>
-      <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr"/>
-      <c r="T24" s="11" t="inlineStr"/>
-      <c r="U24" s="11" t="inlineStr"/>
-      <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="11" t="inlineStr"/>
-      <c r="X24" s="12" t="inlineStr"/>
-      <c r="Y24" s="12" t="inlineStr"/>
-      <c r="Z24" s="12" t="inlineStr"/>
-      <c r="AA24" s="12" t="inlineStr"/>
-      <c r="AB24" s="12" t="inlineStr"/>
-      <c r="AC24" s="12" t="inlineStr"/>
-      <c r="AD24" s="12" t="inlineStr"/>
-      <c r="AE24" s="12" t="inlineStr"/>
-      <c r="AF24" s="13" t="inlineStr"/>
+          <t>Developmental psychology</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>MMST</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+        </is>
+      </c>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y24" s="12" t="inlineStr">
+        <is>
+          <t>Verbal WM (untrained)</t>
+        </is>
+      </c>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Reasoning</t>
+        </is>
+      </c>
+      <c r="AB24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE24" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF24" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG24" s="13" t="inlineStr"/>
       <c r="AH24" s="13" t="inlineStr"/>
-      <c r="AI24" s="14" t="inlineStr"/>
-      <c r="AJ24" s="14" t="inlineStr"/>
-      <c r="AK24" s="14" t="inlineStr"/>
-      <c r="AL24" s="14" t="inlineStr"/>
-      <c r="AM24" s="14" t="inlineStr"/>
-      <c r="AN24" s="14" t="inlineStr"/>
-      <c r="AO24" s="15" t="inlineStr"/>
+      <c r="AI24" s="14" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ24" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK24" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(低基线者近迁移更大)</t>
+        </is>
+      </c>
+      <c r="AL24" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM24" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN24" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO24" s="15" t="inlineStr">
+        <is>
+          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Schmicker</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
+          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>BMC research notes</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr"/>
-      <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-      <c r="U25" s="11" t="inlineStr"/>
-      <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="11" t="inlineStr"/>
-      <c r="X25" s="12" t="inlineStr"/>
-      <c r="Y25" s="12" t="inlineStr"/>
-      <c r="Z25" s="12" t="inlineStr"/>
+          <t>Current aging science</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q25" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V25" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X25" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y25" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span</t>
+        </is>
+      </c>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AA25" s="12" t="inlineStr"/>
-      <c r="AB25" s="12" t="inlineStr"/>
-      <c r="AC25" s="12" t="inlineStr"/>
-      <c r="AD25" s="12" t="inlineStr"/>
-      <c r="AE25" s="12" t="inlineStr"/>
-      <c r="AF25" s="13" t="inlineStr"/>
+      <c r="AB25" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD25" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE25" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF25" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG25" s="13" t="inlineStr"/>
       <c r="AH25" s="13" t="inlineStr"/>
-      <c r="AI25" s="14" t="inlineStr"/>
-      <c r="AJ25" s="14" t="inlineStr"/>
-      <c r="AK25" s="14" t="inlineStr"/>
-      <c r="AL25" s="14" t="inlineStr"/>
-      <c r="AM25" s="14" t="inlineStr"/>
-      <c r="AN25" s="14" t="inlineStr"/>
-      <c r="AO25" s="15" t="inlineStr"/>
+      <c r="AI25" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ25" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK25" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL25" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM25" s="14" t="inlineStr">
+        <is>
+          <t>CRI(认知储备指数)</t>
+        </is>
+      </c>
+      <c r="AN25" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO25" s="15" t="inlineStr">
+        <is>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
+          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr"/>
-      <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr"/>
-      <c r="T26" s="11" t="inlineStr"/>
-      <c r="U26" s="11" t="inlineStr"/>
-      <c r="V26" s="11" t="inlineStr"/>
-      <c r="W26" s="11" t="inlineStr"/>
-      <c r="X26" s="12" t="inlineStr"/>
-      <c r="Y26" s="12" t="inlineStr"/>
-      <c r="Z26" s="12" t="inlineStr"/>
-      <c r="AA26" s="12" t="inlineStr"/>
-      <c r="AB26" s="12" t="inlineStr"/>
-      <c r="AC26" s="12" t="inlineStr"/>
-      <c r="AD26" s="12" t="inlineStr"/>
-      <c r="AE26" s="12" t="inlineStr"/>
-      <c r="AF26" s="13" t="inlineStr"/>
+          <t>BMC research notes</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>≥24</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>N-back (adaptive, 1-3 back)</t>
+        </is>
+      </c>
+      <c r="Q26" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R26" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V26" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>PsychoPy自制</t>
+        </is>
+      </c>
+      <c r="X26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y26" s="12" t="inlineStr">
+        <is>
+          <t>N-back (untrained level)</t>
+        </is>
+      </c>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span; Corsi; Stroop</t>
+        </is>
+      </c>
+      <c r="AB26" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD26" s="12" t="inlineStr">
+        <is>
+          <t>η²p=0.05(训练×年龄交互)</t>
+        </is>
+      </c>
+      <c r="AE26" s="12" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF26" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
       <c r="AG26" s="13" t="inlineStr"/>
       <c r="AH26" s="13" t="inlineStr"/>
-      <c r="AI26" s="14" t="inlineStr"/>
-      <c r="AJ26" s="14" t="inlineStr"/>
-      <c r="AK26" s="14" t="inlineStr"/>
-      <c r="AL26" s="14" t="inlineStr"/>
-      <c r="AM26" s="14" t="inlineStr"/>
-      <c r="AN26" s="14" t="inlineStr"/>
-      <c r="AO26" s="15" t="inlineStr"/>
+      <c r="AI26" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ26" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK26" s="14" t="inlineStr">
+        <is>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+        </is>
+      </c>
+      <c r="AL26" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AM26" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN26" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO26" s="15" t="inlineStr">
+        <is>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Jaeggi</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
+          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>大学</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="n">
-        <v>13.2</v>
+        <v>183</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>GDS+GAD</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
@@ -3428,7 +5412,7 @@
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>verbal n-back</t>
+          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr">
@@ -3437,14 +5421,16 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S27" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T27" s="11" t="inlineStr">
         <is>
-          <t>2-4周</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
@@ -3459,7 +5445,7 @@
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(tablet)</t>
         </is>
       </c>
       <c r="X27" s="12" t="inlineStr">
@@ -3469,7 +5455,7 @@
       </c>
       <c r="Y27" s="12" t="inlineStr">
         <is>
-          <t>spatial n-back</t>
+          <t>Reading Span; Symmetry Span</t>
         </is>
       </c>
       <c r="Z27" s="12" t="inlineStr">
@@ -3479,18 +5465,16 @@
       </c>
       <c r="AA27" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence (Raven)</t>
+          <t>Letter Sets; Visual LTM</t>
         </is>
       </c>
       <c r="AB27" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC27" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="AD27" s="12" t="inlineStr">
         <is>
@@ -3511,7 +5495,7 @@
       <c r="AH27" s="13" t="inlineStr"/>
       <c r="AI27" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ27" s="14" t="inlineStr">
@@ -3521,17 +5505,17 @@
       </c>
       <c r="AK27" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL27" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM27" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN27" s="14" t="inlineStr">
@@ -3541,54 +5525,54 @@
       </c>
       <c r="AO27" s="15" t="inlineStr">
         <is>
-          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
+          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="K28" s="10" t="inlineStr"/>
       <c r="L28" s="10" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -3602,12 +5586,12 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>verbal n-back</t>
         </is>
       </c>
       <c r="Q28" s="11" t="inlineStr">
@@ -3616,13 +5600,15 @@
         </is>
       </c>
       <c r="R28" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S28" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="T28" s="11" t="n">
-        <v>3</v>
+      <c r="T28" s="11" t="inlineStr">
+        <is>
+          <t>2-4周</t>
+        </is>
       </c>
       <c r="U28" s="11" t="inlineStr">
         <is>
@@ -3646,7 +5632,7 @@
       </c>
       <c r="Y28" s="12" t="inlineStr">
         <is>
-          <t>WM criterion task (CWMS)</t>
+          <t>spatial n-back</t>
         </is>
       </c>
       <c r="Z28" s="12" t="inlineStr">
@@ -3656,7 +5642,7 @@
       </c>
       <c r="AA28" s="12" t="inlineStr">
         <is>
-          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
+          <t>fluid intelligence (Raven)</t>
         </is>
       </c>
       <c r="AB28" s="12" t="inlineStr">
@@ -3671,12 +5657,12 @@
       </c>
       <c r="AD28" s="12" t="inlineStr">
         <is>
-          <t>d&gt;=0.8 (large effect)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE28" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF28" s="13" t="inlineStr">
@@ -3688,27 +5674,27 @@
       <c r="AH28" s="13" t="inlineStr"/>
       <c r="AI28" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ28" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK28" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL28" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM28" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN28" s="14" t="inlineStr">
@@ -3718,25 +5704,25 @@
       </c>
       <c r="AO28" s="15" t="inlineStr">
         <is>
-          <t>评估日常生活能力迁移效应</t>
+          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
+          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -3755,19 +5741,17 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K29" s="10" t="n">
-        <v>57</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
       <c r="L29" s="10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -3825,7 +5809,7 @@
       </c>
       <c r="Y29" s="12" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>WM criterion task (CWMS)</t>
         </is>
       </c>
       <c r="Z29" s="12" t="inlineStr">
@@ -3835,22 +5819,22 @@
       </c>
       <c r="AA29" s="12" t="inlineStr">
         <is>
-          <t>Language comprehension; Cattell fluid intelligence</t>
+          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
         </is>
       </c>
       <c r="AB29" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC29" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD29" s="12" t="inlineStr">
         <is>
-          <t>η²=0.15-0.26 (transfer)</t>
+          <t>d&gt;=0.8 (large effect)</t>
         </is>
       </c>
       <c r="AE29" s="12" t="inlineStr">
@@ -3897,58 +5881,60 @@
       </c>
       <c r="AO29" s="15" t="inlineStr">
         <is>
-          <t>6个月随访；语言理解力迁移</t>
+          <t>评估日常生活能力迁移效应</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
+          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>Neuroreport</t>
+          <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>69.7</v>
+        <v>69</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L30" s="10" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>10.5</v>
+      </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
@@ -3958,39 +5944,41 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>CACT (computer-assisted cognitive training)</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R30" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S30" s="11" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="S30" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T30" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
-          <t>Maxmedica CACT</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X30" s="12" t="inlineStr">
@@ -4000,15 +5988,19 @@
       </c>
       <c r="Y30" s="12" t="inlineStr">
         <is>
-          <t>Verbal WM task; Digit span forward</t>
+          <t>WM updating task</t>
         </is>
       </c>
       <c r="Z30" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA30" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="12" t="inlineStr">
+        <is>
+          <t>Language comprehension; Cattell fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB30" s="12" t="inlineStr">
         <is>
           <t>是</t>
@@ -4016,12 +6008,12 @@
       </c>
       <c r="AC30" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD30" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²=0.15-0.26 (transfer)</t>
         </is>
       </c>
       <c r="AE30" s="12" t="inlineStr">
@@ -4068,56 +6060,58 @@
       </c>
       <c r="AO30" s="15" t="inlineStr">
         <is>
-          <t>tDCS联合CACT；anodal vs sham tDCS</t>
+          <t>6个月随访；语言理解力迁移</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
+          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Neuroreport</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K31" s="10" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>68</v>
+      </c>
       <c r="L31" s="10" t="inlineStr"/>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>MoCA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
@@ -4127,27 +6121,25 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>adaptive spatial n-back</t>
+          <t>CACT (computer-assisted cognitive training)</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S31" s="11" t="n">
-        <v>20</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S31" s="11" t="inlineStr"/>
       <c r="T31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" s="11" t="inlineStr">
         <is>
@@ -4161,7 +6153,7 @@
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Maxmedica CACT</t>
         </is>
       </c>
       <c r="X31" s="12" t="inlineStr">
@@ -4171,7 +6163,7 @@
       </c>
       <c r="Y31" s="12" t="inlineStr">
         <is>
-          <t>WM composite score (5 tasks)</t>
+          <t>Verbal WM task; Digit span forward</t>
         </is>
       </c>
       <c r="Z31" s="12" t="inlineStr">
@@ -4182,12 +6174,12 @@
       <c r="AA31" s="12" t="inlineStr"/>
       <c r="AB31" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC31" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD31" s="12" t="inlineStr">
@@ -4197,7 +6189,7 @@
       </c>
       <c r="AE31" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF31" s="13" t="inlineStr">
@@ -4209,22 +6201,22 @@
       <c r="AH31" s="13" t="inlineStr"/>
       <c r="AI31" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ31" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK31" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL31" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM31" s="14" t="inlineStr">
@@ -4239,58 +6231,56 @@
       </c>
       <c r="AO31" s="15" t="inlineStr">
         <is>
-          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
+          <t>tDCS联合CACT；anodal vs sham tDCS</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>VK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
+          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>83.5</v>
+        <v>69.5</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" s="10" t="n">
-        <v>79</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr"/>
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
@@ -4300,23 +6290,27 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>computer-assisted cognitive training (multi-domain)</t>
+          <t>adaptive spatial n-back</t>
         </is>
       </c>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R32" s="11" t="inlineStr"/>
-      <c r="S32" s="11" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S32" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="T32" s="11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U32" s="11" t="inlineStr">
         <is>
@@ -4325,7 +6319,7 @@
       </c>
       <c r="V32" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W32" s="11" t="inlineStr">
@@ -4340,27 +6334,23 @@
       </c>
       <c r="Y32" s="12" t="inlineStr">
         <is>
-          <t>Primary WM; secondary WM (verbal/visual)</t>
+          <t>WM composite score (5 tasks)</t>
         </is>
       </c>
       <c r="Z32" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA32" s="12" t="inlineStr">
-        <is>
-          <t>Information processing speed; learning; interference tendency</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="12" t="inlineStr"/>
       <c r="AB32" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC32" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD32" s="12" t="inlineStr">
@@ -4370,7 +6360,7 @@
       </c>
       <c r="AE32" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF32" s="13" t="inlineStr">
@@ -4382,22 +6372,22 @@
       <c r="AH32" s="13" t="inlineStr"/>
       <c r="AI32" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ32" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK32" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL32" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM32" s="14" t="inlineStr">
@@ -4412,52 +6402,54 @@
       </c>
       <c r="AO32" s="15" t="inlineStr">
         <is>
-          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
+          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VK</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Novel television-based cognitive training improves working memory and executive function.</t>
+          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>70.5</v>
+        <v>83.5</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>79</v>
+      </c>
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -4471,27 +6463,27 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
+          <t>computer-assisted cognitive training (multi-domain)</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R33" s="11" t="n">
-        <v>25</v>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr"/>
       <c r="S33" s="11" t="inlineStr"/>
-      <c r="T33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="n">
+        <v>14</v>
+      </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr">
@@ -4501,7 +6493,7 @@
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
-          <t>CogniFit</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X33" s="12" t="inlineStr">
@@ -4511,7 +6503,7 @@
       </c>
       <c r="Y33" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (validated)</t>
+          <t>Primary WM; secondary WM (verbal/visual)</t>
         </is>
       </c>
       <c r="Z33" s="12" t="inlineStr">
@@ -4521,17 +6513,17 @@
       </c>
       <c r="AA33" s="12" t="inlineStr">
         <is>
-          <t>Executive function tasks</t>
+          <t>Information processing speed; learning; interference tendency</t>
         </is>
       </c>
       <c r="AB33" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC33" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD33" s="12" t="inlineStr">
@@ -4583,35 +6575,35 @@
       </c>
       <c r="AO33" s="15" t="inlineStr">
         <is>
-          <t>互动电视（iTV）平台认知训练</t>
+          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Impact of working memory training on memory performance in old-old adults.</t>
+          <t>Novel television-based cognitive training improves working memory and executive function.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -4620,13 +6612,13 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>80</v>
+        <v>70.5</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="10" t="inlineStr"/>
@@ -4642,12 +6634,12 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>WM process-based training (visual/spatial)</t>
+          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
         </is>
       </c>
       <c r="Q34" s="11" t="inlineStr">
@@ -4656,14 +6648,10 @@
         </is>
       </c>
       <c r="R34" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="S34" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T34" s="11" t="n">
-        <v>12</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -4676,7 +6664,7 @@
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>CogniFit</t>
         </is>
       </c>
       <c r="X34" s="12" t="inlineStr">
@@ -4686,7 +6674,7 @@
       </c>
       <c r="Y34" s="12" t="inlineStr">
         <is>
-          <t>Visual WM (VLMT)</t>
+          <t>WM tasks (validated)</t>
         </is>
       </c>
       <c r="Z34" s="12" t="inlineStr">
@@ -4696,17 +6684,17 @@
       </c>
       <c r="AA34" s="12" t="inlineStr">
         <is>
-          <t>Visual episodic memory</t>
+          <t>Executive function tasks</t>
         </is>
       </c>
       <c r="AB34" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC34" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD34" s="12" t="inlineStr">
@@ -4758,35 +6746,35 @@
       </c>
       <c r="AO34" s="15" t="inlineStr">
         <is>
-          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
+          <t>互动电视（iTV）平台认知训练</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
+          <t>Impact of working memory training on memory performance in old-old adults.</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -4795,13 +6783,13 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
@@ -4817,12 +6805,12 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>adaptive verbal + spatial n-back</t>
+          <t>WM process-based training (visual/spatial)</t>
         </is>
       </c>
       <c r="Q35" s="11" t="inlineStr">
@@ -4831,13 +6819,13 @@
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr">
-        <is>
-          <t>4-8周</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="S35" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="U35" s="11" t="inlineStr">
         <is>
@@ -4851,7 +6839,7 @@
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
-          <t>自制（居家在线）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X35" s="12" t="inlineStr">
@@ -4861,7 +6849,7 @@
       </c>
       <c r="Y35" s="12" t="inlineStr">
         <is>
-          <t>Digit span</t>
+          <t>Visual WM (VLMT)</t>
         </is>
       </c>
       <c r="Z35" s="12" t="inlineStr">
@@ -4871,17 +6859,17 @@
       </c>
       <c r="AA35" s="12" t="inlineStr">
         <is>
-          <t>Abstract relational reasoning</t>
+          <t>Visual episodic memory</t>
         </is>
       </c>
       <c r="AB35" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC35" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD35" s="12" t="inlineStr">
@@ -4891,7 +6879,7 @@
       </c>
       <c r="AE35" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF35" s="13" t="inlineStr">
@@ -4933,35 +6921,35 @@
       </c>
       <c r="AO35" s="15" t="inlineStr">
         <is>
-          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
+          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
+          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -4970,13 +6958,13 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>66</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="10" t="inlineStr"/>
@@ -4997,7 +6985,7 @@
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>adaptive n-back</t>
+          <t>adaptive verbal + spatial n-back</t>
         </is>
       </c>
       <c r="Q36" s="11" t="inlineStr">
@@ -5006,11 +6994,13 @@
         </is>
       </c>
       <c r="R36" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="n">
-        <v>4</v>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>4-8周</t>
+        </is>
       </c>
       <c r="U36" s="11" t="inlineStr">
         <is>
@@ -5024,7 +7014,7 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家在线）</t>
         </is>
       </c>
       <c r="X36" s="12" t="inlineStr">
@@ -5034,15 +7024,19 @@
       </c>
       <c r="Y36" s="12" t="inlineStr">
         <is>
-          <t>multimodal dual-task (visual+auditory)</t>
+          <t>Digit span</t>
         </is>
       </c>
       <c r="Z36" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA36" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="12" t="inlineStr">
+        <is>
+          <t>Abstract relational reasoning</t>
+        </is>
+      </c>
       <c r="AB36" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -5055,29 +7049,21 @@
       </c>
       <c r="AD36" s="12" t="inlineStr">
         <is>
-          <t>p&lt;0.05</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE36" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF36" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG36" s="13" t="inlineStr">
-        <is>
-          <t>fMRI</t>
-        </is>
-      </c>
-      <c r="AH36" s="13" t="inlineStr">
-        <is>
-          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG36" s="13" t="inlineStr"/>
+      <c r="AH36" s="13" t="inlineStr"/>
       <c r="AI36" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -5110,17 +7096,17 @@
       </c>
       <c r="AO36" s="15" t="inlineStr">
         <is>
-          <t>双任务迁移；fMRI子研究；先导研究</t>
+          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -5128,17 +7114,17 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
+          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -5147,10 +7133,14 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>137</v>
-      </c>
-      <c r="I37" s="10" t="inlineStr"/>
-      <c r="J37" s="10" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
       <c r="M37" s="10" t="inlineStr">
@@ -5165,12 +7155,12 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>Visual and Spatial WM training</t>
+          <t>adaptive n-back</t>
         </is>
       </c>
       <c r="Q37" s="11" t="inlineStr">
@@ -5178,17 +7168,21 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R37" s="11" t="inlineStr"/>
+      <c r="R37" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="U37" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V37" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W37" s="11" t="inlineStr">
@@ -5203,7 +7197,7 @@
       </c>
       <c r="Y37" s="12" t="inlineStr">
         <is>
-          <t>Visual WM; Spatial WM</t>
+          <t>multimodal dual-task (visual+auditory)</t>
         </is>
       </c>
       <c r="Z37" s="12" t="inlineStr">
@@ -5214,44 +7208,52 @@
       <c r="AA37" s="12" t="inlineStr"/>
       <c r="AB37" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC37" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD37" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>p&lt;0.05</t>
         </is>
       </c>
       <c r="AE37" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF37" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG37" s="13" t="inlineStr"/>
-      <c r="AH37" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG37" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH37" s="13" t="inlineStr">
+        <is>
+          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
+        </is>
+      </c>
       <c r="AI37" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ37" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK37" s="14" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL37" s="14" t="inlineStr">
@@ -5271,35 +7273,35 @@
       </c>
       <c r="AO37" s="15" t="inlineStr">
         <is>
-          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
+          <t>双任务迁移；fMRI子研究；先导研究</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>JA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
+          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Scientific reports</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -5308,7 +7310,7 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="I38" s="10" t="inlineStr"/>
       <c r="J38" s="10" t="inlineStr"/>
@@ -5326,12 +7328,12 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>commercial brain training app (multi-domain)</t>
+          <t>Visual and Spatial WM training</t>
         </is>
       </c>
       <c r="Q38" s="11" t="inlineStr">
@@ -5341,22 +7343,20 @@
       </c>
       <c r="R38" s="11" t="inlineStr"/>
       <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="n">
-        <v>12</v>
-      </c>
+      <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
-          <t>商业脑训练app</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X38" s="12" t="inlineStr">
@@ -5366,27 +7366,23 @@
       </c>
       <c r="Y38" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (trained domain)</t>
+          <t>Visual WM; Spatial WM</t>
         </is>
       </c>
       <c r="Z38" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA38" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; attention; language</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="12" t="inlineStr"/>
       <c r="AB38" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC38" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD38" s="12" t="inlineStr">
@@ -5396,7 +7392,7 @@
       </c>
       <c r="AE38" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF38" s="13" t="inlineStr">
@@ -5408,17 +7404,17 @@
       <c r="AH38" s="13" t="inlineStr"/>
       <c r="AI38" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ38" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK38" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AL38" s="14" t="inlineStr">
@@ -5438,35 +7434,35 @@
       </c>
       <c r="AO38" s="15" t="inlineStr">
         <is>
-          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
+          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
+          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -5475,7 +7471,7 @@
         </is>
       </c>
       <c r="H39" s="10" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="I39" s="10" t="inlineStr"/>
       <c r="J39" s="10" t="inlineStr"/>
@@ -5493,12 +7489,12 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>Cogmed (adaptive WM training)</t>
+          <t>commercial brain training app (multi-domain)</t>
         </is>
       </c>
       <c r="Q39" s="11" t="inlineStr">
@@ -5506,14 +7502,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R39" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S39" s="11" t="n">
-        <v>40</v>
-      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr"/>
       <c r="T39" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U39" s="11" t="inlineStr">
         <is>
@@ -5527,7 +7519,7 @@
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>Cogmed</t>
+          <t>商业脑训练app</t>
         </is>
       </c>
       <c r="X39" s="12" t="inlineStr">
@@ -5537,15 +7529,19 @@
       </c>
       <c r="Y39" s="12" t="inlineStr">
         <is>
-          <t>n-back (0-back, 1-back, 2-back)</t>
+          <t>WM tasks (trained domain)</t>
         </is>
       </c>
       <c r="Z39" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA39" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; attention; language</t>
+        </is>
+      </c>
       <c r="AB39" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -5563,24 +7559,16 @@
       </c>
       <c r="AE39" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF39" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG39" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH39" s="13" t="inlineStr">
-        <is>
-          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG39" s="13" t="inlineStr"/>
+      <c r="AH39" s="13" t="inlineStr"/>
       <c r="AI39" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -5613,25 +7601,25 @@
       </c>
       <c r="AO39" s="15" t="inlineStr">
         <is>
-          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
+          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>An evaluation of a working memory training scheme in older adults.</t>
+          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -5641,7 +7629,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -5650,14 +7638,10 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I40" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>4</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr"/>
+      <c r="J40" s="10" t="inlineStr"/>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
       <c r="M40" s="10" t="inlineStr">
@@ -5672,12 +7656,12 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
+          <t>Cogmed (adaptive WM training)</t>
         </is>
       </c>
       <c r="Q40" s="11" t="inlineStr">
@@ -5685,8 +7669,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R40" s="11" t="inlineStr"/>
-      <c r="S40" s="11" t="inlineStr"/>
+      <c r="R40" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S40" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="T40" s="11" t="n">
         <v>5</v>
       </c>
@@ -5702,7 +7690,7 @@
       </c>
       <c r="W40" s="11" t="inlineStr">
         <is>
-          <t>自制（在线）</t>
+          <t>Cogmed</t>
         </is>
       </c>
       <c r="X40" s="12" t="inlineStr">
@@ -5712,27 +7700,23 @@
       </c>
       <c r="Y40" s="12" t="inlineStr">
         <is>
-          <t>Auditory STM span; visuospatial STM</t>
+          <t>n-back (0-back, 1-back, 2-back)</t>
         </is>
       </c>
       <c r="Z40" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA40" s="12" t="inlineStr">
-        <is>
-          <t>Long-term episodic memory</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr"/>
       <c r="AB40" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC40" s="12" t="inlineStr">
         <is>
-          <t>3;6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD40" s="12" t="inlineStr">
@@ -5747,11 +7731,19 @@
       </c>
       <c r="AF40" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG40" s="13" t="inlineStr"/>
-      <c r="AH40" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG40" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH40" s="13" t="inlineStr">
+        <is>
+          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
+        </is>
+      </c>
       <c r="AI40" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -5759,7 +7751,7 @@
       </c>
       <c r="AJ40" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK40" s="14" t="inlineStr">
@@ -5784,25 +7776,25 @@
       </c>
       <c r="AO40" s="15" t="inlineStr">
         <is>
-          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
+          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
+          <t>An evaluation of a working memory training scheme in older adults.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -5812,7 +7804,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -5821,10 +7813,14 @@
         </is>
       </c>
       <c r="H41" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="I41" s="10" t="inlineStr"/>
-      <c r="J41" s="10" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K41" s="10" t="inlineStr"/>
       <c r="L41" s="10" t="inlineStr"/>
       <c r="M41" s="10" t="inlineStr">
@@ -5839,12 +7835,12 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>computerized WM training (web-based)</t>
+          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
         </is>
       </c>
       <c r="Q41" s="11" t="inlineStr">
@@ -5855,7 +7851,7 @@
       <c r="R41" s="11" t="inlineStr"/>
       <c r="S41" s="11" t="inlineStr"/>
       <c r="T41" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U41" s="11" t="inlineStr">
         <is>
@@ -5869,7 +7865,7 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制（在线）</t>
         </is>
       </c>
       <c r="X41" s="12" t="inlineStr">
@@ -5879,23 +7875,27 @@
       </c>
       <c r="Y41" s="12" t="inlineStr">
         <is>
-          <t>Self-perceived cognitive failures (CFQ)</t>
+          <t>Auditory STM span; visuospatial STM</t>
         </is>
       </c>
       <c r="Z41" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA41" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="inlineStr">
+        <is>
+          <t>Long-term episodic memory</t>
+        </is>
+      </c>
       <c r="AB41" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC41" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>3;6</t>
         </is>
       </c>
       <c r="AD41" s="12" t="inlineStr">
@@ -5922,7 +7922,7 @@
       </c>
       <c r="AJ41" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK41" s="14" t="inlineStr">
@@ -5947,35 +7947,35 @@
       </c>
       <c r="AO41" s="15" t="inlineStr">
         <is>
-          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
+          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
+          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>BMC geriatrics</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -5984,14 +7984,10 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>3.5</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr"/>
+      <c r="J42" s="10" t="inlineStr"/>
       <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr">
@@ -6006,12 +8002,12 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>computerized WM training (web-based)</t>
         </is>
       </c>
       <c r="Q42" s="11" t="inlineStr">
@@ -6019,14 +8015,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R42" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S42" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr"/>
       <c r="T42" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U42" s="11" t="inlineStr">
         <is>
@@ -6040,7 +8032,7 @@
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X42" s="12" t="inlineStr">
@@ -6050,7 +8042,7 @@
       </c>
       <c r="Y42" s="12" t="inlineStr">
         <is>
-          <t>n-back task</t>
+          <t>Self-perceived cognitive failures (CFQ)</t>
         </is>
       </c>
       <c r="Z42" s="12" t="inlineStr">
@@ -6061,39 +8053,31 @@
       <c r="AA42" s="12" t="inlineStr"/>
       <c r="AB42" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC42" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD42" s="12" t="inlineStr">
         <is>
-          <t>Cohen's d medium-large</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE42" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF42" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG42" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH42" s="13" t="inlineStr">
-        <is>
-          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG42" s="13" t="inlineStr"/>
+      <c r="AH42" s="13" t="inlineStr"/>
       <c r="AI42" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6126,35 +8110,35 @@
       </c>
       <c r="AO42" s="15" t="inlineStr">
         <is>
-          <t>先导研究；ERP神经相关；6个月随访</t>
+          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
+          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>BMC geriatrics</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -6163,10 +8147,14 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>97</v>
-      </c>
-      <c r="I43" s="10" t="inlineStr"/>
-      <c r="J43" s="10" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr"/>
       <c r="M43" s="10" t="inlineStr">
@@ -6181,12 +8169,12 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>web-based WM or logic &amp; planning training</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q43" s="11" t="inlineStr">
@@ -6194,10 +8182,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R43" s="11" t="inlineStr"/>
-      <c r="S43" s="11" t="inlineStr"/>
+      <c r="R43" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T43" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U43" s="11" t="inlineStr">
         <is>
@@ -6211,7 +8203,7 @@
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X43" s="12" t="inlineStr">
@@ -6221,46 +8213,50 @@
       </c>
       <c r="Y43" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>n-back task</t>
         </is>
       </c>
       <c r="Z43" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA43" s="12" t="inlineStr">
-        <is>
-          <t>Planning; reasoning; processing speed; verbal fluency</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="12" t="inlineStr"/>
       <c r="AB43" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC43" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD43" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>Cohen's d medium-large</t>
         </is>
       </c>
       <c r="AE43" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF43" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG43" s="13" t="inlineStr"/>
-      <c r="AH43" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG43" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH43" s="13" t="inlineStr">
+        <is>
+          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
+        </is>
+      </c>
       <c r="AI43" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6293,35 +8289,35 @@
       </c>
       <c r="AO43" s="15" t="inlineStr">
         <is>
-          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
+          <t>先导研究；ERP神经相关；6个月随访</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
+          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Gerontology</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -6330,14 +8326,10 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>4</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr"/>
+      <c r="J44" s="10" t="inlineStr"/>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
       <c r="M44" s="10" t="inlineStr">
@@ -6352,24 +8344,24 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>WM span tasks (5 tasks)</t>
+          <t>web-based WM or logic &amp; planning training</t>
         </is>
       </c>
       <c r="Q44" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R44" s="11" t="n">
-        <v>10</v>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr"/>
       <c r="S44" s="11" t="inlineStr"/>
-      <c r="T44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="U44" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -6382,7 +8374,7 @@
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X44" s="12" t="inlineStr">
@@ -6392,7 +8384,7 @@
       </c>
       <c r="Y44" s="12" t="inlineStr">
         <is>
-          <t>trained WM tasks</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z44" s="12" t="inlineStr">
@@ -6402,7 +8394,7 @@
       </c>
       <c r="AA44" s="12" t="inlineStr">
         <is>
-          <t>Executive functions (2 tests)</t>
+          <t>Planning; reasoning; processing speed; verbal fluency</t>
         </is>
       </c>
       <c r="AB44" s="12" t="inlineStr">
@@ -6417,7 +8409,7 @@
       </c>
       <c r="AD44" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.8 (trained tasks)</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE44" s="12" t="inlineStr">
@@ -6434,17 +8426,17 @@
       <c r="AH44" s="13" t="inlineStr"/>
       <c r="AI44" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ44" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK44" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL44" s="14" t="inlineStr">
@@ -6464,35 +8456,35 @@
       </c>
       <c r="AO44" s="15" t="inlineStr">
         <is>
-          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
+          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
+          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Gerontology</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -6501,13 +8493,13 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>66</v>
+        <v>86.8</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
@@ -6523,20 +8515,22 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
-          <t>memory updating task (predictable vs unpredictable)</t>
+          <t>WM span tasks (5 tasks)</t>
         </is>
       </c>
       <c r="Q45" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R45" s="11" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S45" s="11" t="inlineStr"/>
       <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
@@ -6561,7 +8555,7 @@
       </c>
       <c r="Y45" s="12" t="inlineStr">
         <is>
-          <t>WM updating task (novel)</t>
+          <t>trained WM tasks</t>
         </is>
       </c>
       <c r="Z45" s="12" t="inlineStr">
@@ -6571,27 +8565,27 @@
       </c>
       <c r="AA45" s="12" t="inlineStr">
         <is>
-          <t>Episodic memory</t>
+          <t>Executive functions (2 tests)</t>
         </is>
       </c>
       <c r="AB45" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC45" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD45" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.5-0.8 (trained tasks)</t>
         </is>
       </c>
       <c r="AE45" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF45" s="13" t="inlineStr">
@@ -6603,7 +8597,7 @@
       <c r="AH45" s="13" t="inlineStr"/>
       <c r="AI45" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ45" s="14" t="inlineStr">
@@ -6613,7 +8607,7 @@
       </c>
       <c r="AK45" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL45" s="14" t="inlineStr">
@@ -6633,30 +8627,30 @@
       </c>
       <c r="AO45" s="15" t="inlineStr">
         <is>
-          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
+          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
+          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Aging brain</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -6670,10 +8664,14 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="I46" s="10" t="inlineStr"/>
-      <c r="J46" s="10" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>5</v>
+      </c>
       <c r="K46" s="10" t="inlineStr"/>
       <c r="L46" s="10" t="inlineStr"/>
       <c r="M46" s="10" t="inlineStr">
@@ -6688,12 +8686,12 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
-          <t>n-back + metacognitive program (EngAge)</t>
+          <t>memory updating task (predictable vs unpredictable)</t>
         </is>
       </c>
       <c r="Q46" s="11" t="inlineStr">
@@ -6701,9 +8699,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R46" s="11" t="n">
-        <v>20</v>
-      </c>
+      <c r="R46" s="11" t="inlineStr"/>
       <c r="S46" s="11" t="inlineStr"/>
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
@@ -6718,7 +8714,7 @@
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
-          <t>自制（居家）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X46" s="12" t="inlineStr">
@@ -6728,7 +8724,7 @@
       </c>
       <c r="Y46" s="12" t="inlineStr">
         <is>
-          <t>non-trained WM measures</t>
+          <t>WM updating task (novel)</t>
         </is>
       </c>
       <c r="Z46" s="12" t="inlineStr">
@@ -6738,7 +8734,7 @@
       </c>
       <c r="AA46" s="12" t="inlineStr">
         <is>
-          <t>Inhibitory control; episodic memory</t>
+          <t>Episodic memory</t>
         </is>
       </c>
       <c r="AB46" s="12" t="inlineStr">
@@ -6748,7 +8744,7 @@
       </c>
       <c r="AC46" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AD46" s="12" t="inlineStr">
@@ -6758,7 +8754,7 @@
       </c>
       <c r="AE46" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF46" s="13" t="inlineStr">
@@ -6775,7 +8771,7 @@
       </c>
       <c r="AJ46" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK46" s="14" t="inlineStr">
@@ -6800,35 +8796,35 @@
       </c>
       <c r="AO46" s="15" t="inlineStr">
         <is>
-          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
+          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
+          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Aging brain</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -6837,18 +8833,12 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>4</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="n">
-        <v>11</v>
-      </c>
+      <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -6861,12 +8851,12 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
+          <t>n-back + metacognitive program (EngAge)</t>
         </is>
       </c>
       <c r="Q47" s="11" t="inlineStr">
@@ -6875,14 +8865,10 @@
         </is>
       </c>
       <c r="R47" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S47" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T47" s="11" t="n">
-        <v>3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -6895,7 +8881,7 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家）</t>
         </is>
       </c>
       <c r="X47" s="12" t="inlineStr">
@@ -6905,7 +8891,7 @@
       </c>
       <c r="Y47" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM; STM tasks</t>
+          <t>non-trained WM measures</t>
         </is>
       </c>
       <c r="Z47" s="12" t="inlineStr">
@@ -6915,7 +8901,7 @@
       </c>
       <c r="AA47" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence; processing speed; inhibitory measures</t>
+          <t>Inhibitory control; episodic memory</t>
         </is>
       </c>
       <c r="AB47" s="12" t="inlineStr">
@@ -6947,27 +8933,27 @@
       <c r="AH47" s="13" t="inlineStr"/>
       <c r="AI47" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ47" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK47" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL47" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM47" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN47" s="14" t="inlineStr">
@@ -6977,35 +8963,35 @@
       </c>
       <c r="AO47" s="15" t="inlineStr">
         <is>
-          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
+          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
+          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in neurology</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -7014,16 +9000,18 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="10" t="inlineStr"/>
-      <c r="L48" s="10" t="inlineStr"/>
+      <c r="L48" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7036,12 +9024,12 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
         <is>
-          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
+          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
         </is>
       </c>
       <c r="Q48" s="11" t="inlineStr">
@@ -7050,22 +9038,22 @@
         </is>
       </c>
       <c r="R48" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S48" s="11" t="n">
         <v>30</v>
       </c>
       <c r="T48" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W48" s="11" t="inlineStr">
@@ -7080,7 +9068,7 @@
       </c>
       <c r="Y48" s="12" t="inlineStr">
         <is>
-          <t>non-verbal logical reasoning</t>
+          <t>visuospatial WM; STM tasks</t>
         </is>
       </c>
       <c r="Z48" s="12" t="inlineStr">
@@ -7090,7 +9078,7 @@
       </c>
       <c r="AA48" s="12" t="inlineStr">
         <is>
-          <t>Attention; memory; executive functions</t>
+          <t>fluid intelligence; processing speed; inhibitory measures</t>
         </is>
       </c>
       <c r="AB48" s="12" t="inlineStr">
@@ -7100,7 +9088,7 @@
       </c>
       <c r="AC48" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD48" s="12" t="inlineStr">
@@ -7110,7 +9098,7 @@
       </c>
       <c r="AE48" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF48" s="13" t="inlineStr">
@@ -7122,7 +9110,7 @@
       <c r="AH48" s="13" t="inlineStr"/>
       <c r="AI48" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ48" s="14" t="inlineStr">
@@ -7132,7 +9120,7 @@
       </c>
       <c r="AK48" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL48" s="14" t="inlineStr">
@@ -7142,7 +9130,7 @@
       </c>
       <c r="AM48" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN48" s="14" t="inlineStr">
@@ -7152,35 +9140,35 @@
       </c>
       <c r="AO48" s="15" t="inlineStr">
         <is>
-          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
+          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
+          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
+          <t>Frontiers in neurology</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -7189,13 +9177,13 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>70</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="K49" s="10" t="inlineStr"/>
       <c r="L49" s="10" t="inlineStr"/>
@@ -7216,7 +9204,7 @@
       </c>
       <c r="P49" s="11" t="inlineStr">
         <is>
-          <t>letter updating task</t>
+          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
         </is>
       </c>
       <c r="Q49" s="11" t="inlineStr">
@@ -7225,13 +9213,13 @@
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T49" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U49" s="11" t="inlineStr">
         <is>
@@ -7240,7 +9228,7 @@
       </c>
       <c r="V49" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>TMS</t>
         </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
@@ -7255,7 +9243,7 @@
       </c>
       <c r="Y49" s="12" t="inlineStr">
         <is>
-          <t>n-back (near transfer)</t>
+          <t>non-verbal logical reasoning</t>
         </is>
       </c>
       <c r="Z49" s="12" t="inlineStr">
@@ -7265,7 +9253,7 @@
       </c>
       <c r="AA49" s="12" t="inlineStr">
         <is>
-          <t>executive/memory tasks</t>
+          <t>Attention; memory; executive functions</t>
         </is>
       </c>
       <c r="AB49" s="12" t="inlineStr">
@@ -7275,7 +9263,7 @@
       </c>
       <c r="AC49" s="12" t="inlineStr">
         <is>
-          <t>1;7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD49" s="12" t="inlineStr">
@@ -7312,7 +9300,7 @@
       </c>
       <c r="AL49" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM49" s="14" t="inlineStr">
@@ -7327,35 +9315,35 @@
       </c>
       <c r="AO49" s="15" t="inlineStr">
         <is>
-          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
+          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
+          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -7364,13 +9352,13 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>487</v>
+        <v>56</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K50" s="10" t="inlineStr"/>
       <c r="L50" s="10" t="inlineStr"/>
@@ -7386,12 +9374,12 @@
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P50" s="11" t="inlineStr">
         <is>
-          <t>syllable span + auditory discrimination (IMPACT program)</t>
+          <t>letter updating task</t>
         </is>
       </c>
       <c r="Q50" s="11" t="inlineStr">
@@ -7399,22 +9387,28 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R50" s="11" t="inlineStr"/>
-      <c r="S50" s="11" t="inlineStr"/>
-      <c r="T50" s="11" t="inlineStr"/>
+      <c r="R50" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S50" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
-          <t>Posit Science (IMPACT)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X50" s="12" t="inlineStr">
@@ -7424,7 +9418,7 @@
       </c>
       <c r="Y50" s="12" t="inlineStr">
         <is>
-          <t>WM factor score</t>
+          <t>n-back (near transfer)</t>
         </is>
       </c>
       <c r="Z50" s="12" t="inlineStr">
@@ -7434,17 +9428,17 @@
       </c>
       <c r="AA50" s="12" t="inlineStr">
         <is>
-          <t>List memory; text memory</t>
+          <t>executive/memory tasks</t>
         </is>
       </c>
       <c r="AB50" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC50" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1;7</t>
         </is>
       </c>
       <c r="AD50" s="12" t="inlineStr">
@@ -7454,7 +9448,7 @@
       </c>
       <c r="AE50" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF50" s="13" t="inlineStr">
@@ -7481,12 +9475,12 @@
       </c>
       <c r="AL50" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM50" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN50" s="14" t="inlineStr">
@@ -7496,35 +9490,35 @@
       </c>
       <c r="AO50" s="15" t="inlineStr">
         <is>
-          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
+          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
+          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -7533,13 +9527,13 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>24</v>
+        <v>487</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
@@ -7560,7 +9554,7 @@
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>syllable span + auditory discrimination (IMPACT program)</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
@@ -7568,15 +9562,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R51" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S51" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T51" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -7589,7 +9577,7 @@
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Posit Science (IMPACT)</t>
         </is>
       </c>
       <c r="X51" s="12" t="inlineStr">
@@ -7599,28 +9587,32 @@
       </c>
       <c r="Y51" s="12" t="inlineStr">
         <is>
-          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
+          <t>WM factor score</t>
         </is>
       </c>
       <c r="Z51" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA51" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="12" t="inlineStr">
+        <is>
+          <t>List memory; text memory</t>
+        </is>
+      </c>
       <c r="AB51" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC51" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD51" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.9</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE51" s="12" t="inlineStr">
@@ -7630,19 +9622,11 @@
       </c>
       <c r="AF51" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG51" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH51" s="13" t="inlineStr">
-        <is>
-          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG51" s="13" t="inlineStr"/>
+      <c r="AH51" s="13" t="inlineStr"/>
       <c r="AI51" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7650,7 +9634,7 @@
       </c>
       <c r="AJ51" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK51" s="14" t="inlineStr">
@@ -7660,12 +9644,12 @@
       </c>
       <c r="AL51" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM51" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN51" s="14" t="inlineStr">
@@ -7675,35 +9659,35 @@
       </c>
       <c r="AO51" s="15" t="inlineStr">
         <is>
-          <t>静息态EEG；额叶振荡活动；先导研究</t>
+          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
+          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -7712,13 +9696,13 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>69.58</v>
+        <v>69</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>7.04</v>
+        <v>3.5</v>
       </c>
       <c r="K52" s="10" t="inlineStr"/>
       <c r="L52" s="10" t="inlineStr"/>
@@ -7734,12 +9718,12 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P52" s="11" t="inlineStr">
         <is>
-          <t>single-domain WM (n-back) or multidomain EF training</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q52" s="11" t="inlineStr">
@@ -7747,10 +9731,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr"/>
-      <c r="S52" s="11" t="inlineStr"/>
+      <c r="R52" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S52" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T52" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U52" s="11" t="inlineStr">
         <is>
@@ -7774,46 +9762,50 @@
       </c>
       <c r="Y52" s="12" t="inlineStr">
         <is>
-          <t>n-back; global EF accuracy</t>
+          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
         </is>
       </c>
       <c r="Z52" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA52" s="12" t="inlineStr">
-        <is>
-          <t>Prospective memory (Virtual Week); fluid intelligence</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr"/>
       <c r="AB52" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC52" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD52" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>d=0.5-0.9</t>
         </is>
       </c>
       <c r="AE52" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF52" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG52" s="13" t="inlineStr"/>
-      <c r="AH52" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG52" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH52" s="13" t="inlineStr">
+        <is>
+          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
+        </is>
+      </c>
       <c r="AI52" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7846,35 +9838,35 @@
       </c>
       <c r="AO52" s="15" t="inlineStr">
         <is>
-          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
+          <t>静息态EEG；额叶振荡活动；先导研究</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Cantarella</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
+          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Psychologie Française</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -7883,13 +9875,13 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>69</v>
+        <v>69.58</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>4</v>
+        <v>7.04</v>
       </c>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
@@ -7905,12 +9897,12 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
+          <t>single-domain WM (n-back) or multidomain EF training</t>
         </is>
       </c>
       <c r="Q53" s="11" t="inlineStr">
@@ -7918,14 +9910,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R53" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S53" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr"/>
       <c r="T53" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U53" s="11" t="inlineStr">
         <is>
@@ -7949,7 +9937,7 @@
       </c>
       <c r="Y53" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM criterion task</t>
+          <t>n-back; global EF accuracy</t>
         </is>
       </c>
       <c r="Z53" s="12" t="inlineStr">
@@ -7959,7 +9947,7 @@
       </c>
       <c r="AA53" s="12" t="inlineStr">
         <is>
-          <t>verbal WM; visuospatial STM; reasoning</t>
+          <t>Prospective memory (Virtual Week); fluid intelligence</t>
         </is>
       </c>
       <c r="AB53" s="12" t="inlineStr">
@@ -7974,7 +9962,7 @@
       </c>
       <c r="AD53" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE53" s="12" t="inlineStr">
@@ -8021,35 +10009,35 @@
       </c>
       <c r="AO53" s="15" t="inlineStr">
         <is>
-          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
+          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Cantarella</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Impact of strategy use during N-Back training in older adults</t>
+          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Journal of Cognitive Psychology</t>
+          <t>Psychologie Française</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -8058,10 +10046,14 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="I54" s="10" t="inlineStr"/>
-      <c r="J54" s="10" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="K54" s="10" t="inlineStr"/>
       <c r="L54" s="10" t="inlineStr"/>
       <c r="M54" s="10" t="inlineStr">
@@ -8076,12 +10068,12 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
         <is>
-          <t>n-back (strategy vs no strategy)</t>
+          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
         </is>
       </c>
       <c r="Q54" s="11" t="inlineStr">
@@ -8089,9 +10081,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr"/>
-      <c r="S54" s="11" t="inlineStr"/>
-      <c r="T54" s="11" t="inlineStr"/>
+      <c r="R54" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S54" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T54" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U54" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -8114,7 +10112,7 @@
       </c>
       <c r="Y54" s="12" t="inlineStr">
         <is>
-          <t>n-back variant</t>
+          <t>visuospatial WM criterion task</t>
         </is>
       </c>
       <c r="Z54" s="12" t="inlineStr">
@@ -8124,7 +10122,7 @@
       </c>
       <c r="AA54" s="12" t="inlineStr">
         <is>
-          <t>P300 transfer measures</t>
+          <t>verbal WM; visuospatial STM; reasoning</t>
         </is>
       </c>
       <c r="AB54" s="12" t="inlineStr">
@@ -8149,19 +10147,11 @@
       </c>
       <c r="AF54" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG54" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH54" s="13" t="inlineStr">
-        <is>
-          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG54" s="13" t="inlineStr"/>
+      <c r="AH54" s="13" t="inlineStr"/>
       <c r="AI54" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8169,7 +10159,7 @@
       </c>
       <c r="AJ54" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK54" s="14" t="inlineStr">
@@ -8194,35 +10184,35 @@
       </c>
       <c r="AO54" s="15" t="inlineStr">
         <is>
-          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
+          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
+          <t>Impact of strategy use during N-Back training in older adults</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Applied Cognitive Psychology</t>
+          <t>Journal of Cognitive Psychology</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -8231,7 +10221,7 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="I55" s="10" t="inlineStr"/>
       <c r="J55" s="10" t="inlineStr"/>
@@ -8249,12 +10239,12 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
         <is>
-          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
+          <t>n-back (strategy vs no strategy)</t>
         </is>
       </c>
       <c r="Q55" s="11" t="inlineStr">
@@ -8287,7 +10277,7 @@
       </c>
       <c r="Y55" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>n-back variant</t>
         </is>
       </c>
       <c r="Z55" s="12" t="inlineStr">
@@ -8297,7 +10287,7 @@
       </c>
       <c r="AA55" s="12" t="inlineStr">
         <is>
-          <t>Short-term memory; processing speed; reasoning</t>
+          <t>P300 transfer measures</t>
         </is>
       </c>
       <c r="AB55" s="12" t="inlineStr">
@@ -8317,16 +10307,24 @@
       </c>
       <c r="AE55" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF55" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG55" s="13" t="inlineStr"/>
-      <c r="AH55" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG55" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH55" s="13" t="inlineStr">
+        <is>
+          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
+        </is>
+      </c>
       <c r="AI55" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8334,7 +10332,7 @@
       </c>
       <c r="AJ55" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK55" s="14" t="inlineStr">
@@ -8359,35 +10357,35 @@
       </c>
       <c r="AO55" s="15" t="inlineStr">
         <is>
-          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
+          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Lange</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+          <t>Applied Cognitive Psychology</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -8396,17 +10394,11 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="I56" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K56" s="10" t="n">
-        <v>100</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr"/>
+      <c r="J56" s="10" t="inlineStr"/>
+      <c r="K56" s="10" t="inlineStr"/>
       <c r="L56" s="10" t="inlineStr"/>
       <c r="M56" s="10" t="inlineStr">
         <is>
@@ -8420,12 +10412,12 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
         <is>
-          <t>adaptive WM updating (numerical updating + 1-back)</t>
+          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
         </is>
       </c>
       <c r="Q56" s="11" t="inlineStr">
@@ -8433,9 +10425,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R56" s="11" t="n">
-        <v>20</v>
-      </c>
+      <c r="R56" s="11" t="inlineStr"/>
       <c r="S56" s="11" t="inlineStr"/>
       <c r="T56" s="11" t="inlineStr"/>
       <c r="U56" s="11" t="inlineStr">
@@ -8460,7 +10450,7 @@
       </c>
       <c r="Y56" s="12" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z56" s="12" t="inlineStr">
@@ -8470,7 +10460,7 @@
       </c>
       <c r="AA56" s="12" t="inlineStr">
         <is>
-          <t>Cognitive reappraisal (emotion regulation task)</t>
+          <t>Short-term memory; processing speed; reasoning</t>
         </is>
       </c>
       <c r="AB56" s="12" t="inlineStr">
@@ -8490,7 +10480,7 @@
       </c>
       <c r="AE56" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF56" s="13" t="inlineStr">
@@ -8531,6 +10521,179 @@
         </is>
       </c>
       <c r="AO56" s="15" t="inlineStr">
+        <is>
+          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="I57" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O57" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P57" s="11" t="inlineStr">
+        <is>
+          <t>adaptive WM updating (numerical updating + 1-back)</t>
+        </is>
+      </c>
+      <c r="Q57" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X57" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y57" s="12" t="inlineStr">
+        <is>
+          <t>WM updating task</t>
+        </is>
+      </c>
+      <c r="Z57" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="12" t="inlineStr">
+        <is>
+          <t>Cognitive reappraisal (emotion regulation task)</t>
+        </is>
+      </c>
+      <c r="AB57" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC57" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD57" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE57" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF57" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG57" s="13" t="inlineStr"/>
+      <c r="AH57" s="13" t="inlineStr"/>
+      <c r="AI57" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ57" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK57" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL57" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM57" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN57" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO57" s="15" t="inlineStr">
         <is>
           <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局</t>
         </is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -7312,8 +7312,14 @@
       <c r="H38" s="10" t="n">
         <v>137</v>
       </c>
-      <c r="I38" s="10" t="inlineStr"/>
-      <c r="J38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="10" t="inlineStr"/>
       <c r="M38" s="10" t="inlineStr">
@@ -7473,8 +7479,12 @@
       <c r="H39" s="10" t="n">
         <v>103</v>
       </c>
-      <c r="I39" s="10" t="inlineStr"/>
-      <c r="J39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>5.5</v>
+      </c>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
       <c r="M39" s="10" t="inlineStr">
@@ -7640,8 +7650,14 @@
       <c r="H40" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="I40" s="10" t="inlineStr"/>
-      <c r="J40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
       <c r="M40" s="10" t="inlineStr">
@@ -7986,8 +8002,12 @@
       <c r="H42" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="I42" s="10" t="inlineStr"/>
-      <c r="J42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>4.54</v>
+      </c>
       <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr">
@@ -8328,8 +8348,14 @@
       <c r="H44" s="10" t="n">
         <v>97</v>
       </c>
-      <c r="I44" s="10" t="inlineStr"/>
-      <c r="J44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
       <c r="M44" s="10" t="inlineStr">
@@ -8835,8 +8861,16 @@
       <c r="H47" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="I47" s="10" t="inlineStr"/>
-      <c r="J47" s="10" t="inlineStr"/>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
       <c r="M47" s="10" t="inlineStr">
@@ -10223,8 +10257,12 @@
       <c r="H55" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>5.37</v>
+      </c>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
       <c r="M55" s="10" t="inlineStr">
@@ -10396,8 +10434,12 @@
       <c r="H56" s="10" t="n">
         <v>91</v>
       </c>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>3.99</v>
+      </c>
       <c r="K56" s="10" t="inlineStr"/>
       <c r="L56" s="10" t="inlineStr"/>
       <c r="M56" s="10" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO57"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -963,266 +963,266 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Borella</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>2019</v>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Is working memory training in older adults sensitive to music?</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Psychological research</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lommen</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The effect of cognitive training in older adults: be aware of CRUNCH.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>社区</t>
         </is>
       </c>
-      <c r="H3" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>69.23999999999999</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>span</t>
-        </is>
-      </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>Categorization WM Span (verbal)</t>
-        </is>
-      </c>
-      <c r="Q3" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R3" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="T3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="H3" t="n">
+        <v>42</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="K3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>未报告(7级量表)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2-back; numerical updating; alpha-span</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>≤30天</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
-        <is>
-          <t>自制(Borella protocol)</t>
-        </is>
-      </c>
-      <c r="X3" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" s="12" t="inlineStr">
-        <is>
-          <t>Backward Corsi blocks</t>
-        </is>
-      </c>
-      <c r="Z3" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" s="12" t="inlineStr">
-        <is>
-          <t>Verbal fluency; Raven matrices; Culture Fair</t>
-        </is>
-      </c>
-      <c r="AB3" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC3" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD3" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AE3" s="12" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AF3" s="13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG3" s="13" t="inlineStr"/>
-      <c r="AH3" s="13" t="inlineStr"/>
-      <c r="AI3" s="14" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AJ3" s="14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AK3" s="14" t="inlineStr">
-        <is>
-          <t>未检验</t>
-        </is>
-      </c>
-      <c r="AL3" s="14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AM3" s="14" t="inlineStr">
-        <is>
-          <t>教育年限</t>
-        </is>
-      </c>
-      <c r="AN3" s="14" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Backward Digit Span</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Faces &amp; Names; Shopping List</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>高/低</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>低&gt;高</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>教育(7级量表)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>期刊</t>
         </is>
       </c>
-      <c r="AO3" s="15" t="inlineStr">
-        <is>
-          <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>按基线EF高/低分组分析调节效应</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Borella</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Is working memory training in older adults sensitive to music?</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Psychological research</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal)</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Salminen</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Age-specific differences of dual n-back training.</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>社区/大学</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr">
-        <is>
-          <t>MMSE</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr">
-        <is>
-          <t>≥28</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>n-back</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>Dual n-back (auditory-visual)</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R4" s="11" t="n">
-        <v>14</v>
-      </c>
       <c r="S4" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
-        <is>
-          <t>3-6</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="U4" s="11" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X4" s="12" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="Y4" s="12" t="inlineStr">
         <is>
-          <t>AV n-back (untrained stimuli)</t>
+          <t>Backward Corsi blocks</t>
         </is>
       </c>
       <c r="Z4" s="12" t="inlineStr">
@@ -1256,18 +1256,16 @@
       </c>
       <c r="AA4" s="12" t="inlineStr">
         <is>
-          <t>Task switching; Attentional blink (T2)</t>
+          <t>Verbal fluency; Raven matrices; Culture Fair</t>
         </is>
       </c>
       <c r="AB4" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC4" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="AD4" s="12" t="inlineStr">
         <is>
@@ -1276,7 +1274,7 @@
       </c>
       <c r="AE4" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF4" s="13" t="inlineStr">
@@ -1293,22 +1291,22 @@
       </c>
       <c r="AJ4" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK4" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL4" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM4" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN4" s="14" t="inlineStr">
@@ -1318,97 +1316,103 @@
       </c>
       <c r="AO4" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
+          <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Tays</t>
+          <t>Salminen</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Longitudinal neurostimulation in older adults improves working memory.</t>
+          <t>Age-specific differences of dual n-back training.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>社区/大学</t>
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>64.38</v>
+        <v>64.8</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>16.78</v>
+        <v>56</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>28.48</v>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>≥28</t>
+        </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>Verbal WM; Visuospatial WM; OSpan</t>
+          <t>Dual n-back (auditory-visual)</t>
         </is>
       </c>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="T5" s="11" t="n">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>3-6</t>
+        </is>
       </c>
       <c r="U5" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V5" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W5" s="11" t="inlineStr">
@@ -1423,7 +1427,7 @@
       </c>
       <c r="Y5" s="12" t="inlineStr">
         <is>
-          <t>Spatial 2-back</t>
+          <t>AV n-back (untrained stimuli)</t>
         </is>
       </c>
       <c r="Z5" s="12" t="inlineStr">
@@ -1433,16 +1437,18 @@
       </c>
       <c r="AA5" s="12" t="inlineStr">
         <is>
-          <t>Digit span; Stroop</t>
+          <t>Task switching; Attentional blink (T2)</t>
         </is>
       </c>
       <c r="AB5" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC5" s="12" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD5" s="12" t="inlineStr">
         <is>
@@ -1451,7 +1457,7 @@
       </c>
       <c r="AE5" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF5" s="13" t="inlineStr">
@@ -1468,22 +1474,22 @@
       </c>
       <c r="AJ5" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK5" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL5" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM5" s="14" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN5" s="14" t="inlineStr">
@@ -1493,35 +1499,35 @@
       </c>
       <c r="AO5" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
+          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Vesterinen</t>
+          <t>Tays</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>N-back training and transfer effects revealed by behavioral responses and EEG.</t>
+          <t>Longitudinal neurostimulation in older adults improves working memory.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Brain and behavior</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1530,66 +1536,60 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>64.38</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>5.08</v>
       </c>
       <c r="K6" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>16.78</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>28.48</v>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>Verbal WM; Visuospatial WM; OSpan</t>
         </is>
       </c>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R6" s="11" t="n">
         <v>10</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T6" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W6" s="11" t="inlineStr">
@@ -1604,24 +1604,26 @@
       </c>
       <c r="Y6" s="12" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>Spatial 2-back</t>
         </is>
       </c>
       <c r="Z6" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>Digit span; Stroop</t>
+        </is>
+      </c>
       <c r="AB6" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC6" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AD6" s="12" t="inlineStr">
         <is>
@@ -1630,24 +1632,16 @@
       </c>
       <c r="AE6" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF6" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr">
-        <is>
-          <t>EEG/ERP</t>
-        </is>
-      </c>
-      <c r="AH6" s="13" t="inlineStr">
-        <is>
-          <t>训练后P300振幅变化与任务难度相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG6" s="13" t="inlineStr"/>
+      <c r="AH6" s="13" t="inlineStr"/>
       <c r="AI6" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1670,7 +1664,7 @@
       </c>
       <c r="AM6" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="AN6" s="14" t="inlineStr">
@@ -1680,35 +1674,35 @@
       </c>
       <c r="AO6" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
+          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Brum</t>
+          <t>Vesterinen</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Verbal working memory training in older adults: an investigation of dose response.</t>
+          <t>N-back training and transfer effects revealed by behavioral responses and EEG.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>Brain and behavior</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1717,25 +1711,27 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>67.17</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>9.5</v>
+        <v>63.11</v>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>CERAD+CDT</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -1745,12 +1741,12 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, Borella protocol)</t>
+          <t>N-back (adaptive)</t>
         </is>
       </c>
       <c r="Q7" s="11" t="inlineStr">
@@ -1759,14 +1755,14 @@
         </is>
       </c>
       <c r="R7" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S7" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="S7" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="T7" s="11" t="n">
-        <v>2</v>
-      </c>
       <c r="U7" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -1779,7 +1775,7 @@
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X7" s="12" t="inlineStr">
@@ -1789,26 +1785,24 @@
       </c>
       <c r="Y7" s="12" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; Visuospatial WM</t>
+          <t>N-back (untrained level)</t>
         </is>
       </c>
       <c r="Z7" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA7" s="12" t="inlineStr">
-        <is>
-          <t>Stroop; Processing speed; Fluid intelligence</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" s="12" t="inlineStr"/>
       <c r="AB7" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC7" s="12" t="n">
-        <v>6</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD7" s="12" t="inlineStr">
         <is>
@@ -1817,16 +1811,24 @@
       </c>
       <c r="AE7" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF7" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG7" s="13" t="inlineStr"/>
-      <c r="AH7" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG7" s="13" t="inlineStr">
+        <is>
+          <t>EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AH7" s="13" t="inlineStr">
+        <is>
+          <t>训练后P300振幅变化与任务难度相关</t>
+        </is>
+      </c>
       <c r="AI7" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1849,7 +1851,7 @@
       </c>
       <c r="AM7" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN7" s="14" t="inlineStr">
@@ -1859,35 +1861,35 @@
       </c>
       <c r="AO7" s="15" t="inlineStr">
         <is>
-          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
+          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Brum</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Gamified working memory intervention enhances prefrontal neurocognitive plasticity during aging.</t>
+          <t>Verbal working memory training in older adults: an investigation of dose response.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1896,46 +1898,40 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>46</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>67.17</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>4.4</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>≥6年</t>
-        </is>
+      <c r="L8" s="10" t="n">
+        <v>9.5</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>CERAD+CDT</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>Gamified N-back (fruit-cutting game)</t>
+          <t>Categorization WM Span (verbal, Borella protocol)</t>
         </is>
       </c>
       <c r="Q8" s="11" t="inlineStr">
@@ -1944,13 +1940,13 @@
         </is>
       </c>
       <c r="R8" s="11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S8" s="11" t="n">
         <v>60</v>
       </c>
       <c r="T8" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U8" s="11" t="inlineStr">
         <is>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
-          <t>自制(JavaScript游戏)</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X8" s="12" t="inlineStr">
@@ -1974,7 +1970,7 @@
       </c>
       <c r="Y8" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>Letter-Number Sequencing; Visuospatial WM</t>
         </is>
       </c>
       <c r="Z8" s="12" t="inlineStr">
@@ -1984,7 +1980,7 @@
       </c>
       <c r="AA8" s="12" t="inlineStr">
         <is>
-          <t>Inhibitory control; Visuospatial; Episodic memory</t>
+          <t>Stroop; Processing speed; Fluid intelligence</t>
         </is>
       </c>
       <c r="AB8" s="12" t="inlineStr">
@@ -2007,19 +2003,11 @@
       </c>
       <c r="AF8" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(sMRI+rs-fMRI)</t>
-        </is>
-      </c>
-      <c r="AH8" s="13" t="inlineStr">
-        <is>
-          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG8" s="13" t="inlineStr"/>
+      <c r="AH8" s="13" t="inlineStr"/>
       <c r="AI8" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2042,7 +2030,7 @@
       </c>
       <c r="AM8" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN8" s="14" t="inlineStr">
@@ -2052,25 +2040,25 @@
       </c>
       <c r="AO8" s="15" t="inlineStr">
         <is>
-          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
+          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Guye</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in older adults: Bayesian evidence supporting the absence of transfer.</t>
+          <t>Gamified working memory intervention enhances prefrontal neurocognitive plasticity during aging.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -2080,7 +2068,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2089,40 +2077,46 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>142</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>未报告(0-7量表)</t>
+          <t>≥6年</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>MMSE+GDS</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>≥26(MMSE)</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
+          <t>Gamified N-back (fruit-cutting game)</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr">
@@ -2131,15 +2125,13 @@
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="T9" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9" s="11" t="inlineStr">
         <is>
@@ -2153,7 +2145,7 @@
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>自制(von Bastian protocol)</t>
+          <t>自制(JavaScript游戏)</t>
         </is>
       </c>
       <c r="X9" s="12" t="inlineStr">
@@ -2163,7 +2155,7 @@
       </c>
       <c r="Y9" s="12" t="inlineStr">
         <is>
-          <t>Visuospatial WM (3 tasks)</t>
+          <t>WM tasks (untrained)</t>
         </is>
       </c>
       <c r="Z9" s="12" t="inlineStr">
@@ -2173,18 +2165,16 @@
       </c>
       <c r="AA9" s="12" t="inlineStr">
         <is>
-          <t>Fluid intelligence; Inhibition; Shifting</t>
+          <t>Inhibitory control; Visuospatial; Episodic memory</t>
         </is>
       </c>
       <c r="AB9" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC9" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="AD9" s="12" t="inlineStr">
         <is>
@@ -2193,16 +2183,24 @@
       </c>
       <c r="AE9" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF9" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG9" s="13" t="inlineStr"/>
-      <c r="AH9" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG9" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI+rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH9" s="13" t="inlineStr">
+        <is>
+          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
+        </is>
+      </c>
       <c r="AI9" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2225,7 +2223,7 @@
       </c>
       <c r="AM9" s="14" t="inlineStr">
         <is>
-          <t>教育(0-7量表)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN9" s="14" t="inlineStr">
@@ -2235,35 +2233,35 @@
       </c>
       <c r="AO9" s="15" t="inlineStr">
         <is>
-          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
+          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Guye</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training Coupled With Transcranial Direct Current Stimulation in Older Adults: A Randomized Controlled Experiment.</t>
+          <t>Working memory training in older adults: Bayesian evidence supporting the absence of transfer.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Spain/Portugal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2272,40 +2270,40 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>68.2</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>5.92</v>
+        <v>3.66</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未报告(0-7量表)</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>MoCA</t>
+          <t>MMSE+GDS</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>≥26</t>
+          <t>≥26(MMSE)</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
         </is>
       </c>
       <c r="Q10" s="11" t="inlineStr">
@@ -2314,18 +2312,16 @@
         </is>
       </c>
       <c r="R10" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>20+20</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="U10" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -2333,12 +2329,12 @@
       </c>
       <c r="V10" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(von Bastian protocol)</t>
         </is>
       </c>
       <c r="X10" s="12" t="inlineStr">
@@ -2348,7 +2344,7 @@
       </c>
       <c r="Y10" s="12" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>Visuospatial WM (3 tasks)</t>
         </is>
       </c>
       <c r="Z10" s="12" t="inlineStr">
@@ -2358,16 +2354,18 @@
       </c>
       <c r="AA10" s="12" t="inlineStr">
         <is>
-          <t>Raven APM (RAPM)</t>
+          <t>Fluid intelligence; Inhibition; Shifting</t>
         </is>
       </c>
       <c r="AB10" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC10" s="12" t="n">
-        <v>0.5</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD10" s="12" t="inlineStr">
         <is>
@@ -2376,7 +2374,7 @@
       </c>
       <c r="AE10" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF10" s="13" t="inlineStr">
@@ -2388,17 +2386,17 @@
       <c r="AH10" s="13" t="inlineStr"/>
       <c r="AI10" s="14" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ10" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK10" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL10" s="14" t="inlineStr">
@@ -2408,7 +2406,7 @@
       </c>
       <c r="AM10" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育(0-7量表)</t>
         </is>
       </c>
       <c r="AN10" s="14" t="inlineStr">
@@ -2418,25 +2416,25 @@
       </c>
       <c r="AO10" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
+          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Rudner</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Speech in Noise Comprehension in Older Adults.</t>
+          <t>Working Memory Training Coupled With Transcranial Direct Current Stimulation in Older Adults: A Randomized Controlled Experiment.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2446,7 +2444,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Spain/Portugal</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2455,16 +2453,16 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>64.95999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>3.77</v>
+        <v>5.92</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -2478,17 +2476,17 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>≥23</t>
+          <t>≥26</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>Reading Span (Cogmed)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr">
@@ -2497,15 +2495,17 @@
         </is>
       </c>
       <c r="R11" s="11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>30-60</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="n">
-        <v>5</v>
+          <t>20+20</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="U11" s="11" t="inlineStr">
         <is>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V11" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>Cogmed</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X11" s="12" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Y11" s="12" t="inlineStr">
         <is>
-          <t>Reading Span (untrained version)</t>
+          <t>Digit Span</t>
         </is>
       </c>
       <c r="Z11" s="12" t="inlineStr">
@@ -2539,18 +2539,16 @@
       </c>
       <c r="AA11" s="12" t="inlineStr">
         <is>
-          <t>Speech-in-noise comprehension</t>
+          <t>Raven APM (RAPM)</t>
         </is>
       </c>
       <c r="AB11" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC11" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD11" s="12" t="inlineStr">
         <is>
@@ -2559,7 +2557,7 @@
       </c>
       <c r="AE11" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF11" s="13" t="inlineStr">
@@ -2571,17 +2569,17 @@
       <c r="AH11" s="13" t="inlineStr"/>
       <c r="AI11" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AJ11" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK11" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL11" s="14" t="inlineStr">
@@ -2601,17 +2599,17 @@
       </c>
       <c r="AO11" s="15" t="inlineStr">
         <is>
-          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
+          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Berryhill</t>
+          <t>Rudner</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -2619,17 +2617,17 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Older Adults Improve on Everyday Tasks after Working Memory Training and Neurostimulation.</t>
+          <t>Working Memory Training and Speech in Noise Comprehension in Older Adults.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Brain stimulation</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -2638,69 +2636,71 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>64.95999999999999</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>3.77</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>15.58</v>
+        <v>50</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>≥23</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
+          <t>Reading Span (Cogmed)</t>
         </is>
       </c>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R12" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="T12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="S12" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Cogmed</t>
         </is>
       </c>
       <c r="X12" s="12" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Y12" s="12" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; 2-back</t>
+          <t>Reading Span (untrained version)</t>
         </is>
       </c>
       <c r="Z12" s="12" t="inlineStr">
@@ -2720,42 +2720,36 @@
       </c>
       <c r="AA12" s="12" t="inlineStr">
         <is>
-          <t>WCPA (everyday scheduling); Road Craft Test</t>
+          <t>Speech-in-noise comprehension</t>
         </is>
       </c>
       <c r="AB12" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC12" s="12" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD12" s="12" t="inlineStr">
         <is>
-          <t>η²=0.073(far transfer)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE12" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF12" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG12" s="13" t="inlineStr">
-        <is>
-          <t>fNIRS</t>
-        </is>
-      </c>
-      <c r="AH12" s="13" t="inlineStr">
-        <is>
-          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr"/>
+      <c r="AH12" s="13" t="inlineStr"/>
       <c r="AI12" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2778,7 +2772,7 @@
       </c>
       <c r="AM12" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN12" s="14" t="inlineStr">
@@ -2788,35 +2782,35 @@
       </c>
       <c r="AO12" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
+          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>13</v>
+      <c r="A13" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Matysiak</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>2019</v>
+          <t>Berryhill</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>2016</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
+          <t>Older Adults Improve on Everyday Tasks after Working Memory Training and Neurostimulation.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in Aging Neuroscience</t>
+          <t>Brain stimulation</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -2825,12 +2819,10 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>69.03</v>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
@@ -2838,12 +2830,10 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>15.58</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -2852,43 +2842,41 @@
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>≥27</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
         </is>
       </c>
       <c r="Q13" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R13" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>45</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U13" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
@@ -2903,7 +2891,7 @@
       </c>
       <c r="Y13" s="12" t="inlineStr">
         <is>
-          <t>OSPAN; WM tasks</t>
+          <t>Letter-Number Sequencing; 2-back</t>
         </is>
       </c>
       <c r="Z13" s="12" t="inlineStr">
@@ -2913,22 +2901,20 @@
       </c>
       <c r="AA13" s="12" t="inlineStr">
         <is>
-          <t>Processing speed; Fluid intelligence</t>
+          <t>WCPA (everyday scheduling); Road Craft Test</t>
         </is>
       </c>
       <c r="AB13" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC13" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AD13" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²=0.073(far transfer)</t>
         </is>
       </c>
       <c r="AE13" s="12" t="inlineStr">
@@ -2938,19 +2924,27 @@
       </c>
       <c r="AF13" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG13" s="13" t="inlineStr"/>
-      <c r="AH13" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="AH13" s="13" t="inlineStr">
+        <is>
+          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
+        </is>
+      </c>
       <c r="AI13" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ13" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK13" s="14" t="inlineStr">
@@ -2975,35 +2969,35 @@
       </c>
       <c r="AO13" s="15" t="inlineStr">
         <is>
-          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
+          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>14</v>
+      <c r="A14" s="9" t="n">
+        <v>13</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>2021</v>
+          <t>Matysiak</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>2019</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
+          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Neural plasticity</t>
+          <t>Frontiers in Aging Neuroscience</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -3012,62 +3006,70 @@
         </is>
       </c>
       <c r="H14" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>MMSE</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>≥27</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Dual n-back (adaptive)</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R14" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>68.84</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Visual Object Memory Task (VOMT)</t>
-        </is>
-      </c>
-      <c r="Q14" s="11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S14" s="11" t="n">
-        <v>60</v>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T14" s="11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
@@ -3082,15 +3084,19 @@
       </c>
       <c r="Y14" s="12" t="inlineStr">
         <is>
-          <t>VOMT (untrained stimuli)</t>
+          <t>OSPAN; WM tasks</t>
         </is>
       </c>
       <c r="Z14" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA14" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB14" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -3113,27 +3119,19 @@
       </c>
       <c r="AF14" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG14" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(rs-fMRI)</t>
-        </is>
-      </c>
-      <c r="AH14" s="13" t="inlineStr">
-        <is>
-          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr"/>
+      <c r="AH14" s="13" t="inlineStr"/>
       <c r="AI14" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ14" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK14" s="14" t="inlineStr">
@@ -3158,35 +3156,35 @@
       </c>
       <c r="AO14" s="15" t="inlineStr">
         <is>
-          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
+          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
+          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
+          <t>Neural plasticity</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -3195,29 +3193,23 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>4.65</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>14.48</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -3227,41 +3219,41 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, modified)</t>
+          <t>Visual Object Memory Task (VOMT)</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V15" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X15" s="12" t="inlineStr">
@@ -3271,26 +3263,24 @@
       </c>
       <c r="Y15" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>VOMT (untrained stimuli)</t>
         </is>
       </c>
       <c r="Z15" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA15" s="12" t="inlineStr">
-        <is>
-          <t>TIADL (everyday functioning); EPT</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr"/>
       <c r="AB15" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>9</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD15" s="12" t="inlineStr">
         <is>
@@ -3304,11 +3294,19 @@
       </c>
       <c r="AF15" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG15" s="13" t="inlineStr"/>
-      <c r="AH15" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG15" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH15" s="13" t="inlineStr">
+        <is>
+          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+        </is>
+      </c>
       <c r="AI15" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -3331,7 +3329,7 @@
       </c>
       <c r="AM15" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN15" s="14" t="inlineStr">
@@ -3341,35 +3339,35 @@
       </c>
       <c r="AO15" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
+          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
+          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -3378,20 +3376,20 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>66.7</v>
+        <v>32</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="K16" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
@@ -3400,22 +3398,22 @@
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Categorization WM Span (verbal, modified)</t>
         </is>
       </c>
       <c r="Q16" s="11" t="inlineStr">
@@ -3424,13 +3422,13 @@
         </is>
       </c>
       <c r="R16" s="11" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="S16" s="11" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="T16" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U16" s="11" t="inlineStr">
         <is>
@@ -3444,7 +3442,7 @@
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X16" s="12" t="inlineStr">
@@ -3454,7 +3452,7 @@
       </c>
       <c r="Y16" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z16" s="12" t="inlineStr">
@@ -3464,18 +3462,16 @@
       </c>
       <c r="AA16" s="12" t="inlineStr">
         <is>
-          <t>Processing speed; Executive function</t>
+          <t>TIADL (everyday functioning); EPT</t>
         </is>
       </c>
       <c r="AB16" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC16" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AD16" s="12" t="inlineStr">
         <is>
@@ -3516,7 +3512,7 @@
       </c>
       <c r="AM16" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN16" s="14" t="inlineStr">
@@ -3526,13 +3522,13 @@
       </c>
       <c r="AO16" s="15" t="inlineStr">
         <is>
-          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -3540,16 +3536,16 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
+          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>Journal of visualized experiments : JoVE</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -3563,19 +3559,25 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>16.14</v>
+        <v>66.7</v>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -3584,7 +3586,7 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -3594,7 +3596,7 @@
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>Adaptive n-back (0-5 back)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -3603,13 +3605,13 @@
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S17" s="11" t="n">
         <v>45</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U17" s="11" t="inlineStr">
         <is>
@@ -3633,7 +3635,7 @@
       </c>
       <c r="Y17" s="12" t="inlineStr">
         <is>
-          <t>Digit Span (backward)</t>
+          <t>WM tasks (untrained)</t>
         </is>
       </c>
       <c r="Z17" s="12" t="inlineStr">
@@ -3643,7 +3645,7 @@
       </c>
       <c r="AA17" s="12" t="inlineStr">
         <is>
-          <t>CERAD episodic memory; Processing speed (LPS)</t>
+          <t>Processing speed; Executive function</t>
         </is>
       </c>
       <c r="AB17" s="12" t="inlineStr">
@@ -3658,7 +3660,7 @@
       </c>
       <c r="AD17" s="12" t="inlineStr">
         <is>
-          <t>d=0.78(教育组间)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE17" s="12" t="inlineStr">
@@ -3680,22 +3682,22 @@
       </c>
       <c r="AJ17" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK17" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL17" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM17" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN17" s="14" t="inlineStr">
@@ -3705,35 +3707,35 @@
       </c>
       <c r="AO17" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
+          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -3742,46 +3744,38 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>16.14</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>Adaptive n-back (0-5 back)</t>
         </is>
       </c>
       <c r="Q18" s="11" t="inlineStr">
@@ -3790,13 +3784,13 @@
         </is>
       </c>
       <c r="R18" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="T18" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U18" s="11" t="inlineStr">
         <is>
@@ -3810,7 +3804,7 @@
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X18" s="12" t="inlineStr">
@@ -3820,7 +3814,7 @@
       </c>
       <c r="Y18" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>Digit Span (backward)</t>
         </is>
       </c>
       <c r="Z18" s="12" t="inlineStr">
@@ -3830,25 +3824,27 @@
       </c>
       <c r="AA18" s="12" t="inlineStr">
         <is>
-          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+          <t>CERAD episodic memory; Processing speed (LPS)</t>
         </is>
       </c>
       <c r="AB18" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC18" s="12" t="n">
-        <v>8</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD18" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.78(教育组间)</t>
         </is>
       </c>
       <c r="AE18" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF18" s="13" t="inlineStr">
@@ -3865,22 +3861,22 @@
       </c>
       <c r="AJ18" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK18" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL18" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM18" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN18" s="14" t="inlineStr">
@@ -3890,75 +3886,83 @@
       </c>
       <c r="AO18" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Olivetti</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
+          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Cognitive processing</t>
+          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>医院/社区</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>11.9</v>
+        <v>36</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>MMSE+CDT</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>≥26(MMSE)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>N-back (0-2 back, adaptive)</t>
+          <t>Categorization WM Span (verbal)</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
@@ -3967,15 +3971,13 @@
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="T19" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U19" s="11" t="inlineStr">
         <is>
@@ -3989,7 +3991,7 @@
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X19" s="12" t="inlineStr">
@@ -3999,28 +4001,30 @@
       </c>
       <c r="Y19" s="12" t="inlineStr">
         <is>
-          <t>Corsi Block; Digit Span</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z19" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA19" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr">
+        <is>
+          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
+        </is>
+      </c>
       <c r="AB19" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC19" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="n">
+        <v>8</v>
       </c>
       <c r="AD19" s="12" t="inlineStr">
         <is>
-          <t>d=2.21(近迁移)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE19" s="12" t="inlineStr">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="AM19" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN19" s="14" t="inlineStr">
@@ -4067,92 +4071,92 @@
       </c>
       <c r="AO19" s="15" t="inlineStr">
         <is>
-          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
+          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Olivetti</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
+          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>International journal of aging &amp; human development</t>
+          <t>Cognitive processing</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院/社区</t>
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>68.55</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>5.74</v>
+        <v>5.89</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>11.9</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE+CDT</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥26(MMSE)</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+          <t>N-back (0-2 back, adaptive)</t>
         </is>
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R20" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S20" s="11" t="n">
-        <v>60</v>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T20" s="11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U20" s="11" t="inlineStr">
         <is>
@@ -4176,19 +4180,15 @@
       </c>
       <c r="Y20" s="12" t="inlineStr">
         <is>
-          <t>Spatial WM (untrained)</t>
+          <t>Corsi Block; Digit Span</t>
         </is>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA20" s="12" t="inlineStr">
-        <is>
-          <t>Reasoning; IADL (everyday function)</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr"/>
       <c r="AB20" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="AD20" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=2.21(近迁移)</t>
         </is>
       </c>
       <c r="AE20" s="12" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AM20" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN20" s="14" t="inlineStr">
@@ -4248,30 +4248,30 @@
       </c>
       <c r="AO20" s="15" t="inlineStr">
         <is>
-          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
+          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>GeroScience</t>
+          <t>International journal of aging &amp; human development</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -4285,19 +4285,21 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>71</v>
+        <v>68.55</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>4.6</v>
+        <v>5.74</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>16.3</v>
+        <v>58</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -4316,22 +4318,22 @@
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>Multidomain cognitive training (WM+processing speed)</t>
+          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="T21" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U21" s="11" t="inlineStr">
         <is>
@@ -4345,7 +4347,7 @@
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet-based)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X21" s="12" t="inlineStr">
@@ -4355,15 +4357,19 @@
       </c>
       <c r="Y21" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (proximal)</t>
+          <t>Spatial WM (untrained)</t>
         </is>
       </c>
       <c r="Z21" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA21" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA21" s="12" t="inlineStr">
+        <is>
+          <t>Reasoning; IADL (everyday function)</t>
+        </is>
+      </c>
       <c r="AB21" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4381,37 +4387,29 @@
       </c>
       <c r="AE21" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF21" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG21" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(sMRI)</t>
-        </is>
-      </c>
-      <c r="AH21" s="13" t="inlineStr">
-        <is>
-          <t>白质高信号负荷高者训练获益更少</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG21" s="13" t="inlineStr"/>
+      <c r="AH21" s="13" t="inlineStr"/>
       <c r="AI21" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ21" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK21" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WMH获益更多)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL21" s="14" t="inlineStr">
@@ -4421,7 +4419,7 @@
       </c>
       <c r="AM21" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN21" s="14" t="inlineStr">
@@ -4431,35 +4429,35 @@
       </c>
       <c r="AO21" s="15" t="inlineStr">
         <is>
-          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
+          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
+          <t>GeroScience</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -4468,27 +4466,19 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -4502,12 +4492,12 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>Multidomain cognitive training (WM+processing speed)</t>
         </is>
       </c>
       <c r="Q22" s="11" t="inlineStr">
@@ -4516,17 +4506,17 @@
         </is>
       </c>
       <c r="R22" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T22" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="S22" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T22" s="11" t="n">
-        <v>6</v>
-      </c>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -4536,7 +4526,7 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(tablet-based)</t>
         </is>
       </c>
       <c r="X22" s="12" t="inlineStr">
@@ -4546,7 +4536,7 @@
       </c>
       <c r="Y22" s="12" t="inlineStr">
         <is>
-          <t>Listening Span</t>
+          <t>WM tasks (proximal)</t>
         </is>
       </c>
       <c r="Z22" s="12" t="inlineStr">
@@ -4582,12 +4572,12 @@
       </c>
       <c r="AG22" s="13" t="inlineStr">
         <is>
-          <t>fMRI</t>
+          <t>fMRI(sMRI)</t>
         </is>
       </c>
       <c r="AH22" s="13" t="inlineStr">
         <is>
-          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+          <t>白质高信号负荷高者训练获益更少</t>
         </is>
       </c>
       <c r="AI22" s="14" t="inlineStr">
@@ -4602,7 +4592,7 @@
       </c>
       <c r="AK22" s="14" t="inlineStr">
         <is>
-          <t>高&gt;低(类年轻激活者获益更多)</t>
+          <t>低&gt;高(低WMH获益更多)</t>
         </is>
       </c>
       <c r="AL22" s="14" t="inlineStr">
@@ -4612,7 +4602,7 @@
       </c>
       <c r="AM22" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN22" s="14" t="inlineStr">
@@ -4622,53 +4612,59 @@
       </c>
       <c r="AO22" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Tagliabue</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
+          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Attention, perception &amp; psychophysics</t>
+          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>社区(在线)</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>48</v>
+        <v>30</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -4687,12 +4683,12 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>DMTS (delayed match-to-sample); Enumeration</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr">
@@ -4701,17 +4697,17 @@
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U23" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr">
@@ -4721,7 +4717,7 @@
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>自制(在线)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X23" s="12" t="inlineStr">
@@ -4731,7 +4727,7 @@
       </c>
       <c r="Y23" s="12" t="inlineStr">
         <is>
-          <t>DMTS (visuospatial WM, k值)</t>
+          <t>Listening Span</t>
         </is>
       </c>
       <c r="Z23" s="12" t="inlineStr">
@@ -4742,11 +4738,13 @@
       <c r="AA23" s="12" t="inlineStr"/>
       <c r="AB23" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC23" s="12" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD23" s="12" t="inlineStr">
         <is>
@@ -4760,11 +4758,19 @@
       </c>
       <c r="AF23" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG23" s="13" t="inlineStr"/>
-      <c r="AH23" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG23" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH23" s="13" t="inlineStr">
+        <is>
+          <t>训练前类年轻脑激活模式预测更大训练获益</t>
+        </is>
+      </c>
       <c r="AI23" s="14" t="inlineStr">
         <is>
           <t>高/低</t>
@@ -4777,7 +4783,7 @@
       </c>
       <c r="AK23" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WM基线者获益更多)</t>
+          <t>高&gt;低(类年轻激活者获益更多)</t>
         </is>
       </c>
       <c r="AL23" s="14" t="inlineStr">
@@ -4787,7 +4793,7 @@
       </c>
       <c r="AM23" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN23" s="14" t="inlineStr">
@@ -4797,53 +4803,53 @@
       </c>
       <c r="AO23" s="15" t="inlineStr">
         <is>
-          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Zinke</t>
+          <t>Tagliabue</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
+          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Developmental psychology</t>
+          <t>Attention, perception &amp; psychophysics</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>社区(在线)</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>77.2</v>
+        <v>68.2</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>8.1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
@@ -4852,7 +4858,7 @@
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>MMST</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -4862,12 +4868,12 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
-          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+          <t>DMTS (delayed match-to-sample); Enumeration</t>
         </is>
       </c>
       <c r="Q24" s="11" t="inlineStr">
@@ -4876,56 +4882,52 @@
         </is>
       </c>
       <c r="R24" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S24" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="T24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>自制(在线)</t>
+        </is>
+      </c>
+      <c r="X24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y24" s="12" t="inlineStr">
+        <is>
+          <t>DMTS (visuospatial WM, k值)</t>
+        </is>
+      </c>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr"/>
+      <c r="AB24" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="U24" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V24" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="X24" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y24" s="12" t="inlineStr">
-        <is>
-          <t>Verbal WM (untrained)</t>
-        </is>
-      </c>
-      <c r="Z24" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA24" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; Reasoning</t>
-        </is>
-      </c>
-      <c r="AB24" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC24" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="AD24" s="12" t="inlineStr">
         <is>
@@ -4956,17 +4958,17 @@
       </c>
       <c r="AK24" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低基线者近迁移更大)</t>
+          <t>低&gt;高(低WM基线者获益更多)</t>
         </is>
       </c>
       <c r="AL24" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM24" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN24" s="14" t="inlineStr">
@@ -4976,30 +4978,30 @@
       </c>
       <c r="AO24" s="15" t="inlineStr">
         <is>
-          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Schmicker</t>
+          <t>Zinke</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
+          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Current aging science</t>
+          <t>Developmental psychology</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -5013,18 +5015,16 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>80.5</v>
+        <v>77.2</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>8.1</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>80</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMST</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U25" s="11" t="inlineStr">
         <is>
@@ -5087,24 +5087,26 @@
       </c>
       <c r="Y25" s="12" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>Verbal WM (untrained)</t>
         </is>
       </c>
       <c r="Z25" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA25" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Reasoning</t>
+        </is>
+      </c>
       <c r="AB25" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC25" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AD25" s="12" t="inlineStr">
         <is>
@@ -5125,7 +5127,7 @@
       <c r="AH25" s="13" t="inlineStr"/>
       <c r="AI25" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ25" s="14" t="inlineStr">
@@ -5135,17 +5137,17 @@
       </c>
       <c r="AK25" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(低基线者近迁移更大)</t>
         </is>
       </c>
       <c r="AL25" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM25" s="14" t="inlineStr">
         <is>
-          <t>CRI(认知储备指数)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN25" s="14" t="inlineStr">
@@ -5155,35 +5157,35 @@
       </c>
       <c r="AO25" s="15" t="inlineStr">
         <is>
-          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
+          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Matysiak</t>
+          <t>Schmicker</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
+          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>BMC research notes</t>
+          <t>Current aging science</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -5192,16 +5194,18 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>66.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K26" s="10" t="n">
-        <v>88</v>
+        <v>6.4</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
@@ -5210,12 +5214,12 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
@@ -5225,7 +5229,7 @@
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>N-back (adaptive)</t>
         </is>
       </c>
       <c r="Q26" s="11" t="inlineStr">
@@ -5234,13 +5238,13 @@
         </is>
       </c>
       <c r="R26" s="11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="T26" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U26" s="11" t="inlineStr">
         <is>
@@ -5254,7 +5258,7 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>PsychoPy自制</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X26" s="12" t="inlineStr">
@@ -5264,19 +5268,15 @@
       </c>
       <c r="Y26" s="12" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>Digit Span</t>
         </is>
       </c>
       <c r="Z26" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA26" s="12" t="inlineStr">
-        <is>
-          <t>Digit Span; Corsi; Stroop</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr"/>
       <c r="AB26" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AD26" s="12" t="inlineStr">
         <is>
-          <t>η²p=0.05(训练×年龄交互)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE26" s="12" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="AK26" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL26" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM26" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>CRI(认知储备指数)</t>
         </is>
       </c>
       <c r="AN26" s="14" t="inlineStr">
@@ -5336,35 +5336,35 @@
       </c>
       <c r="AO26" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Jaeggi</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
+          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
+          <t>BMC research notes</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -5373,22 +5373,16 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>183</v>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>88</v>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -5397,12 +5391,12 @@
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>GDS+GAD</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -5412,7 +5406,7 @@
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr">
@@ -5421,17 +5415,13 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="T27" s="11" t="inlineStr">
-        <is>
-          <t>2-10</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="U27" s="11" t="inlineStr">
         <is>
@@ -5445,7 +5435,7 @@
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet)</t>
+          <t>PsychoPy自制</t>
         </is>
       </c>
       <c r="X27" s="12" t="inlineStr">
@@ -5455,7 +5445,7 @@
       </c>
       <c r="Y27" s="12" t="inlineStr">
         <is>
-          <t>Reading Span; Symmetry Span</t>
+          <t>N-back (untrained level)</t>
         </is>
       </c>
       <c r="Z27" s="12" t="inlineStr">
@@ -5465,20 +5455,22 @@
       </c>
       <c r="AA27" s="12" t="inlineStr">
         <is>
-          <t>Letter Sets; Visual LTM</t>
+          <t>Digit Span; Corsi; Stroop</t>
         </is>
       </c>
       <c r="AB27" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC27" s="12" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD27" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²p=0.05(训练×年龄交互)</t>
         </is>
       </c>
       <c r="AE27" s="12" t="inlineStr">
@@ -5505,12 +5497,12 @@
       </c>
       <c r="AK27" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL27" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM27" s="14" t="inlineStr">
@@ -5525,58 +5517,68 @@
       </c>
       <c r="AO27" s="15" t="inlineStr">
         <is>
-          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>Jaeggi</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
+          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>大学</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="n">
-        <v>13.2</v>
+        <v>183</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>GDS+GAD</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
@@ -5591,7 +5593,7 @@
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>verbal n-back</t>
+          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
         </is>
       </c>
       <c r="Q28" s="11" t="inlineStr">
@@ -5600,14 +5602,16 @@
         </is>
       </c>
       <c r="R28" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S28" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T28" s="11" t="inlineStr">
         <is>
-          <t>2-4周</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="U28" s="11" t="inlineStr">
@@ -5622,7 +5626,7 @@
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(tablet)</t>
         </is>
       </c>
       <c r="X28" s="12" t="inlineStr">
@@ -5632,7 +5636,7 @@
       </c>
       <c r="Y28" s="12" t="inlineStr">
         <is>
-          <t>spatial n-back</t>
+          <t>Reading Span; Symmetry Span</t>
         </is>
       </c>
       <c r="Z28" s="12" t="inlineStr">
@@ -5642,18 +5646,16 @@
       </c>
       <c r="AA28" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence (Raven)</t>
+          <t>Letter Sets; Visual LTM</t>
         </is>
       </c>
       <c r="AB28" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC28" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC28" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="AD28" s="12" t="inlineStr">
         <is>
@@ -5674,7 +5676,7 @@
       <c r="AH28" s="13" t="inlineStr"/>
       <c r="AI28" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ28" s="14" t="inlineStr">
@@ -5684,17 +5686,17 @@
       </c>
       <c r="AK28" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL28" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM28" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN28" s="14" t="inlineStr">
@@ -5704,54 +5706,54 @@
       </c>
       <c r="AO28" s="15" t="inlineStr">
         <is>
-          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
+          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="10" t="inlineStr"/>
       <c r="L29" s="10" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -5765,12 +5767,12 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>verbal n-back</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
@@ -5779,13 +5781,15 @@
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S29" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="T29" s="11" t="n">
-        <v>3</v>
+      <c r="T29" s="11" t="inlineStr">
+        <is>
+          <t>2-4周</t>
+        </is>
       </c>
       <c r="U29" s="11" t="inlineStr">
         <is>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="Y29" s="12" t="inlineStr">
         <is>
-          <t>WM criterion task (CWMS)</t>
+          <t>spatial n-back</t>
         </is>
       </c>
       <c r="Z29" s="12" t="inlineStr">
@@ -5819,7 +5823,7 @@
       </c>
       <c r="AA29" s="12" t="inlineStr">
         <is>
-          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
+          <t>fluid intelligence (Raven)</t>
         </is>
       </c>
       <c r="AB29" s="12" t="inlineStr">
@@ -5834,12 +5838,12 @@
       </c>
       <c r="AD29" s="12" t="inlineStr">
         <is>
-          <t>d&gt;=0.8 (large effect)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE29" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF29" s="13" t="inlineStr">
@@ -5851,27 +5855,27 @@
       <c r="AH29" s="13" t="inlineStr"/>
       <c r="AI29" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ29" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK29" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL29" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM29" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN29" s="14" t="inlineStr">
@@ -5881,25 +5885,25 @@
       </c>
       <c r="AO29" s="15" t="inlineStr">
         <is>
-          <t>评估日常生活能力迁移效应</t>
+          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
+          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -5918,19 +5922,17 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K30" s="10" t="n">
-        <v>57</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K30" s="10" t="inlineStr"/>
       <c r="L30" s="10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -5988,7 +5990,7 @@
       </c>
       <c r="Y30" s="12" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>WM criterion task (CWMS)</t>
         </is>
       </c>
       <c r="Z30" s="12" t="inlineStr">
@@ -5998,22 +6000,22 @@
       </c>
       <c r="AA30" s="12" t="inlineStr">
         <is>
-          <t>Language comprehension; Cattell fluid intelligence</t>
+          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
         </is>
       </c>
       <c r="AB30" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC30" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD30" s="12" t="inlineStr">
         <is>
-          <t>η²=0.15-0.26 (transfer)</t>
+          <t>d&gt;=0.8 (large effect)</t>
         </is>
       </c>
       <c r="AE30" s="12" t="inlineStr">
@@ -6060,58 +6062,60 @@
       </c>
       <c r="AO30" s="15" t="inlineStr">
         <is>
-          <t>6个月随访；语言理解力迁移</t>
+          <t>评估日常生活能力迁移效应</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
+          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Neuroreport</t>
+          <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>69.7</v>
+        <v>69</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L31" s="10" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>10.5</v>
+      </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
@@ -6121,39 +6125,41 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>CACT (computer-assisted cognitive training)</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S31" s="11" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="S31" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T31" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>Maxmedica CACT</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X31" s="12" t="inlineStr">
@@ -6163,15 +6169,19 @@
       </c>
       <c r="Y31" s="12" t="inlineStr">
         <is>
-          <t>Verbal WM task; Digit span forward</t>
+          <t>WM updating task</t>
         </is>
       </c>
       <c r="Z31" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA31" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA31" s="12" t="inlineStr">
+        <is>
+          <t>Language comprehension; Cattell fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB31" s="12" t="inlineStr">
         <is>
           <t>是</t>
@@ -6179,12 +6189,12 @@
       </c>
       <c r="AC31" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD31" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²=0.15-0.26 (transfer)</t>
         </is>
       </c>
       <c r="AE31" s="12" t="inlineStr">
@@ -6231,56 +6241,58 @@
       </c>
       <c r="AO31" s="15" t="inlineStr">
         <is>
-          <t>tDCS联合CACT；anodal vs sham tDCS</t>
+          <t>6个月随访；语言理解力迁移</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
+          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Neuroreport</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K32" s="10" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>68</v>
+      </c>
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>MoCA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
@@ -6290,27 +6302,25 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>adaptive spatial n-back</t>
+          <t>CACT (computer-assisted cognitive training)</t>
         </is>
       </c>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R32" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S32" s="11" t="n">
-        <v>20</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S32" s="11" t="inlineStr"/>
       <c r="T32" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" s="11" t="inlineStr">
         <is>
@@ -6324,7 +6334,7 @@
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Maxmedica CACT</t>
         </is>
       </c>
       <c r="X32" s="12" t="inlineStr">
@@ -6334,7 +6344,7 @@
       </c>
       <c r="Y32" s="12" t="inlineStr">
         <is>
-          <t>WM composite score (5 tasks)</t>
+          <t>Verbal WM task; Digit span forward</t>
         </is>
       </c>
       <c r="Z32" s="12" t="inlineStr">
@@ -6345,12 +6355,12 @@
       <c r="AA32" s="12" t="inlineStr"/>
       <c r="AB32" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC32" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD32" s="12" t="inlineStr">
@@ -6360,7 +6370,7 @@
       </c>
       <c r="AE32" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF32" s="13" t="inlineStr">
@@ -6372,22 +6382,22 @@
       <c r="AH32" s="13" t="inlineStr"/>
       <c r="AI32" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ32" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK32" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL32" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM32" s="14" t="inlineStr">
@@ -6402,58 +6412,56 @@
       </c>
       <c r="AO32" s="15" t="inlineStr">
         <is>
-          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
+          <t>tDCS联合CACT；anodal vs sham tDCS</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>VK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
+          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>83.5</v>
+        <v>69.5</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" s="10" t="n">
-        <v>79</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="10" t="inlineStr"/>
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
@@ -6463,23 +6471,27 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>computer-assisted cognitive training (multi-domain)</t>
+          <t>adaptive spatial n-back</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R33" s="11" t="inlineStr"/>
-      <c r="S33" s="11" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="T33" s="11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
@@ -6488,7 +6500,7 @@
       </c>
       <c r="V33" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
@@ -6503,27 +6515,23 @@
       </c>
       <c r="Y33" s="12" t="inlineStr">
         <is>
-          <t>Primary WM; secondary WM (verbal/visual)</t>
+          <t>WM composite score (5 tasks)</t>
         </is>
       </c>
       <c r="Z33" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA33" s="12" t="inlineStr">
-        <is>
-          <t>Information processing speed; learning; interference tendency</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="inlineStr"/>
       <c r="AB33" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC33" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD33" s="12" t="inlineStr">
@@ -6533,7 +6541,7 @@
       </c>
       <c r="AE33" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF33" s="13" t="inlineStr">
@@ -6545,22 +6553,22 @@
       <c r="AH33" s="13" t="inlineStr"/>
       <c r="AI33" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ33" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK33" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL33" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM33" s="14" t="inlineStr">
@@ -6575,52 +6583,54 @@
       </c>
       <c r="AO33" s="15" t="inlineStr">
         <is>
-          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
+          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VK</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Novel television-based cognitive training improves working memory and executive function.</t>
+          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>70.5</v>
+        <v>83.5</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="K34" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>79</v>
+      </c>
       <c r="L34" s="10" t="inlineStr"/>
       <c r="M34" s="10" t="inlineStr">
         <is>
@@ -6634,27 +6644,27 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
+          <t>computer-assisted cognitive training (multi-domain)</t>
         </is>
       </c>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R34" s="11" t="n">
-        <v>25</v>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="inlineStr"/>
       <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="n">
+        <v>14</v>
+      </c>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -6664,7 +6674,7 @@
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>CogniFit</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X34" s="12" t="inlineStr">
@@ -6674,7 +6684,7 @@
       </c>
       <c r="Y34" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (validated)</t>
+          <t>Primary WM; secondary WM (verbal/visual)</t>
         </is>
       </c>
       <c r="Z34" s="12" t="inlineStr">
@@ -6684,17 +6694,17 @@
       </c>
       <c r="AA34" s="12" t="inlineStr">
         <is>
-          <t>Executive function tasks</t>
+          <t>Information processing speed; learning; interference tendency</t>
         </is>
       </c>
       <c r="AB34" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC34" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD34" s="12" t="inlineStr">
@@ -6746,35 +6756,35 @@
       </c>
       <c r="AO34" s="15" t="inlineStr">
         <is>
-          <t>互动电视（iTV）平台认知训练</t>
+          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Impact of working memory training on memory performance in old-old adults.</t>
+          <t>Novel television-based cognitive training improves working memory and executive function.</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -6783,13 +6793,13 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>80</v>
+        <v>70.5</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
@@ -6805,12 +6815,12 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>WM process-based training (visual/spatial)</t>
+          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
         </is>
       </c>
       <c r="Q35" s="11" t="inlineStr">
@@ -6819,14 +6829,10 @@
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="S35" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T35" s="11" t="n">
-        <v>12</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
       <c r="U35" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -6839,7 +6845,7 @@
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>CogniFit</t>
         </is>
       </c>
       <c r="X35" s="12" t="inlineStr">
@@ -6849,7 +6855,7 @@
       </c>
       <c r="Y35" s="12" t="inlineStr">
         <is>
-          <t>Visual WM (VLMT)</t>
+          <t>WM tasks (validated)</t>
         </is>
       </c>
       <c r="Z35" s="12" t="inlineStr">
@@ -6859,17 +6865,17 @@
       </c>
       <c r="AA35" s="12" t="inlineStr">
         <is>
-          <t>Visual episodic memory</t>
+          <t>Executive function tasks</t>
         </is>
       </c>
       <c r="AB35" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC35" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD35" s="12" t="inlineStr">
@@ -6921,35 +6927,35 @@
       </c>
       <c r="AO35" s="15" t="inlineStr">
         <is>
-          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
+          <t>互动电视（iTV）平台认知训练</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
+          <t>Impact of working memory training on memory performance in old-old adults.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -6958,13 +6964,13 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="10" t="inlineStr"/>
@@ -6980,12 +6986,12 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>adaptive verbal + spatial n-back</t>
+          <t>WM process-based training (visual/spatial)</t>
         </is>
       </c>
       <c r="Q36" s="11" t="inlineStr">
@@ -6994,13 +7000,13 @@
         </is>
       </c>
       <c r="R36" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="inlineStr">
-        <is>
-          <t>4-8周</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="S36" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T36" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="U36" s="11" t="inlineStr">
         <is>
@@ -7014,7 +7020,7 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>自制（居家在线）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X36" s="12" t="inlineStr">
@@ -7024,7 +7030,7 @@
       </c>
       <c r="Y36" s="12" t="inlineStr">
         <is>
-          <t>Digit span</t>
+          <t>Visual WM (VLMT)</t>
         </is>
       </c>
       <c r="Z36" s="12" t="inlineStr">
@@ -7034,17 +7040,17 @@
       </c>
       <c r="AA36" s="12" t="inlineStr">
         <is>
-          <t>Abstract relational reasoning</t>
+          <t>Visual episodic memory</t>
         </is>
       </c>
       <c r="AB36" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC36" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD36" s="12" t="inlineStr">
@@ -7054,7 +7060,7 @@
       </c>
       <c r="AE36" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF36" s="13" t="inlineStr">
@@ -7096,35 +7102,35 @@
       </c>
       <c r="AO36" s="15" t="inlineStr">
         <is>
-          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
+          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
+          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -7133,13 +7139,13 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>66</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
@@ -7160,7 +7166,7 @@
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>adaptive n-back</t>
+          <t>adaptive verbal + spatial n-back</t>
         </is>
       </c>
       <c r="Q37" s="11" t="inlineStr">
@@ -7169,11 +7175,13 @@
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="n">
-        <v>4</v>
+      <c r="T37" s="11" t="inlineStr">
+        <is>
+          <t>4-8周</t>
+        </is>
       </c>
       <c r="U37" s="11" t="inlineStr">
         <is>
@@ -7187,7 +7195,7 @@
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家在线）</t>
         </is>
       </c>
       <c r="X37" s="12" t="inlineStr">
@@ -7197,15 +7205,19 @@
       </c>
       <c r="Y37" s="12" t="inlineStr">
         <is>
-          <t>multimodal dual-task (visual+auditory)</t>
+          <t>Digit span</t>
         </is>
       </c>
       <c r="Z37" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA37" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="12" t="inlineStr">
+        <is>
+          <t>Abstract relational reasoning</t>
+        </is>
+      </c>
       <c r="AB37" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -7218,29 +7230,21 @@
       </c>
       <c r="AD37" s="12" t="inlineStr">
         <is>
-          <t>p&lt;0.05</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE37" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF37" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG37" s="13" t="inlineStr">
-        <is>
-          <t>fMRI</t>
-        </is>
-      </c>
-      <c r="AH37" s="13" t="inlineStr">
-        <is>
-          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG37" s="13" t="inlineStr"/>
+      <c r="AH37" s="13" t="inlineStr"/>
       <c r="AI37" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7273,17 +7277,17 @@
       </c>
       <c r="AO37" s="15" t="inlineStr">
         <is>
-          <t>双任务迁移；fMRI子研究；先导研究</t>
+          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -7291,17 +7295,17 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
+          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -7310,15 +7314,13 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="10" t="inlineStr"/>
@@ -7334,12 +7336,12 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>Visual and Spatial WM training</t>
+          <t>adaptive n-back</t>
         </is>
       </c>
       <c r="Q38" s="11" t="inlineStr">
@@ -7347,17 +7349,21 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R38" s="11" t="inlineStr"/>
+      <c r="R38" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
@@ -7372,7 +7378,7 @@
       </c>
       <c r="Y38" s="12" t="inlineStr">
         <is>
-          <t>Visual WM; Spatial WM</t>
+          <t>multimodal dual-task (visual+auditory)</t>
         </is>
       </c>
       <c r="Z38" s="12" t="inlineStr">
@@ -7383,44 +7389,52 @@
       <c r="AA38" s="12" t="inlineStr"/>
       <c r="AB38" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC38" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD38" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>p&lt;0.05</t>
         </is>
       </c>
       <c r="AE38" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF38" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG38" s="13" t="inlineStr"/>
-      <c r="AH38" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG38" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH38" s="13" t="inlineStr">
+        <is>
+          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
+        </is>
+      </c>
       <c r="AI38" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ38" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK38" s="14" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL38" s="14" t="inlineStr">
@@ -7440,35 +7454,35 @@
       </c>
       <c r="AO38" s="15" t="inlineStr">
         <is>
-          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
+          <t>双任务迁移；fMRI子研究；先导研究</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>JA</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
+          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Scientific reports</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -7477,13 +7491,15 @@
         </is>
       </c>
       <c r="H39" s="10" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>5.5</v>
+        <v>67</v>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
@@ -7499,12 +7515,12 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>commercial brain training app (multi-domain)</t>
+          <t>Visual and Spatial WM training</t>
         </is>
       </c>
       <c r="Q39" s="11" t="inlineStr">
@@ -7514,22 +7530,20 @@
       </c>
       <c r="R39" s="11" t="inlineStr"/>
       <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="n">
-        <v>12</v>
-      </c>
+      <c r="T39" s="11" t="inlineStr"/>
       <c r="U39" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V39" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>商业脑训练app</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X39" s="12" t="inlineStr">
@@ -7539,27 +7553,23 @@
       </c>
       <c r="Y39" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (trained domain)</t>
+          <t>Visual WM; Spatial WM</t>
         </is>
       </c>
       <c r="Z39" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA39" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; attention; language</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="12" t="inlineStr"/>
       <c r="AB39" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC39" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD39" s="12" t="inlineStr">
@@ -7569,7 +7579,7 @@
       </c>
       <c r="AE39" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF39" s="13" t="inlineStr">
@@ -7581,17 +7591,17 @@
       <c r="AH39" s="13" t="inlineStr"/>
       <c r="AI39" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ39" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK39" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AL39" s="14" t="inlineStr">
@@ -7611,35 +7621,35 @@
       </c>
       <c r="AO39" s="15" t="inlineStr">
         <is>
-          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
+          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
+          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -7648,15 +7658,13 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>70.56999999999999</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>5.5</v>
       </c>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
@@ -7672,12 +7680,12 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>Cogmed (adaptive WM training)</t>
+          <t>commercial brain training app (multi-domain)</t>
         </is>
       </c>
       <c r="Q40" s="11" t="inlineStr">
@@ -7685,14 +7693,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R40" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S40" s="11" t="n">
-        <v>40</v>
-      </c>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr"/>
       <c r="T40" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U40" s="11" t="inlineStr">
         <is>
@@ -7706,7 +7710,7 @@
       </c>
       <c r="W40" s="11" t="inlineStr">
         <is>
-          <t>Cogmed</t>
+          <t>商业脑训练app</t>
         </is>
       </c>
       <c r="X40" s="12" t="inlineStr">
@@ -7716,15 +7720,19 @@
       </c>
       <c r="Y40" s="12" t="inlineStr">
         <is>
-          <t>n-back (0-back, 1-back, 2-back)</t>
+          <t>WM tasks (trained domain)</t>
         </is>
       </c>
       <c r="Z40" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA40" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; attention; language</t>
+        </is>
+      </c>
       <c r="AB40" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -7742,24 +7750,16 @@
       </c>
       <c r="AE40" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF40" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG40" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH40" s="13" t="inlineStr">
-        <is>
-          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG40" s="13" t="inlineStr"/>
+      <c r="AH40" s="13" t="inlineStr"/>
       <c r="AI40" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7792,25 +7792,25 @@
       </c>
       <c r="AO40" s="15" t="inlineStr">
         <is>
-          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
+          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>An evaluation of a working memory training scheme in older adults.</t>
+          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -7829,13 +7829,15 @@
         </is>
       </c>
       <c r="H41" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>4</v>
+        <v>75.8</v>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K41" s="10" t="inlineStr"/>
       <c r="L41" s="10" t="inlineStr"/>
@@ -7851,12 +7853,12 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
+          <t>Cogmed (adaptive WM training)</t>
         </is>
       </c>
       <c r="Q41" s="11" t="inlineStr">
@@ -7864,8 +7866,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R41" s="11" t="inlineStr"/>
-      <c r="S41" s="11" t="inlineStr"/>
+      <c r="R41" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S41" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="T41" s="11" t="n">
         <v>5</v>
       </c>
@@ -7881,7 +7887,7 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>自制（在线）</t>
+          <t>Cogmed</t>
         </is>
       </c>
       <c r="X41" s="12" t="inlineStr">
@@ -7891,27 +7897,23 @@
       </c>
       <c r="Y41" s="12" t="inlineStr">
         <is>
-          <t>Auditory STM span; visuospatial STM</t>
+          <t>n-back (0-back, 1-back, 2-back)</t>
         </is>
       </c>
       <c r="Z41" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA41" s="12" t="inlineStr">
-        <is>
-          <t>Long-term episodic memory</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="inlineStr"/>
       <c r="AB41" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC41" s="12" t="inlineStr">
         <is>
-          <t>3;6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD41" s="12" t="inlineStr">
@@ -7926,11 +7928,19 @@
       </c>
       <c r="AF41" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG41" s="13" t="inlineStr"/>
-      <c r="AH41" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG41" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH41" s="13" t="inlineStr">
+        <is>
+          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
+        </is>
+      </c>
       <c r="AI41" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7938,7 +7948,7 @@
       </c>
       <c r="AJ41" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK41" s="14" t="inlineStr">
@@ -7963,25 +7973,25 @@
       </c>
       <c r="AO41" s="15" t="inlineStr">
         <is>
-          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
+          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
+          <t>An evaluation of a working memory training scheme in older adults.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -7991,7 +8001,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -8000,13 +8010,13 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>70.39</v>
+        <v>70</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
@@ -8022,12 +8032,12 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>computerized WM training (web-based)</t>
+          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
         </is>
       </c>
       <c r="Q42" s="11" t="inlineStr">
@@ -8038,7 +8048,7 @@
       <c r="R42" s="11" t="inlineStr"/>
       <c r="S42" s="11" t="inlineStr"/>
       <c r="T42" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U42" s="11" t="inlineStr">
         <is>
@@ -8052,7 +8062,7 @@
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制（在线）</t>
         </is>
       </c>
       <c r="X42" s="12" t="inlineStr">
@@ -8062,23 +8072,27 @@
       </c>
       <c r="Y42" s="12" t="inlineStr">
         <is>
-          <t>Self-perceived cognitive failures (CFQ)</t>
+          <t>Auditory STM span; visuospatial STM</t>
         </is>
       </c>
       <c r="Z42" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA42" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="12" t="inlineStr">
+        <is>
+          <t>Long-term episodic memory</t>
+        </is>
+      </c>
       <c r="AB42" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC42" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>3;6</t>
         </is>
       </c>
       <c r="AD42" s="12" t="inlineStr">
@@ -8105,7 +8119,7 @@
       </c>
       <c r="AJ42" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK42" s="14" t="inlineStr">
@@ -8130,35 +8144,35 @@
       </c>
       <c r="AO42" s="15" t="inlineStr">
         <is>
-          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
+          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
+          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>BMC geriatrics</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -8167,13 +8181,13 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>69</v>
+        <v>70.39</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>3.5</v>
+        <v>4.54</v>
       </c>
       <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr"/>
@@ -8189,12 +8203,12 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>computerized WM training (web-based)</t>
         </is>
       </c>
       <c r="Q43" s="11" t="inlineStr">
@@ -8202,14 +8216,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R43" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S43" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr"/>
       <c r="T43" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U43" s="11" t="inlineStr">
         <is>
@@ -8223,7 +8233,7 @@
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X43" s="12" t="inlineStr">
@@ -8233,7 +8243,7 @@
       </c>
       <c r="Y43" s="12" t="inlineStr">
         <is>
-          <t>n-back task</t>
+          <t>Self-perceived cognitive failures (CFQ)</t>
         </is>
       </c>
       <c r="Z43" s="12" t="inlineStr">
@@ -8244,39 +8254,31 @@
       <c r="AA43" s="12" t="inlineStr"/>
       <c r="AB43" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC43" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD43" s="12" t="inlineStr">
         <is>
-          <t>Cohen's d medium-large</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE43" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF43" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG43" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH43" s="13" t="inlineStr">
-        <is>
-          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG43" s="13" t="inlineStr"/>
+      <c r="AH43" s="13" t="inlineStr"/>
       <c r="AI43" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8309,35 +8311,35 @@
       </c>
       <c r="AO43" s="15" t="inlineStr">
         <is>
-          <t>先导研究；ERP神经相关；6个月随访</t>
+          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
+          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>BMC geriatrics</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -8346,15 +8348,13 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>69</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>3.5</v>
       </c>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>web-based WM or logic &amp; planning training</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q44" s="11" t="inlineStr">
@@ -8383,10 +8383,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R44" s="11" t="inlineStr"/>
-      <c r="S44" s="11" t="inlineStr"/>
+      <c r="R44" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S44" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T44" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U44" s="11" t="inlineStr">
         <is>
@@ -8400,7 +8404,7 @@
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X44" s="12" t="inlineStr">
@@ -8410,46 +8414,50 @@
       </c>
       <c r="Y44" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>n-back task</t>
         </is>
       </c>
       <c r="Z44" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA44" s="12" t="inlineStr">
-        <is>
-          <t>Planning; reasoning; processing speed; verbal fluency</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr"/>
       <c r="AB44" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC44" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD44" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>Cohen's d medium-large</t>
         </is>
       </c>
       <c r="AE44" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF44" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG44" s="13" t="inlineStr"/>
-      <c r="AH44" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG44" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH44" s="13" t="inlineStr">
+        <is>
+          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
+        </is>
+      </c>
       <c r="AI44" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8482,35 +8490,35 @@
       </c>
       <c r="AO44" s="15" t="inlineStr">
         <is>
-          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
+          <t>先导研究；ERP神经相关；6个月随访</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
+          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Gerontology</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -8519,13 +8527,15 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>4</v>
+        <v>70.5</v>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
@@ -8541,24 +8551,24 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
-          <t>WM span tasks (5 tasks)</t>
+          <t>web-based WM or logic &amp; planning training</t>
         </is>
       </c>
       <c r="Q45" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R45" s="11" t="n">
-        <v>10</v>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="inlineStr"/>
       <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="U45" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -8571,7 +8581,7 @@
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X45" s="12" t="inlineStr">
@@ -8581,7 +8591,7 @@
       </c>
       <c r="Y45" s="12" t="inlineStr">
         <is>
-          <t>trained WM tasks</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z45" s="12" t="inlineStr">
@@ -8591,7 +8601,7 @@
       </c>
       <c r="AA45" s="12" t="inlineStr">
         <is>
-          <t>Executive functions (2 tests)</t>
+          <t>Planning; reasoning; processing speed; verbal fluency</t>
         </is>
       </c>
       <c r="AB45" s="12" t="inlineStr">
@@ -8606,7 +8616,7 @@
       </c>
       <c r="AD45" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.8 (trained tasks)</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE45" s="12" t="inlineStr">
@@ -8623,17 +8633,17 @@
       <c r="AH45" s="13" t="inlineStr"/>
       <c r="AI45" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ45" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK45" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL45" s="14" t="inlineStr">
@@ -8653,35 +8663,35 @@
       </c>
       <c r="AO45" s="15" t="inlineStr">
         <is>
-          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
+          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
+          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Gerontology</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -8690,13 +8700,13 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>66</v>
+        <v>86.8</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" s="10" t="inlineStr"/>
       <c r="L46" s="10" t="inlineStr"/>
@@ -8712,20 +8722,22 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
-          <t>memory updating task (predictable vs unpredictable)</t>
+          <t>WM span tasks (5 tasks)</t>
         </is>
       </c>
       <c r="Q46" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R46" s="11" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S46" s="11" t="inlineStr"/>
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
@@ -8750,7 +8762,7 @@
       </c>
       <c r="Y46" s="12" t="inlineStr">
         <is>
-          <t>WM updating task (novel)</t>
+          <t>trained WM tasks</t>
         </is>
       </c>
       <c r="Z46" s="12" t="inlineStr">
@@ -8760,27 +8772,27 @@
       </c>
       <c r="AA46" s="12" t="inlineStr">
         <is>
-          <t>Episodic memory</t>
+          <t>Executive functions (2 tests)</t>
         </is>
       </c>
       <c r="AB46" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC46" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD46" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.5-0.8 (trained tasks)</t>
         </is>
       </c>
       <c r="AE46" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF46" s="13" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="AH46" s="13" t="inlineStr"/>
       <c r="AI46" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ46" s="14" t="inlineStr">
@@ -8802,7 +8814,7 @@
       </c>
       <c r="AK46" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL46" s="14" t="inlineStr">
@@ -8822,30 +8834,30 @@
       </c>
       <c r="AO46" s="15" t="inlineStr">
         <is>
-          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
+          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
+          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Aging brain</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -8859,17 +8871,13 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
@@ -8885,12 +8893,12 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
         <is>
-          <t>n-back + metacognitive program (EngAge)</t>
+          <t>memory updating task (predictable vs unpredictable)</t>
         </is>
       </c>
       <c r="Q47" s="11" t="inlineStr">
@@ -8898,9 +8906,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R47" s="11" t="n">
-        <v>20</v>
-      </c>
+      <c r="R47" s="11" t="inlineStr"/>
       <c r="S47" s="11" t="inlineStr"/>
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
@@ -8915,7 +8921,7 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>自制（居家）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X47" s="12" t="inlineStr">
@@ -8925,7 +8931,7 @@
       </c>
       <c r="Y47" s="12" t="inlineStr">
         <is>
-          <t>non-trained WM measures</t>
+          <t>WM updating task (novel)</t>
         </is>
       </c>
       <c r="Z47" s="12" t="inlineStr">
@@ -8935,7 +8941,7 @@
       </c>
       <c r="AA47" s="12" t="inlineStr">
         <is>
-          <t>Inhibitory control; episodic memory</t>
+          <t>Episodic memory</t>
         </is>
       </c>
       <c r="AB47" s="12" t="inlineStr">
@@ -8945,7 +8951,7 @@
       </c>
       <c r="AC47" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AD47" s="12" t="inlineStr">
@@ -8955,7 +8961,7 @@
       </c>
       <c r="AE47" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF47" s="13" t="inlineStr">
@@ -8972,7 +8978,7 @@
       </c>
       <c r="AJ47" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK47" s="14" t="inlineStr">
@@ -8997,35 +9003,35 @@
       </c>
       <c r="AO47" s="15" t="inlineStr">
         <is>
-          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
+          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
+          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Aging brain</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -9034,18 +9040,20 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="I48" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>4</v>
+        <v>119</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K48" s="10" t="inlineStr"/>
-      <c r="L48" s="10" t="n">
-        <v>11</v>
-      </c>
+      <c r="L48" s="10" t="inlineStr"/>
       <c r="M48" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9058,12 +9066,12 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
+          <t>n-back + metacognitive program (EngAge)</t>
         </is>
       </c>
       <c r="Q48" s="11" t="inlineStr">
@@ -9072,14 +9080,10 @@
         </is>
       </c>
       <c r="R48" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S48" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T48" s="11" t="n">
-        <v>3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -9092,7 +9096,7 @@
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家）</t>
         </is>
       </c>
       <c r="X48" s="12" t="inlineStr">
@@ -9102,7 +9106,7 @@
       </c>
       <c r="Y48" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM; STM tasks</t>
+          <t>non-trained WM measures</t>
         </is>
       </c>
       <c r="Z48" s="12" t="inlineStr">
@@ -9112,7 +9116,7 @@
       </c>
       <c r="AA48" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence; processing speed; inhibitory measures</t>
+          <t>Inhibitory control; episodic memory</t>
         </is>
       </c>
       <c r="AB48" s="12" t="inlineStr">
@@ -9144,27 +9148,27 @@
       <c r="AH48" s="13" t="inlineStr"/>
       <c r="AI48" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ48" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK48" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL48" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM48" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN48" s="14" t="inlineStr">
@@ -9174,35 +9178,35 @@
       </c>
       <c r="AO48" s="15" t="inlineStr">
         <is>
-          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
+          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
+          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in neurology</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -9211,16 +9215,18 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9233,12 +9239,12 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P49" s="11" t="inlineStr">
         <is>
-          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
+          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
         </is>
       </c>
       <c r="Q49" s="11" t="inlineStr">
@@ -9247,22 +9253,22 @@
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S49" s="11" t="n">
         <v>30</v>
       </c>
       <c r="T49" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
@@ -9277,7 +9283,7 @@
       </c>
       <c r="Y49" s="12" t="inlineStr">
         <is>
-          <t>non-verbal logical reasoning</t>
+          <t>visuospatial WM; STM tasks</t>
         </is>
       </c>
       <c r="Z49" s="12" t="inlineStr">
@@ -9287,7 +9293,7 @@
       </c>
       <c r="AA49" s="12" t="inlineStr">
         <is>
-          <t>Attention; memory; executive functions</t>
+          <t>fluid intelligence; processing speed; inhibitory measures</t>
         </is>
       </c>
       <c r="AB49" s="12" t="inlineStr">
@@ -9297,7 +9303,7 @@
       </c>
       <c r="AC49" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD49" s="12" t="inlineStr">
@@ -9307,7 +9313,7 @@
       </c>
       <c r="AE49" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF49" s="13" t="inlineStr">
@@ -9319,7 +9325,7 @@
       <c r="AH49" s="13" t="inlineStr"/>
       <c r="AI49" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ49" s="14" t="inlineStr">
@@ -9329,7 +9335,7 @@
       </c>
       <c r="AK49" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL49" s="14" t="inlineStr">
@@ -9339,7 +9345,7 @@
       </c>
       <c r="AM49" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN49" s="14" t="inlineStr">
@@ -9349,35 +9355,35 @@
       </c>
       <c r="AO49" s="15" t="inlineStr">
         <is>
-          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
+          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
+          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
+          <t>Frontiers in neurology</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -9386,13 +9392,13 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>70</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="K50" s="10" t="inlineStr"/>
       <c r="L50" s="10" t="inlineStr"/>
@@ -9413,7 +9419,7 @@
       </c>
       <c r="P50" s="11" t="inlineStr">
         <is>
-          <t>letter updating task</t>
+          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
         </is>
       </c>
       <c r="Q50" s="11" t="inlineStr">
@@ -9422,13 +9428,13 @@
         </is>
       </c>
       <c r="R50" s="11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S50" s="11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T50" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U50" s="11" t="inlineStr">
         <is>
@@ -9437,7 +9443,7 @@
       </c>
       <c r="V50" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>TMS</t>
         </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
@@ -9452,7 +9458,7 @@
       </c>
       <c r="Y50" s="12" t="inlineStr">
         <is>
-          <t>n-back (near transfer)</t>
+          <t>non-verbal logical reasoning</t>
         </is>
       </c>
       <c r="Z50" s="12" t="inlineStr">
@@ -9462,7 +9468,7 @@
       </c>
       <c r="AA50" s="12" t="inlineStr">
         <is>
-          <t>executive/memory tasks</t>
+          <t>Attention; memory; executive functions</t>
         </is>
       </c>
       <c r="AB50" s="12" t="inlineStr">
@@ -9472,7 +9478,7 @@
       </c>
       <c r="AC50" s="12" t="inlineStr">
         <is>
-          <t>1;7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD50" s="12" t="inlineStr">
@@ -9509,7 +9515,7 @@
       </c>
       <c r="AL50" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM50" s="14" t="inlineStr">
@@ -9524,35 +9530,35 @@
       </c>
       <c r="AO50" s="15" t="inlineStr">
         <is>
-          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
+          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
+          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -9561,13 +9567,13 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>487</v>
+        <v>56</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
@@ -9583,12 +9589,12 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>syllable span + auditory discrimination (IMPACT program)</t>
+          <t>letter updating task</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
@@ -9596,22 +9602,28 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R51" s="11" t="inlineStr"/>
-      <c r="S51" s="11" t="inlineStr"/>
-      <c r="T51" s="11" t="inlineStr"/>
+      <c r="R51" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S51" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>Posit Science (IMPACT)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X51" s="12" t="inlineStr">
@@ -9621,7 +9633,7 @@
       </c>
       <c r="Y51" s="12" t="inlineStr">
         <is>
-          <t>WM factor score</t>
+          <t>n-back (near transfer)</t>
         </is>
       </c>
       <c r="Z51" s="12" t="inlineStr">
@@ -9631,17 +9643,17 @@
       </c>
       <c r="AA51" s="12" t="inlineStr">
         <is>
-          <t>List memory; text memory</t>
+          <t>executive/memory tasks</t>
         </is>
       </c>
       <c r="AB51" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC51" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1;7</t>
         </is>
       </c>
       <c r="AD51" s="12" t="inlineStr">
@@ -9651,7 +9663,7 @@
       </c>
       <c r="AE51" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF51" s="13" t="inlineStr">
@@ -9678,12 +9690,12 @@
       </c>
       <c r="AL51" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM51" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN51" s="14" t="inlineStr">
@@ -9693,35 +9705,35 @@
       </c>
       <c r="AO51" s="15" t="inlineStr">
         <is>
-          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
+          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
+          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -9730,13 +9742,13 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>24</v>
+        <v>487</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="K52" s="10" t="inlineStr"/>
       <c r="L52" s="10" t="inlineStr"/>
@@ -9757,7 +9769,7 @@
       </c>
       <c r="P52" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>syllable span + auditory discrimination (IMPACT program)</t>
         </is>
       </c>
       <c r="Q52" s="11" t="inlineStr">
@@ -9765,15 +9777,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R52" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S52" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T52" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -9786,7 +9792,7 @@
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Posit Science (IMPACT)</t>
         </is>
       </c>
       <c r="X52" s="12" t="inlineStr">
@@ -9796,28 +9802,32 @@
       </c>
       <c r="Y52" s="12" t="inlineStr">
         <is>
-          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
+          <t>WM factor score</t>
         </is>
       </c>
       <c r="Z52" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA52" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr">
+        <is>
+          <t>List memory; text memory</t>
+        </is>
+      </c>
       <c r="AB52" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC52" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD52" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.9</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE52" s="12" t="inlineStr">
@@ -9827,19 +9837,11 @@
       </c>
       <c r="AF52" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG52" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH52" s="13" t="inlineStr">
-        <is>
-          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG52" s="13" t="inlineStr"/>
+      <c r="AH52" s="13" t="inlineStr"/>
       <c r="AI52" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9847,7 +9849,7 @@
       </c>
       <c r="AJ52" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK52" s="14" t="inlineStr">
@@ -9857,12 +9859,12 @@
       </c>
       <c r="AL52" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM52" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN52" s="14" t="inlineStr">
@@ -9872,35 +9874,35 @@
       </c>
       <c r="AO52" s="15" t="inlineStr">
         <is>
-          <t>静息态EEG；额叶振荡活动；先导研究</t>
+          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
+          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -9909,13 +9911,13 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>69.58</v>
+        <v>69</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>7.04</v>
+        <v>3.5</v>
       </c>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
@@ -9931,12 +9933,12 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>single-domain WM (n-back) or multidomain EF training</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q53" s="11" t="inlineStr">
@@ -9944,10 +9946,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr"/>
-      <c r="S53" s="11" t="inlineStr"/>
+      <c r="R53" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S53" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T53" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U53" s="11" t="inlineStr">
         <is>
@@ -9971,46 +9977,50 @@
       </c>
       <c r="Y53" s="12" t="inlineStr">
         <is>
-          <t>n-back; global EF accuracy</t>
+          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
         </is>
       </c>
       <c r="Z53" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA53" s="12" t="inlineStr">
-        <is>
-          <t>Prospective memory (Virtual Week); fluid intelligence</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="inlineStr"/>
       <c r="AB53" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC53" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD53" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>d=0.5-0.9</t>
         </is>
       </c>
       <c r="AE53" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF53" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG53" s="13" t="inlineStr"/>
-      <c r="AH53" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG53" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH53" s="13" t="inlineStr">
+        <is>
+          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
+        </is>
+      </c>
       <c r="AI53" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10043,35 +10053,35 @@
       </c>
       <c r="AO53" s="15" t="inlineStr">
         <is>
-          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
+          <t>静息态EEG；额叶振荡活动；先导研究</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Cantarella</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
+          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Psychologie Française</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -10080,13 +10090,13 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>69</v>
+        <v>69.58</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>4</v>
+        <v>7.04</v>
       </c>
       <c r="K54" s="10" t="inlineStr"/>
       <c r="L54" s="10" t="inlineStr"/>
@@ -10102,12 +10112,12 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
         <is>
-          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
+          <t>single-domain WM (n-back) or multidomain EF training</t>
         </is>
       </c>
       <c r="Q54" s="11" t="inlineStr">
@@ -10115,14 +10125,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R54" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S54" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr"/>
       <c r="T54" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U54" s="11" t="inlineStr">
         <is>
@@ -10146,7 +10152,7 @@
       </c>
       <c r="Y54" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM criterion task</t>
+          <t>n-back; global EF accuracy</t>
         </is>
       </c>
       <c r="Z54" s="12" t="inlineStr">
@@ -10156,7 +10162,7 @@
       </c>
       <c r="AA54" s="12" t="inlineStr">
         <is>
-          <t>verbal WM; visuospatial STM; reasoning</t>
+          <t>Prospective memory (Virtual Week); fluid intelligence</t>
         </is>
       </c>
       <c r="AB54" s="12" t="inlineStr">
@@ -10171,7 +10177,7 @@
       </c>
       <c r="AD54" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE54" s="12" t="inlineStr">
@@ -10218,35 +10224,35 @@
       </c>
       <c r="AO54" s="15" t="inlineStr">
         <is>
-          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
+          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Cantarella</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Impact of strategy use during N-Back training in older adults</t>
+          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Journal of Cognitive Psychology</t>
+          <t>Psychologie Française</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -10255,13 +10261,13 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>61.86</v>
+        <v>69</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>5.37</v>
+        <v>4</v>
       </c>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
@@ -10277,12 +10283,12 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
         <is>
-          <t>n-back (strategy vs no strategy)</t>
+          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
         </is>
       </c>
       <c r="Q55" s="11" t="inlineStr">
@@ -10290,9 +10296,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R55" s="11" t="inlineStr"/>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
+      <c r="R55" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S55" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T55" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U55" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -10315,7 +10327,7 @@
       </c>
       <c r="Y55" s="12" t="inlineStr">
         <is>
-          <t>n-back variant</t>
+          <t>visuospatial WM criterion task</t>
         </is>
       </c>
       <c r="Z55" s="12" t="inlineStr">
@@ -10325,7 +10337,7 @@
       </c>
       <c r="AA55" s="12" t="inlineStr">
         <is>
-          <t>P300 transfer measures</t>
+          <t>verbal WM; visuospatial STM; reasoning</t>
         </is>
       </c>
       <c r="AB55" s="12" t="inlineStr">
@@ -10350,19 +10362,11 @@
       </c>
       <c r="AF55" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG55" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH55" s="13" t="inlineStr">
-        <is>
-          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG55" s="13" t="inlineStr"/>
+      <c r="AH55" s="13" t="inlineStr"/>
       <c r="AI55" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10370,7 +10374,7 @@
       </c>
       <c r="AJ55" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK55" s="14" t="inlineStr">
@@ -10395,35 +10399,35 @@
       </c>
       <c r="AO55" s="15" t="inlineStr">
         <is>
-          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
+          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
+          <t>Impact of strategy use during N-Back training in older adults</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Applied Cognitive Psychology</t>
+          <t>Journal of Cognitive Psychology</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -10432,13 +10436,13 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>66.84999999999999</v>
+        <v>61.86</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>3.99</v>
+        <v>5.37</v>
       </c>
       <c r="K56" s="10" t="inlineStr"/>
       <c r="L56" s="10" t="inlineStr"/>
@@ -10454,12 +10458,12 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
         <is>
-          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
+          <t>n-back (strategy vs no strategy)</t>
         </is>
       </c>
       <c r="Q56" s="11" t="inlineStr">
@@ -10492,7 +10496,7 @@
       </c>
       <c r="Y56" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>n-back variant</t>
         </is>
       </c>
       <c r="Z56" s="12" t="inlineStr">
@@ -10502,7 +10506,7 @@
       </c>
       <c r="AA56" s="12" t="inlineStr">
         <is>
-          <t>Short-term memory; processing speed; reasoning</t>
+          <t>P300 transfer measures</t>
         </is>
       </c>
       <c r="AB56" s="12" t="inlineStr">
@@ -10522,16 +10526,24 @@
       </c>
       <c r="AE56" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF56" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG56" s="13" t="inlineStr"/>
-      <c r="AH56" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG56" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH56" s="13" t="inlineStr">
+        <is>
+          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
+        </is>
+      </c>
       <c r="AI56" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10539,7 +10551,7 @@
       </c>
       <c r="AJ56" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK56" s="14" t="inlineStr">
@@ -10564,35 +10576,35 @@
       </c>
       <c r="AO56" s="15" t="inlineStr">
         <is>
-          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
+          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Chai</t>
+          <t>Lange</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+          <t>Applied Cognitive Psychology</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -10601,17 +10613,15 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>70</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K57" s="10" t="n">
-        <v>100</v>
-      </c>
+        <v>3.99</v>
+      </c>
+      <c r="K57" s="10" t="inlineStr"/>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr">
         <is>
@@ -10625,12 +10635,12 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
         <is>
-          <t>adaptive WM updating (numerical updating + 1-back)</t>
+          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
         </is>
       </c>
       <c r="Q57" s="11" t="inlineStr">
@@ -10638,9 +10648,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R57" s="11" t="n">
-        <v>20</v>
-      </c>
+      <c r="R57" s="11" t="inlineStr"/>
       <c r="S57" s="11" t="inlineStr"/>
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
@@ -10665,7 +10673,7 @@
       </c>
       <c r="Y57" s="12" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z57" s="12" t="inlineStr">
@@ -10675,7 +10683,7 @@
       </c>
       <c r="AA57" s="12" t="inlineStr">
         <is>
-          <t>Cognitive reappraisal (emotion regulation task)</t>
+          <t>Short-term memory; processing speed; reasoning</t>
         </is>
       </c>
       <c r="AB57" s="12" t="inlineStr">
@@ -10695,7 +10703,7 @@
       </c>
       <c r="AE57" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF57" s="13" t="inlineStr">
@@ -10736,6 +10744,179 @@
         </is>
       </c>
       <c r="AO57" s="15" t="inlineStr">
+        <is>
+          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Chai</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="I58" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L58" s="10" t="inlineStr"/>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O58" s="11" t="inlineStr">
+        <is>
+          <t>n-back</t>
+        </is>
+      </c>
+      <c r="P58" s="11" t="inlineStr">
+        <is>
+          <t>adaptive WM updating (numerical updating + 1-back)</t>
+        </is>
+      </c>
+      <c r="Q58" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R58" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>自制</t>
+        </is>
+      </c>
+      <c r="X58" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y58" s="12" t="inlineStr">
+        <is>
+          <t>WM updating task</t>
+        </is>
+      </c>
+      <c r="Z58" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="12" t="inlineStr">
+        <is>
+          <t>Cognitive reappraisal (emotion regulation task)</t>
+        </is>
+      </c>
+      <c r="AB58" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC58" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AD58" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE58" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF58" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG58" s="13" t="inlineStr"/>
+      <c r="AH58" s="13" t="inlineStr"/>
+      <c r="AI58" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ58" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK58" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL58" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM58" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AN58" s="14" t="inlineStr">
+        <is>
+          <t>期刊</t>
+        </is>
+      </c>
+      <c r="AO58" s="15" t="inlineStr">
         <is>
           <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局</t>
         </is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO58"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -963,251 +963,249 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lommen</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>The effect of cognitive training in older adults: be aware of CRUNCH.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Borella</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Is working memory training in older adults sensitive to music?</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Psychological research</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>社区</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I3" t="n">
-        <v>67.93000000000001</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K3" t="n">
-        <v>50</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>未报告(7级量表)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>MMSE</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2-back; numerical updating; alpha-span</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>15-20</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>≤30天</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="H3" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>span</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>Categorization WM Span (verbal)</t>
+        </is>
+      </c>
+      <c r="Q3" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R3" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" s="11" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Backward Digit Span</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Faces &amp; Names; Shopping List</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>高/低</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>低&gt;高</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>教育(7级量表)</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>自制(Borella protocol)</t>
+        </is>
+      </c>
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
+        <is>
+          <t>Backward Corsi blocks</t>
+        </is>
+      </c>
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>Verbal fluency; Raven matrices; Culture Fair</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AE3" s="12" t="inlineStr">
+        <is>
+          <t>正向迁移</t>
+        </is>
+      </c>
+      <c r="AF3" s="13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG3" s="13" t="inlineStr"/>
+      <c r="AH3" s="13" t="inlineStr"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="AJ3" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AK3" s="14" t="inlineStr">
+        <is>
+          <t>未检验</t>
+        </is>
+      </c>
+      <c r="AL3" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AM3" s="14" t="inlineStr">
+        <is>
+          <t>教育年限</t>
+        </is>
+      </c>
+      <c r="AN3" s="14" t="inlineStr">
         <is>
           <t>期刊</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>按基线EF高/低分组分析调节效应</t>
+      <c r="AO3" s="15" t="inlineStr">
+        <is>
+          <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Salminen</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Is working memory training in older adults sensitive to music?</t>
+          <t>Age-specific differences of dual n-back training.</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>社区/大学</t>
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>69.23999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>13.84</v>
+        <v>56</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥28</t>
         </is>
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>Dual n-back (auditory-visual)</t>
         </is>
       </c>
       <c r="Q4" s="11" t="inlineStr">
@@ -1216,13 +1214,15 @@
         </is>
       </c>
       <c r="R4" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="T4" s="11" t="n">
-        <v>2</v>
+        <v>50</v>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>3-6</t>
+        </is>
       </c>
       <c r="U4" s="11" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="W4" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X4" s="12" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="Y4" s="12" t="inlineStr">
         <is>
-          <t>Backward Corsi blocks</t>
+          <t>AV n-back (untrained stimuli)</t>
         </is>
       </c>
       <c r="Z4" s="12" t="inlineStr">
@@ -1256,16 +1256,18 @@
       </c>
       <c r="AA4" s="12" t="inlineStr">
         <is>
-          <t>Verbal fluency; Raven matrices; Culture Fair</t>
+          <t>Task switching; Attentional blink (T2)</t>
         </is>
       </c>
       <c r="AB4" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC4" s="12" t="n">
-        <v>6</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD4" s="12" t="inlineStr">
         <is>
@@ -1274,7 +1276,7 @@
       </c>
       <c r="AE4" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF4" s="13" t="inlineStr">
@@ -1291,22 +1293,22 @@
       </c>
       <c r="AJ4" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK4" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL4" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM4" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN4" s="14" t="inlineStr">
@@ -1316,103 +1318,97 @@
       </c>
       <c r="AO4" s="15" t="inlineStr">
         <is>
-          <t>4组：Mozart/Albinoni/White noise/Active control；音乐为背景条件非干预</t>
+          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Salminen</t>
+          <t>Tays</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Age-specific differences of dual n-back training.</t>
+          <t>Longitudinal neurostimulation in older adults improves working memory.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>社区/大学</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>64.8</v>
+        <v>64.38</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>5.1</v>
+        <v>5.08</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>16.78</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>≥28</t>
-        </is>
+      <c r="N5" s="10" t="n">
+        <v>28.48</v>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (auditory-visual)</t>
+          <t>Verbal WM; Visuospatial WM; OSpan</t>
         </is>
       </c>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" s="11" t="inlineStr">
-        <is>
-          <t>3-6</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="U5" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V5" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W5" s="11" t="inlineStr">
@@ -1427,7 +1423,7 @@
       </c>
       <c r="Y5" s="12" t="inlineStr">
         <is>
-          <t>AV n-back (untrained stimuli)</t>
+          <t>Spatial 2-back</t>
         </is>
       </c>
       <c r="Z5" s="12" t="inlineStr">
@@ -1437,18 +1433,16 @@
       </c>
       <c r="AA5" s="12" t="inlineStr">
         <is>
-          <t>Task switching; Attentional blink (T2)</t>
+          <t>Digit span; Stroop</t>
         </is>
       </c>
       <c r="AB5" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC5" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AD5" s="12" t="inlineStr">
         <is>
@@ -1457,7 +1451,7 @@
       </c>
       <c r="AE5" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF5" s="13" t="inlineStr">
@@ -1474,22 +1468,22 @@
       </c>
       <c r="AJ5" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK5" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL5" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM5" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="AN5" s="14" t="inlineStr">
@@ -1499,35 +1493,35 @@
       </c>
       <c r="AO5" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值24.4岁)对比；老年组训练增益小于年轻组</t>
+          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Tays</t>
+          <t>Vesterinen</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Longitudinal neurostimulation in older adults improves working memory.</t>
+          <t>N-back training and transfer effects revealed by behavioral responses and EEG.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Brain and behavior</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1536,60 +1530,66 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>5.08</v>
+        <v>63.11</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K6" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>16.78</v>
+        <v>54</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>28.48</v>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>Verbal WM; Visuospatial WM; OSpan</t>
+          <t>N-back (adaptive)</t>
         </is>
       </c>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R6" s="11" t="n">
         <v>10</v>
       </c>
       <c r="S6" s="11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="T6" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W6" s="11" t="inlineStr">
@@ -1604,26 +1604,24 @@
       </c>
       <c r="Y6" s="12" t="inlineStr">
         <is>
-          <t>Spatial 2-back</t>
+          <t>N-back (untrained level)</t>
         </is>
       </c>
       <c r="Z6" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA6" s="12" t="inlineStr">
-        <is>
-          <t>Digit span; Stroop</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr"/>
       <c r="AB6" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC6" s="12" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD6" s="12" t="inlineStr">
         <is>
@@ -1632,16 +1630,24 @@
       </c>
       <c r="AE6" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF6" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr"/>
-      <c r="AH6" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG6" s="13" t="inlineStr">
+        <is>
+          <t>EEG/ERP</t>
+        </is>
+      </c>
+      <c r="AH6" s="13" t="inlineStr">
+        <is>
+          <t>训练后P300振幅变化与任务难度相关</t>
+        </is>
+      </c>
       <c r="AI6" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1664,7 +1670,7 @@
       </c>
       <c r="AM6" s="14" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN6" s="14" t="inlineStr">
@@ -1674,35 +1680,35 @@
       </c>
       <c r="AO6" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：1.5mA/10min，4组(PFC/PPC/交替/sham)；长期随访仅active tDCS组维持</t>
+          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Vesterinen</t>
+          <t>Brum</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>N-back training and transfer effects revealed by behavioral responses and EEG.</t>
+          <t>Verbal working memory training in older adults: an investigation of dose response.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Brain and behavior</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1711,27 +1717,25 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>67.17</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>9.5</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>CERAD+CDT</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -1741,12 +1745,12 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>Categorization WM Span (verbal, Borella protocol)</t>
         </is>
       </c>
       <c r="Q7" s="11" t="inlineStr">
@@ -1755,13 +1759,13 @@
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" s="11" t="inlineStr">
         <is>
@@ -1775,7 +1779,7 @@
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X7" s="12" t="inlineStr">
@@ -1785,24 +1789,26 @@
       </c>
       <c r="Y7" s="12" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>Letter-Number Sequencing; Visuospatial WM</t>
         </is>
       </c>
       <c r="Z7" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA7" s="12" t="inlineStr">
+        <is>
+          <t>Stroop; Processing speed; Fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB7" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC7" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="AD7" s="12" t="inlineStr">
         <is>
@@ -1811,24 +1817,16 @@
       </c>
       <c r="AE7" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF7" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG7" s="13" t="inlineStr">
-        <is>
-          <t>EEG/ERP</t>
-        </is>
-      </c>
-      <c r="AH7" s="13" t="inlineStr">
-        <is>
-          <t>训练后P300振幅变化与任务难度相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG7" s="13" t="inlineStr"/>
+      <c r="AH7" s="13" t="inlineStr"/>
       <c r="AI7" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -1851,7 +1849,7 @@
       </c>
       <c r="AM7" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN7" s="14" t="inlineStr">
@@ -1861,35 +1859,35 @@
       </c>
       <c r="AO7" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.15岁)对比；EEG P300成分分析</t>
+          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Brum</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Verbal working memory training in older adults: an investigation of dose response.</t>
+          <t>Gamified working memory intervention enhances prefrontal neurocognitive plasticity during aging.</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1898,40 +1896,46 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>67.17</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>4.4</v>
+        <v>76</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n">
-        <v>9.5</v>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>≥6年</t>
+        </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>CERAD+CDT</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, Borella protocol)</t>
+          <t>Gamified N-back (fruit-cutting game)</t>
         </is>
       </c>
       <c r="Q8" s="11" t="inlineStr">
@@ -1940,13 +1944,13 @@
         </is>
       </c>
       <c r="R8" s="11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S8" s="11" t="n">
         <v>60</v>
       </c>
       <c r="T8" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U8" s="11" t="inlineStr">
         <is>
@@ -1960,7 +1964,7 @@
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制(JavaScript游戏)</t>
         </is>
       </c>
       <c r="X8" s="12" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="Y8" s="12" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; Visuospatial WM</t>
+          <t>WM tasks (untrained)</t>
         </is>
       </c>
       <c r="Z8" s="12" t="inlineStr">
@@ -1980,7 +1984,7 @@
       </c>
       <c r="AA8" s="12" t="inlineStr">
         <is>
-          <t>Stroop; Processing speed; Fluid intelligence</t>
+          <t>Inhibitory control; Visuospatial; Episodic memory</t>
         </is>
       </c>
       <c r="AB8" s="12" t="inlineStr">
@@ -2003,11 +2007,19 @@
       </c>
       <c r="AF8" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr"/>
-      <c r="AH8" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG8" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI+rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH8" s="13" t="inlineStr">
+        <is>
+          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
+        </is>
+      </c>
       <c r="AI8" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2030,7 +2042,7 @@
       </c>
       <c r="AM8" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN8" s="14" t="inlineStr">
@@ -2040,25 +2052,25 @@
       </c>
       <c r="AO8" s="15" t="inlineStr">
         <is>
-          <t>含Study2(6sessions, N=50)；本行为Study1数据；巴西葡语版Borella protocol</t>
+          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Guye</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Gamified working memory intervention enhances prefrontal neurocognitive plasticity during aging.</t>
+          <t>Working memory training in older adults: Bayesian evidence supporting the absence of transfer.</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -2068,7 +2080,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -2077,46 +2089,40 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>142</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>48</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>≥6年</t>
+          <t>未报告(0-7量表)</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MMSE+GDS</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>≥26(MMSE)</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Gamified N-back (fruit-cutting game)</t>
+          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
         </is>
       </c>
       <c r="Q9" s="11" t="inlineStr">
@@ -2125,13 +2131,15 @@
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="S9" s="11" t="n">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T9" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9" s="11" t="inlineStr">
         <is>
@@ -2145,7 +2153,7 @@
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>自制(JavaScript游戏)</t>
+          <t>自制(von Bastian protocol)</t>
         </is>
       </c>
       <c r="X9" s="12" t="inlineStr">
@@ -2155,7 +2163,7 @@
       </c>
       <c r="Y9" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>Visuospatial WM (3 tasks)</t>
         </is>
       </c>
       <c r="Z9" s="12" t="inlineStr">
@@ -2165,16 +2173,18 @@
       </c>
       <c r="AA9" s="12" t="inlineStr">
         <is>
-          <t>Inhibitory control; Visuospatial; Episodic memory</t>
+          <t>Fluid intelligence; Inhibition; Shifting</t>
         </is>
       </c>
       <c r="AB9" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC9" s="12" t="n">
-        <v>6</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD9" s="12" t="inlineStr">
         <is>
@@ -2183,24 +2193,16 @@
       </c>
       <c r="AE9" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF9" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG9" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(sMRI+rs-fMRI)</t>
-        </is>
-      </c>
-      <c r="AH9" s="13" t="inlineStr">
-        <is>
-          <t>左额极皮层厚度增加，功能同质性降低，与左下颞回连接减弱</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG9" s="13" t="inlineStr"/>
+      <c r="AH9" s="13" t="inlineStr"/>
       <c r="AI9" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2223,7 +2225,7 @@
       </c>
       <c r="AM9" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育(0-7量表)</t>
         </is>
       </c>
       <c r="AN9" s="14" t="inlineStr">
@@ -2233,35 +2235,35 @@
       </c>
       <c r="AO9" s="15" t="inlineStr">
         <is>
-          <t>游戏化WM干预；含结构MRI和静息态fMRI；6月随访</t>
+          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Guye</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in older adults: Bayesian evidence supporting the absence of transfer.</t>
+          <t>Working Memory Training Coupled With Transcranial Direct Current Stimulation in Older Adults: A Randomized Controlled Experiment.</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Spain/Portugal</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2270,40 +2272,40 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>70.34999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>3.66</v>
+        <v>5.92</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>未报告(0-7量表)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>MMSE+GDS</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>≥26(MMSE)</t>
+          <t>≥26</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>Heterogeneous WM tasks (spatial, binding, updating)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q10" s="11" t="inlineStr">
@@ -2312,15 +2314,17 @@
         </is>
       </c>
       <c r="R10" s="11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
-          <t>30-45</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="n">
-        <v>5</v>
+          <t>20+20</t>
+        </is>
+      </c>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="U10" s="11" t="inlineStr">
         <is>
@@ -2329,12 +2333,12 @@
       </c>
       <c r="V10" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
-          <t>自制(von Bastian protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X10" s="12" t="inlineStr">
@@ -2344,7 +2348,7 @@
       </c>
       <c r="Y10" s="12" t="inlineStr">
         <is>
-          <t>Visuospatial WM (3 tasks)</t>
+          <t>Digit Span</t>
         </is>
       </c>
       <c r="Z10" s="12" t="inlineStr">
@@ -2354,18 +2358,16 @@
       </c>
       <c r="AA10" s="12" t="inlineStr">
         <is>
-          <t>Fluid intelligence; Inhibition; Shifting</t>
+          <t>Raven APM (RAPM)</t>
         </is>
       </c>
       <c r="AB10" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC10" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>0.5</v>
       </c>
       <c r="AD10" s="12" t="inlineStr">
         <is>
@@ -2374,7 +2376,7 @@
       </c>
       <c r="AE10" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF10" s="13" t="inlineStr">
@@ -2386,17 +2388,17 @@
       <c r="AH10" s="13" t="inlineStr"/>
       <c r="AI10" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>低</t>
         </is>
       </c>
       <c r="AJ10" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK10" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL10" s="14" t="inlineStr">
@@ -2406,7 +2408,7 @@
       </c>
       <c r="AM10" s="14" t="inlineStr">
         <is>
-          <t>教育(0-7量表)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN10" s="14" t="inlineStr">
@@ -2416,25 +2418,25 @@
       </c>
       <c r="AO10" s="15" t="inlineStr">
         <is>
-          <t>Bayesian LMM分析；大样本(N=142)；结论：无近迁移无远迁移</t>
+          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Rudner</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training Coupled With Transcranial Direct Current Stimulation in Older Adults: A Randomized Controlled Experiment.</t>
+          <t>Working Memory Training and Speech in Noise Comprehension in Older Adults.</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -2444,7 +2446,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Spain/Portugal</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -2453,16 +2455,16 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>68.2</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>5.92</v>
+        <v>3.77</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -2476,17 +2478,17 @@
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>≥26</t>
+          <t>≥23</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Reading Span (Cogmed)</t>
         </is>
       </c>
       <c r="Q11" s="11" t="inlineStr">
@@ -2495,18 +2497,16 @@
         </is>
       </c>
       <c r="R11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="T11" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>20+20</t>
-        </is>
-      </c>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="U11" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V11" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Cogmed</t>
         </is>
       </c>
       <c r="X11" s="12" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="Y11" s="12" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>Reading Span (untrained version)</t>
         </is>
       </c>
       <c r="Z11" s="12" t="inlineStr">
@@ -2539,16 +2539,18 @@
       </c>
       <c r="AA11" s="12" t="inlineStr">
         <is>
-          <t>Raven APM (RAPM)</t>
+          <t>Speech-in-noise comprehension</t>
         </is>
       </c>
       <c r="AB11" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC11" s="12" t="n">
-        <v>0.5</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD11" s="12" t="inlineStr">
         <is>
@@ -2557,7 +2559,7 @@
       </c>
       <c r="AE11" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF11" s="13" t="inlineStr">
@@ -2569,17 +2571,17 @@
       <c r="AH11" s="13" t="inlineStr"/>
       <c r="AI11" s="14" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ11" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK11" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL11" s="14" t="inlineStr">
@@ -2599,17 +2601,17 @@
       </c>
       <c r="AO11" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：2mA/20min/DLPFC；3组(atDCS+WMT/stDCS+WMT/double-sham)；低认知表现者获益更多</t>
+          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Rudner</t>
+          <t>Berryhill</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -2617,17 +2619,17 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Speech in Noise Comprehension in Older Adults.</t>
+          <t>Older Adults Improve on Everyday Tasks after Working Memory Training and Neurostimulation.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Brain stimulation</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -2636,71 +2638,69 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>64.95999999999999</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>3.77</v>
+        <v>69.03</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K12" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>54</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>15.58</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>MoCA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>≥23</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>Reading Span (Cogmed)</t>
+          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
         </is>
       </c>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R12" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>30-60</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="S12" s="11" t="n">
+        <v>45</v>
       </c>
       <c r="T12" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U12" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
-          <t>Cogmed</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X12" s="12" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Y12" s="12" t="inlineStr">
         <is>
-          <t>Reading Span (untrained version)</t>
+          <t>Letter-Number Sequencing; 2-back</t>
         </is>
       </c>
       <c r="Z12" s="12" t="inlineStr">
@@ -2720,36 +2720,42 @@
       </c>
       <c r="AA12" s="12" t="inlineStr">
         <is>
-          <t>Speech-in-noise comprehension</t>
+          <t>WCPA (everyday scheduling); Road Craft Test</t>
         </is>
       </c>
       <c r="AB12" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC12" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AD12" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²=0.073(far transfer)</t>
         </is>
       </c>
       <c r="AE12" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF12" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG12" s="13" t="inlineStr"/>
-      <c r="AH12" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG12" s="13" t="inlineStr">
+        <is>
+          <t>fNIRS</t>
+        </is>
+      </c>
+      <c r="AH12" s="13" t="inlineStr">
+        <is>
+          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
+        </is>
+      </c>
       <c r="AI12" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2772,7 +2778,7 @@
       </c>
       <c r="AM12" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN12" s="14" t="inlineStr">
@@ -2782,35 +2788,35 @@
       </c>
       <c r="AO12" s="15" t="inlineStr">
         <is>
-          <t>交叉设计：两组各完成adaptive+placebo Cogmed各25sessions；远迁移至言语噪声理解</t>
+          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>12</v>
+      <c r="A13" s="9" t="n">
+        <v>13</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Berryhill</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>2016</v>
+          <t>Matysiak</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>2019</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Older Adults Improve on Everyday Tasks after Working Memory Training and Neurostimulation.</t>
+          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Brain stimulation</t>
+          <t>Frontiers in Aging Neuroscience</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -2819,10 +2825,12 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>69.03</v>
+        <v>83</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
@@ -2830,10 +2838,12 @@
         </is>
       </c>
       <c r="K13" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>15.58</v>
+        <v>65</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -2842,41 +2852,43 @@
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>≥27</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>Subtract-2 task; Visuospatial WM (location/visual recall)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q13" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R13" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T13" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="S13" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T13" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="U13" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
@@ -2891,7 +2903,7 @@
       </c>
       <c r="Y13" s="12" t="inlineStr">
         <is>
-          <t>Letter-Number Sequencing; 2-back</t>
+          <t>OSPAN; WM tasks</t>
         </is>
       </c>
       <c r="Z13" s="12" t="inlineStr">
@@ -2901,20 +2913,22 @@
       </c>
       <c r="AA13" s="12" t="inlineStr">
         <is>
-          <t>WCPA (everyday scheduling); Road Craft Test</t>
+          <t>Processing speed; Fluid intelligence</t>
         </is>
       </c>
       <c r="AB13" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC13" s="12" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD13" s="12" t="inlineStr">
         <is>
-          <t>η²=0.073(far transfer)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE13" s="12" t="inlineStr">
@@ -2924,27 +2938,19 @@
       </c>
       <c r="AF13" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG13" s="13" t="inlineStr">
-        <is>
-          <t>fNIRS</t>
-        </is>
-      </c>
-      <c r="AH13" s="13" t="inlineStr">
-        <is>
-          <t>2mA tDCS组前额叶激活变化与远迁移相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG13" s="13" t="inlineStr"/>
+      <c r="AH13" s="13" t="inlineStr"/>
       <c r="AI13" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ13" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK13" s="14" t="inlineStr">
@@ -2969,35 +2975,35 @@
       </c>
       <c r="AO13" s="15" t="inlineStr">
         <is>
-          <t>tDCS参数：1mA/2mA/sham，15min，右PFC(F4)；2mA组远迁移显著优于sham</t>
+          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="9" t="n">
-        <v>13</v>
+      <c r="A14" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Matysiak</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>2019</v>
+          <t>Pergher</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>2021</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Capacity as a Predictor of Cognitive Training Efficacy in the Elderly Population.</t>
+          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in Aging Neuroscience</t>
+          <t>Neural plasticity</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -3006,70 +3012,62 @@
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4.65</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>14.48</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>≥27</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Visual Object Memory Task (VOMT)</t>
         </is>
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R14" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="S14" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="T14" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
@@ -3084,19 +3082,15 @@
       </c>
       <c r="Y14" s="12" t="inlineStr">
         <is>
-          <t>OSPAN; WM tasks</t>
+          <t>VOMT (untrained stimuli)</t>
         </is>
       </c>
       <c r="Z14" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA14" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; Fluid intelligence</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr"/>
       <c r="AB14" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -3119,19 +3113,27 @@
       </c>
       <c r="AF14" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG14" s="13" t="inlineStr"/>
-      <c r="AH14" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG14" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(rs-fMRI)</t>
+        </is>
+      </c>
+      <c r="AH14" s="13" t="inlineStr">
+        <is>
+          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
+        </is>
+      </c>
       <c r="AI14" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ14" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK14" s="14" t="inlineStr">
@@ -3156,35 +3158,35 @@
       </c>
       <c r="AO14" s="15" t="inlineStr">
         <is>
-          <t>入组≥60岁，均值未直接报告；基线WM能力作为主要调节变量；波兰华沙社区</t>
+          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Cognitive Aftereffects of Acute tDCS Coupled with Cognitive Training: An fMRI Study in Healthy Seniors.</t>
+          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Neural plasticity</t>
+          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -3193,23 +3195,29 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>68.84</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>4.65</v>
+        <v>32</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>14.48</v>
+        <v>50</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -3219,41 +3227,41 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>Visual Object Memory Task (VOMT)</t>
+          <t>Categorization WM Span (verbal, modified)</t>
         </is>
       </c>
       <c r="Q15" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V15" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X15" s="12" t="inlineStr">
@@ -3263,24 +3271,26 @@
       </c>
       <c r="Y15" s="12" t="inlineStr">
         <is>
-          <t>VOMT (untrained stimuli)</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z15" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA15" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>TIADL (everyday functioning); EPT</t>
+        </is>
+      </c>
       <c r="AB15" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC15" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="AD15" s="12" t="inlineStr">
         <is>
@@ -3294,19 +3304,11 @@
       </c>
       <c r="AF15" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG15" s="13" t="inlineStr">
-        <is>
-          <t>fMRI(rs-fMRI)</t>
-        </is>
-      </c>
-      <c r="AH15" s="13" t="inlineStr">
-        <is>
-          <t>tDCS调节静息态功能连接，与WM训练效果相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG15" s="13" t="inlineStr"/>
+      <c r="AH15" s="13" t="inlineStr"/>
       <c r="AI15" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -3329,7 +3331,7 @@
       </c>
       <c r="AM15" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN15" s="14" t="inlineStr">
@@ -3339,35 +3341,35 @@
       </c>
       <c r="AO15" s="15" t="inlineStr">
         <is>
-          <t>交叉设计：2种tDCS蒙太奇+sham；急性单次tDCS+WM训练；含rs-fMRI</t>
+          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Improving Everyday Functioning in the Old-Old with Working Memory Training.</t>
+          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>The American journal of geriatric psychiatry : official journal of the American Association for Geriatric Psychiatry</t>
+          <t>Journal of visualized experiments : JoVE</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -3376,20 +3378,20 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>85</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>66.7</v>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
       </c>
-      <c r="K16" s="10" t="n">
-        <v>50</v>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
@@ -3398,22 +3400,22 @@
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal, modified)</t>
+          <t>Dual n-back (adaptive)</t>
         </is>
       </c>
       <c r="Q16" s="11" t="inlineStr">
@@ -3422,13 +3424,13 @@
         </is>
       </c>
       <c r="R16" s="11" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="S16" s="11" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="T16" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U16" s="11" t="inlineStr">
         <is>
@@ -3442,7 +3444,7 @@
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X16" s="12" t="inlineStr">
@@ -3452,7 +3454,7 @@
       </c>
       <c r="Y16" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>WM tasks (untrained)</t>
         </is>
       </c>
       <c r="Z16" s="12" t="inlineStr">
@@ -3462,16 +3464,18 @@
       </c>
       <c r="AA16" s="12" t="inlineStr">
         <is>
-          <t>TIADL (everyday functioning); EPT</t>
+          <t>Processing speed; Executive function</t>
         </is>
       </c>
       <c r="AB16" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC16" s="12" t="n">
-        <v>9</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD16" s="12" t="inlineStr">
         <is>
@@ -3512,7 +3516,7 @@
       </c>
       <c r="AM16" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN16" s="14" t="inlineStr">
@@ -3522,13 +3526,13 @@
       </c>
       <c r="AO16" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-85岁)；年龄范围未报告均值；9月随访；日常功能迁移</t>
+          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
@@ -3536,16 +3540,16 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Older Participants: A Control Group Training Regimen and Initial Intellectual Functioning Assessment.</t>
+          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Journal of visualized experiments : JoVE</t>
+          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -3559,25 +3563,19 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>66.06999999999999</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>16.14</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -3586,7 +3584,7 @@
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -3596,7 +3594,7 @@
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>Dual n-back (adaptive)</t>
+          <t>Adaptive n-back (0-5 back)</t>
         </is>
       </c>
       <c r="Q17" s="11" t="inlineStr">
@@ -3605,13 +3603,13 @@
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S17" s="11" t="n">
         <v>45</v>
       </c>
       <c r="T17" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U17" s="11" t="inlineStr">
         <is>
@@ -3635,7 +3633,7 @@
       </c>
       <c r="Y17" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (untrained)</t>
+          <t>Digit Span (backward)</t>
         </is>
       </c>
       <c r="Z17" s="12" t="inlineStr">
@@ -3645,7 +3643,7 @@
       </c>
       <c r="AA17" s="12" t="inlineStr">
         <is>
-          <t>Processing speed; Executive function</t>
+          <t>CERAD episodic memory; Processing speed (LPS)</t>
         </is>
       </c>
       <c r="AB17" s="12" t="inlineStr">
@@ -3660,7 +3658,7 @@
       </c>
       <c r="AD17" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.78(教育组间)</t>
         </is>
       </c>
       <c r="AE17" s="12" t="inlineStr">
@@ -3682,22 +3680,22 @@
       </c>
       <c r="AJ17" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK17" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL17" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM17" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN17" s="14" t="inlineStr">
@@ -3707,35 +3705,35 @@
       </c>
       <c r="AO17" s="15" t="inlineStr">
         <is>
-          <t>JoVE方法论文，详细描述训练流程；含实际结果数据(N=85)</t>
+          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Borella</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Working memory training improvements and gains in non-trained cognitive tasks in young and older adults.</t>
+          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Neuropsychology, development, and cognition. Section B, Aging, neuropsychology and cognition</t>
+          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -3744,38 +3742,46 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>16.14</v>
+        <v>36</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>SVAMA</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>Adaptive n-back (0-5 back)</t>
+          <t>Categorization WM Span (verbal)</t>
         </is>
       </c>
       <c r="Q18" s="11" t="inlineStr">
@@ -3784,13 +3790,13 @@
         </is>
       </c>
       <c r="R18" s="11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S18" s="11" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="T18" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U18" s="11" t="inlineStr">
         <is>
@@ -3804,7 +3810,7 @@
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(Borella protocol)</t>
         </is>
       </c>
       <c r="X18" s="12" t="inlineStr">
@@ -3814,7 +3820,7 @@
       </c>
       <c r="Y18" s="12" t="inlineStr">
         <is>
-          <t>Digit Span (backward)</t>
+          <t>Dot Matrix (visuospatial WM)</t>
         </is>
       </c>
       <c r="Z18" s="12" t="inlineStr">
@@ -3824,27 +3830,25 @@
       </c>
       <c r="AA18" s="12" t="inlineStr">
         <is>
-          <t>CERAD episodic memory; Processing speed (LPS)</t>
+          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
         </is>
       </c>
       <c r="AB18" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC18" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>8</v>
       </c>
       <c r="AD18" s="12" t="inlineStr">
         <is>
-          <t>d=0.78(教育组间)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE18" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF18" s="13" t="inlineStr">
@@ -3861,22 +3865,22 @@
       </c>
       <c r="AJ18" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK18" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL18" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM18" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>词汇测试</t>
         </is>
       </c>
       <c r="AN18" s="14" t="inlineStr">
@@ -3886,83 +3890,75 @@
       </c>
       <c r="AO18" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值25.93岁)对比；老年组训练增益显著小于年轻组</t>
+          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Borella</t>
+          <t>Olivetti</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Working memory training in old age: an examination of transfer and maintenance effects.</t>
+          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Archives of clinical neuropsychology : the official journal of the National Academy of Neuropsychologists</t>
+          <t>Cognitive processing</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院/社区</t>
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>11.9</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>SVAMA</t>
+          <t>MMSE+CDT</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥26(MMSE)</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>Categorization WM Span (verbal)</t>
+          <t>N-back (0-2 back, adaptive)</t>
         </is>
       </c>
       <c r="Q19" s="11" t="inlineStr">
@@ -3971,13 +3967,15 @@
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" s="11" t="n">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
       </c>
       <c r="T19" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U19" s="11" t="inlineStr">
         <is>
@@ -3991,7 +3989,7 @@
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>自制(Borella protocol)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X19" s="12" t="inlineStr">
@@ -4001,30 +3999,28 @@
       </c>
       <c r="Y19" s="12" t="inlineStr">
         <is>
-          <t>Dot Matrix (visuospatial WM)</t>
+          <t>Corsi Block; Digit Span</t>
         </is>
       </c>
       <c r="Z19" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA19" s="12" t="inlineStr">
-        <is>
-          <t>Short-term memory; Reasoning; Inhibition; Processing speed</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr"/>
       <c r="AB19" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC19" s="12" t="n">
-        <v>8</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD19" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=2.21(近迁移)</t>
         </is>
       </c>
       <c r="AE19" s="12" t="inlineStr">
@@ -4061,7 +4057,7 @@
       </c>
       <c r="AM19" s="14" t="inlineStr">
         <is>
-          <t>词汇测试</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN19" s="14" t="inlineStr">
@@ -4071,92 +4067,92 @@
       </c>
       <c r="AO19" s="15" t="inlineStr">
         <is>
-          <t>old-old样本(75-87岁)；年龄范围未报告均值(估算约81岁)；8月随访维持效应</t>
+          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Olivetti</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Feasibility of using a computer-assisted working memory training program for healthy older women.</t>
+          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Cognitive processing</t>
+          <t>International journal of aging &amp; human development</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>医院/社区</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>68.40000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>11.9</v>
+        <v>58</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>MMSE+CDT</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>≥26(MMSE)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>N-back (0-2 back, adaptive)</t>
+          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
         </is>
       </c>
       <c r="Q20" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R20" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+      <c r="S20" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="T20" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U20" s="11" t="inlineStr">
         <is>
@@ -4180,15 +4176,19 @@
       </c>
       <c r="Y20" s="12" t="inlineStr">
         <is>
-          <t>Corsi Block; Digit Span</t>
+          <t>Spatial WM (untrained)</t>
         </is>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA20" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>Reasoning; IADL (everyday function)</t>
+        </is>
+      </c>
       <c r="AB20" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="AD20" s="12" t="inlineStr">
         <is>
-          <t>d=2.21(近迁移)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE20" s="12" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AM20" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN20" s="14" t="inlineStr">
@@ -4248,30 +4248,30 @@
       </c>
       <c r="AO20" s="15" t="inlineStr">
         <is>
-          <t>全女性样本；伊朗波斯语版；小样本(N=20)；效应量大(d=2.21)</t>
+          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Heinzel</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>The Effects of Cognitive Training on Cognitive Abilities and Everyday Function: A 10-Week Randomized Controlled Trial.</t>
+          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>International journal of aging &amp; human development</t>
+          <t>GeroScience</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -4285,21 +4285,19 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>68.55</v>
+        <v>71</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>5.74</v>
+        <v>4.6</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -4318,22 +4316,22 @@
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>Spatial WM; Numerical WM; Reasoning tasks</t>
+          <t>Multidomain cognitive training (WM+processing speed)</t>
         </is>
       </c>
       <c r="Q21" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="T21" s="11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U21" s="11" t="inlineStr">
         <is>
@@ -4347,7 +4345,7 @@
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(tablet-based)</t>
         </is>
       </c>
       <c r="X21" s="12" t="inlineStr">
@@ -4357,19 +4355,15 @@
       </c>
       <c r="Y21" s="12" t="inlineStr">
         <is>
-          <t>Spatial WM (untrained)</t>
+          <t>WM tasks (proximal)</t>
         </is>
       </c>
       <c r="Z21" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA21" s="12" t="inlineStr">
-        <is>
-          <t>Reasoning; IADL (everyday function)</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA21" s="12" t="inlineStr"/>
       <c r="AB21" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -4387,29 +4381,37 @@
       </c>
       <c r="AE21" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF21" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG21" s="13" t="inlineStr"/>
-      <c r="AH21" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG21" s="13" t="inlineStr">
+        <is>
+          <t>fMRI(sMRI)</t>
+        </is>
+      </c>
+      <c r="AH21" s="13" t="inlineStr">
+        <is>
+          <t>白质高信号负荷高者训练获益更少</t>
+        </is>
+      </c>
       <c r="AI21" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ21" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK21" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(低WMH获益更多)</t>
         </is>
       </c>
       <c r="AL21" s="14" t="inlineStr">
@@ -4419,7 +4421,7 @@
       </c>
       <c r="AM21" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN21" s="14" t="inlineStr">
@@ -4429,35 +4431,35 @@
       </c>
       <c r="AO21" s="15" t="inlineStr">
         <is>
-          <t>含日常功能结局(IADL)；训练内容包含推理任务，干预较宽泛</t>
+          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Heinzel</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Higher white matter hyperintensity load adversely affects pre-post proximal cognitive training performance in healthy older adults.</t>
+          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>GeroScience</t>
+          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -4466,19 +4468,27 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>16.3</v>
+        <v>30</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -4492,12 +4502,12 @@
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>Multidomain cognitive training (WM+processing speed)</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q22" s="11" t="inlineStr">
@@ -4506,17 +4516,17 @@
         </is>
       </c>
       <c r="R22" s="11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S22" s="11" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="T22" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -4526,7 +4536,7 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet-based)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X22" s="12" t="inlineStr">
@@ -4536,7 +4546,7 @@
       </c>
       <c r="Y22" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (proximal)</t>
+          <t>Listening Span</t>
         </is>
       </c>
       <c r="Z22" s="12" t="inlineStr">
@@ -4572,12 +4582,12 @@
       </c>
       <c r="AG22" s="13" t="inlineStr">
         <is>
-          <t>fMRI(sMRI)</t>
+          <t>fMRI</t>
         </is>
       </c>
       <c r="AH22" s="13" t="inlineStr">
         <is>
-          <t>白质高信号负荷高者训练获益更少</t>
+          <t>训练前类年轻脑激活模式预测更大训练获益</t>
         </is>
       </c>
       <c r="AI22" s="14" t="inlineStr">
@@ -4592,7 +4602,7 @@
       </c>
       <c r="AK22" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WMH获益更多)</t>
+          <t>高&gt;低(类年轻激活者获益更多)</t>
         </is>
       </c>
       <c r="AL22" s="14" t="inlineStr">
@@ -4602,7 +4612,7 @@
       </c>
       <c r="AM22" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN22" s="14" t="inlineStr">
@@ -4612,59 +4622,53 @@
       </c>
       <c r="AO22" s="15" t="inlineStr">
         <is>
-          <t>白质高信号(WMH)作为调节变量；高WMH负荷者训练获益受损；含MRI</t>
+          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Tagliabue</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Youth-like brain activation linked with greater cognitive training gains in older adults: Insights from the ACTOP study.</t>
+          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Cortex; a journal devoted to the study of the nervous system and behavior</t>
+          <t>Attention, perception &amp; psychophysics</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>社区(在线)</t>
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>104</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>48</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -4683,12 +4687,12 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>DMTS (delayed match-to-sample); Enumeration</t>
         </is>
       </c>
       <c r="Q23" s="11" t="inlineStr">
@@ -4697,17 +4701,17 @@
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="T23" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U23" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr">
@@ -4717,7 +4721,7 @@
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制(在线)</t>
         </is>
       </c>
       <c r="X23" s="12" t="inlineStr">
@@ -4727,7 +4731,7 @@
       </c>
       <c r="Y23" s="12" t="inlineStr">
         <is>
-          <t>Listening Span</t>
+          <t>DMTS (visuospatial WM, k值)</t>
         </is>
       </c>
       <c r="Z23" s="12" t="inlineStr">
@@ -4738,13 +4742,11 @@
       <c r="AA23" s="12" t="inlineStr"/>
       <c r="AB23" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC23" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="AD23" s="12" t="inlineStr">
         <is>
@@ -4758,19 +4760,11 @@
       </c>
       <c r="AF23" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG23" s="13" t="inlineStr">
-        <is>
-          <t>fMRI</t>
-        </is>
-      </c>
-      <c r="AH23" s="13" t="inlineStr">
-        <is>
-          <t>训练前类年轻脑激活模式预测更大训练获益</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG23" s="13" t="inlineStr"/>
+      <c r="AH23" s="13" t="inlineStr"/>
       <c r="AI23" s="14" t="inlineStr">
         <is>
           <t>高/低</t>
@@ -4783,7 +4777,7 @@
       </c>
       <c r="AK23" s="14" t="inlineStr">
         <is>
-          <t>高&gt;低(类年轻激活者获益更多)</t>
+          <t>低&gt;高(低WM基线者获益更多)</t>
         </is>
       </c>
       <c r="AL23" s="14" t="inlineStr">
@@ -4793,7 +4787,7 @@
       </c>
       <c r="AM23" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN23" s="14" t="inlineStr">
@@ -4803,93 +4797,93 @@
       </c>
       <c r="AO23" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(20-35岁)对比；脑激活模式作为调节变量；ACTOP研究</t>
+          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Tagliabue</t>
+          <t>Zinke</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Training attentive individuation leads to visuo-spatial working memory improvement in low-performing older adults: An online study.</t>
+          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Attention, perception &amp; psychophysics</t>
+          <t>Developmental psychology</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>社区(在线)</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>68.2</v>
+        <v>77.2</v>
       </c>
       <c r="J24" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>MMST</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+        </is>
+      </c>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="O24" s="11" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>DMTS (delayed match-to-sample); Enumeration</t>
-        </is>
-      </c>
-      <c r="Q24" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R24" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S24" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T24" s="11" t="n">
-        <v>2</v>
-      </c>
       <c r="U24" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -4902,7 +4896,7 @@
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
-          <t>自制(在线)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X24" s="12" t="inlineStr">
@@ -4912,22 +4906,26 @@
       </c>
       <c r="Y24" s="12" t="inlineStr">
         <is>
-          <t>DMTS (visuospatial WM, k值)</t>
+          <t>Verbal WM (untrained)</t>
         </is>
       </c>
       <c r="Z24" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA24" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; Reasoning</t>
+        </is>
+      </c>
       <c r="AB24" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="AC24" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AD24" s="12" t="inlineStr">
         <is>
@@ -4958,17 +4956,17 @@
       </c>
       <c r="AK24" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低WM基线者获益更多)</t>
+          <t>低&gt;高(低基线者近迁移更大)</t>
         </is>
       </c>
       <c r="AL24" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM24" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN24" s="14" t="inlineStr">
@@ -4978,30 +4976,30 @@
       </c>
       <c r="AO24" s="15" t="inlineStr">
         <is>
-          <t>在线研究；视觉注意个体化训练改善空间WM；低基线WM者获益更多；3月随访</t>
+          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Zinke</t>
+          <t>Schmicker</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Working memory training and transfer in older adults: effects of age, baseline performance, and training gains.</t>
+          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Developmental psychology</t>
+          <t>Current aging science</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -5015,16 +5013,18 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>77.2</v>
+        <v>80.5</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>80</v>
+        <v>6.4</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>MMST</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>K-ABC spatial WM; Subtract-2; Tower of London</t>
+          <t>N-back (adaptive)</t>
         </is>
       </c>
       <c r="Q25" s="11" t="inlineStr">
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T25" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U25" s="11" t="inlineStr">
         <is>
@@ -5087,26 +5087,24 @@
       </c>
       <c r="Y25" s="12" t="inlineStr">
         <is>
-          <t>Verbal WM (untrained)</t>
+          <t>Digit Span</t>
         </is>
       </c>
       <c r="Z25" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA25" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; Reasoning</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr"/>
       <c r="AB25" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC25" s="12" t="n">
-        <v>9</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD25" s="12" t="inlineStr">
         <is>
@@ -5127,7 +5125,7 @@
       <c r="AH25" s="13" t="inlineStr"/>
       <c r="AI25" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ25" s="14" t="inlineStr">
@@ -5137,17 +5135,17 @@
       </c>
       <c r="AK25" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(低基线者近迁移更大)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL25" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM25" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>CRI(认知储备指数)</t>
         </is>
       </c>
       <c r="AN25" s="14" t="inlineStr">
@@ -5157,35 +5155,35 @@
       </c>
       <c r="AO25" s="15" t="inlineStr">
         <is>
-          <t>宽年龄范围(65-95岁)；9月随访；基线WM水平调节迁移效应；年龄作为连续调节变量</t>
+          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Schmicker</t>
+          <t>Matysiak</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>The Impact of Working Memory Training on Cognitive Abilities in Older Adults: The Role of Cognitive Reserve.</t>
+          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Current aging science</t>
+          <t>BMC research notes</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -5194,18 +5192,16 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>80.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>3.55</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>88</v>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
@@ -5214,12 +5210,12 @@
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥24</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
@@ -5229,7 +5225,7 @@
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive)</t>
+          <t>N-back (adaptive, 1-3 back)</t>
         </is>
       </c>
       <c r="Q26" s="11" t="inlineStr">
@@ -5238,13 +5234,13 @@
         </is>
       </c>
       <c r="R26" s="11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="T26" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U26" s="11" t="inlineStr">
         <is>
@@ -5258,7 +5254,7 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>PsychoPy自制</t>
         </is>
       </c>
       <c r="X26" s="12" t="inlineStr">
@@ -5268,15 +5264,19 @@
       </c>
       <c r="Y26" s="12" t="inlineStr">
         <is>
-          <t>Digit Span</t>
+          <t>N-back (untrained level)</t>
         </is>
       </c>
       <c r="Z26" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA26" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>Digit Span; Corsi; Stroop</t>
+        </is>
+      </c>
       <c r="AB26" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AD26" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>η²p=0.05(训练×年龄交互)</t>
         </is>
       </c>
       <c r="AE26" s="12" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="AK26" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高(老年&lt;年轻训练增益)</t>
         </is>
       </c>
       <c r="AL26" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM26" s="14" t="inlineStr">
         <is>
-          <t>CRI(认知储备指数)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN26" s="14" t="inlineStr">
@@ -5336,35 +5336,35 @@
       </c>
       <c r="AO26" s="15" t="inlineStr">
         <is>
-          <t>认知储备(CRI)作为调节变量；小样本(N=21)；old-old样本(均值80.5岁)</t>
+          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Matysiak</t>
+          <t>Jaeggi</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Limited training and transfer effects in older and young adults who participated in 12 sessions of process-based working memory training. A three-armed pretest-posttest design study.</t>
+          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>BMC research notes</t>
+          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -5373,16 +5373,22 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="I27" s="10" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K27" s="10" t="n">
-        <v>88</v>
+        <v>183</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
@@ -5391,12 +5397,12 @@
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>GDS+GAD</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>≥24</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -5406,7 +5412,7 @@
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, 1-3 back)</t>
+          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
         </is>
       </c>
       <c r="Q27" s="11" t="inlineStr">
@@ -5415,13 +5421,17 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="S27" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T27" s="11" t="n">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>30-45</t>
+        </is>
+      </c>
+      <c r="T27" s="11" t="inlineStr">
+        <is>
+          <t>2-10</t>
+        </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
         <is>
@@ -5435,7 +5445,7 @@
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
-          <t>PsychoPy自制</t>
+          <t>自制(tablet)</t>
         </is>
       </c>
       <c r="X27" s="12" t="inlineStr">
@@ -5445,7 +5455,7 @@
       </c>
       <c r="Y27" s="12" t="inlineStr">
         <is>
-          <t>N-back (untrained level)</t>
+          <t>Reading Span; Symmetry Span</t>
         </is>
       </c>
       <c r="Z27" s="12" t="inlineStr">
@@ -5455,22 +5465,20 @@
       </c>
       <c r="AA27" s="12" t="inlineStr">
         <is>
-          <t>Digit Span; Corsi; Stroop</t>
+          <t>Letter Sets; Visual LTM</t>
         </is>
       </c>
       <c r="AB27" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC27" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="AD27" s="12" t="inlineStr">
         <is>
-          <t>η²p=0.05(训练×年龄交互)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE27" s="12" t="inlineStr">
@@ -5497,12 +5505,12 @@
       </c>
       <c r="AK27" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高(老年&lt;年轻训练增益)</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL27" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM27" s="14" t="inlineStr">
@@ -5517,68 +5525,58 @@
       </c>
       <c r="AO27" s="15" t="inlineStr">
         <is>
-          <t>含年轻组(均值26.48岁)对比；老年组训练增益显著小于年轻组；迁移效应有限</t>
+          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Jaeggi</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Investigating the Effects of Spacing on Working Memory Training Outcome: A Randomized, Controlled, Multisite Trial in Older Adults.</t>
+          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>The journals of gerontology. Series B, Psychological sciences and social sciences</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>大学</t>
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>183</v>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>65</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="n">
+        <v>13.2</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>GDS+GAD</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
@@ -5593,7 +5591,7 @@
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>N-back (adaptive, tablet-based, picture stimuli)</t>
+          <t>verbal n-back</t>
         </is>
       </c>
       <c r="Q28" s="11" t="inlineStr">
@@ -5602,16 +5600,14 @@
         </is>
       </c>
       <c r="R28" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>30-45</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="S28" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="T28" s="11" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-4周</t>
         </is>
       </c>
       <c r="U28" s="11" t="inlineStr">
@@ -5626,7 +5622,7 @@
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>自制(tablet)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X28" s="12" t="inlineStr">
@@ -5636,7 +5632,7 @@
       </c>
       <c r="Y28" s="12" t="inlineStr">
         <is>
-          <t>Reading Span; Symmetry Span</t>
+          <t>spatial n-back</t>
         </is>
       </c>
       <c r="Z28" s="12" t="inlineStr">
@@ -5646,16 +5642,18 @@
       </c>
       <c r="AA28" s="12" t="inlineStr">
         <is>
-          <t>Letter Sets; Visual LTM</t>
+          <t>fluid intelligence (Raven)</t>
         </is>
       </c>
       <c r="AB28" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AC28" s="12" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AC28" s="12" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="AD28" s="12" t="inlineStr">
         <is>
@@ -5676,7 +5674,7 @@
       <c r="AH28" s="13" t="inlineStr"/>
       <c r="AI28" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ28" s="14" t="inlineStr">
@@ -5686,17 +5684,17 @@
       </c>
       <c r="AK28" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL28" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM28" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN28" s="14" t="inlineStr">
@@ -5706,54 +5704,54 @@
       </c>
       <c r="AO28" s="15" t="inlineStr">
         <is>
-          <t>间距效应研究：3种训练间距条件(每天2次/每天1次/隔天)；多中心RCT；入组≥65岁均值未报告</t>
+          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Individual differences in cognitive plasticity: an investigation of training curves in younger and older adults.</t>
+          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>International journal of geriatric psychiatry</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>大学</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>70.8</v>
+        <v>69.5</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="10" t="inlineStr"/>
       <c r="L29" s="10" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -5767,12 +5765,12 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>verbal n-back</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q29" s="11" t="inlineStr">
@@ -5781,15 +5779,13 @@
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S29" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="T29" s="11" t="inlineStr">
-        <is>
-          <t>2-4周</t>
-        </is>
+      <c r="T29" s="11" t="n">
+        <v>3</v>
       </c>
       <c r="U29" s="11" t="inlineStr">
         <is>
@@ -5813,7 +5809,7 @@
       </c>
       <c r="Y29" s="12" t="inlineStr">
         <is>
-          <t>spatial n-back</t>
+          <t>WM criterion task (CWMS)</t>
         </is>
       </c>
       <c r="Z29" s="12" t="inlineStr">
@@ -5823,7 +5819,7 @@
       </c>
       <c r="AA29" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence (Raven)</t>
+          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
         </is>
       </c>
       <c r="AB29" s="12" t="inlineStr">
@@ -5838,12 +5834,12 @@
       </c>
       <c r="AD29" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d&gt;=0.8 (large effect)</t>
         </is>
       </c>
       <c r="AE29" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF29" s="13" t="inlineStr">
@@ -5855,27 +5851,27 @@
       <c r="AH29" s="13" t="inlineStr"/>
       <c r="AI29" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ29" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK29" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL29" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM29" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN29" s="14" t="inlineStr">
@@ -5885,25 +5881,25 @@
       </c>
       <c r="AO29" s="15" t="inlineStr">
         <is>
-          <t>潜增长曲线模型分析训练曲线；含年轻与老年成人比较</t>
+          <t>评估日常生活能力迁移效应</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Benefits in tasks related to everyday life competences after a working memory training in older adults.</t>
+          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -5922,17 +5918,19 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="10" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>57</v>
+      </c>
       <c r="L30" s="10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
@@ -5990,7 +5988,7 @@
       </c>
       <c r="Y30" s="12" t="inlineStr">
         <is>
-          <t>WM criterion task (CWMS)</t>
+          <t>WM updating task</t>
         </is>
       </c>
       <c r="Z30" s="12" t="inlineStr">
@@ -6000,22 +5998,22 @@
       </c>
       <c r="AA30" s="12" t="inlineStr">
         <is>
-          <t>Everyday Problem Test; TIADL; Cattell; Raven RSPM</t>
+          <t>Language comprehension; Cattell fluid intelligence</t>
         </is>
       </c>
       <c r="AB30" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC30" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD30" s="12" t="inlineStr">
         <is>
-          <t>d&gt;=0.8 (large effect)</t>
+          <t>η²=0.15-0.26 (transfer)</t>
         </is>
       </c>
       <c r="AE30" s="12" t="inlineStr">
@@ -6062,60 +6060,58 @@
       </c>
       <c r="AO30" s="15" t="inlineStr">
         <is>
-          <t>评估日常生活能力迁移效应</t>
+          <t>6个月随访；语言理解力迁移</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Gains in language comprehension relating to working memory training in healthy older adults.</t>
+          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>International journal of geriatric psychiatry</t>
+          <t>Neuroreport</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>69</v>
+        <v>69.7</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="L31" s="10" t="n">
-        <v>10.5</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="L31" s="10" t="inlineStr"/>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
@@ -6125,41 +6121,39 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>CACT (computer-assisted cognitive training)</t>
         </is>
       </c>
       <c r="Q31" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S31" s="11" t="n">
-        <v>30</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S31" s="11" t="inlineStr"/>
       <c r="T31" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Maxmedica CACT</t>
         </is>
       </c>
       <c r="X31" s="12" t="inlineStr">
@@ -6169,19 +6163,15 @@
       </c>
       <c r="Y31" s="12" t="inlineStr">
         <is>
-          <t>WM updating task</t>
+          <t>Verbal WM task; Digit span forward</t>
         </is>
       </c>
       <c r="Z31" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA31" s="12" t="inlineStr">
-        <is>
-          <t>Language comprehension; Cattell fluid intelligence</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="12" t="inlineStr"/>
       <c r="AB31" s="12" t="inlineStr">
         <is>
           <t>是</t>
@@ -6189,12 +6179,12 @@
       </c>
       <c r="AC31" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD31" s="12" t="inlineStr">
         <is>
-          <t>η²=0.15-0.26 (transfer)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE31" s="12" t="inlineStr">
@@ -6241,58 +6231,56 @@
       </c>
       <c r="AO31" s="15" t="inlineStr">
         <is>
-          <t>6个月随访；语言理解力迁移</t>
+          <t>tDCS联合CACT；anodal vs sham tDCS</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>SH</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Long-term effects of transcranial direct current stimulation combined with computer-assisted cognitive training in healthy older adults.</t>
+          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Neuroreport</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K32" s="10" t="n">
-        <v>68</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr"/>
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
@@ -6302,25 +6290,27 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>CACT (computer-assisted cognitive training)</t>
+          <t>adaptive spatial n-back</t>
         </is>
       </c>
       <c r="Q32" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R32" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S32" s="11" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="S32" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="T32" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" s="11" t="inlineStr">
         <is>
@@ -6334,7 +6324,7 @@
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
-          <t>Maxmedica CACT</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X32" s="12" t="inlineStr">
@@ -6344,7 +6334,7 @@
       </c>
       <c r="Y32" s="12" t="inlineStr">
         <is>
-          <t>Verbal WM task; Digit span forward</t>
+          <t>WM composite score (5 tasks)</t>
         </is>
       </c>
       <c r="Z32" s="12" t="inlineStr">
@@ -6355,12 +6345,12 @@
       <c r="AA32" s="12" t="inlineStr"/>
       <c r="AB32" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC32" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD32" s="12" t="inlineStr">
@@ -6370,7 +6360,7 @@
       </c>
       <c r="AE32" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF32" s="13" t="inlineStr">
@@ -6382,22 +6372,22 @@
       <c r="AH32" s="13" t="inlineStr"/>
       <c r="AI32" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ32" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK32" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL32" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM32" s="14" t="inlineStr">
@@ -6412,56 +6402,58 @@
       </c>
       <c r="AO32" s="15" t="inlineStr">
         <is>
-          <t>tDCS联合CACT；anodal vs sham tDCS</t>
+          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>VK</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Older adults with lower working memory capacity benefit from transcranial direct current stimulation when combined with working memory training: A preliminary study.</t>
+          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Aging &amp; mental health</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>社区</t>
+          <t>医院</t>
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>69.5</v>
+        <v>83.5</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K33" s="10" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>79</v>
+      </c>
       <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>MoCA</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
@@ -6471,27 +6463,23 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>adaptive spatial n-back</t>
+          <t>computer-assisted cognitive training (multi-domain)</t>
         </is>
       </c>
       <c r="Q33" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R33" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" s="11" t="n">
-        <v>20</v>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr"/>
       <c r="T33" s="11" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
@@ -6500,7 +6488,7 @@
       </c>
       <c r="V33" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
@@ -6515,23 +6503,27 @@
       </c>
       <c r="Y33" s="12" t="inlineStr">
         <is>
-          <t>WM composite score (5 tasks)</t>
+          <t>Primary WM; secondary WM (verbal/visual)</t>
         </is>
       </c>
       <c r="Z33" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA33" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>Information processing speed; learning; interference tendency</t>
+        </is>
+      </c>
       <c r="AB33" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC33" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD33" s="12" t="inlineStr">
@@ -6541,7 +6533,7 @@
       </c>
       <c r="AE33" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF33" s="13" t="inlineStr">
@@ -6553,22 +6545,22 @@
       <c r="AH33" s="13" t="inlineStr"/>
       <c r="AI33" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ33" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK33" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL33" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM33" s="14" t="inlineStr">
@@ -6583,54 +6575,52 @@
       </c>
       <c r="AO33" s="15" t="inlineStr">
         <is>
-          <t>低WM capacity者从tDCS中获益更多；YO vs OO分组分析</t>
+          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>VK</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Long-term improvements in cognitive performance through computer-assisted cognitive training: a pilot study in a residential home for older people.</t>
+          <t>Novel television-based cognitive training improves working memory and executive function.</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Aging &amp; mental health</t>
+          <t>PloS one</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>社区</t>
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>83.5</v>
+        <v>70.5</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" s="10" t="n">
-        <v>79</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="K34" s="10" t="inlineStr"/>
       <c r="L34" s="10" t="inlineStr"/>
       <c r="M34" s="10" t="inlineStr">
         <is>
@@ -6644,27 +6634,27 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>computer-assisted cognitive training (multi-domain)</t>
+          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
         </is>
       </c>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R34" s="11" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>25</v>
+      </c>
       <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="n">
-        <v>14</v>
-      </c>
+      <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -6674,7 +6664,7 @@
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>CogniFit</t>
         </is>
       </c>
       <c r="X34" s="12" t="inlineStr">
@@ -6684,7 +6674,7 @@
       </c>
       <c r="Y34" s="12" t="inlineStr">
         <is>
-          <t>Primary WM; secondary WM (verbal/visual)</t>
+          <t>WM tasks (validated)</t>
         </is>
       </c>
       <c r="Z34" s="12" t="inlineStr">
@@ -6694,17 +6684,17 @@
       </c>
       <c r="AA34" s="12" t="inlineStr">
         <is>
-          <t>Information processing speed; learning; interference tendency</t>
+          <t>Executive function tasks</t>
         </is>
       </c>
       <c r="AB34" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC34" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD34" s="12" t="inlineStr">
@@ -6756,35 +6746,35 @@
       </c>
       <c r="AO34" s="15" t="inlineStr">
         <is>
-          <t>单组前后测；养老院居民；老老年（75-91岁）</t>
+          <t>互动电视（iTV）平台认知训练</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Novel television-based cognitive training improves working memory and executive function.</t>
+          <t>Impact of working memory training on memory performance in old-old adults.</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>PloS one</t>
+          <t>Psychology and aging</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -6793,13 +6783,13 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>70.5</v>
+        <v>80</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr"/>
@@ -6815,12 +6805,12 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>CogniFit iTV (21 cognitive tasks incl. WM)</t>
+          <t>WM process-based training (visual/spatial)</t>
         </is>
       </c>
       <c r="Q35" s="11" t="inlineStr">
@@ -6829,10 +6819,14 @@
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S35" s="11" t="inlineStr"/>
-      <c r="T35" s="11" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="S35" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="U35" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -6845,7 +6839,7 @@
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
-          <t>CogniFit</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X35" s="12" t="inlineStr">
@@ -6855,7 +6849,7 @@
       </c>
       <c r="Y35" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (validated)</t>
+          <t>Visual WM (VLMT)</t>
         </is>
       </c>
       <c r="Z35" s="12" t="inlineStr">
@@ -6865,17 +6859,17 @@
       </c>
       <c r="AA35" s="12" t="inlineStr">
         <is>
-          <t>Executive function tasks</t>
+          <t>Visual episodic memory</t>
         </is>
       </c>
       <c r="AB35" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC35" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AD35" s="12" t="inlineStr">
@@ -6927,35 +6921,35 @@
       </c>
       <c r="AO35" s="15" t="inlineStr">
         <is>
-          <t>互动电视（iTV）平台认知训练</t>
+          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Impact of working memory training on memory performance in old-old adults.</t>
+          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Psychology and aging</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -6964,13 +6958,13 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="10" t="inlineStr"/>
@@ -6986,12 +6980,12 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>WM process-based training (visual/spatial)</t>
+          <t>adaptive verbal + spatial n-back</t>
         </is>
       </c>
       <c r="Q36" s="11" t="inlineStr">
@@ -7000,13 +6994,13 @@
         </is>
       </c>
       <c r="R36" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="S36" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="T36" s="11" t="n">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr">
+        <is>
+          <t>4-8周</t>
+        </is>
       </c>
       <c r="U36" s="11" t="inlineStr">
         <is>
@@ -7020,7 +7014,7 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家在线）</t>
         </is>
       </c>
       <c r="X36" s="12" t="inlineStr">
@@ -7030,7 +7024,7 @@
       </c>
       <c r="Y36" s="12" t="inlineStr">
         <is>
-          <t>Visual WM (VLMT)</t>
+          <t>Digit span</t>
         </is>
       </c>
       <c r="Z36" s="12" t="inlineStr">
@@ -7040,17 +7034,17 @@
       </c>
       <c r="AA36" s="12" t="inlineStr">
         <is>
-          <t>Visual episodic memory</t>
+          <t>Abstract relational reasoning</t>
         </is>
       </c>
       <c r="AB36" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC36" s="12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD36" s="12" t="inlineStr">
@@ -7060,7 +7054,7 @@
       </c>
       <c r="AE36" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF36" s="13" t="inlineStr">
@@ -7102,50 +7096,50 @@
       </c>
       <c r="AO36" s="15" t="inlineStr">
         <is>
-          <t>老老年（~80岁）；1年随访；身体锻炼主动对照组</t>
+          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Frontiers in human neuroscience</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>社区</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
         <v>40</v>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>SJ</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Experimental investigation of training schedule on home-based working memory training in healthy older adults.</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Frontiers in psychology</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="n">
-        <v>71</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>66</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K37" s="10" t="inlineStr"/>
       <c r="L37" s="10" t="inlineStr"/>
@@ -7166,7 +7160,7 @@
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>adaptive verbal + spatial n-back</t>
+          <t>adaptive n-back</t>
         </is>
       </c>
       <c r="Q37" s="11" t="inlineStr">
@@ -7175,13 +7169,11 @@
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S37" s="11" t="inlineStr"/>
-      <c r="T37" s="11" t="inlineStr">
-        <is>
-          <t>4-8周</t>
-        </is>
+      <c r="T37" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="U37" s="11" t="inlineStr">
         <is>
@@ -7195,7 +7187,7 @@
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
-          <t>自制（居家在线）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X37" s="12" t="inlineStr">
@@ -7205,19 +7197,15 @@
       </c>
       <c r="Y37" s="12" t="inlineStr">
         <is>
-          <t>Digit span</t>
+          <t>multimodal dual-task (visual+auditory)</t>
         </is>
       </c>
       <c r="Z37" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA37" s="12" t="inlineStr">
-        <is>
-          <t>Abstract relational reasoning</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="12" t="inlineStr"/>
       <c r="AB37" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -7230,21 +7218,29 @@
       </c>
       <c r="AD37" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>p&lt;0.05</t>
         </is>
       </c>
       <c r="AE37" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF37" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG37" s="13" t="inlineStr"/>
-      <c r="AH37" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG37" s="13" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="AH37" s="13" t="inlineStr">
+        <is>
+          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
+        </is>
+      </c>
       <c r="AI37" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7277,17 +7273,17 @@
       </c>
       <c r="AO37" s="15" t="inlineStr">
         <is>
-          <t>训练时间表（密集vs分散）；居家无监督在线训练</t>
+          <t>双任务迁移；fMRI子研究；先导研究</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>JA</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -7295,17 +7291,17 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Transfer Effects to a Multimodal Dual-Task after Working Memory Training and Associated Neural Correlates in Older Adults - A Pilot Study.</t>
+          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Scientific reports</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -7314,13 +7310,15 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>4</v>
+        <v>67</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K38" s="10" t="inlineStr"/>
       <c r="L38" s="10" t="inlineStr"/>
@@ -7336,12 +7334,12 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>adaptive n-back</t>
+          <t>Visual and Spatial WM training</t>
         </is>
       </c>
       <c r="Q38" s="11" t="inlineStr">
@@ -7349,21 +7347,17 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R38" s="11" t="n">
-        <v>12</v>
-      </c>
+      <c r="R38" s="11" t="inlineStr"/>
       <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
@@ -7378,7 +7372,7 @@
       </c>
       <c r="Y38" s="12" t="inlineStr">
         <is>
-          <t>multimodal dual-task (visual+auditory)</t>
+          <t>Visual WM; Spatial WM</t>
         </is>
       </c>
       <c r="Z38" s="12" t="inlineStr">
@@ -7389,52 +7383,44 @@
       <c r="AA38" s="12" t="inlineStr"/>
       <c r="AB38" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC38" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD38" s="12" t="inlineStr">
         <is>
-          <t>p&lt;0.05</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE38" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF38" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG38" s="13" t="inlineStr">
-        <is>
-          <t>fMRI</t>
-        </is>
-      </c>
-      <c r="AH38" s="13" t="inlineStr">
-        <is>
-          <t>DLPFC活动变化预测双任务表现；左侧DLPFC→听觉双任务成本</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG38" s="13" t="inlineStr"/>
+      <c r="AH38" s="13" t="inlineStr"/>
       <c r="AI38" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ38" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK38" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AL38" s="14" t="inlineStr">
@@ -7454,35 +7440,35 @@
       </c>
       <c r="AO38" s="15" t="inlineStr">
         <is>
-          <t>双任务迁移；fMRI子研究；先导研究</t>
+          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>JA</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Task demands, tDCS intensity, and the COMT val(158)met polymorphism impact tDCS-linked working memory training gains.</t>
+          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Scientific reports</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -7491,15 +7477,13 @@
         </is>
       </c>
       <c r="H39" s="10" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>70.56999999999999</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>5.5</v>
       </c>
       <c r="K39" s="10" t="inlineStr"/>
       <c r="L39" s="10" t="inlineStr"/>
@@ -7515,12 +7499,12 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>Visual and Spatial WM training</t>
+          <t>commercial brain training app (multi-domain)</t>
         </is>
       </c>
       <c r="Q39" s="11" t="inlineStr">
@@ -7530,20 +7514,22 @@
       </c>
       <c r="R39" s="11" t="inlineStr"/>
       <c r="S39" s="11" t="inlineStr"/>
-      <c r="T39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="n">
+        <v>12</v>
+      </c>
       <c r="U39" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V39" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业脑训练app</t>
         </is>
       </c>
       <c r="X39" s="12" t="inlineStr">
@@ -7553,23 +7539,27 @@
       </c>
       <c r="Y39" s="12" t="inlineStr">
         <is>
-          <t>Visual WM; Spatial WM</t>
+          <t>WM tasks (trained domain)</t>
         </is>
       </c>
       <c r="Z39" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA39" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="12" t="inlineStr">
+        <is>
+          <t>Processing speed; attention; language</t>
+        </is>
+      </c>
       <c r="AB39" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC39" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD39" s="12" t="inlineStr">
@@ -7579,7 +7569,7 @@
       </c>
       <c r="AE39" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF39" s="13" t="inlineStr">
@@ -7591,17 +7581,17 @@
       <c r="AH39" s="13" t="inlineStr"/>
       <c r="AI39" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ39" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK39" s="14" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL39" s="14" t="inlineStr">
@@ -7621,35 +7611,35 @@
       </c>
       <c r="AO39" s="15" t="inlineStr">
         <is>
-          <t>COMT val158met基因型调节tDCS-WM训练效益；不同tDCS强度（1/1.5/2mA）</t>
+          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Practice makes perfect, but to what end? Computerised brain training has limited cognitive benefits in healthy ageing.</t>
+          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -7658,13 +7648,15 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>5.5</v>
+        <v>75.8</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K40" s="10" t="inlineStr"/>
       <c r="L40" s="10" t="inlineStr"/>
@@ -7680,12 +7672,12 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>commercial brain training app (multi-domain)</t>
+          <t>Cogmed (adaptive WM training)</t>
         </is>
       </c>
       <c r="Q40" s="11" t="inlineStr">
@@ -7693,10 +7685,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R40" s="11" t="inlineStr"/>
-      <c r="S40" s="11" t="inlineStr"/>
+      <c r="R40" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="S40" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="T40" s="11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="U40" s="11" t="inlineStr">
         <is>
@@ -7710,7 +7706,7 @@
       </c>
       <c r="W40" s="11" t="inlineStr">
         <is>
-          <t>商业脑训练app</t>
+          <t>Cogmed</t>
         </is>
       </c>
       <c r="X40" s="12" t="inlineStr">
@@ -7720,19 +7716,15 @@
       </c>
       <c r="Y40" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (trained domain)</t>
+          <t>n-back (0-back, 1-back, 2-back)</t>
         </is>
       </c>
       <c r="Z40" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA40" s="12" t="inlineStr">
-        <is>
-          <t>Processing speed; attention; language</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr"/>
       <c r="AB40" s="12" t="inlineStr">
         <is>
           <t>否</t>
@@ -7750,16 +7742,24 @@
       </c>
       <c r="AE40" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF40" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG40" s="13" t="inlineStr"/>
-      <c r="AH40" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG40" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH40" s="13" t="inlineStr">
+        <is>
+          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
+        </is>
+      </c>
       <c r="AI40" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7792,25 +7792,25 @@
       </c>
       <c r="AO40" s="15" t="inlineStr">
         <is>
-          <t>商业脑训练app；仅练习效应，无迁移；3个月干预</t>
+          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Changes in Neural Activity Underlying Working Memory after Computerized Cognitive Training in Older Adults.</t>
+          <t>An evaluation of a working memory training scheme in older adults.</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -7829,15 +7829,13 @@
         </is>
       </c>
       <c r="H41" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="K41" s="10" t="inlineStr"/>
       <c r="L41" s="10" t="inlineStr"/>
@@ -7853,12 +7851,12 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>Cogmed (adaptive WM training)</t>
+          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
         </is>
       </c>
       <c r="Q41" s="11" t="inlineStr">
@@ -7866,12 +7864,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R41" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="S41" s="11" t="n">
-        <v>40</v>
-      </c>
+      <c r="R41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr"/>
       <c r="T41" s="11" t="n">
         <v>5</v>
       </c>
@@ -7887,7 +7881,7 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>Cogmed</t>
+          <t>自制（在线）</t>
         </is>
       </c>
       <c r="X41" s="12" t="inlineStr">
@@ -7897,23 +7891,27 @@
       </c>
       <c r="Y41" s="12" t="inlineStr">
         <is>
-          <t>n-back (0-back, 1-back, 2-back)</t>
+          <t>Auditory STM span; visuospatial STM</t>
         </is>
       </c>
       <c r="Z41" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA41" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="inlineStr">
+        <is>
+          <t>Long-term episodic memory</t>
+        </is>
+      </c>
       <c r="AB41" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC41" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>3;6</t>
         </is>
       </c>
       <c r="AD41" s="12" t="inlineStr">
@@ -7928,19 +7926,11 @@
       </c>
       <c r="AF41" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG41" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH41" s="13" t="inlineStr">
-        <is>
-          <t>P3a和P3b波幅增大（自适应训练组）；P3波幅与任务表现正相关</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG41" s="13" t="inlineStr"/>
+      <c r="AH41" s="13" t="inlineStr"/>
       <c r="AI41" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7948,7 +7938,7 @@
       </c>
       <c r="AJ41" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK41" s="14" t="inlineStr">
@@ -7973,25 +7963,25 @@
       </c>
       <c r="AO41" s="15" t="inlineStr">
         <is>
-          <t>Cogmed自适应vs非自适应；ERP神经指标变化</t>
+          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>An evaluation of a working memory training scheme in older adults.</t>
+          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -8001,7 +7991,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -8010,13 +8000,13 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>70</v>
+        <v>70.39</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="K42" s="10" t="inlineStr"/>
       <c r="L42" s="10" t="inlineStr"/>
@@ -8032,12 +8022,12 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>Baddeley WM model-based (auditory+visuospatial span)</t>
+          <t>computerized WM training (web-based)</t>
         </is>
       </c>
       <c r="Q42" s="11" t="inlineStr">
@@ -8048,7 +8038,7 @@
       <c r="R42" s="11" t="inlineStr"/>
       <c r="S42" s="11" t="inlineStr"/>
       <c r="T42" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U42" s="11" t="inlineStr">
         <is>
@@ -8062,7 +8052,7 @@
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>自制（在线）</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X42" s="12" t="inlineStr">
@@ -8072,27 +8062,23 @@
       </c>
       <c r="Y42" s="12" t="inlineStr">
         <is>
-          <t>Auditory STM span; visuospatial STM</t>
+          <t>Self-perceived cognitive failures (CFQ)</t>
         </is>
       </c>
       <c r="Z42" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA42" s="12" t="inlineStr">
-        <is>
-          <t>Long-term episodic memory</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="12" t="inlineStr"/>
       <c r="AB42" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC42" s="12" t="inlineStr">
         <is>
-          <t>3;6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD42" s="12" t="inlineStr">
@@ -8119,7 +8105,7 @@
       </c>
       <c r="AJ42" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK42" s="14" t="inlineStr">
@@ -8144,35 +8130,35 @@
       </c>
       <c r="AO42" s="15" t="inlineStr">
         <is>
-          <t>心理压力与训练时间交互关系；auditory STM span扩展但WM容量无提升</t>
+          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Self-Perceived Benefits of Cognitive Training in Healthy Older Adults.</t>
+          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>BMC geriatrics</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -8181,13 +8167,13 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>70.39</v>
+        <v>69</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>4.54</v>
+        <v>3.5</v>
       </c>
       <c r="K43" s="10" t="inlineStr"/>
       <c r="L43" s="10" t="inlineStr"/>
@@ -8203,12 +8189,12 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>computerized WM training (web-based)</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q43" s="11" t="inlineStr">
@@ -8216,10 +8202,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R43" s="11" t="inlineStr"/>
-      <c r="S43" s="11" t="inlineStr"/>
+      <c r="R43" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T43" s="11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U43" s="11" t="inlineStr">
         <is>
@@ -8233,7 +8223,7 @@
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X43" s="12" t="inlineStr">
@@ -8243,7 +8233,7 @@
       </c>
       <c r="Y43" s="12" t="inlineStr">
         <is>
-          <t>Self-perceived cognitive failures (CFQ)</t>
+          <t>n-back task</t>
         </is>
       </c>
       <c r="Z43" s="12" t="inlineStr">
@@ -8254,31 +8244,39 @@
       <c r="AA43" s="12" t="inlineStr"/>
       <c r="AB43" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC43" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD43" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>Cohen's d medium-large</t>
         </is>
       </c>
       <c r="AE43" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF43" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG43" s="13" t="inlineStr"/>
-      <c r="AH43" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG43" s="13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+      <c r="AH43" s="13" t="inlineStr">
+        <is>
+          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
+        </is>
+      </c>
       <c r="AI43" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8311,35 +8309,35 @@
       </c>
       <c r="AO43" s="15" t="inlineStr">
         <is>
-          <t>主观感知认知获益；WM vs 逻辑规划训练比较；自我报告结局</t>
+          <t>先导研究；ERP神经相关；6个月随访</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Short- and long-term cognitive and electrophysiological effects of a brief working memory training in older adults: a pilot study.</t>
+          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>BMC geriatrics</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -8348,13 +8346,15 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>3.5</v>
+        <v>70.5</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>web-based WM or logic &amp; planning training</t>
         </is>
       </c>
       <c r="Q44" s="11" t="inlineStr">
@@ -8383,14 +8383,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R44" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S44" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr"/>
       <c r="T44" s="11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U44" s="11" t="inlineStr">
         <is>
@@ -8404,7 +8400,7 @@
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>商业软件</t>
         </is>
       </c>
       <c r="X44" s="12" t="inlineStr">
@@ -8414,50 +8410,46 @@
       </c>
       <c r="Y44" s="12" t="inlineStr">
         <is>
-          <t>n-back task</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z44" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA44" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>Planning; reasoning; processing speed; verbal fluency</t>
+        </is>
+      </c>
       <c r="AB44" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC44" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD44" s="12" t="inlineStr">
         <is>
-          <t>Cohen's d medium-large</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE44" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF44" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG44" s="13" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="AH44" s="13" t="inlineStr">
-        <is>
-          <t>训练后及6个月随访时TG出现左侧化ERP激活；近迁移仅ERP层面显著</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG44" s="13" t="inlineStr"/>
+      <c r="AH44" s="13" t="inlineStr"/>
       <c r="AI44" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8490,35 +8482,35 @@
       </c>
       <c r="AO44" s="15" t="inlineStr">
         <is>
-          <t>先导研究；ERP神经相关；6个月随访</t>
+          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Comparison of Cognitive Change after Working Memory Training and Logic and Planning Training in Healthy Older Adults.</t>
+          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Gerontology</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -8527,15 +8519,13 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>86.8</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="K45" s="10" t="inlineStr"/>
       <c r="L45" s="10" t="inlineStr"/>
@@ -8551,24 +8541,24 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
-          <t>web-based WM or logic &amp; planning training</t>
+          <t>WM span tasks (5 tasks)</t>
         </is>
       </c>
       <c r="Q45" s="11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R45" s="11" t="inlineStr"/>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="n">
-        <v>8</v>
-      </c>
+      <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -8581,7 +8571,7 @@
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X45" s="12" t="inlineStr">
@@ -8591,7 +8581,7 @@
       </c>
       <c r="Y45" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>trained WM tasks</t>
         </is>
       </c>
       <c r="Z45" s="12" t="inlineStr">
@@ -8601,7 +8591,7 @@
       </c>
       <c r="AA45" s="12" t="inlineStr">
         <is>
-          <t>Planning; reasoning; processing speed; verbal fluency</t>
+          <t>Executive functions (2 tests)</t>
         </is>
       </c>
       <c r="AB45" s="12" t="inlineStr">
@@ -8616,7 +8606,7 @@
       </c>
       <c r="AD45" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>d=0.5-0.8 (trained tasks)</t>
         </is>
       </c>
       <c r="AE45" s="12" t="inlineStr">
@@ -8633,17 +8623,17 @@
       <c r="AH45" s="13" t="inlineStr"/>
       <c r="AI45" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ45" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK45" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL45" s="14" t="inlineStr">
@@ -8663,35 +8653,35 @@
       </c>
       <c r="AO45" s="15" t="inlineStr">
         <is>
-          <t>Bayesian分析；WM vs 逻辑规划训练；认知天花板效应可能</t>
+          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Potentials and limits of plasticity induced by working memory training in old-old age.</t>
+          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Gerontology</t>
+          <t>Frontiers in psychology</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -8700,13 +8690,13 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>86.8</v>
+        <v>66</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K46" s="10" t="inlineStr"/>
       <c r="L46" s="10" t="inlineStr"/>
@@ -8722,22 +8712,20 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
-          <t>WM span tasks (5 tasks)</t>
+          <t>memory updating task (predictable vs unpredictable)</t>
         </is>
       </c>
       <c r="Q46" s="11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R46" s="11" t="n">
-        <v>10</v>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="inlineStr"/>
       <c r="S46" s="11" t="inlineStr"/>
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
@@ -8762,7 +8750,7 @@
       </c>
       <c r="Y46" s="12" t="inlineStr">
         <is>
-          <t>trained WM tasks</t>
+          <t>WM updating task (novel)</t>
         </is>
       </c>
       <c r="Z46" s="12" t="inlineStr">
@@ -8772,27 +8760,27 @@
       </c>
       <c r="AA46" s="12" t="inlineStr">
         <is>
-          <t>Executive functions (2 tests)</t>
+          <t>Episodic memory</t>
         </is>
       </c>
       <c r="AB46" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC46" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AD46" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.8 (trained tasks)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE46" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF46" s="13" t="inlineStr">
@@ -8804,7 +8792,7 @@
       <c r="AH46" s="13" t="inlineStr"/>
       <c r="AI46" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ46" s="14" t="inlineStr">
@@ -8814,7 +8802,7 @@
       </c>
       <c r="AK46" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL46" s="14" t="inlineStr">
@@ -8834,30 +8822,30 @@
       </c>
       <c r="AO46" s="15" t="inlineStr">
         <is>
-          <t>老老年（~87岁）；低基线WM容量者获益更多；无迁移效应</t>
+          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>To Switch or Not to Switch: Role of Cognitive Control in Working Memory Training in Older Adults.</t>
+          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in psychology</t>
+          <t>Aging brain</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -8871,13 +8859,17 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>5</v>
+        <v>119</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K47" s="10" t="inlineStr"/>
       <c r="L47" s="10" t="inlineStr"/>
@@ -8893,12 +8885,12 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
         <is>
-          <t>memory updating task (predictable vs unpredictable)</t>
+          <t>n-back + metacognitive program (EngAge)</t>
         </is>
       </c>
       <c r="Q47" s="11" t="inlineStr">
@@ -8906,7 +8898,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R47" s="11" t="inlineStr"/>
+      <c r="R47" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="S47" s="11" t="inlineStr"/>
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
@@ -8921,7 +8915,7 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>自制（居家）</t>
         </is>
       </c>
       <c r="X47" s="12" t="inlineStr">
@@ -8931,7 +8925,7 @@
       </c>
       <c r="Y47" s="12" t="inlineStr">
         <is>
-          <t>WM updating task (novel)</t>
+          <t>non-trained WM measures</t>
         </is>
       </c>
       <c r="Z47" s="12" t="inlineStr">
@@ -8941,7 +8935,7 @@
       </c>
       <c r="AA47" s="12" t="inlineStr">
         <is>
-          <t>Episodic memory</t>
+          <t>Inhibitory control; episodic memory</t>
         </is>
       </c>
       <c r="AB47" s="12" t="inlineStr">
@@ -8951,7 +8945,7 @@
       </c>
       <c r="AC47" s="12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD47" s="12" t="inlineStr">
@@ -8961,7 +8955,7 @@
       </c>
       <c r="AE47" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF47" s="13" t="inlineStr">
@@ -8978,7 +8972,7 @@
       </c>
       <c r="AJ47" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK47" s="14" t="inlineStr">
@@ -9003,35 +8997,35 @@
       </c>
       <c r="AO47" s="15" t="inlineStr">
         <is>
-          <t>不可预测vs可预测记忆更新训练；个体学习率预测迁移</t>
+          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>EngAge - A metacognitive intervention to supplement working memory training: A feasibility study in older adults.</t>
+          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Aging brain</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -9040,20 +9034,18 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>119</v>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="K48" s="10" t="inlineStr"/>
-      <c r="L48" s="10" t="inlineStr"/>
+      <c r="L48" s="10" t="n">
+        <v>11</v>
+      </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9066,12 +9058,12 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
         <is>
-          <t>n-back + metacognitive program (EngAge)</t>
+          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
         </is>
       </c>
       <c r="Q48" s="11" t="inlineStr">
@@ -9080,10 +9072,14 @@
         </is>
       </c>
       <c r="R48" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S48" s="11" t="inlineStr"/>
-      <c r="T48" s="11" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="S48" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T48" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U48" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -9096,7 +9092,7 @@
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
-          <t>自制（居家）</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X48" s="12" t="inlineStr">
@@ -9106,7 +9102,7 @@
       </c>
       <c r="Y48" s="12" t="inlineStr">
         <is>
-          <t>non-trained WM measures</t>
+          <t>visuospatial WM; STM tasks</t>
         </is>
       </c>
       <c r="Z48" s="12" t="inlineStr">
@@ -9116,7 +9112,7 @@
       </c>
       <c r="AA48" s="12" t="inlineStr">
         <is>
-          <t>Inhibitory control; episodic memory</t>
+          <t>fluid intelligence; processing speed; inhibitory measures</t>
         </is>
       </c>
       <c r="AB48" s="12" t="inlineStr">
@@ -9148,27 +9144,27 @@
       <c r="AH48" s="13" t="inlineStr"/>
       <c r="AI48" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>高/低</t>
         </is>
       </c>
       <c r="AJ48" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK48" s="14" t="inlineStr">
         <is>
-          <t>未检验</t>
+          <t>低&gt;高</t>
         </is>
       </c>
       <c r="AL48" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM48" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN48" s="14" t="inlineStr">
@@ -9178,35 +9174,35 @@
       </c>
       <c r="AO48" s="15" t="inlineStr">
         <is>
-          <t>WM训练+EngAge元认知干预；元认知附加效应不显著；可行性研究</t>
+          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training for Healthy Older Adults: The Role of Individual Characteristics in Explaining Short- and Long-Term Gains.</t>
+          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Frontiers in neurology</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -9215,18 +9211,16 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="n">
-        <v>11</v>
-      </c>
+      <c r="L49" s="10" t="inlineStr"/>
       <c r="M49" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9239,12 +9233,12 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P49" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS, Borella 2010 procedure)</t>
+          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
         </is>
       </c>
       <c r="Q49" s="11" t="inlineStr">
@@ -9253,22 +9247,22 @@
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S49" s="11" t="n">
         <v>30</v>
       </c>
       <c r="T49" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>TMS</t>
         </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
@@ -9283,7 +9277,7 @@
       </c>
       <c r="Y49" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM; STM tasks</t>
+          <t>non-verbal logical reasoning</t>
         </is>
       </c>
       <c r="Z49" s="12" t="inlineStr">
@@ -9293,7 +9287,7 @@
       </c>
       <c r="AA49" s="12" t="inlineStr">
         <is>
-          <t>fluid intelligence; processing speed; inhibitory measures</t>
+          <t>Attention; memory; executive functions</t>
         </is>
       </c>
       <c r="AB49" s="12" t="inlineStr">
@@ -9303,7 +9297,7 @@
       </c>
       <c r="AC49" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD49" s="12" t="inlineStr">
@@ -9313,7 +9307,7 @@
       </c>
       <c r="AE49" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF49" s="13" t="inlineStr">
@@ -9325,7 +9319,7 @@
       <c r="AH49" s="13" t="inlineStr"/>
       <c r="AI49" s="14" t="inlineStr">
         <is>
-          <t>高/低</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AJ49" s="14" t="inlineStr">
@@ -9335,7 +9329,7 @@
       </c>
       <c r="AK49" s="14" t="inlineStr">
         <is>
-          <t>低&gt;高</t>
+          <t>未检验</t>
         </is>
       </c>
       <c r="AL49" s="14" t="inlineStr">
@@ -9345,7 +9339,7 @@
       </c>
       <c r="AM49" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN49" s="14" t="inlineStr">
@@ -9355,35 +9349,35 @@
       </c>
       <c r="AO49" s="15" t="inlineStr">
         <is>
-          <t>4项研究合并分析；年龄、教育、词汇量、基线WM预测训练效益</t>
+          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>The Effect of Transcranial Random Noise Stimulation on Cognitive Training Outcome in Healthy Aging.</t>
+          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in neurology</t>
+          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -9392,13 +9386,13 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>70</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="K50" s="10" t="inlineStr"/>
       <c r="L50" s="10" t="inlineStr"/>
@@ -9419,7 +9413,7 @@
       </c>
       <c r="P50" s="11" t="inlineStr">
         <is>
-          <t>executive function training (cognitive flexibility+inhibitory control+WM)</t>
+          <t>letter updating task</t>
         </is>
       </c>
       <c r="Q50" s="11" t="inlineStr">
@@ -9428,13 +9422,13 @@
         </is>
       </c>
       <c r="R50" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S50" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T50" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U50" s="11" t="inlineStr">
         <is>
@@ -9443,7 +9437,7 @@
       </c>
       <c r="V50" s="11" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
@@ -9458,7 +9452,7 @@
       </c>
       <c r="Y50" s="12" t="inlineStr">
         <is>
-          <t>non-verbal logical reasoning</t>
+          <t>n-back (near transfer)</t>
         </is>
       </c>
       <c r="Z50" s="12" t="inlineStr">
@@ -9468,7 +9462,7 @@
       </c>
       <c r="AA50" s="12" t="inlineStr">
         <is>
-          <t>Attention; memory; executive functions</t>
+          <t>executive/memory tasks</t>
         </is>
       </c>
       <c r="AB50" s="12" t="inlineStr">
@@ -9478,7 +9472,7 @@
       </c>
       <c r="AC50" s="12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1;7</t>
         </is>
       </c>
       <c r="AD50" s="12" t="inlineStr">
@@ -9515,7 +9509,7 @@
       </c>
       <c r="AL50" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM50" s="14" t="inlineStr">
@@ -9530,35 +9524,35 @@
       </c>
       <c r="AO50" s="15" t="inlineStr">
         <is>
-          <t>tRNS联合执行功能训练；年龄与逻辑推理改善相关（1mA组）</t>
+          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Randomized trial of cognitive training and brain stimulation in non-demented older adults.</t>
+          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>Alzheimer's &amp; dementia (New York, N. Y.)</t>
+          <t>Frontiers in human neuroscience</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -9567,13 +9561,13 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>56</v>
+        <v>487</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K51" s="10" t="inlineStr"/>
       <c r="L51" s="10" t="inlineStr"/>
@@ -9589,12 +9583,12 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
         <is>
-          <t>letter updating task</t>
+          <t>syllable span + auditory discrimination (IMPACT program)</t>
         </is>
       </c>
       <c r="Q51" s="11" t="inlineStr">
@@ -9602,28 +9596,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R51" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="S51" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="T51" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>自制</t>
+          <t>Posit Science (IMPACT)</t>
         </is>
       </c>
       <c r="X51" s="12" t="inlineStr">
@@ -9633,7 +9621,7 @@
       </c>
       <c r="Y51" s="12" t="inlineStr">
         <is>
-          <t>n-back (near transfer)</t>
+          <t>WM factor score</t>
         </is>
       </c>
       <c r="Z51" s="12" t="inlineStr">
@@ -9643,17 +9631,17 @@
       </c>
       <c r="AA51" s="12" t="inlineStr">
         <is>
-          <t>executive/memory tasks</t>
+          <t>List memory; text memory</t>
         </is>
       </c>
       <c r="AB51" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC51" s="12" t="inlineStr">
         <is>
-          <t>1;7</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD51" s="12" t="inlineStr">
@@ -9663,7 +9651,7 @@
       </c>
       <c r="AE51" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF51" s="13" t="inlineStr">
@@ -9690,12 +9678,12 @@
       </c>
       <c r="AL51" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AM51" s="14" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>教育年限</t>
         </is>
       </c>
       <c r="AN51" s="14" t="inlineStr">
@@ -9705,35 +9693,35 @@
       </c>
       <c r="AO51" s="15" t="inlineStr">
         <is>
-          <t>tDCS-assisted letter updating；n-back近迁移显著</t>
+          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Evaluating the relationship between change in performance on training tasks and on untrained outcomes.</t>
+          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in human neuroscience</t>
+          <t>Frontiers in aging neuroscience</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -9742,13 +9730,13 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>487</v>
+        <v>24</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="K52" s="10" t="inlineStr"/>
       <c r="L52" s="10" t="inlineStr"/>
@@ -9769,7 +9757,7 @@
       </c>
       <c r="P52" s="11" t="inlineStr">
         <is>
-          <t>syllable span + auditory discrimination (IMPACT program)</t>
+          <t>verbal WM span (CWMS)</t>
         </is>
       </c>
       <c r="Q52" s="11" t="inlineStr">
@@ -9777,9 +9765,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr"/>
-      <c r="S52" s="11" t="inlineStr"/>
-      <c r="T52" s="11" t="inlineStr"/>
+      <c r="R52" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S52" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T52" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="U52" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -9792,7 +9786,7 @@
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
-          <t>Posit Science (IMPACT)</t>
+          <t>自制</t>
         </is>
       </c>
       <c r="X52" s="12" t="inlineStr">
@@ -9802,32 +9796,28 @@
       </c>
       <c r="Y52" s="12" t="inlineStr">
         <is>
-          <t>WM factor score</t>
+          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
         </is>
       </c>
       <c r="Z52" s="12" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA52" s="12" t="inlineStr">
-        <is>
-          <t>List memory; text memory</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr"/>
       <c r="AB52" s="12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AC52" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD52" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>d=0.5-0.9</t>
         </is>
       </c>
       <c r="AE52" s="12" t="inlineStr">
@@ -9837,11 +9827,19 @@
       </c>
       <c r="AF52" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG52" s="13" t="inlineStr"/>
-      <c r="AH52" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG52" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH52" s="13" t="inlineStr">
+        <is>
+          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
+        </is>
+      </c>
       <c r="AI52" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9849,7 +9847,7 @@
       </c>
       <c r="AJ52" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK52" s="14" t="inlineStr">
@@ -9859,12 +9857,12 @@
       </c>
       <c r="AL52" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AM52" s="14" t="inlineStr">
         <is>
-          <t>教育年限</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AN52" s="14" t="inlineStr">
@@ -9874,35 +9872,35 @@
       </c>
       <c r="AO52" s="15" t="inlineStr">
         <is>
-          <t>结构方程模型分析训练-迁移增益关系；IMPACT研究二次分析；N=487</t>
+          <t>静息态EEG；额叶振荡活动；先导研究</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Working Memory Training and Cortical Arousal in Healthy Older Adults: A Resting-State EEG Pilot Study.</t>
+          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Frontiers in aging neuroscience</t>
+          <t>Psychological research</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -9911,13 +9909,13 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>69</v>
+        <v>69.58</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>3.5</v>
+        <v>7.04</v>
       </c>
       <c r="K53" s="10" t="inlineStr"/>
       <c r="L53" s="10" t="inlineStr"/>
@@ -9933,12 +9931,12 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>verbal WM span (CWMS)</t>
+          <t>single-domain WM (n-back) or multidomain EF training</t>
         </is>
       </c>
       <c r="Q53" s="11" t="inlineStr">
@@ -9946,14 +9944,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R53" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S53" s="11" t="n">
-        <v>30</v>
-      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr"/>
       <c r="T53" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U53" s="11" t="inlineStr">
         <is>
@@ -9977,50 +9971,46 @@
       </c>
       <c r="Y53" s="12" t="inlineStr">
         <is>
-          <t>CWMS criterion; inhibitory control (intrusion errors)</t>
+          <t>n-back; global EF accuracy</t>
         </is>
       </c>
       <c r="Z53" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA53" s="12" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>Prospective memory (Virtual Week); fluid intelligence</t>
+        </is>
+      </c>
       <c r="AB53" s="12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AC53" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AD53" s="12" t="inlineStr">
         <is>
-          <t>d=0.5-0.9</t>
+          <t>未报告 (Bayesian)</t>
         </is>
       </c>
       <c r="AE53" s="12" t="inlineStr">
         <is>
-          <t>正向迁移</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="AF53" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG53" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH53" s="13" t="inlineStr">
-        <is>
-          <t>训练后TG前额left ROI高b/a比率增大；与WM表现正相关；随访持续</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG53" s="13" t="inlineStr"/>
+      <c r="AH53" s="13" t="inlineStr"/>
       <c r="AI53" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10053,35 +10043,35 @@
       </c>
       <c r="AO53" s="15" t="inlineStr">
         <is>
-          <t>静息态EEG；额叶振荡活动；先导研究</t>
+          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Cantarella</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>A comparison of single-domain and multidomain executive functions cognitive training for enhancing cognition and well-being in older adults.</t>
+          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Psychological research</t>
+          <t>Psychologie Française</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -10090,13 +10080,13 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>69.58</v>
+        <v>69</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>7.04</v>
+        <v>4</v>
       </c>
       <c r="K54" s="10" t="inlineStr"/>
       <c r="L54" s="10" t="inlineStr"/>
@@ -10112,12 +10102,12 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>span</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
         <is>
-          <t>single-domain WM (n-back) or multidomain EF training</t>
+          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
         </is>
       </c>
       <c r="Q54" s="11" t="inlineStr">
@@ -10125,10 +10115,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr"/>
-      <c r="S54" s="11" t="inlineStr"/>
+      <c r="R54" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S54" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T54" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U54" s="11" t="inlineStr">
         <is>
@@ -10152,7 +10146,7 @@
       </c>
       <c r="Y54" s="12" t="inlineStr">
         <is>
-          <t>n-back; global EF accuracy</t>
+          <t>visuospatial WM criterion task</t>
         </is>
       </c>
       <c r="Z54" s="12" t="inlineStr">
@@ -10162,7 +10156,7 @@
       </c>
       <c r="AA54" s="12" t="inlineStr">
         <is>
-          <t>Prospective memory (Virtual Week); fluid intelligence</t>
+          <t>verbal WM; visuospatial STM; reasoning</t>
         </is>
       </c>
       <c r="AB54" s="12" t="inlineStr">
@@ -10177,7 +10171,7 @@
       </c>
       <c r="AD54" s="12" t="inlineStr">
         <is>
-          <t>未报告 (Bayesian)</t>
+          <t>未报告</t>
         </is>
       </c>
       <c r="AE54" s="12" t="inlineStr">
@@ -10224,35 +10218,35 @@
       </c>
       <c r="AO54" s="15" t="inlineStr">
         <is>
-          <t>单域WM vs 多域EF训练比较；Bayesian分析；主观认知自评提升</t>
+          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Cantarella</t>
+          <t>Pergher</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>The influence of training task stimuli on transfer effects of working memory training in aging</t>
+          <t>Impact of strategy use during N-Back training in older adults</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Psychologie Française</t>
+          <t>Journal of Cognitive Psychology</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -10261,13 +10255,13 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>69</v>
+        <v>61.86</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>4</v>
+        <v>5.37</v>
       </c>
       <c r="K55" s="10" t="inlineStr"/>
       <c r="L55" s="10" t="inlineStr"/>
@@ -10283,12 +10277,12 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>span</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
         <is>
-          <t>visuospatial WM training (neutral vs emotional stimuli)</t>
+          <t>n-back (strategy vs no strategy)</t>
         </is>
       </c>
       <c r="Q55" s="11" t="inlineStr">
@@ -10296,15 +10290,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R55" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="S55" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="T55" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
       <c r="U55" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -10327,7 +10315,7 @@
       </c>
       <c r="Y55" s="12" t="inlineStr">
         <is>
-          <t>visuospatial WM criterion task</t>
+          <t>n-back variant</t>
         </is>
       </c>
       <c r="Z55" s="12" t="inlineStr">
@@ -10337,7 +10325,7 @@
       </c>
       <c r="AA55" s="12" t="inlineStr">
         <is>
-          <t>verbal WM; visuospatial STM; reasoning</t>
+          <t>P300 transfer measures</t>
         </is>
       </c>
       <c r="AB55" s="12" t="inlineStr">
@@ -10362,11 +10350,19 @@
       </c>
       <c r="AF55" s="13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG55" s="13" t="inlineStr"/>
-      <c r="AH55" s="13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AG55" s="13" t="inlineStr">
+        <is>
+          <t>EEG</t>
+        </is>
+      </c>
+      <c r="AH55" s="13" t="inlineStr">
+        <is>
+          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
+        </is>
+      </c>
       <c r="AI55" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10374,7 +10370,7 @@
       </c>
       <c r="AJ55" s="14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AK55" s="14" t="inlineStr">
@@ -10399,35 +10395,35 @@
       </c>
       <c r="AO55" s="15" t="inlineStr">
         <is>
-          <t>训练刺激材料情绪效价对迁移效应的影响（中性vs正性图片）</t>
+          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Pergher</t>
+          <t>Lange</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Impact of strategy use during N-Back training in older adults</t>
+          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Journal of Cognitive Psychology</t>
+          <t>Applied Cognitive Psychology</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -10436,13 +10432,13 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>61.86</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>5.37</v>
+        <v>3.99</v>
       </c>
       <c r="K56" s="10" t="inlineStr"/>
       <c r="L56" s="10" t="inlineStr"/>
@@ -10458,12 +10454,12 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>n-back</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
         <is>
-          <t>n-back (strategy vs no strategy)</t>
+          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
         </is>
       </c>
       <c r="Q56" s="11" t="inlineStr">
@@ -10496,7 +10492,7 @@
       </c>
       <c r="Y56" s="12" t="inlineStr">
         <is>
-          <t>n-back variant</t>
+          <t>WM tasks (near transfer)</t>
         </is>
       </c>
       <c r="Z56" s="12" t="inlineStr">
@@ -10506,7 +10502,7 @@
       </c>
       <c r="AA56" s="12" t="inlineStr">
         <is>
-          <t>P300 transfer measures</t>
+          <t>Short-term memory; processing speed; reasoning</t>
         </is>
       </c>
       <c r="AB56" s="12" t="inlineStr">
@@ -10526,24 +10522,16 @@
       </c>
       <c r="AE56" s="12" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>无迁移</t>
         </is>
       </c>
       <c r="AF56" s="13" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AG56" s="13" t="inlineStr">
-        <is>
-          <t>EEG</t>
-        </is>
-      </c>
-      <c r="AH56" s="13" t="inlineStr">
-        <is>
-          <t>P300变化；策略使用影响训练组间差异；个体特征影响P300</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AG56" s="13" t="inlineStr"/>
+      <c r="AH56" s="13" t="inlineStr"/>
       <c r="AI56" s="14" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10551,7 +10539,7 @@
       </c>
       <c r="AJ56" s="14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AK56" s="14" t="inlineStr">
@@ -10576,35 +10564,35 @@
       </c>
       <c r="AO56" s="15" t="inlineStr">
         <is>
-          <t>N-back训练中策略使用的影响；EEG P300；个体差异调节</t>
+          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Chai</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>2015</v>
+        <v>2026</v>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Experimental evaluation of near‐ and far‐transfer effects of an adaptive multicomponent working memory training</t>
+          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Applied Cognitive Psychology</t>
+          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
@@ -10613,15 +10601,17 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>66.84999999999999</v>
+        <v>70</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="K57" s="10" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K57" s="10" t="n">
+        <v>100</v>
+      </c>
       <c r="L57" s="10" t="inlineStr"/>
       <c r="M57" s="10" t="inlineStr">
         <is>
@@ -10635,12 +10625,12 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>n-back</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
         <is>
-          <t>adaptive multicomponent WM training (phonological+visuospatial+CE)</t>
+          <t>adaptive WM updating (numerical updating + 1-back)</t>
         </is>
       </c>
       <c r="Q57" s="11" t="inlineStr">
@@ -10648,7 +10638,9 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R57" s="11" t="inlineStr"/>
+      <c r="R57" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="S57" s="11" t="inlineStr"/>
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
@@ -10673,7 +10665,7 @@
       </c>
       <c r="Y57" s="12" t="inlineStr">
         <is>
-          <t>WM tasks (near transfer)</t>
+          <t>WM updating task</t>
         </is>
       </c>
       <c r="Z57" s="12" t="inlineStr">
@@ -10683,7 +10675,7 @@
       </c>
       <c r="AA57" s="12" t="inlineStr">
         <is>
-          <t>Short-term memory; processing speed; reasoning</t>
+          <t>Cognitive reappraisal (emotion regulation task)</t>
         </is>
       </c>
       <c r="AB57" s="12" t="inlineStr">
@@ -10703,7 +10695,7 @@
       </c>
       <c r="AE57" s="12" t="inlineStr">
         <is>
-          <t>无迁移</t>
+          <t>正向迁移</t>
         </is>
       </c>
       <c r="AF57" s="13" t="inlineStr">
@@ -10744,179 +10736,6 @@
         </is>
       </c>
       <c r="AO57" s="15" t="inlineStr">
-        <is>
-          <t>主动对照组与训练组在近迁移上表现相似；日常生活评估（ambulatory assessment）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Chai</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>The Impact of Working Memory Training on Cognitive Reappraisal Ability    Among Older Women</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>JOURNAL OF COGNITIVE ENHANCEMENT</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>社区</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="I58" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K58" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L58" s="10" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="N58" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="O58" s="11" t="inlineStr">
-        <is>
-          <t>n-back</t>
-        </is>
-      </c>
-      <c r="P58" s="11" t="inlineStr">
-        <is>
-          <t>adaptive WM updating (numerical updating + 1-back)</t>
-        </is>
-      </c>
-      <c r="Q58" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="R58" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="S58" s="11" t="inlineStr"/>
-      <c r="T58" s="11" t="inlineStr"/>
-      <c r="U58" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="V58" s="11" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>自制</t>
-        </is>
-      </c>
-      <c r="X58" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y58" s="12" t="inlineStr">
-        <is>
-          <t>WM updating task</t>
-        </is>
-      </c>
-      <c r="Z58" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA58" s="12" t="inlineStr">
-        <is>
-          <t>Cognitive reappraisal (emotion regulation task)</t>
-        </is>
-      </c>
-      <c r="AB58" s="12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC58" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AD58" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AE58" s="12" t="inlineStr">
-        <is>
-          <t>正向迁移</t>
-        </is>
-      </c>
-      <c r="AF58" s="13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AG58" s="13" t="inlineStr"/>
-      <c r="AH58" s="13" t="inlineStr"/>
-      <c r="AI58" s="14" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AJ58" s="14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AK58" s="14" t="inlineStr">
-        <is>
-          <t>未检验</t>
-        </is>
-      </c>
-      <c r="AL58" s="14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AM58" s="14" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="AN58" s="14" t="inlineStr">
-        <is>
-          <t>期刊</t>
-        </is>
-      </c>
-      <c r="AO58" s="15" t="inlineStr">
         <is>
           <t>仅老年女性样本；认知重评情绪调节能力作为远迁移结局</t>
         </is>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -6412,7 +6412,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>VK</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -6439,13 +6439,15 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>4</v>
+        <v>69.7</v>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="K33" s="10" t="n">
         <v>79</v>
@@ -6463,7 +6465,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
@@ -6476,10 +6478,12 @@
           <t>否</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="n">
+        <v>10</v>
+      </c>
       <c r="S33" s="11" t="inlineStr"/>
       <c r="T33" s="11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="V33" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>tDCS</t>
         </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
@@ -6648,10 +6652,12 @@
         </is>
       </c>
       <c r="R34" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S34" s="11" t="inlineStr"/>
-      <c r="T34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="U34" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -6783,7 +6789,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>80</v>
@@ -6791,7 +6797,9 @@
       <c r="J35" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>59</v>
+      </c>
       <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -7672,7 +7680,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -8902,7 +8910,9 @@
         <v>20</v>
       </c>
       <c r="S47" s="11" t="inlineStr"/>
-      <c r="T47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="n">
+        <v>5</v>
+      </c>
       <c r="U47" s="11" t="inlineStr">
         <is>
           <t>是</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -6271,12 +6271,14 @@
         <v>28</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>69.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K32" s="10" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>50</v>
+      </c>
       <c r="L32" s="10" t="inlineStr"/>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -6412,7 +6414,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Günther</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -6430,19 +6432,19 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>医院</t>
+          <t>养老院</t>
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>69.7</v>
+        <v>83.5</v>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
@@ -6478,12 +6480,14 @@
           <t>否</t>
         </is>
       </c>
-      <c r="R33" s="11" t="n">
-        <v>10</v>
+      <c r="R33" s="11" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="S33" s="11" t="inlineStr"/>
       <c r="T33" s="11" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="V33" s="11" t="inlineStr">
         <is>
-          <t>tDCS</t>
+          <t>无</t>
         </is>
       </c>
       <c r="W33" s="11" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -6973,10 +6973,10 @@
         <v>71</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>66</v>
+        <v>65.89</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>5.5</v>
+        <v>6.78</v>
       </c>
       <c r="K36" s="10" t="inlineStr"/>
       <c r="L36" s="10" t="inlineStr"/>
@@ -7009,10 +7009,8 @@
         <v>16</v>
       </c>
       <c r="S36" s="11" t="inlineStr"/>
-      <c r="T36" s="11" t="inlineStr">
-        <is>
-          <t>4-8周</t>
-        </is>
+      <c r="T36" s="11" t="n">
+        <v>6</v>
       </c>
       <c r="U36" s="11" t="inlineStr">
         <is>
@@ -7145,24 +7143,28 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>66</v>
+        <v>65.78</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="inlineStr"/>
+        <v>3.04</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>15.53</v>
+      </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
@@ -7230,7 +7232,7 @@
       </c>
       <c r="AD37" s="12" t="inlineStr">
         <is>
-          <t>p&lt;0.05</t>
+          <t>η²p=0.444</t>
         </is>
       </c>
       <c r="AE37" s="12" t="inlineStr">
@@ -7325,7 +7327,7 @@
         <v>137</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>67</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
@@ -7359,9 +7361,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R38" s="11" t="inlineStr"/>
-      <c r="S38" s="11" t="inlineStr"/>
-      <c r="T38" s="11" t="inlineStr"/>
+      <c r="R38" s="11" t="inlineStr">
+        <is>
+          <t>5-10</t>
+        </is>
+      </c>
+      <c r="S38" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="T38" s="11" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="U38" s="11" t="inlineStr">
         <is>
           <t>否</t>
@@ -7524,7 +7536,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R39" s="11" t="inlineStr"/>
+      <c r="R39" s="11" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
+      </c>
       <c r="S39" s="11" t="inlineStr"/>
       <c r="T39" s="11" t="n">
         <v>12</v>
@@ -7844,21 +7860,23 @@
         <v>36</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>70</v>
+        <v>69.89</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="10" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>68</v>
+      </c>
       <c r="L41" s="10" t="inlineStr"/>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="O41" s="11" t="inlineStr">
@@ -7876,8 +7894,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R41" s="11" t="inlineStr"/>
-      <c r="S41" s="11" t="inlineStr"/>
+      <c r="R41" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S41" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T41" s="11" t="n">
         <v>5</v>
       </c>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -8046,17 +8046,17 @@
       <c r="L42" s="10" t="inlineStr"/>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥27</t>
         </is>
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
@@ -8069,8 +8069,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R42" s="11" t="inlineStr"/>
-      <c r="S42" s="11" t="inlineStr"/>
+      <c r="R42" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="S42" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T42" s="11" t="n">
         <v>8</v>
       </c>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>BrainGymmer</t>
         </is>
       </c>
       <c r="X42" s="12" t="inlineStr">
@@ -8204,21 +8208,25 @@
         <v>30</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="inlineStr"/>
+        <v>2.89</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>11.27</v>
+      </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥27</t>
         </is>
       </c>
       <c r="O43" s="11" t="inlineStr">
@@ -8383,28 +8391,26 @@
         <v>97</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+        <v>70.39</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>4.54</v>
       </c>
       <c r="K44" s="10" t="inlineStr"/>
       <c r="L44" s="10" t="inlineStr"/>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥27</t>
         </is>
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
@@ -8417,8 +8423,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R44" s="11" t="inlineStr"/>
-      <c r="S44" s="11" t="inlineStr"/>
+      <c r="R44" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="S44" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T44" s="11" t="n">
         <v>8</v>
       </c>
@@ -8434,7 +8444,7 @@
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>商业软件</t>
+          <t>BrainGymmer</t>
         </is>
       </c>
       <c r="X44" s="12" t="inlineStr">
@@ -8553,7 +8563,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>86.8</v>
@@ -8561,11 +8571,13 @@
       <c r="J45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="n">
+        <v>70</v>
+      </c>
       <c r="L45" s="10" t="inlineStr"/>
       <c r="M45" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMST</t>
         </is>
       </c>
       <c r="N45" s="10" t="inlineStr">
@@ -8585,14 +8597,18 @@
       </c>
       <c r="Q45" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="R45" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S45" s="11" t="inlineStr"/>
-      <c r="T45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="T45" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="U45" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -8724,24 +8740,28 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>66</v>
+        <v>68.81</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K46" s="10" t="inlineStr"/>
-      <c r="L46" s="10" t="inlineStr"/>
+        <v>5.18</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>15.05</v>
+      </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE-2</t>
         </is>
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>≥25</t>
         </is>
       </c>
       <c r="O46" s="11" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>69</v>
@@ -9176,10 +9176,8 @@
           <t>是</t>
         </is>
       </c>
-      <c r="AC48" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+      <c r="AC48" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="AD48" s="12" t="inlineStr">
         <is>
@@ -9267,24 +9265,28 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="10" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>16.4</v>
+      </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MoCA</t>
         </is>
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=24</t>
         </is>
       </c>
       <c r="O49" s="11" t="inlineStr">
@@ -9318,7 +9320,7 @@
       </c>
       <c r="V49" s="11" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>tRNS</t>
         </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
@@ -9444,8 +9446,10 @@
       <c r="H50" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="I50" s="10" t="n">
-        <v>70</v>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>未报告</t>
+        </is>
       </c>
       <c r="J50" s="10" t="n">
         <v>4</v>
@@ -9620,13 +9624,17 @@
         <v>487</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>74</v>
+        <v>75.3</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="L51" s="10" t="n">
+        <v>15.65</v>
+      </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -9652,8 +9660,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R51" s="11" t="inlineStr"/>
-      <c r="S51" s="11" t="inlineStr"/>
+      <c r="R51" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="S51" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
@@ -9794,16 +9806,18 @@
       <c r="J52" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="K52" s="10" t="inlineStr"/>
+      <c r="K52" s="10" t="n">
+        <v>79</v>
+      </c>
       <c r="L52" s="10" t="inlineStr"/>
       <c r="M52" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=27</t>
         </is>
       </c>
       <c r="O52" s="11" t="inlineStr">

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -9987,16 +9987,20 @@
       <c r="J53" s="10" t="n">
         <v>7.04</v>
       </c>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L53" s="10" t="n">
+        <v>13.33</v>
+      </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N53" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>29.80</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
@@ -10014,8 +10018,12 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr"/>
-      <c r="S53" s="11" t="inlineStr"/>
+      <c r="R53" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S53" s="11" t="n">
+        <v>45</v>
+      </c>
       <c r="T53" s="11" t="n">
         <v>4</v>
       </c>
@@ -10056,13 +10064,11 @@
       </c>
       <c r="AB53" s="12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AC53" s="12" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="AD53" s="12" t="inlineStr">
         <is>
@@ -10150,16 +10156,20 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>69</v>
+        <v>68.44</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="10" t="inlineStr"/>
-      <c r="L54" s="10" t="inlineStr"/>
+      <c r="K54" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>11.76</v>
+      </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10325,7 +10335,7 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>61.86</v>
@@ -10333,16 +10343,20 @@
       <c r="J55" s="10" t="n">
         <v>5.37</v>
       </c>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="L55" s="10" t="n">
+        <v>8.6</v>
+      </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=27</t>
         </is>
       </c>
       <c r="O55" s="11" t="inlineStr">
@@ -10360,9 +10374,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R55" s="11" t="inlineStr"/>
-      <c r="S55" s="11" t="inlineStr"/>
-      <c r="T55" s="11" t="inlineStr"/>
+      <c r="R55" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S55" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T55" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="U55" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -10510,8 +10530,12 @@
       <c r="J56" s="10" t="n">
         <v>3.99</v>
       </c>
-      <c r="K56" s="10" t="inlineStr"/>
-      <c r="L56" s="10" t="inlineStr"/>
+      <c r="K56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L56" s="10" t="n">
+        <v>14.03</v>
+      </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -10537,9 +10561,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="R56" s="11" t="inlineStr"/>
-      <c r="S56" s="11" t="inlineStr"/>
-      <c r="T56" s="11" t="inlineStr"/>
+      <c r="R56" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="S56" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="T56" s="11" t="n">
+        <v>6</v>
+      </c>
       <c r="U56" s="11" t="inlineStr">
         <is>
           <t>是</t>
@@ -10671,26 +10701,28 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>70</v>
+        <v>70.64</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>5</v>
+        <v>5.47</v>
       </c>
       <c r="K57" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="L57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="n">
+        <v>11.14</v>
+      </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N57" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=25</t>
         </is>
       </c>
       <c r="O57" s="11" t="inlineStr">
@@ -10711,8 +10743,12 @@
       <c r="R57" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="S57" s="11" t="inlineStr"/>
-      <c r="T57" s="11" t="inlineStr"/>
+      <c r="S57" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T57" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="U57" s="11" t="inlineStr">
         <is>
           <t>是</t>

--- a/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表.xlsx
@@ -6480,18 +6480,18 @@
           <t>否</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="S33" s="11" t="inlineStr"/>
+      <c r="R33" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="S33" s="11" t="n">
+        <v>45</v>
+      </c>
       <c r="T33" s="11" t="n">
         <v>14</v>
       </c>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr">
@@ -6623,21 +6623,25 @@
         <v>119</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="10" t="inlineStr"/>
-      <c r="L34" s="10" t="inlineStr"/>
+      <c r="K34" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>19.6</v>
+      </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=27</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
@@ -6658,7 +6662,9 @@
       <c r="R34" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S34" s="11" t="inlineStr"/>
+      <c r="S34" s="11" t="n">
+        <v>20</v>
+      </c>
       <c r="T34" s="11" t="n">
         <v>8</v>
       </c>
@@ -6799,7 +6805,7 @@
         <v>80</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K35" s="10" t="n">
         <v>59</v>
@@ -6817,7 +6823,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
@@ -6886,7 +6892,7 @@
       </c>
       <c r="AD35" s="12" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>eta2p=0.46</t>
         </is>
       </c>
       <c r="AE35" s="12" t="inlineStr">
@@ -7686,16 +7692,20 @@
           <t>未报告</t>
         </is>
       </c>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" s="10" t="inlineStr"/>
+      <c r="K40" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>17.7</v>
+      </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>&gt;=26</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
@@ -8915,26 +8925,26 @@
       <c r="H47" s="10" t="n">
         <v>119</v>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>未报告</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="inlineStr"/>
+      <c r="I47" s="10" t="n">
+        <v>72.86</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>16.6</v>
+      </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="N47" s="10" t="inlineStr">
         <is>
-          <t>未报告</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
@@ -8955,7 +8965,9 @@
       <c r="R47" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="S47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="T47" s="11" t="n">
         <v>5</v>
       </c>
